--- a/data/MAIRE.MI.xlsx
+++ b/data/MAIRE.MI.xlsx
@@ -62886,6 +62886,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2719">
+      <c r="A2719" s="1" t="n">
+        <v>46279.2916666667</v>
+      </c>
+      <c r="B2719" t="n">
+        <v>495983</v>
+      </c>
+      <c r="C2719" t="n">
+        <v>12.6000003814697</v>
+      </c>
+      <c r="D2719" t="n">
+        <v>12.1000003814697</v>
+      </c>
+      <c r="E2719" t="n">
+        <v>12.5200004577637</v>
+      </c>
+      <c r="F2719" t="n">
+        <v>12.1000003814697</v>
+      </c>
+      <c r="G2719" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/MAIRE.MI.xlsx
+++ b/data/MAIRE.MI.xlsx
@@ -62909,6 +62909,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2720">
+      <c r="A2720" s="1" t="n">
+        <v>46280.2916666667</v>
+      </c>
+      <c r="B2720" t="n">
+        <v>401104</v>
+      </c>
+      <c r="C2720" t="n">
+        <v>12.3800001144409</v>
+      </c>
+      <c r="D2720" t="n">
+        <v>12.0500001907349</v>
+      </c>
+      <c r="E2720" t="n">
+        <v>12.1499996185303</v>
+      </c>
+      <c r="F2720" t="n">
+        <v>12.25</v>
+      </c>
+      <c r="G2720" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/MAIRE.MI.xlsx
+++ b/data/MAIRE.MI.xlsx
@@ -62932,6 +62932,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2721">
+      <c r="A2721" s="1" t="n">
+        <v>46281.2916666667</v>
+      </c>
+      <c r="B2721" t="n">
+        <v>410206</v>
+      </c>
+      <c r="C2721" t="n">
+        <v>12.6000003814697</v>
+      </c>
+      <c r="D2721" t="n">
+        <v>12.2600002288818</v>
+      </c>
+      <c r="E2721" t="n">
+        <v>12.2600002288818</v>
+      </c>
+      <c r="F2721" t="n">
+        <v>12.4499998092651</v>
+      </c>
+      <c r="G2721" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/MAIRE.MI.xlsx
+++ b/data/MAIRE.MI.xlsx
@@ -62955,6 +62955,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2722">
+      <c r="A2722" s="1" t="n">
+        <v>46282.2916666667</v>
+      </c>
+      <c r="B2722" t="n">
+        <v>567178</v>
+      </c>
+      <c r="C2722" t="n">
+        <v>12.75</v>
+      </c>
+      <c r="D2722" t="n">
+        <v>12.5200004577637</v>
+      </c>
+      <c r="E2722" t="n">
+        <v>12.5200004577637</v>
+      </c>
+      <c r="F2722" t="n">
+        <v>12.5699996948242</v>
+      </c>
+      <c r="G2722" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/MAIRE.MI.xlsx
+++ b/data/MAIRE.MI.xlsx
@@ -62796,22 +62796,22 @@
     </row>
     <row r="2715">
       <c r="A2715" s="1" t="n">
-        <v>46273.2916666667</v>
+        <v>46272.2916666667</v>
       </c>
       <c r="B2715" t="n">
-        <v>391324</v>
+        <v>332727</v>
       </c>
       <c r="C2715" t="n">
-        <v>12.789999961853</v>
+        <v>12.4700002670288</v>
       </c>
       <c r="D2715" t="n">
-        <v>12.3900003433228</v>
+        <v>12.2299995422363</v>
       </c>
       <c r="E2715" t="n">
+        <v>12.2299995422363</v>
+      </c>
+      <c r="F2715" t="n">
         <v>12.4300003051758</v>
-      </c>
-      <c r="F2715" t="n">
-        <v>12.6700000762939</v>
       </c>
       <c r="G2715" t="s">
         <v>7</v>
@@ -62819,22 +62819,22 @@
     </row>
     <row r="2716">
       <c r="A2716" s="1" t="n">
-        <v>46274.2916666667</v>
+        <v>46273.2916666667</v>
       </c>
       <c r="B2716" t="n">
-        <v>514185</v>
+        <v>391324</v>
       </c>
       <c r="C2716" t="n">
-        <v>12.6800003051758</v>
+        <v>12.789999961853</v>
       </c>
       <c r="D2716" t="n">
-        <v>12.2799997329712</v>
+        <v>12.3900003433228</v>
       </c>
       <c r="E2716" t="n">
-        <v>12.6499996185303</v>
+        <v>12.4300003051758</v>
       </c>
       <c r="F2716" t="n">
-        <v>12.3800001144409</v>
+        <v>12.6700000762939</v>
       </c>
       <c r="G2716" t="s">
         <v>7</v>
@@ -62842,22 +62842,22 @@
     </row>
     <row r="2717">
       <c r="A2717" s="1" t="n">
-        <v>46275.2916666667</v>
+        <v>46274.2916666667</v>
       </c>
       <c r="B2717" t="n">
-        <v>314776</v>
+        <v>514185</v>
       </c>
       <c r="C2717" t="n">
-        <v>12.6099996566772</v>
+        <v>12.6800003051758</v>
       </c>
       <c r="D2717" t="n">
-        <v>12.2600002288818</v>
+        <v>12.2799997329712</v>
       </c>
       <c r="E2717" t="n">
-        <v>12.3299999237061</v>
+        <v>12.6499996185303</v>
       </c>
       <c r="F2717" t="n">
-        <v>12.3000001907349</v>
+        <v>12.3800001144409</v>
       </c>
       <c r="G2717" t="s">
         <v>7</v>
@@ -62865,22 +62865,22 @@
     </row>
     <row r="2718">
       <c r="A2718" s="1" t="n">
-        <v>46276.2916666667</v>
+        <v>46275.2916666667</v>
       </c>
       <c r="B2718" t="n">
-        <v>367278</v>
+        <v>314776</v>
       </c>
       <c r="C2718" t="n">
-        <v>12.6700000762939</v>
+        <v>12.6099996566772</v>
       </c>
       <c r="D2718" t="n">
-        <v>12.289999961853</v>
+        <v>12.2600002288818</v>
       </c>
       <c r="E2718" t="n">
-        <v>12.289999961853</v>
+        <v>12.3299999237061</v>
       </c>
       <c r="F2718" t="n">
-        <v>12.6099996566772</v>
+        <v>12.3000001907349</v>
       </c>
       <c r="G2718" t="s">
         <v>7</v>
@@ -62888,22 +62888,22 @@
     </row>
     <row r="2719">
       <c r="A2719" s="1" t="n">
-        <v>46279.2916666667</v>
+        <v>46276.2916666667</v>
       </c>
       <c r="B2719" t="n">
-        <v>495983</v>
+        <v>367278</v>
       </c>
       <c r="C2719" t="n">
-        <v>12.6000003814697</v>
+        <v>12.6700000762939</v>
       </c>
       <c r="D2719" t="n">
-        <v>12.1000003814697</v>
+        <v>12.289999961853</v>
       </c>
       <c r="E2719" t="n">
-        <v>12.5200004577637</v>
+        <v>12.289999961853</v>
       </c>
       <c r="F2719" t="n">
-        <v>12.1000003814697</v>
+        <v>12.6099996566772</v>
       </c>
       <c r="G2719" t="s">
         <v>7</v>
@@ -62911,22 +62911,22 @@
     </row>
     <row r="2720">
       <c r="A2720" s="1" t="n">
-        <v>46280.2916666667</v>
+        <v>46279.2916666667</v>
       </c>
       <c r="B2720" t="n">
-        <v>401104</v>
+        <v>495983</v>
       </c>
       <c r="C2720" t="n">
-        <v>12.3800001144409</v>
+        <v>12.6000003814697</v>
       </c>
       <c r="D2720" t="n">
-        <v>12.0500001907349</v>
+        <v>12.1000003814697</v>
       </c>
       <c r="E2720" t="n">
-        <v>12.1499996185303</v>
+        <v>12.5200004577637</v>
       </c>
       <c r="F2720" t="n">
-        <v>12.25</v>
+        <v>12.1000003814697</v>
       </c>
       <c r="G2720" t="s">
         <v>7</v>
@@ -62934,22 +62934,22 @@
     </row>
     <row r="2721">
       <c r="A2721" s="1" t="n">
-        <v>46281.2916666667</v>
+        <v>46280.2916666667</v>
       </c>
       <c r="B2721" t="n">
-        <v>410206</v>
+        <v>401104</v>
       </c>
       <c r="C2721" t="n">
-        <v>12.6000003814697</v>
+        <v>12.3800001144409</v>
       </c>
       <c r="D2721" t="n">
-        <v>12.2600002288818</v>
+        <v>12.0500001907349</v>
       </c>
       <c r="E2721" t="n">
-        <v>12.2600002288818</v>
+        <v>12.1499996185303</v>
       </c>
       <c r="F2721" t="n">
-        <v>12.4499998092651</v>
+        <v>12.25</v>
       </c>
       <c r="G2721" t="s">
         <v>7</v>
@@ -62957,24 +62957,47 @@
     </row>
     <row r="2722">
       <c r="A2722" s="1" t="n">
-        <v>46282.2916666667</v>
+        <v>46281.2916666667</v>
       </c>
       <c r="B2722" t="n">
-        <v>567178</v>
+        <v>410206</v>
       </c>
       <c r="C2722" t="n">
-        <v>12.75</v>
+        <v>12.6000003814697</v>
       </c>
       <c r="D2722" t="n">
-        <v>12.5200004577637</v>
+        <v>12.2600002288818</v>
       </c>
       <c r="E2722" t="n">
-        <v>12.5200004577637</v>
+        <v>12.2600002288818</v>
       </c>
       <c r="F2722" t="n">
-        <v>12.5699996948242</v>
+        <v>12.4499998092651</v>
       </c>
       <c r="G2722" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2723">
+      <c r="A2723" s="1" t="n">
+        <v>46283.2916666667</v>
+      </c>
+      <c r="B2723" t="n">
+        <v>641808</v>
+      </c>
+      <c r="C2723" t="n">
+        <v>12.6800003051758</v>
+      </c>
+      <c r="D2723" t="n">
+        <v>12.3100004196167</v>
+      </c>
+      <c r="E2723" t="n">
+        <v>12.6099996566772</v>
+      </c>
+      <c r="F2723" t="n">
+        <v>12.4099998474121</v>
+      </c>
+      <c r="G2723" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/MAIRE.MI.xlsx
+++ b/data/MAIRE.MI.xlsx
@@ -63270,8 +63270,31 @@
       <c r="E2735" t="n">
         <v>12.4899997711182</v>
       </c>
-      <c r="F2735"/>
+      <c r="F2735" t="n">
+        <v>12.5500001907349</v>
+      </c>
       <c r="G2735" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2736">
+      <c r="A2736" s="1" t="n">
+        <v>46301.2916666667</v>
+      </c>
+      <c r="B2736" t="n">
+        <v>893098</v>
+      </c>
+      <c r="C2736" t="n">
+        <v>12.6700000762939</v>
+      </c>
+      <c r="D2736" t="n">
+        <v>12.3400001525879</v>
+      </c>
+      <c r="E2736" t="n">
+        <v>12.5299997329712</v>
+      </c>
+      <c r="F2736"/>
+      <c r="G2736" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/MAIRE.MI.xlsx
+++ b/data/MAIRE.MI.xlsx
@@ -63293,8 +63293,31 @@
       <c r="E2736" t="n">
         <v>12.5299997329712</v>
       </c>
-      <c r="F2736"/>
+      <c r="F2736" t="n">
+        <v>12.5200004577637</v>
+      </c>
       <c r="G2736" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2737">
+      <c r="A2737" s="1" t="n">
+        <v>46302.2916666667</v>
+      </c>
+      <c r="B2737" t="n">
+        <v>624101</v>
+      </c>
+      <c r="C2737" t="n">
+        <v>12.5799999237061</v>
+      </c>
+      <c r="D2737" t="n">
+        <v>12.1599998474121</v>
+      </c>
+      <c r="E2737" t="n">
+        <v>12.3900003433228</v>
+      </c>
+      <c r="F2737"/>
+      <c r="G2737" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/MAIRE.MI.xlsx
+++ b/data/MAIRE.MI.xlsx
@@ -63316,8 +63316,31 @@
       <c r="E2737" t="n">
         <v>12.3900003433228</v>
       </c>
-      <c r="F2737"/>
+      <c r="F2737" t="n">
+        <v>12.1599998474121</v>
+      </c>
       <c r="G2737" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2738">
+      <c r="A2738" s="1" t="n">
+        <v>46303.2916666667</v>
+      </c>
+      <c r="B2738" t="n">
+        <v>1025554</v>
+      </c>
+      <c r="C2738" t="n">
+        <v>12.789999961853</v>
+      </c>
+      <c r="D2738" t="n">
+        <v>12.039999961853</v>
+      </c>
+      <c r="E2738" t="n">
+        <v>12.0799999237061</v>
+      </c>
+      <c r="F2738"/>
+      <c r="G2738" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/MAIRE.MI.xlsx
+++ b/data/MAIRE.MI.xlsx
@@ -63339,8 +63339,31 @@
       <c r="E2738" t="n">
         <v>12.0799999237061</v>
       </c>
-      <c r="F2738"/>
+      <c r="F2738" t="n">
+        <v>12.5500001907349</v>
+      </c>
       <c r="G2738" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2739">
+      <c r="A2739" s="1" t="n">
+        <v>46304.2916666667</v>
+      </c>
+      <c r="B2739" t="n">
+        <v>498357</v>
+      </c>
+      <c r="C2739" t="n">
+        <v>12.9200000762939</v>
+      </c>
+      <c r="D2739" t="n">
+        <v>12.5200004577637</v>
+      </c>
+      <c r="E2739" t="n">
+        <v>12.6099996566772</v>
+      </c>
+      <c r="F2739"/>
+      <c r="G2739" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/MAIRE.MI.xlsx
+++ b/data/MAIRE.MI.xlsx
@@ -63369,6 +63369,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2740">
+      <c r="A2740" s="1" t="n">
+        <v>46307.2916666667</v>
+      </c>
+      <c r="B2740" t="n">
+        <v>978922</v>
+      </c>
+      <c r="C2740" t="n">
+        <v>12.9200000762939</v>
+      </c>
+      <c r="D2740" t="n">
+        <v>12.6899995803833</v>
+      </c>
+      <c r="E2740" t="n">
+        <v>12.7700004577637</v>
+      </c>
+      <c r="F2740" t="n">
+        <v>12.7200002670288</v>
+      </c>
+      <c r="G2740" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/MAIRE.MI.xlsx
+++ b/data/MAIRE.MI.xlsx
@@ -421,7 +421,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G2" t="n">
-        <v>1.71284735202789</v>
+        <v>1.71284711360931</v>
       </c>
       <c r="H2" t="s">
         <v>8</v>
@@ -447,7 +447,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G3" t="n">
-        <v>1.66390907764435</v>
+        <v>1.66390919685364</v>
       </c>
       <c r="H3" t="s">
         <v>8</v>
@@ -473,7 +473,7 @@
         <v>2.39400005340576</v>
       </c>
       <c r="G4" t="n">
-        <v>1.67369627952576</v>
+        <v>1.67369663715363</v>
       </c>
       <c r="H4" t="s">
         <v>8</v>
@@ -499,7 +499,7 @@
         <v>2.33800005912781</v>
       </c>
       <c r="G5" t="n">
-        <v>1.63454592227936</v>
+        <v>1.63454580307007</v>
       </c>
       <c r="H5" t="s">
         <v>8</v>
@@ -551,7 +551,7 @@
         <v>2.24600005149841</v>
       </c>
       <c r="G7" t="n">
-        <v>1.57022678852081</v>
+        <v>1.57022643089294</v>
       </c>
       <c r="H7" t="s">
         <v>8</v>
@@ -577,7 +577,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G8" t="n">
-        <v>1.5800142288208</v>
+        <v>1.58001434803009</v>
       </c>
       <c r="H8" t="s">
         <v>8</v>
@@ -603,7 +603,7 @@
         <v>2.28800010681152</v>
       </c>
       <c r="G9" t="n">
-        <v>1.59958982467651</v>
+        <v>1.59958970546722</v>
       </c>
       <c r="H9" t="s">
         <v>8</v>
@@ -629,7 +629,7 @@
         <v>2.24200010299683</v>
       </c>
       <c r="G10" t="n">
-        <v>1.56742990016937</v>
+        <v>1.56743013858795</v>
       </c>
       <c r="H10" t="s">
         <v>8</v>
@@ -655,7 +655,7 @@
         <v>2.11199998855591</v>
       </c>
       <c r="G11" t="n">
-        <v>1.47654414176941</v>
+        <v>1.47654449939728</v>
       </c>
       <c r="H11" t="s">
         <v>8</v>
@@ -681,7 +681,7 @@
         <v>2</v>
       </c>
       <c r="G12" t="n">
-        <v>1.39824271202087</v>
+        <v>1.39824247360229</v>
       </c>
       <c r="H12" t="s">
         <v>8</v>
@@ -707,7 +707,7 @@
         <v>1.99899995326996</v>
       </c>
       <c r="G13" t="n">
-        <v>1.39754366874695</v>
+        <v>1.39754354953766</v>
       </c>
       <c r="H13" t="s">
         <v>8</v>
@@ -733,7 +733,7 @@
         <v>1.86600005626678</v>
       </c>
       <c r="G14" t="n">
-        <v>1.30456042289734</v>
+        <v>1.30456054210663</v>
       </c>
       <c r="H14" t="s">
         <v>8</v>
@@ -759,7 +759,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G15" t="n">
-        <v>1.36328673362732</v>
+        <v>1.36328661441803</v>
       </c>
       <c r="H15" t="s">
         <v>8</v>
@@ -863,7 +863,7 @@
         <v>2.09400010108948</v>
       </c>
       <c r="G19" t="n">
-        <v>1.46396017074585</v>
+        <v>1.46396028995514</v>
       </c>
       <c r="H19" t="s">
         <v>8</v>
@@ -889,7 +889,7 @@
         <v>2.18199992179871</v>
       </c>
       <c r="G20" t="n">
-        <v>1.52548265457153</v>
+        <v>1.52548277378082</v>
       </c>
       <c r="H20" t="s">
         <v>8</v>
@@ -941,7 +941,7 @@
         <v>2.15400004386902</v>
       </c>
       <c r="G22" t="n">
-        <v>1.50590753555298</v>
+        <v>1.5059072971344</v>
       </c>
       <c r="H22" t="s">
         <v>8</v>
@@ -967,7 +967,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G23" t="n">
-        <v>1.45417237281799</v>
+        <v>1.45417249202728</v>
       </c>
       <c r="H23" t="s">
         <v>8</v>
@@ -1019,7 +1019,7 @@
         <v>2.12199997901917</v>
       </c>
       <c r="G25" t="n">
-        <v>1.48353564739227</v>
+        <v>1.48353552818298</v>
       </c>
       <c r="H25" t="s">
         <v>8</v>
@@ -1071,7 +1071,7 @@
         <v>1.91299998760223</v>
       </c>
       <c r="G27" t="n">
-        <v>1.33741927146912</v>
+        <v>1.33741939067841</v>
       </c>
       <c r="H27" t="s">
         <v>8</v>
@@ -1097,7 +1097,7 @@
         <v>1.85500001907349</v>
       </c>
       <c r="G28" t="n">
-        <v>1.29687011241913</v>
+        <v>1.29686999320984</v>
       </c>
       <c r="H28" t="s">
         <v>8</v>
@@ -1201,7 +1201,7 @@
         <v>2.10999989509583</v>
       </c>
       <c r="G32" t="n">
-        <v>1.47514605522156</v>
+        <v>1.47514593601227</v>
       </c>
       <c r="H32" t="s">
         <v>8</v>
@@ -1279,7 +1279,7 @@
         <v>2.26399993896484</v>
       </c>
       <c r="G35" t="n">
-        <v>1.58281075954437</v>
+        <v>1.58281064033508</v>
       </c>
       <c r="H35" t="s">
         <v>8</v>
@@ -1331,7 +1331,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G37" t="n">
-        <v>1.5800142288208</v>
+        <v>1.58001434803009</v>
       </c>
       <c r="H37" t="s">
         <v>8</v>
@@ -1357,7 +1357,7 @@
         <v>2.23200011253357</v>
       </c>
       <c r="G38" t="n">
-        <v>1.56043899059296</v>
+        <v>1.56043887138367</v>
       </c>
       <c r="H38" t="s">
         <v>8</v>
@@ -1461,7 +1461,7 @@
         <v>2.38599991798401</v>
       </c>
       <c r="G42" t="n">
-        <v>1.66810369491577</v>
+        <v>1.66810309886932</v>
       </c>
       <c r="H42" t="s">
         <v>8</v>
@@ -1487,7 +1487,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G43" t="n">
-        <v>1.67789113521576</v>
+        <v>1.67789125442505</v>
       </c>
       <c r="H43" t="s">
         <v>8</v>
@@ -1513,7 +1513,7 @@
         <v>2.3659999370575</v>
       </c>
       <c r="G44" t="n">
-        <v>1.65412104129791</v>
+        <v>1.65412092208862</v>
       </c>
       <c r="H44" t="s">
         <v>8</v>
@@ -1539,7 +1539,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G45" t="n">
-        <v>1.68488276004791</v>
+        <v>1.68488240242004</v>
       </c>
       <c r="H45" t="s">
         <v>8</v>
@@ -1565,7 +1565,7 @@
         <v>2.47199988365173</v>
       </c>
       <c r="G46" t="n">
-        <v>1.72822785377502</v>
+        <v>1.72822797298431</v>
       </c>
       <c r="H46" t="s">
         <v>8</v>
@@ -1591,7 +1591,7 @@
         <v>2.46399998664856</v>
       </c>
       <c r="G47" t="n">
-        <v>1.72263526916504</v>
+        <v>1.72263503074646</v>
       </c>
       <c r="H47" t="s">
         <v>8</v>
@@ -1617,7 +1617,7 @@
         <v>2.44199991226196</v>
       </c>
       <c r="G48" t="n">
-        <v>1.70725417137146</v>
+        <v>1.70725429058075</v>
       </c>
       <c r="H48" t="s">
         <v>8</v>
@@ -1643,7 +1643,7 @@
         <v>2.58999991416931</v>
       </c>
       <c r="G49" t="n">
-        <v>1.81072425842285</v>
+        <v>1.81072402000427</v>
       </c>
       <c r="H49" t="s">
         <v>8</v>
@@ -1695,7 +1695,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G51" t="n">
-        <v>1.80373299121857</v>
+        <v>1.80373322963715</v>
       </c>
       <c r="H51" t="s">
         <v>8</v>
@@ -1721,7 +1721,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G52" t="n">
-        <v>1.81771540641785</v>
+        <v>1.81771552562714</v>
       </c>
       <c r="H52" t="s">
         <v>8</v>
@@ -1747,7 +1747,7 @@
         <v>2.49799990653992</v>
       </c>
       <c r="G53" t="n">
-        <v>1.74640500545502</v>
+        <v>1.7464052438736</v>
       </c>
       <c r="H53" t="s">
         <v>8</v>
@@ -1773,7 +1773,7 @@
         <v>2.67000007629395</v>
       </c>
       <c r="G54" t="n">
-        <v>1.86665415763855</v>
+        <v>1.86665403842926</v>
       </c>
       <c r="H54" t="s">
         <v>8</v>
@@ -1799,7 +1799,7 @@
         <v>2.67199993133545</v>
       </c>
       <c r="G55" t="n">
-        <v>1.86805236339569</v>
+        <v>1.8680522441864</v>
       </c>
       <c r="H55" t="s">
         <v>8</v>
@@ -1851,7 +1851,7 @@
         <v>2.69600009918213</v>
       </c>
       <c r="G57" t="n">
-        <v>1.88483130931854</v>
+        <v>1.88483154773712</v>
       </c>
       <c r="H57" t="s">
         <v>8</v>
@@ -1877,7 +1877,7 @@
         <v>2.68400001525879</v>
       </c>
       <c r="G58" t="n">
-        <v>1.87644195556641</v>
+        <v>1.87644159793854</v>
       </c>
       <c r="H58" t="s">
         <v>8</v>
@@ -1903,7 +1903,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G59" t="n">
-        <v>1.80373299121857</v>
+        <v>1.80373322963715</v>
       </c>
       <c r="H59" t="s">
         <v>8</v>
@@ -1929,7 +1929,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G60" t="n">
-        <v>1.80373299121857</v>
+        <v>1.80373322963715</v>
       </c>
       <c r="H60" t="s">
         <v>8</v>
@@ -1955,7 +1955,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G61" t="n">
-        <v>1.78275954723358</v>
+        <v>1.782759308815</v>
       </c>
       <c r="H61" t="s">
         <v>8</v>
@@ -1981,7 +1981,7 @@
         <v>2.61800003051758</v>
       </c>
       <c r="G62" t="n">
-        <v>1.83029937744141</v>
+        <v>1.83029997348785</v>
       </c>
       <c r="H62" t="s">
         <v>8</v>
@@ -2007,7 +2007,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G63" t="n">
-        <v>1.85267162322998</v>
+        <v>1.85267150402069</v>
       </c>
       <c r="H63" t="s">
         <v>8</v>
@@ -2033,7 +2033,7 @@
         <v>2.59200000762939</v>
       </c>
       <c r="G64" t="n">
-        <v>1.81212258338928</v>
+        <v>1.81212246417999</v>
       </c>
       <c r="H64" t="s">
         <v>8</v>
@@ -2085,7 +2085,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G66" t="n">
-        <v>1.76178574562073</v>
+        <v>1.76178586483002</v>
       </c>
       <c r="H66" t="s">
         <v>8</v>
@@ -2111,7 +2111,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G67" t="n">
-        <v>1.74081218242645</v>
+        <v>1.74081206321716</v>
       </c>
       <c r="H67" t="s">
         <v>8</v>
@@ -2137,7 +2137,7 @@
         <v>2.45199990272522</v>
       </c>
       <c r="G68" t="n">
-        <v>1.71424520015717</v>
+        <v>1.71424567699432</v>
       </c>
       <c r="H68" t="s">
         <v>8</v>
@@ -2163,7 +2163,7 @@
         <v>2.54399991035461</v>
       </c>
       <c r="G69" t="n">
-        <v>1.77856481075287</v>
+        <v>1.77856469154358</v>
       </c>
       <c r="H69" t="s">
         <v>8</v>
@@ -2189,7 +2189,7 @@
         <v>2.61800003051758</v>
       </c>
       <c r="G70" t="n">
-        <v>1.83029937744141</v>
+        <v>1.83029997348785</v>
       </c>
       <c r="H70" t="s">
         <v>8</v>
@@ -2215,7 +2215,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G71" t="n">
-        <v>1.85267162322998</v>
+        <v>1.85267150402069</v>
       </c>
       <c r="H71" t="s">
         <v>8</v>
@@ -2241,7 +2241,7 @@
         <v>2.69199991226196</v>
       </c>
       <c r="G72" t="n">
-        <v>1.88203454017639</v>
+        <v>1.88203418254852</v>
       </c>
       <c r="H72" t="s">
         <v>8</v>
@@ -2267,7 +2267,7 @@
         <v>2.66799998283386</v>
       </c>
       <c r="G73" t="n">
-        <v>1.86525559425354</v>
+        <v>1.86525571346283</v>
       </c>
       <c r="H73" t="s">
         <v>8</v>
@@ -2293,7 +2293,7 @@
         <v>2.67000007629395</v>
       </c>
       <c r="G74" t="n">
-        <v>1.86665415763855</v>
+        <v>1.86665403842926</v>
       </c>
       <c r="H74" t="s">
         <v>8</v>
@@ -2319,7 +2319,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G75" t="n">
-        <v>1.88762772083282</v>
+        <v>1.88762760162354</v>
       </c>
       <c r="H75" t="s">
         <v>8</v>
@@ -2345,7 +2345,7 @@
         <v>2.67000007629395</v>
       </c>
       <c r="G76" t="n">
-        <v>1.86665415763855</v>
+        <v>1.86665403842926</v>
       </c>
       <c r="H76" t="s">
         <v>8</v>
@@ -2397,7 +2397,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G78" t="n">
-        <v>1.84568071365356</v>
+        <v>1.84568047523499</v>
       </c>
       <c r="H78" t="s">
         <v>8</v>
@@ -2423,7 +2423,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G79" t="n">
-        <v>1.85267162322998</v>
+        <v>1.85267150402069</v>
       </c>
       <c r="H79" t="s">
         <v>8</v>
@@ -2449,7 +2449,7 @@
         <v>2.66000008583069</v>
       </c>
       <c r="G80" t="n">
-        <v>1.85966277122498</v>
+        <v>1.85966289043427</v>
       </c>
       <c r="H80" t="s">
         <v>8</v>
@@ -2475,7 +2475,7 @@
         <v>2.64800000190735</v>
       </c>
       <c r="G81" t="n">
-        <v>1.85127353668213</v>
+        <v>1.85127305984497</v>
       </c>
       <c r="H81" t="s">
         <v>8</v>
@@ -2501,7 +2501,7 @@
         <v>2.64800000190735</v>
       </c>
       <c r="G82" t="n">
-        <v>1.85127353668213</v>
+        <v>1.85127305984497</v>
       </c>
       <c r="H82" t="s">
         <v>8</v>
@@ -2527,7 +2527,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G83" t="n">
-        <v>1.85267162322998</v>
+        <v>1.85267150402069</v>
       </c>
       <c r="H83" t="s">
         <v>8</v>
@@ -2553,7 +2553,7 @@
         <v>2.64800000190735</v>
       </c>
       <c r="G84" t="n">
-        <v>1.85127353668213</v>
+        <v>1.85127305984497</v>
       </c>
       <c r="H84" t="s">
         <v>8</v>
@@ -2579,7 +2579,7 @@
         <v>2.59599995613098</v>
       </c>
       <c r="G85" t="n">
-        <v>1.84771466255188</v>
+        <v>1.84771454334259</v>
       </c>
       <c r="H85" t="s">
         <v>8</v>
@@ -2605,7 +2605,7 @@
         <v>2.40400004386902</v>
       </c>
       <c r="G86" t="n">
-        <v>1.71105802059174</v>
+        <v>1.71105766296387</v>
       </c>
       <c r="H86" t="s">
         <v>8</v>
@@ -2631,7 +2631,7 @@
         <v>2.48600006103516</v>
       </c>
       <c r="G87" t="n">
-        <v>1.76942181587219</v>
+        <v>1.7694216966629</v>
       </c>
       <c r="H87" t="s">
         <v>8</v>
@@ -2683,7 +2683,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G89" t="n">
-        <v>1.75091600418091</v>
+        <v>1.7509161233902</v>
       </c>
       <c r="H89" t="s">
         <v>8</v>
@@ -2709,7 +2709,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G90" t="n">
-        <v>1.7082108259201</v>
+        <v>1.70821070671082</v>
       </c>
       <c r="H90" t="s">
         <v>8</v>
@@ -2735,7 +2735,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G91" t="n">
-        <v>1.7437983751297</v>
+        <v>1.74379849433899</v>
       </c>
       <c r="H91" t="s">
         <v>8</v>
@@ -2787,7 +2787,7 @@
         <v>2.56800007820129</v>
       </c>
       <c r="G93" t="n">
-        <v>1.82778537273407</v>
+        <v>1.82778549194336</v>
       </c>
       <c r="H93" t="s">
         <v>8</v>
@@ -2813,7 +2813,7 @@
         <v>2.59800004959106</v>
       </c>
       <c r="G94" t="n">
-        <v>1.84913814067841</v>
+        <v>1.84913802146912</v>
       </c>
       <c r="H94" t="s">
         <v>8</v>
@@ -2839,7 +2839,7 @@
         <v>2.60199999809265</v>
       </c>
       <c r="G95" t="n">
-        <v>1.85198497772217</v>
+        <v>1.85198521614075</v>
       </c>
       <c r="H95" t="s">
         <v>8</v>
@@ -2917,7 +2917,7 @@
         <v>2.61800003051758</v>
       </c>
       <c r="G98" t="n">
-        <v>1.86337327957153</v>
+        <v>1.86337292194366</v>
       </c>
       <c r="H98" t="s">
         <v>8</v>
@@ -2943,7 +2943,7 @@
         <v>2.58999991416931</v>
       </c>
       <c r="G99" t="n">
-        <v>1.84344387054443</v>
+        <v>1.84344410896301</v>
       </c>
       <c r="H99" t="s">
         <v>8</v>
@@ -2969,7 +2969,7 @@
         <v>2.62800002098083</v>
       </c>
       <c r="G100" t="n">
-        <v>1.87049043178558</v>
+        <v>1.87049031257629</v>
       </c>
       <c r="H100" t="s">
         <v>8</v>
@@ -3047,7 +3047,7 @@
         <v>2.55599999427795</v>
       </c>
       <c r="G103" t="n">
-        <v>1.81924438476562</v>
+        <v>1.81924414634705</v>
       </c>
       <c r="H103" t="s">
         <v>8</v>
@@ -3073,7 +3073,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G104" t="n">
-        <v>1.82209146022797</v>
+        <v>1.82209157943726</v>
       </c>
       <c r="H104" t="s">
         <v>8</v>
@@ -3125,7 +3125,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G106" t="n">
-        <v>1.83632659912109</v>
+        <v>1.83632683753967</v>
       </c>
       <c r="H106" t="s">
         <v>8</v>
@@ -3151,7 +3151,7 @@
         <v>2.5239999294281</v>
       </c>
       <c r="G107" t="n">
-        <v>1.79646849632263</v>
+        <v>1.79646801948547</v>
       </c>
       <c r="H107" t="s">
         <v>8</v>
@@ -3203,7 +3203,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G109" t="n">
-        <v>1.76515102386475</v>
+        <v>1.76515114307404</v>
       </c>
       <c r="H109" t="s">
         <v>8</v>
@@ -3229,7 +3229,7 @@
         <v>2.46399998664856</v>
       </c>
       <c r="G110" t="n">
-        <v>1.75376307964325</v>
+        <v>1.75376296043396</v>
       </c>
       <c r="H110" t="s">
         <v>8</v>
@@ -3255,7 +3255,7 @@
         <v>2.51600003242493</v>
       </c>
       <c r="G111" t="n">
-        <v>1.79077398777008</v>
+        <v>1.79077422618866</v>
       </c>
       <c r="H111" t="s">
         <v>8</v>
@@ -3281,7 +3281,7 @@
         <v>2.46600008010864</v>
       </c>
       <c r="G112" t="n">
-        <v>1.7551863193512</v>
+        <v>1.75518667697906</v>
       </c>
       <c r="H112" t="s">
         <v>8</v>
@@ -3307,7 +3307,7 @@
         <v>2.50399994850159</v>
       </c>
       <c r="G113" t="n">
-        <v>1.78223299980164</v>
+        <v>1.78223288059235</v>
       </c>
       <c r="H113" t="s">
         <v>8</v>
@@ -3359,7 +3359,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G115" t="n">
-        <v>1.67974030971527</v>
+        <v>1.67974042892456</v>
       </c>
       <c r="H115" t="s">
         <v>8</v>
@@ -3385,7 +3385,7 @@
         <v>2.31599998474121</v>
       </c>
       <c r="G116" t="n">
-        <v>1.64842319488525</v>
+        <v>1.64842343330383</v>
       </c>
       <c r="H116" t="s">
         <v>8</v>
@@ -3411,7 +3411,7 @@
         <v>2.31800007820129</v>
       </c>
       <c r="G117" t="n">
-        <v>1.64984691143036</v>
+        <v>1.64984703063965</v>
       </c>
       <c r="H117" t="s">
         <v>8</v>
@@ -3437,7 +3437,7 @@
         <v>2.22399997711182</v>
       </c>
       <c r="G118" t="n">
-        <v>1.58294177055359</v>
+        <v>1.58294188976288</v>
       </c>
       <c r="H118" t="s">
         <v>8</v>
@@ -3489,7 +3489,7 @@
         <v>2.42400002479553</v>
       </c>
       <c r="G120" t="n">
-        <v>1.72529268264771</v>
+        <v>1.72529292106628</v>
       </c>
       <c r="H120" t="s">
         <v>8</v>
@@ -3567,7 +3567,7 @@
         <v>2.36400008201599</v>
       </c>
       <c r="G123" t="n">
-        <v>1.6825875043869</v>
+        <v>1.68258762359619</v>
       </c>
       <c r="H123" t="s">
         <v>8</v>
@@ -3645,7 +3645,7 @@
         <v>2.23000001907349</v>
       </c>
       <c r="G126" t="n">
-        <v>1.58721244335175</v>
+        <v>1.58721256256104</v>
       </c>
       <c r="H126" t="s">
         <v>8</v>
@@ -3697,7 +3697,7 @@
         <v>2.26200008392334</v>
       </c>
       <c r="G128" t="n">
-        <v>1.60998868942261</v>
+        <v>1.6099888086319</v>
       </c>
       <c r="H128" t="s">
         <v>8</v>
@@ -3749,7 +3749,7 @@
         <v>2.29200005531311</v>
       </c>
       <c r="G130" t="n">
-        <v>1.63134133815765</v>
+        <v>1.63134121894836</v>
       </c>
       <c r="H130" t="s">
         <v>8</v>
@@ -3775,7 +3775,7 @@
         <v>2.25399994850159</v>
       </c>
       <c r="G131" t="n">
-        <v>1.60429453849792</v>
+        <v>1.60429465770721</v>
       </c>
       <c r="H131" t="s">
         <v>8</v>
@@ -3853,7 +3853,7 @@
         <v>2.25</v>
       </c>
       <c r="G134" t="n">
-        <v>1.60144734382629</v>
+        <v>1.60144746303558</v>
       </c>
       <c r="H134" t="s">
         <v>8</v>
@@ -3879,7 +3879,7 @@
         <v>2.30399990081787</v>
       </c>
       <c r="G135" t="n">
-        <v>1.63988220691681</v>
+        <v>1.6398823261261</v>
       </c>
       <c r="H135" t="s">
         <v>8</v>
@@ -3931,7 +3931,7 @@
         <v>2.29200005531311</v>
       </c>
       <c r="G137" t="n">
-        <v>1.63134133815765</v>
+        <v>1.63134121894836</v>
       </c>
       <c r="H137" t="s">
         <v>8</v>
@@ -3957,7 +3957,7 @@
         <v>2.35599994659424</v>
       </c>
       <c r="G138" t="n">
-        <v>1.67689347267151</v>
+        <v>1.67689335346222</v>
       </c>
       <c r="H138" t="s">
         <v>8</v>
@@ -3983,7 +3983,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G139" t="n">
-        <v>1.67262315750122</v>
+        <v>1.67262279987335</v>
       </c>
       <c r="H139" t="s">
         <v>8</v>
@@ -4009,7 +4009,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G140" t="n">
-        <v>1.7082108259201</v>
+        <v>1.70821070671082</v>
       </c>
       <c r="H140" t="s">
         <v>8</v>
@@ -4035,7 +4035,7 @@
         <v>2.34800004959106</v>
       </c>
       <c r="G141" t="n">
-        <v>1.67119932174683</v>
+        <v>1.67119944095612</v>
       </c>
       <c r="H141" t="s">
         <v>8</v>
@@ -4061,7 +4061,7 @@
         <v>2.3659999370575</v>
       </c>
       <c r="G142" t="n">
-        <v>1.68401110172272</v>
+        <v>1.68401098251343</v>
       </c>
       <c r="H142" t="s">
         <v>8</v>
@@ -4087,7 +4087,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G143" t="n">
-        <v>1.63703513145447</v>
+        <v>1.63703501224518</v>
       </c>
       <c r="H143" t="s">
         <v>8</v>
@@ -4113,7 +4113,7 @@
         <v>2.31399989128113</v>
       </c>
       <c r="G144" t="n">
-        <v>1.64699971675873</v>
+        <v>1.64699995517731</v>
       </c>
       <c r="H144" t="s">
         <v>8</v>
@@ -4139,7 +4139,7 @@
         <v>2.32200002670288</v>
       </c>
       <c r="G145" t="n">
-        <v>1.65269386768341</v>
+        <v>1.65269374847412</v>
       </c>
       <c r="H145" t="s">
         <v>8</v>
@@ -4217,7 +4217,7 @@
         <v>2.25799989700317</v>
       </c>
       <c r="G148" t="n">
-        <v>1.60714173316956</v>
+        <v>1.60714149475098</v>
       </c>
       <c r="H148" t="s">
         <v>8</v>
@@ -4243,7 +4243,7 @@
         <v>2.27600002288818</v>
       </c>
       <c r="G149" t="n">
-        <v>1.61995315551758</v>
+        <v>1.61995303630829</v>
       </c>
       <c r="H149" t="s">
         <v>8</v>
@@ -4295,7 +4295,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G151" t="n">
-        <v>1.55874252319336</v>
+        <v>1.55874228477478</v>
       </c>
       <c r="H151" t="s">
         <v>8</v>
@@ -4321,7 +4321,7 @@
         <v>2.2260000705719</v>
       </c>
       <c r="G152" t="n">
-        <v>1.58436548709869</v>
+        <v>1.58436524868011</v>
       </c>
       <c r="H152" t="s">
         <v>8</v>
@@ -4347,7 +4347,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G153" t="n">
-        <v>1.54450726509094</v>
+        <v>1.54450738430023</v>
       </c>
       <c r="H153" t="s">
         <v>8</v>
@@ -4373,7 +4373,7 @@
         <v>2.15199995040894</v>
       </c>
       <c r="G154" t="n">
-        <v>1.53169560432434</v>
+        <v>1.53169548511505</v>
       </c>
       <c r="H154" t="s">
         <v>8</v>
@@ -4425,7 +4425,7 @@
         <v>2.13199996948242</v>
       </c>
       <c r="G156" t="n">
-        <v>1.51746046543121</v>
+        <v>1.51746034622192</v>
       </c>
       <c r="H156" t="s">
         <v>8</v>
@@ -4451,7 +4451,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G157" t="n">
-        <v>1.49468433856964</v>
+        <v>1.49468421936035</v>
       </c>
       <c r="H157" t="s">
         <v>8</v>
@@ -4477,7 +4477,7 @@
         <v>2.11199998855591</v>
       </c>
       <c r="G158" t="n">
-        <v>1.50322532653809</v>
+        <v>1.50322544574738</v>
       </c>
       <c r="H158" t="s">
         <v>8</v>
@@ -4503,7 +4503,7 @@
         <v>2.09400010108948</v>
       </c>
       <c r="G159" t="n">
-        <v>1.49041390419006</v>
+        <v>1.49041378498077</v>
       </c>
       <c r="H159" t="s">
         <v>8</v>
@@ -4529,7 +4529,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G160" t="n">
-        <v>1.4804493188858</v>
+        <v>1.48044919967651</v>
       </c>
       <c r="H160" t="s">
         <v>8</v>
@@ -4581,7 +4581,7 @@
         <v>2.03800010681152</v>
       </c>
       <c r="G162" t="n">
-        <v>1.45055556297302</v>
+        <v>1.45055568218231</v>
       </c>
       <c r="H162" t="s">
         <v>8</v>
@@ -4607,7 +4607,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G163" t="n">
-        <v>1.45197904109955</v>
+        <v>1.45197916030884</v>
       </c>
       <c r="H163" t="s">
         <v>8</v>
@@ -4633,7 +4633,7 @@
         <v>2.02600002288818</v>
       </c>
       <c r="G164" t="n">
-        <v>1.44201469421387</v>
+        <v>1.44201457500458</v>
       </c>
       <c r="H164" t="s">
         <v>8</v>
@@ -4659,7 +4659,7 @@
         <v>2.06800007820129</v>
       </c>
       <c r="G165" t="n">
-        <v>1.47190821170807</v>
+        <v>1.47190809249878</v>
       </c>
       <c r="H165" t="s">
         <v>8</v>
@@ -4685,7 +4685,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G166" t="n">
-        <v>1.4804493188858</v>
+        <v>1.48044919967651</v>
       </c>
       <c r="H166" t="s">
         <v>8</v>
@@ -4711,7 +4711,7 @@
         <v>2.06800007820129</v>
       </c>
       <c r="G167" t="n">
-        <v>1.47190821170807</v>
+        <v>1.47190809249878</v>
       </c>
       <c r="H167" t="s">
         <v>8</v>
@@ -4737,7 +4737,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G168" t="n">
-        <v>1.4804493188858</v>
+        <v>1.48044919967651</v>
       </c>
       <c r="H168" t="s">
         <v>8</v>
@@ -4763,7 +4763,7 @@
         <v>2.04200005531311</v>
       </c>
       <c r="G169" t="n">
-        <v>1.45340263843536</v>
+        <v>1.45340251922607</v>
       </c>
       <c r="H169" t="s">
         <v>8</v>
@@ -4789,7 +4789,7 @@
         <v>2.02800011634827</v>
       </c>
       <c r="G170" t="n">
-        <v>1.4434380531311</v>
+        <v>1.44343817234039</v>
       </c>
       <c r="H170" t="s">
         <v>8</v>
@@ -4841,7 +4841,7 @@
         <v>2.13000011444092</v>
       </c>
       <c r="G172" t="n">
-        <v>1.51603698730469</v>
+        <v>1.51603710651398</v>
       </c>
       <c r="H172" t="s">
         <v>8</v>
@@ -4893,7 +4893,7 @@
         <v>2.15199995040894</v>
       </c>
       <c r="G174" t="n">
-        <v>1.53169560432434</v>
+        <v>1.53169548511505</v>
       </c>
       <c r="H174" t="s">
         <v>8</v>
@@ -4919,7 +4919,7 @@
         <v>2.12199997901917</v>
       </c>
       <c r="G175" t="n">
-        <v>1.51034307479858</v>
+        <v>1.51034295558929</v>
       </c>
       <c r="H175" t="s">
         <v>8</v>
@@ -4945,7 +4945,7 @@
         <v>2.16199994087219</v>
       </c>
       <c r="G176" t="n">
-        <v>1.53881311416626</v>
+        <v>1.53881323337555</v>
       </c>
       <c r="H176" t="s">
         <v>8</v>
@@ -4971,7 +4971,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G177" t="n">
-        <v>1.54450726509094</v>
+        <v>1.54450738430023</v>
       </c>
       <c r="H177" t="s">
         <v>8</v>
@@ -5023,7 +5023,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G179" t="n">
-        <v>1.52315473556519</v>
+        <v>1.5231546163559</v>
       </c>
       <c r="H179" t="s">
         <v>8</v>
@@ -5101,7 +5101,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G182" t="n">
-        <v>1.50891935825348</v>
+        <v>1.5089191198349</v>
       </c>
       <c r="H182" t="s">
         <v>8</v>
@@ -5153,7 +5153,7 @@
         <v>2.13000011444092</v>
       </c>
       <c r="G184" t="n">
-        <v>1.51603698730469</v>
+        <v>1.51603710651398</v>
       </c>
       <c r="H184" t="s">
         <v>8</v>
@@ -5179,7 +5179,7 @@
         <v>2.06800007820129</v>
       </c>
       <c r="G185" t="n">
-        <v>1.47190821170807</v>
+        <v>1.47190809249878</v>
       </c>
       <c r="H185" t="s">
         <v>8</v>
@@ -5257,7 +5257,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G188" t="n">
-        <v>1.46621417999268</v>
+        <v>1.46621429920197</v>
       </c>
       <c r="H188" t="s">
         <v>8</v>
@@ -5283,7 +5283,7 @@
         <v>2.08800005912781</v>
       </c>
       <c r="G189" t="n">
-        <v>1.4861433506012</v>
+        <v>1.48614346981049</v>
       </c>
       <c r="H189" t="s">
         <v>8</v>
@@ -5309,7 +5309,7 @@
         <v>2.06800007820129</v>
       </c>
       <c r="G190" t="n">
-        <v>1.47190821170807</v>
+        <v>1.47190809249878</v>
       </c>
       <c r="H190" t="s">
         <v>8</v>
@@ -5335,7 +5335,7 @@
         <v>2.11199998855591</v>
       </c>
       <c r="G191" t="n">
-        <v>1.50322532653809</v>
+        <v>1.50322544574738</v>
       </c>
       <c r="H191" t="s">
         <v>8</v>
@@ -5361,7 +5361,7 @@
         <v>2.2039999961853</v>
       </c>
       <c r="G192" t="n">
-        <v>1.56870687007904</v>
+        <v>1.56870663166046</v>
       </c>
       <c r="H192" t="s">
         <v>8</v>
@@ -5387,7 +5387,7 @@
         <v>2.20199990272522</v>
       </c>
       <c r="G193" t="n">
-        <v>1.56728315353394</v>
+        <v>1.56728327274323</v>
       </c>
       <c r="H193" t="s">
         <v>8</v>
@@ -5465,7 +5465,7 @@
         <v>2.17400002479553</v>
       </c>
       <c r="G196" t="n">
-        <v>1.54735398292542</v>
+        <v>1.5473541021347</v>
       </c>
       <c r="H196" t="s">
         <v>8</v>
@@ -5491,7 +5491,7 @@
         <v>2.13000011444092</v>
       </c>
       <c r="G197" t="n">
-        <v>1.51603698730469</v>
+        <v>1.51603710651398</v>
       </c>
       <c r="H197" t="s">
         <v>8</v>
@@ -5517,7 +5517,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G198" t="n">
-        <v>1.4804493188858</v>
+        <v>1.48044919967651</v>
       </c>
       <c r="H198" t="s">
         <v>8</v>
@@ -5543,7 +5543,7 @@
         <v>2.08800005912781</v>
       </c>
       <c r="G199" t="n">
-        <v>1.4861433506012</v>
+        <v>1.48614346981049</v>
       </c>
       <c r="H199" t="s">
         <v>8</v>
@@ -5647,7 +5647,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G203" t="n">
-        <v>1.54450726509094</v>
+        <v>1.54450738430023</v>
       </c>
       <c r="H203" t="s">
         <v>8</v>
@@ -5673,7 +5673,7 @@
         <v>2.16799998283386</v>
       </c>
       <c r="G204" t="n">
-        <v>1.54308366775513</v>
+        <v>1.54308354854584</v>
       </c>
       <c r="H204" t="s">
         <v>8</v>
@@ -5699,7 +5699,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G205" t="n">
-        <v>1.55162465572357</v>
+        <v>1.55162489414215</v>
       </c>
       <c r="H205" t="s">
         <v>8</v>
@@ -5725,7 +5725,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G206" t="n">
-        <v>1.55874252319336</v>
+        <v>1.55874228477478</v>
       </c>
       <c r="H206" t="s">
         <v>8</v>
@@ -5751,7 +5751,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G207" t="n">
-        <v>1.55874252319336</v>
+        <v>1.55874228477478</v>
       </c>
       <c r="H207" t="s">
         <v>8</v>
@@ -5803,7 +5803,7 @@
         <v>2.19199991226196</v>
       </c>
       <c r="G209" t="n">
-        <v>1.5601658821106</v>
+        <v>1.56016576290131</v>
       </c>
       <c r="H209" t="s">
         <v>8</v>
@@ -5855,7 +5855,7 @@
         <v>2.23000001907349</v>
       </c>
       <c r="G211" t="n">
-        <v>1.58721244335175</v>
+        <v>1.58721256256104</v>
       </c>
       <c r="H211" t="s">
         <v>8</v>
@@ -5959,7 +5959,7 @@
         <v>2.16199994087219</v>
       </c>
       <c r="G215" t="n">
-        <v>1.53881311416626</v>
+        <v>1.53881323337555</v>
       </c>
       <c r="H215" t="s">
         <v>8</v>
@@ -5985,7 +5985,7 @@
         <v>2.15799999237061</v>
       </c>
       <c r="G216" t="n">
-        <v>1.53596603870392</v>
+        <v>1.5359662771225</v>
       </c>
       <c r="H216" t="s">
         <v>8</v>
@@ -6011,7 +6011,7 @@
         <v>2.21600008010864</v>
       </c>
       <c r="G217" t="n">
-        <v>1.57724797725677</v>
+        <v>1.57724785804749</v>
       </c>
       <c r="H217" t="s">
         <v>8</v>
@@ -6037,7 +6037,7 @@
         <v>2.22399997711182</v>
       </c>
       <c r="G218" t="n">
-        <v>1.58294177055359</v>
+        <v>1.58294188976288</v>
       </c>
       <c r="H218" t="s">
         <v>8</v>
@@ -6115,7 +6115,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G221" t="n">
-        <v>1.63703513145447</v>
+        <v>1.63703501224518</v>
       </c>
       <c r="H221" t="s">
         <v>8</v>
@@ -6141,7 +6141,7 @@
         <v>2.3659999370575</v>
       </c>
       <c r="G222" t="n">
-        <v>1.68401110172272</v>
+        <v>1.68401098251343</v>
       </c>
       <c r="H222" t="s">
         <v>8</v>
@@ -6167,7 +6167,7 @@
         <v>2.40400004386902</v>
       </c>
       <c r="G223" t="n">
-        <v>1.71105802059174</v>
+        <v>1.71105766296387</v>
       </c>
       <c r="H223" t="s">
         <v>8</v>
@@ -6193,7 +6193,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G224" t="n">
-        <v>1.71532845497131</v>
+        <v>1.71532821655273</v>
       </c>
       <c r="H224" t="s">
         <v>8</v>
@@ -6219,7 +6219,7 @@
         <v>2.45600008964539</v>
       </c>
       <c r="G225" t="n">
-        <v>1.74806916713715</v>
+        <v>1.74806880950928</v>
       </c>
       <c r="H225" t="s">
         <v>8</v>
@@ -6271,7 +6271,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G227" t="n">
-        <v>1.75091600418091</v>
+        <v>1.7509161233902</v>
       </c>
       <c r="H227" t="s">
         <v>8</v>
@@ -6297,7 +6297,7 @@
         <v>2.43400001525879</v>
       </c>
       <c r="G228" t="n">
-        <v>1.73241055011749</v>
+        <v>1.73241019248962</v>
       </c>
       <c r="H228" t="s">
         <v>8</v>
@@ -6323,7 +6323,7 @@
         <v>2.38199996948242</v>
       </c>
       <c r="G229" t="n">
-        <v>1.69539892673492</v>
+        <v>1.6953991651535</v>
       </c>
       <c r="H229" t="s">
         <v>8</v>
@@ -6349,7 +6349,7 @@
         <v>2.43600010871887</v>
       </c>
       <c r="G230" t="n">
-        <v>1.73383378982544</v>
+        <v>1.73383402824402</v>
       </c>
       <c r="H230" t="s">
         <v>8</v>
@@ -6375,7 +6375,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G231" t="n">
-        <v>1.75803363323212</v>
+        <v>1.75803351402283</v>
       </c>
       <c r="H231" t="s">
         <v>8</v>
@@ -6401,7 +6401,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G232" t="n">
-        <v>1.72956311702728</v>
+        <v>1.72956347465515</v>
       </c>
       <c r="H232" t="s">
         <v>8</v>
@@ -6453,7 +6453,7 @@
         <v>2.28800010681152</v>
       </c>
       <c r="G234" t="n">
-        <v>1.6284943819046</v>
+        <v>1.62849426269531</v>
       </c>
       <c r="H234" t="s">
         <v>8</v>
@@ -6479,7 +6479,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G235" t="n">
-        <v>1.67262315750122</v>
+        <v>1.67262279987335</v>
       </c>
       <c r="H235" t="s">
         <v>8</v>
@@ -6505,7 +6505,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G236" t="n">
-        <v>1.69397568702698</v>
+        <v>1.69397580623627</v>
       </c>
       <c r="H236" t="s">
         <v>8</v>
@@ -6557,7 +6557,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G238" t="n">
-        <v>1.73668086528778</v>
+        <v>1.73668110370636</v>
       </c>
       <c r="H238" t="s">
         <v>8</v>
@@ -6583,7 +6583,7 @@
         <v>2.43799996376038</v>
       </c>
       <c r="G239" t="n">
-        <v>1.73525750637054</v>
+        <v>1.73525726795197</v>
       </c>
       <c r="H239" t="s">
         <v>8</v>
@@ -6609,7 +6609,7 @@
         <v>2.50999999046326</v>
       </c>
       <c r="G240" t="n">
-        <v>1.78650391101837</v>
+        <v>1.78650367259979</v>
       </c>
       <c r="H240" t="s">
         <v>8</v>
@@ -6635,7 +6635,7 @@
         <v>2.55599999427795</v>
       </c>
       <c r="G241" t="n">
-        <v>1.81924438476562</v>
+        <v>1.81924414634705</v>
       </c>
       <c r="H241" t="s">
         <v>8</v>
@@ -6687,7 +6687,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G243" t="n">
-        <v>1.85056173801422</v>
+        <v>1.85056149959564</v>
       </c>
       <c r="H243" t="s">
         <v>8</v>
@@ -6713,7 +6713,7 @@
         <v>2.57599997520447</v>
       </c>
       <c r="G244" t="n">
-        <v>1.83347940444946</v>
+        <v>1.83347916603088</v>
       </c>
       <c r="H244" t="s">
         <v>8</v>
@@ -6739,7 +6739,7 @@
         <v>2.62800002098083</v>
       </c>
       <c r="G245" t="n">
-        <v>1.87049043178558</v>
+        <v>1.87049031257629</v>
       </c>
       <c r="H245" t="s">
         <v>8</v>
@@ -6765,7 +6765,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G246" t="n">
-        <v>1.85056173801422</v>
+        <v>1.85056149959564</v>
       </c>
       <c r="H246" t="s">
         <v>8</v>
@@ -6791,7 +6791,7 @@
         <v>2.59200000762939</v>
       </c>
       <c r="G247" t="n">
-        <v>1.84486758708954</v>
+        <v>1.84486746788025</v>
       </c>
       <c r="H247" t="s">
         <v>8</v>
@@ -6843,7 +6843,7 @@
         <v>2.59800004959106</v>
       </c>
       <c r="G249" t="n">
-        <v>1.84913814067841</v>
+        <v>1.84913802146912</v>
       </c>
       <c r="H249" t="s">
         <v>8</v>
@@ -6869,7 +6869,7 @@
         <v>2.6159999370575</v>
       </c>
       <c r="G250" t="n">
-        <v>1.86194932460785</v>
+        <v>1.86194968223572</v>
       </c>
       <c r="H250" t="s">
         <v>8</v>
@@ -6921,7 +6921,7 @@
         <v>2.57800006866455</v>
       </c>
       <c r="G252" t="n">
-        <v>1.83490312099457</v>
+        <v>1.83490288257599</v>
       </c>
       <c r="H252" t="s">
         <v>8</v>
@@ -6947,7 +6947,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G253" t="n">
-        <v>1.83632659912109</v>
+        <v>1.83632683753967</v>
       </c>
       <c r="H253" t="s">
         <v>8</v>
@@ -6973,7 +6973,7 @@
         <v>2.60599994659424</v>
       </c>
       <c r="G254" t="n">
-        <v>1.85483169555664</v>
+        <v>1.85483229160309</v>
       </c>
       <c r="H254" t="s">
         <v>8</v>
@@ -6999,7 +6999,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G255" t="n">
-        <v>1.83632659912109</v>
+        <v>1.83632683753967</v>
       </c>
       <c r="H255" t="s">
         <v>8</v>
@@ -7025,7 +7025,7 @@
         <v>2.58999991416931</v>
       </c>
       <c r="G256" t="n">
-        <v>1.84344387054443</v>
+        <v>1.84344410896301</v>
       </c>
       <c r="H256" t="s">
         <v>8</v>
@@ -7051,7 +7051,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G257" t="n">
-        <v>1.83632659912109</v>
+        <v>1.83632683753967</v>
       </c>
       <c r="H257" t="s">
         <v>8</v>
@@ -7077,7 +7077,7 @@
         <v>2.71600008010864</v>
       </c>
       <c r="G258" t="n">
-        <v>1.93312501907349</v>
+        <v>1.93312549591064</v>
       </c>
       <c r="H258" t="s">
         <v>8</v>
@@ -7103,7 +7103,7 @@
         <v>2.75</v>
       </c>
       <c r="G259" t="n">
-        <v>1.95732462406158</v>
+        <v>1.95732498168945</v>
       </c>
       <c r="H259" t="s">
         <v>8</v>
@@ -7129,7 +7129,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G260" t="n">
-        <v>1.92173707485199</v>
+        <v>1.9217369556427</v>
       </c>
       <c r="H260" t="s">
         <v>8</v>
@@ -7155,7 +7155,7 @@
         <v>2.71000003814697</v>
       </c>
       <c r="G261" t="n">
-        <v>1.92885458469391</v>
+        <v>1.9288547039032</v>
       </c>
       <c r="H261" t="s">
         <v>8</v>
@@ -7233,7 +7233,7 @@
         <v>2.71000003814697</v>
       </c>
       <c r="G264" t="n">
-        <v>1.92885458469391</v>
+        <v>1.9288547039032</v>
       </c>
       <c r="H264" t="s">
         <v>8</v>
@@ -7337,7 +7337,7 @@
         <v>2.68600010871887</v>
       </c>
       <c r="G268" t="n">
-        <v>1.9117728471756</v>
+        <v>1.91177272796631</v>
       </c>
       <c r="H268" t="s">
         <v>8</v>
@@ -7363,7 +7363,7 @@
         <v>2.69600009918213</v>
       </c>
       <c r="G269" t="n">
-        <v>1.91888988018036</v>
+        <v>1.91889023780823</v>
       </c>
       <c r="H269" t="s">
         <v>8</v>
@@ -7389,7 +7389,7 @@
         <v>2.66199994087219</v>
       </c>
       <c r="G270" t="n">
-        <v>1.89469015598297</v>
+        <v>1.89469027519226</v>
       </c>
       <c r="H270" t="s">
         <v>8</v>
@@ -7415,7 +7415,7 @@
         <v>2.55599999427795</v>
       </c>
       <c r="G271" t="n">
-        <v>1.81924438476562</v>
+        <v>1.81924414634705</v>
       </c>
       <c r="H271" t="s">
         <v>8</v>
@@ -7441,7 +7441,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G272" t="n">
-        <v>1.83632659912109</v>
+        <v>1.83632683753967</v>
       </c>
       <c r="H272" t="s">
         <v>8</v>
@@ -7467,7 +7467,7 @@
         <v>2.60199999809265</v>
       </c>
       <c r="G273" t="n">
-        <v>1.85198497772217</v>
+        <v>1.85198521614075</v>
       </c>
       <c r="H273" t="s">
         <v>8</v>
@@ -7493,7 +7493,7 @@
         <v>2.62400007247925</v>
       </c>
       <c r="G274" t="n">
-        <v>1.8676438331604</v>
+        <v>1.86764371395111</v>
       </c>
       <c r="H274" t="s">
         <v>8</v>
@@ -7519,7 +7519,7 @@
         <v>2.67000007629395</v>
       </c>
       <c r="G275" t="n">
-        <v>1.90038430690765</v>
+        <v>1.90038454532623</v>
       </c>
       <c r="H275" t="s">
         <v>8</v>
@@ -7545,7 +7545,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G276" t="n">
-        <v>1.85056173801422</v>
+        <v>1.85056149959564</v>
       </c>
       <c r="H276" t="s">
         <v>8</v>
@@ -7571,7 +7571,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G277" t="n">
-        <v>1.85056173801422</v>
+        <v>1.85056149959564</v>
       </c>
       <c r="H277" t="s">
         <v>8</v>
@@ -7597,7 +7597,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G278" t="n">
-        <v>1.83632659912109</v>
+        <v>1.83632683753967</v>
       </c>
       <c r="H278" t="s">
         <v>8</v>
@@ -7623,7 +7623,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G279" t="n">
-        <v>1.85056173801422</v>
+        <v>1.85056149959564</v>
       </c>
       <c r="H279" t="s">
         <v>8</v>
@@ -7649,7 +7649,7 @@
         <v>2.58800005912781</v>
       </c>
       <c r="G280" t="n">
-        <v>1.84202027320862</v>
+        <v>1.8420205116272</v>
       </c>
       <c r="H280" t="s">
         <v>8</v>
@@ -7675,7 +7675,7 @@
         <v>2.64800000190735</v>
       </c>
       <c r="G281" t="n">
-        <v>1.88472580909729</v>
+        <v>1.884725689888</v>
       </c>
       <c r="H281" t="s">
         <v>8</v>
@@ -7701,7 +7701,7 @@
         <v>2.61800003051758</v>
       </c>
       <c r="G282" t="n">
-        <v>1.86337327957153</v>
+        <v>1.86337292194366</v>
       </c>
       <c r="H282" t="s">
         <v>8</v>
@@ -7727,7 +7727,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G283" t="n">
-        <v>1.85056173801422</v>
+        <v>1.85056149959564</v>
       </c>
       <c r="H283" t="s">
         <v>8</v>
@@ -7753,7 +7753,7 @@
         <v>2.58800005912781</v>
       </c>
       <c r="G284" t="n">
-        <v>1.84202027320862</v>
+        <v>1.8420205116272</v>
       </c>
       <c r="H284" t="s">
         <v>8</v>
@@ -7779,7 +7779,7 @@
         <v>2.58800005912781</v>
       </c>
       <c r="G285" t="n">
-        <v>1.84202027320862</v>
+        <v>1.8420205116272</v>
       </c>
       <c r="H285" t="s">
         <v>8</v>
@@ -7805,7 +7805,7 @@
         <v>2.59800004959106</v>
       </c>
       <c r="G286" t="n">
-        <v>1.84913814067841</v>
+        <v>1.84913802146912</v>
       </c>
       <c r="H286" t="s">
         <v>8</v>
@@ -7831,7 +7831,7 @@
         <v>2.59599995613098</v>
       </c>
       <c r="G287" t="n">
-        <v>1.84771466255188</v>
+        <v>1.84771454334259</v>
       </c>
       <c r="H287" t="s">
         <v>8</v>
@@ -7857,7 +7857,7 @@
         <v>2.62400007247925</v>
       </c>
       <c r="G288" t="n">
-        <v>1.8676438331604</v>
+        <v>1.86764371395111</v>
       </c>
       <c r="H288" t="s">
         <v>8</v>
@@ -7909,7 +7909,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G290" t="n">
-        <v>1.87903189659119</v>
+        <v>1.8790317773819</v>
       </c>
       <c r="H290" t="s">
         <v>8</v>
@@ -7935,7 +7935,7 @@
         <v>2.59200000762939</v>
       </c>
       <c r="G291" t="n">
-        <v>1.84486758708954</v>
+        <v>1.84486746788025</v>
       </c>
       <c r="H291" t="s">
         <v>8</v>
@@ -7961,7 +7961,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G292" t="n">
-        <v>1.85056173801422</v>
+        <v>1.85056149959564</v>
       </c>
       <c r="H292" t="s">
         <v>8</v>
@@ -8013,7 +8013,7 @@
         <v>2.53200006484985</v>
       </c>
       <c r="G294" t="n">
-        <v>1.80216264724731</v>
+        <v>1.80216240882874</v>
       </c>
       <c r="H294" t="s">
         <v>8</v>
@@ -8039,7 +8039,7 @@
         <v>2.58599996566772</v>
       </c>
       <c r="G295" t="n">
-        <v>1.84059703350067</v>
+        <v>1.84059691429138</v>
       </c>
       <c r="H295" t="s">
         <v>8</v>
@@ -8117,7 +8117,7 @@
         <v>2.51799988746643</v>
       </c>
       <c r="G298" t="n">
-        <v>1.79219746589661</v>
+        <v>1.79219782352448</v>
       </c>
       <c r="H298" t="s">
         <v>8</v>
@@ -8169,7 +8169,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G300" t="n">
-        <v>1.88614916801453</v>
+        <v>1.88614940643311</v>
       </c>
       <c r="H300" t="s">
         <v>8</v>
@@ -8195,7 +8195,7 @@
         <v>2.64800000190735</v>
       </c>
       <c r="G301" t="n">
-        <v>1.88472580909729</v>
+        <v>1.884725689888</v>
       </c>
       <c r="H301" t="s">
         <v>8</v>
@@ -8221,7 +8221,7 @@
         <v>2.65599989891052</v>
       </c>
       <c r="G302" t="n">
-        <v>1.8904196023941</v>
+        <v>1.89041996002197</v>
       </c>
       <c r="H302" t="s">
         <v>8</v>
@@ -8247,7 +8247,7 @@
         <v>2.69600009918213</v>
       </c>
       <c r="G303" t="n">
-        <v>1.91888988018036</v>
+        <v>1.91889023780823</v>
       </c>
       <c r="H303" t="s">
         <v>8</v>
@@ -8273,7 +8273,7 @@
         <v>2.67000007629395</v>
       </c>
       <c r="G304" t="n">
-        <v>1.90038430690765</v>
+        <v>1.90038454532623</v>
       </c>
       <c r="H304" t="s">
         <v>8</v>
@@ -8299,7 +8299,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G305" t="n">
-        <v>1.87903189659119</v>
+        <v>1.8790317773819</v>
       </c>
       <c r="H305" t="s">
         <v>8</v>
@@ -8325,7 +8325,7 @@
         <v>2.68600010871887</v>
       </c>
       <c r="G306" t="n">
-        <v>1.9117728471756</v>
+        <v>1.91177272796631</v>
       </c>
       <c r="H306" t="s">
         <v>8</v>
@@ -8377,7 +8377,7 @@
         <v>2.66000008583069</v>
       </c>
       <c r="G308" t="n">
-        <v>1.89326691627502</v>
+        <v>1.89326703548431</v>
       </c>
       <c r="H308" t="s">
         <v>8</v>
@@ -8403,7 +8403,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G309" t="n">
-        <v>1.85056173801422</v>
+        <v>1.85056149959564</v>
       </c>
       <c r="H309" t="s">
         <v>8</v>
@@ -8429,7 +8429,7 @@
         <v>2.76999998092651</v>
       </c>
       <c r="G310" t="n">
-        <v>1.97155976295471</v>
+        <v>1.97156000137329</v>
       </c>
       <c r="H310" t="s">
         <v>8</v>
@@ -8455,7 +8455,7 @@
         <v>3.13800001144409</v>
       </c>
       <c r="G311" t="n">
-        <v>2.23348546028137</v>
+        <v>2.23348569869995</v>
       </c>
       <c r="H311" t="s">
         <v>8</v>
@@ -8585,7 +8585,7 @@
         <v>3.56399989128113</v>
       </c>
       <c r="G316" t="n">
-        <v>2.53669309616089</v>
+        <v>2.53669261932373</v>
       </c>
       <c r="H316" t="s">
         <v>8</v>
@@ -8611,7 +8611,7 @@
         <v>3.52800011634827</v>
       </c>
       <c r="G317" t="n">
-        <v>2.51106977462769</v>
+        <v>2.51106953620911</v>
       </c>
       <c r="H317" t="s">
         <v>8</v>
@@ -8637,7 +8637,7 @@
         <v>3.46600008010864</v>
       </c>
       <c r="G318" t="n">
-        <v>2.46694087982178</v>
+        <v>2.46694135665894</v>
       </c>
       <c r="H318" t="s">
         <v>8</v>
@@ -8663,7 +8663,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G319" t="n">
-        <v>2.51961040496826</v>
+        <v>2.51961088180542</v>
       </c>
       <c r="H319" t="s">
         <v>8</v>
@@ -8689,7 +8689,7 @@
         <v>3.49000000953674</v>
       </c>
       <c r="G320" t="n">
-        <v>2.48402333259583</v>
+        <v>2.48402309417725</v>
       </c>
       <c r="H320" t="s">
         <v>8</v>
@@ -8741,7 +8741,7 @@
         <v>3.5</v>
       </c>
       <c r="G322" t="n">
-        <v>2.49114036560059</v>
+        <v>2.49114084243774</v>
       </c>
       <c r="H322" t="s">
         <v>8</v>
@@ -8767,7 +8767,7 @@
         <v>3.5</v>
       </c>
       <c r="G323" t="n">
-        <v>2.49114036560059</v>
+        <v>2.49114084243774</v>
       </c>
       <c r="H323" t="s">
         <v>8</v>
@@ -8793,7 +8793,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G324" t="n">
-        <v>2.56231594085693</v>
+        <v>2.56231617927551</v>
       </c>
       <c r="H324" t="s">
         <v>8</v>
@@ -8845,7 +8845,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G326" t="n">
-        <v>2.64772629737854</v>
+        <v>2.6477267742157</v>
       </c>
       <c r="H326" t="s">
         <v>8</v>
@@ -8871,7 +8871,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G327" t="n">
-        <v>2.67619657516479</v>
+        <v>2.67619681358337</v>
       </c>
       <c r="H327" t="s">
         <v>8</v>
@@ -8897,7 +8897,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G328" t="n">
-        <v>2.63349151611328</v>
+        <v>2.6334912776947</v>
       </c>
       <c r="H328" t="s">
         <v>8</v>
@@ -8975,7 +8975,7 @@
         <v>3.55599999427795</v>
       </c>
       <c r="G331" t="n">
-        <v>2.53099918365479</v>
+        <v>2.53099870681763</v>
       </c>
       <c r="H331" t="s">
         <v>8</v>
@@ -9001,7 +9001,7 @@
         <v>3.48000001907349</v>
       </c>
       <c r="G332" t="n">
-        <v>2.47690534591675</v>
+        <v>2.47690558433533</v>
       </c>
       <c r="H332" t="s">
         <v>8</v>
@@ -9027,7 +9027,7 @@
         <v>3.58999991416931</v>
       </c>
       <c r="G333" t="n">
-        <v>2.55519866943359</v>
+        <v>2.55519843101501</v>
       </c>
       <c r="H333" t="s">
         <v>8</v>
@@ -9079,7 +9079,7 @@
         <v>3.51399993896484</v>
       </c>
       <c r="G335" t="n">
-        <v>2.50110483169556</v>
+        <v>2.50110530853271</v>
       </c>
       <c r="H335" t="s">
         <v>8</v>
@@ -9131,7 +9131,7 @@
         <v>3.65599989891052</v>
       </c>
       <c r="G337" t="n">
-        <v>2.60217452049255</v>
+        <v>2.60217428207397</v>
       </c>
       <c r="H337" t="s">
         <v>8</v>
@@ -9157,7 +9157,7 @@
         <v>3.71399998664856</v>
       </c>
       <c r="G338" t="n">
-        <v>2.64345574378967</v>
+        <v>2.64345598220825</v>
       </c>
       <c r="H338" t="s">
         <v>8</v>
@@ -9183,7 +9183,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G339" t="n">
-        <v>2.63349151611328</v>
+        <v>2.6334912776947</v>
       </c>
       <c r="H339" t="s">
         <v>8</v>
@@ -9209,7 +9209,7 @@
         <v>3.64800000190735</v>
       </c>
       <c r="G340" t="n">
-        <v>2.59648013114929</v>
+        <v>2.59648036956787</v>
       </c>
       <c r="H340" t="s">
         <v>8</v>
@@ -9235,7 +9235,7 @@
         <v>3.6159999370575</v>
       </c>
       <c r="G341" t="n">
-        <v>2.64103293418884</v>
+        <v>2.64103317260742</v>
       </c>
       <c r="H341" t="s">
         <v>8</v>
@@ -9261,7 +9261,7 @@
         <v>3.53800010681152</v>
       </c>
       <c r="G342" t="n">
-        <v>2.58406376838684</v>
+        <v>2.584064245224</v>
       </c>
       <c r="H342" t="s">
         <v>8</v>
@@ -9287,7 +9287,7 @@
         <v>3.67000007629395</v>
       </c>
       <c r="G343" t="n">
-        <v>2.68047332763672</v>
+        <v>2.6804735660553</v>
       </c>
       <c r="H343" t="s">
         <v>8</v>
@@ -9313,7 +9313,7 @@
         <v>3.67400002479553</v>
       </c>
       <c r="G344" t="n">
-        <v>2.68339514732361</v>
+        <v>2.68339490890503</v>
       </c>
       <c r="H344" t="s">
         <v>8</v>
@@ -9339,7 +9339,7 @@
         <v>3.73000001907349</v>
       </c>
       <c r="G345" t="n">
-        <v>2.7242956161499</v>
+        <v>2.72429585456848</v>
       </c>
       <c r="H345" t="s">
         <v>8</v>
@@ -9365,7 +9365,7 @@
         <v>3.80999994277954</v>
       </c>
       <c r="G346" t="n">
-        <v>2.78272581100464</v>
+        <v>2.78272557258606</v>
       </c>
       <c r="H346" t="s">
         <v>8</v>
@@ -9417,7 +9417,7 @@
         <v>3.7039999961853</v>
       </c>
       <c r="G348" t="n">
-        <v>2.7053062915802</v>
+        <v>2.70530605316162</v>
       </c>
       <c r="H348" t="s">
         <v>8</v>
@@ -9495,7 +9495,7 @@
         <v>3.58999991416931</v>
       </c>
       <c r="G351" t="n">
-        <v>2.62204337120056</v>
+        <v>2.62204313278198</v>
       </c>
       <c r="H351" t="s">
         <v>8</v>
@@ -9521,7 +9521,7 @@
         <v>3.58999991416931</v>
       </c>
       <c r="G352" t="n">
-        <v>2.62204337120056</v>
+        <v>2.62204313278198</v>
       </c>
       <c r="H352" t="s">
         <v>8</v>
@@ -9547,7 +9547,7 @@
         <v>3.57800006866455</v>
       </c>
       <c r="G353" t="n">
-        <v>2.61327910423279</v>
+        <v>2.61327886581421</v>
       </c>
       <c r="H353" t="s">
         <v>8</v>
@@ -9573,7 +9573,7 @@
         <v>3.62400007247925</v>
       </c>
       <c r="G354" t="n">
-        <v>2.64687585830688</v>
+        <v>2.64687633514404</v>
       </c>
       <c r="H354" t="s">
         <v>8</v>
@@ -9703,7 +9703,7 @@
         <v>3.71600008010864</v>
       </c>
       <c r="G359" t="n">
-        <v>2.71407079696655</v>
+        <v>2.71407055854797</v>
       </c>
       <c r="H359" t="s">
         <v>8</v>
@@ -9755,7 +9755,7 @@
         <v>3.67000007629395</v>
       </c>
       <c r="G361" t="n">
-        <v>2.68047332763672</v>
+        <v>2.6804735660553</v>
       </c>
       <c r="H361" t="s">
         <v>8</v>
@@ -9781,7 +9781,7 @@
         <v>3.73000001907349</v>
       </c>
       <c r="G362" t="n">
-        <v>2.7242956161499</v>
+        <v>2.72429585456848</v>
       </c>
       <c r="H362" t="s">
         <v>8</v>
@@ -9807,7 +9807,7 @@
         <v>3.86999988555908</v>
       </c>
       <c r="G363" t="n">
-        <v>2.8265483379364</v>
+        <v>2.82654809951782</v>
       </c>
       <c r="H363" t="s">
         <v>8</v>
@@ -9859,7 +9859,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G365" t="n">
-        <v>3.12600183486938</v>
+        <v>3.12600159645081</v>
       </c>
       <c r="H365" t="s">
         <v>8</v>
@@ -9911,7 +9911,7 @@
         <v>4.51999998092651</v>
       </c>
       <c r="G367" t="n">
-        <v>3.30129146575928</v>
+        <v>3.3012912273407</v>
       </c>
       <c r="H367" t="s">
         <v>8</v>
@@ -9937,7 +9937,7 @@
         <v>4.53000020980835</v>
       </c>
       <c r="G368" t="n">
-        <v>3.30859518051147</v>
+        <v>3.30859470367432</v>
       </c>
       <c r="H368" t="s">
         <v>8</v>
@@ -9963,7 +9963,7 @@
         <v>4.41400003433228</v>
       </c>
       <c r="G369" t="n">
-        <v>3.22387170791626</v>
+        <v>3.22387194633484</v>
       </c>
       <c r="H369" t="s">
         <v>8</v>
@@ -10015,7 +10015,7 @@
         <v>4.38000011444092</v>
       </c>
       <c r="G371" t="n">
-        <v>3.19903922080994</v>
+        <v>3.19903898239136</v>
       </c>
       <c r="H371" t="s">
         <v>8</v>
@@ -10041,7 +10041,7 @@
         <v>4.35799980163574</v>
       </c>
       <c r="G372" t="n">
-        <v>3.18297100067139</v>
+        <v>3.18297052383423</v>
       </c>
       <c r="H372" t="s">
         <v>8</v>
@@ -10067,7 +10067,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G373" t="n">
-        <v>3.1406090259552</v>
+        <v>3.14060950279236</v>
       </c>
       <c r="H373" t="s">
         <v>8</v>
@@ -10093,7 +10093,7 @@
         <v>4.2519998550415</v>
       </c>
       <c r="G374" t="n">
-        <v>3.10555124282837</v>
+        <v>3.10555100440979</v>
       </c>
       <c r="H374" t="s">
         <v>8</v>
@@ -10145,7 +10145,7 @@
         <v>4.21400022506714</v>
       </c>
       <c r="G376" t="n">
-        <v>3.07779741287231</v>
+        <v>3.07779717445374</v>
       </c>
       <c r="H376" t="s">
         <v>8</v>
@@ -10171,7 +10171,7 @@
         <v>4.27199983596802</v>
       </c>
       <c r="G377" t="n">
-        <v>3.12015819549561</v>
+        <v>3.12015867233276</v>
       </c>
       <c r="H377" t="s">
         <v>8</v>
@@ -10197,7 +10197,7 @@
         <v>4.23400020599365</v>
       </c>
       <c r="G378" t="n">
-        <v>3.09240436553955</v>
+        <v>3.09240484237671</v>
       </c>
       <c r="H378" t="s">
         <v>8</v>
@@ -10223,7 +10223,7 @@
         <v>4.38399982452393</v>
       </c>
       <c r="G379" t="n">
-        <v>3.20196080207825</v>
+        <v>3.20196008682251</v>
       </c>
       <c r="H379" t="s">
         <v>8</v>
@@ -10275,7 +10275,7 @@
         <v>4.22599983215332</v>
       </c>
       <c r="G381" t="n">
-        <v>3.08656144142151</v>
+        <v>3.08656120300293</v>
       </c>
       <c r="H381" t="s">
         <v>8</v>
@@ -10301,7 +10301,7 @@
         <v>4.22399997711182</v>
       </c>
       <c r="G382" t="n">
-        <v>3.08510041236877</v>
+        <v>3.08510088920593</v>
       </c>
       <c r="H382" t="s">
         <v>8</v>
@@ -10327,7 +10327,7 @@
         <v>4.12400007247925</v>
       </c>
       <c r="G383" t="n">
-        <v>3.01206350326538</v>
+        <v>3.0120632648468</v>
       </c>
       <c r="H383" t="s">
         <v>8</v>
@@ -10353,7 +10353,7 @@
         <v>4.06799983978271</v>
       </c>
       <c r="G384" t="n">
-        <v>2.97116184234619</v>
+        <v>2.97116231918335</v>
       </c>
       <c r="H384" t="s">
         <v>8</v>
@@ -10379,7 +10379,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G385" t="n">
-        <v>2.95801615715027</v>
+        <v>2.95801591873169</v>
       </c>
       <c r="H385" t="s">
         <v>8</v>
@@ -10405,7 +10405,7 @@
         <v>4.15199995040894</v>
       </c>
       <c r="G386" t="n">
-        <v>3.03251361846924</v>
+        <v>3.03251385688782</v>
       </c>
       <c r="H386" t="s">
         <v>8</v>
@@ -10431,7 +10431,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G387" t="n">
-        <v>3.1406090259552</v>
+        <v>3.14060950279236</v>
       </c>
       <c r="H387" t="s">
         <v>8</v>
@@ -10457,7 +10457,7 @@
         <v>4.23799991607666</v>
       </c>
       <c r="G388" t="n">
-        <v>3.09532618522644</v>
+        <v>3.09532594680786</v>
       </c>
       <c r="H388" t="s">
         <v>8</v>
@@ -10483,7 +10483,7 @@
         <v>4.18800020217896</v>
       </c>
       <c r="G389" t="n">
-        <v>3.05880737304688</v>
+        <v>3.05880689620972</v>
       </c>
       <c r="H389" t="s">
         <v>8</v>
@@ -10535,7 +10535,7 @@
         <v>4.17000007629395</v>
       </c>
       <c r="G391" t="n">
-        <v>3.04566049575806</v>
+        <v>3.04566073417664</v>
       </c>
       <c r="H391" t="s">
         <v>8</v>
@@ -10561,7 +10561,7 @@
         <v>4.12200021743774</v>
       </c>
       <c r="G392" t="n">
-        <v>3.01060271263123</v>
+        <v>3.01060247421265</v>
       </c>
       <c r="H392" t="s">
         <v>8</v>
@@ -10613,7 +10613,7 @@
         <v>4.22800016403198</v>
       </c>
       <c r="G394" t="n">
-        <v>3.08802270889282</v>
+        <v>3.08802247047424</v>
       </c>
       <c r="H394" t="s">
         <v>8</v>
@@ -10665,7 +10665,7 @@
         <v>4.23400020599365</v>
       </c>
       <c r="G396" t="n">
-        <v>3.09240436553955</v>
+        <v>3.09240484237671</v>
       </c>
       <c r="H396" t="s">
         <v>8</v>
@@ -10691,7 +10691,7 @@
         <v>4.27799987792969</v>
       </c>
       <c r="G397" t="n">
-        <v>3.12454080581665</v>
+        <v>3.12454104423523</v>
       </c>
       <c r="H397" t="s">
         <v>8</v>
@@ -10717,7 +10717,7 @@
         <v>4.25400018692017</v>
       </c>
       <c r="G398" t="n">
-        <v>3.10701179504395</v>
+        <v>3.10701203346252</v>
       </c>
       <c r="H398" t="s">
         <v>8</v>
@@ -10743,7 +10743,7 @@
         <v>4.21400022506714</v>
       </c>
       <c r="G399" t="n">
-        <v>3.07779741287231</v>
+        <v>3.07779717445374</v>
       </c>
       <c r="H399" t="s">
         <v>8</v>
@@ -10769,7 +10769,7 @@
         <v>4.26800012588501</v>
       </c>
       <c r="G400" t="n">
-        <v>3.11723709106445</v>
+        <v>3.11723756790161</v>
       </c>
       <c r="H400" t="s">
         <v>8</v>
@@ -10795,7 +10795,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G401" t="n">
-        <v>3.16982412338257</v>
+        <v>3.16982460021973</v>
       </c>
       <c r="H401" t="s">
         <v>8</v>
@@ -10847,7 +10847,7 @@
         <v>4.51999998092651</v>
       </c>
       <c r="G403" t="n">
-        <v>3.30129146575928</v>
+        <v>3.3012912273407</v>
       </c>
       <c r="H403" t="s">
         <v>8</v>
@@ -10873,7 +10873,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G404" t="n">
-        <v>3.35972118377686</v>
+        <v>3.35972142219543</v>
       </c>
       <c r="H404" t="s">
         <v>8</v>
@@ -10951,7 +10951,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G407" t="n">
-        <v>3.4473659992218</v>
+        <v>3.44736623764038</v>
       </c>
       <c r="H407" t="s">
         <v>8</v>
@@ -10977,7 +10977,7 @@
         <v>4.63800001144409</v>
       </c>
       <c r="G408" t="n">
-        <v>3.38747596740723</v>
+        <v>3.38747549057007</v>
       </c>
       <c r="H408" t="s">
         <v>8</v>
@@ -11003,7 +11003,7 @@
         <v>4.59000015258789</v>
       </c>
       <c r="G409" t="n">
-        <v>3.35241794586182</v>
+        <v>3.35241770744324</v>
       </c>
       <c r="H409" t="s">
         <v>8</v>
@@ -11029,7 +11029,7 @@
         <v>4.60599994659424</v>
       </c>
       <c r="G410" t="n">
-        <v>3.36410307884216</v>
+        <v>3.3641037940979</v>
       </c>
       <c r="H410" t="s">
         <v>8</v>
@@ -11055,7 +11055,7 @@
         <v>4.71000003814697</v>
       </c>
       <c r="G411" t="n">
-        <v>3.44006299972534</v>
+        <v>3.44006252288818</v>
       </c>
       <c r="H411" t="s">
         <v>8</v>
@@ -11081,7 +11081,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G412" t="n">
-        <v>3.49118876457214</v>
+        <v>3.4911892414093</v>
       </c>
       <c r="H412" t="s">
         <v>8</v>
@@ -11107,7 +11107,7 @@
         <v>4.78999996185303</v>
       </c>
       <c r="G413" t="n">
-        <v>3.49849247932434</v>
+        <v>3.49849224090576</v>
       </c>
       <c r="H413" t="s">
         <v>8</v>
@@ -11133,7 +11133,7 @@
         <v>4.67000007629395</v>
       </c>
       <c r="G414" t="n">
-        <v>3.41084766387939</v>
+        <v>3.41084742546082</v>
       </c>
       <c r="H414" t="s">
         <v>8</v>
@@ -11159,7 +11159,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G415" t="n">
-        <v>3.43275904655457</v>
+        <v>3.43275856971741</v>
       </c>
       <c r="H415" t="s">
         <v>8</v>
@@ -11185,7 +11185,7 @@
         <v>5.04500007629395</v>
       </c>
       <c r="G416" t="n">
-        <v>3.68473815917969</v>
+        <v>3.68473863601685</v>
       </c>
       <c r="H416" t="s">
         <v>8</v>
@@ -11237,7 +11237,7 @@
         <v>5</v>
       </c>
       <c r="G418" t="n">
-        <v>3.65187120437622</v>
+        <v>3.65187168121338</v>
       </c>
       <c r="H418" t="s">
         <v>8</v>
@@ -11289,7 +11289,7 @@
         <v>5.03999996185303</v>
       </c>
       <c r="G420" t="n">
-        <v>3.68108558654785</v>
+        <v>3.68108582496643</v>
       </c>
       <c r="H420" t="s">
         <v>8</v>
@@ -11315,7 +11315,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G421" t="n">
-        <v>3.68839049339294</v>
+        <v>3.68839001655579</v>
       </c>
       <c r="H421" t="s">
         <v>8</v>
@@ -11341,7 +11341,7 @@
         <v>4.99599981307983</v>
       </c>
       <c r="G422" t="n">
-        <v>3.64894914627075</v>
+        <v>3.64894962310791</v>
       </c>
       <c r="H422" t="s">
         <v>8</v>
@@ -11367,7 +11367,7 @@
         <v>4.98600006103516</v>
       </c>
       <c r="G423" t="n">
-        <v>3.64164590835571</v>
+        <v>3.64164543151855</v>
       </c>
       <c r="H423" t="s">
         <v>8</v>
@@ -11393,7 +11393,7 @@
         <v>4.9060001373291</v>
       </c>
       <c r="G424" t="n">
-        <v>3.58321642875671</v>
+        <v>3.58321619033813</v>
       </c>
       <c r="H424" t="s">
         <v>8</v>
@@ -11419,7 +11419,7 @@
         <v>4.86999988555908</v>
       </c>
       <c r="G425" t="n">
-        <v>3.5569224357605</v>
+        <v>3.55692267417908</v>
       </c>
       <c r="H425" t="s">
         <v>8</v>
@@ -11471,7 +11471,7 @@
         <v>5.09499979019165</v>
       </c>
       <c r="G427" t="n">
-        <v>3.72125649452209</v>
+        <v>3.72125625610352</v>
       </c>
       <c r="H427" t="s">
         <v>8</v>
@@ -11549,7 +11549,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G430" t="n">
-        <v>3.8709831237793</v>
+        <v>3.87098360061646</v>
       </c>
       <c r="H430" t="s">
         <v>8</v>
@@ -11575,7 +11575,7 @@
         <v>5.28000020980835</v>
       </c>
       <c r="G431" t="n">
-        <v>3.85637617111206</v>
+        <v>3.8563756942749</v>
       </c>
       <c r="H431" t="s">
         <v>8</v>
@@ -11627,7 +11627,7 @@
         <v>5.30499982833862</v>
       </c>
       <c r="G433" t="n">
-        <v>3.87463569641113</v>
+        <v>3.87463474273682</v>
       </c>
       <c r="H433" t="s">
         <v>8</v>
@@ -11653,7 +11653,7 @@
         <v>5.30999994277954</v>
       </c>
       <c r="G434" t="n">
-        <v>3.87828707695007</v>
+        <v>3.87828660011292</v>
       </c>
       <c r="H434" t="s">
         <v>8</v>
@@ -11679,7 +11679,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G435" t="n">
-        <v>3.94402098655701</v>
+        <v>3.94402050971985</v>
       </c>
       <c r="H435" t="s">
         <v>8</v>
@@ -11705,7 +11705,7 @@
         <v>5.30499982833862</v>
       </c>
       <c r="G436" t="n">
-        <v>3.87463569641113</v>
+        <v>3.87463474273682</v>
       </c>
       <c r="H436" t="s">
         <v>8</v>
@@ -11731,7 +11731,7 @@
         <v>5.2350001335144</v>
       </c>
       <c r="G437" t="n">
-        <v>3.82350969314575</v>
+        <v>3.82350945472717</v>
       </c>
       <c r="H437" t="s">
         <v>8</v>
@@ -11757,7 +11757,7 @@
         <v>4.80399990081787</v>
       </c>
       <c r="G438" t="n">
-        <v>3.50871729850769</v>
+        <v>3.50871777534485</v>
       </c>
       <c r="H438" t="s">
         <v>8</v>
@@ -11783,7 +11783,7 @@
         <v>4.84999990463257</v>
       </c>
       <c r="G439" t="n">
-        <v>3.54231476783752</v>
+        <v>3.54231524467468</v>
       </c>
       <c r="H439" t="s">
         <v>8</v>
@@ -11809,7 +11809,7 @@
         <v>4.67600011825562</v>
       </c>
       <c r="G440" t="n">
-        <v>3.41523027420044</v>
+        <v>3.41522979736328</v>
       </c>
       <c r="H440" t="s">
         <v>8</v>
@@ -11835,7 +11835,7 @@
         <v>4.76999998092651</v>
       </c>
       <c r="G441" t="n">
-        <v>3.48388504981995</v>
+        <v>3.48388481140137</v>
       </c>
       <c r="H441" t="s">
         <v>8</v>
@@ -11861,7 +11861,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G442" t="n">
-        <v>3.35972118377686</v>
+        <v>3.35972142219543</v>
       </c>
       <c r="H442" t="s">
         <v>8</v>
@@ -11887,7 +11887,7 @@
         <v>4.57000017166138</v>
       </c>
       <c r="G443" t="n">
-        <v>3.33781051635742</v>
+        <v>3.33781003952026</v>
       </c>
       <c r="H443" t="s">
         <v>8</v>
@@ -11913,7 +11913,7 @@
         <v>4.51000022888184</v>
       </c>
       <c r="G444" t="n">
-        <v>3.29398775100708</v>
+        <v>3.2939875125885</v>
       </c>
       <c r="H444" t="s">
         <v>8</v>
@@ -11965,7 +11965,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G446" t="n">
-        <v>3.32320284843445</v>
+        <v>3.32320237159729</v>
       </c>
       <c r="H446" t="s">
         <v>8</v>
@@ -12017,7 +12017,7 @@
         <v>4.68200016021729</v>
       </c>
       <c r="G448" t="n">
-        <v>3.41961216926575</v>
+        <v>3.41961264610291</v>
       </c>
       <c r="H448" t="s">
         <v>8</v>
@@ -12043,7 +12043,7 @@
         <v>4.71000003814697</v>
       </c>
       <c r="G449" t="n">
-        <v>3.44006299972534</v>
+        <v>3.44006252288818</v>
       </c>
       <c r="H449" t="s">
         <v>8</v>
@@ -12069,7 +12069,7 @@
         <v>4.78599977493286</v>
       </c>
       <c r="G450" t="n">
-        <v>3.49557042121887</v>
+        <v>3.49557065963745</v>
       </c>
       <c r="H450" t="s">
         <v>8</v>
@@ -12095,7 +12095,7 @@
         <v>4.63600015640259</v>
       </c>
       <c r="G451" t="n">
-        <v>3.38601469993591</v>
+        <v>3.38601517677307</v>
       </c>
       <c r="H451" t="s">
         <v>8</v>
@@ -12147,7 +12147,7 @@
         <v>4.65799999237061</v>
       </c>
       <c r="G453" t="n">
-        <v>3.40208315849304</v>
+        <v>3.40208292007446</v>
       </c>
       <c r="H453" t="s">
         <v>8</v>
@@ -12199,7 +12199,7 @@
         <v>4.5479998588562</v>
       </c>
       <c r="G455" t="n">
-        <v>3.32174205780029</v>
+        <v>3.32174158096313</v>
       </c>
       <c r="H455" t="s">
         <v>8</v>
@@ -12225,7 +12225,7 @@
         <v>4.61800003051758</v>
       </c>
       <c r="G456" t="n">
-        <v>3.37286829948425</v>
+        <v>3.37286853790283</v>
       </c>
       <c r="H456" t="s">
         <v>8</v>
@@ -12251,7 +12251,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G457" t="n">
-        <v>3.32320284843445</v>
+        <v>3.32320237159729</v>
       </c>
       <c r="H457" t="s">
         <v>8</v>
@@ -12303,7 +12303,7 @@
         <v>4.67600011825562</v>
       </c>
       <c r="G459" t="n">
-        <v>3.41523027420044</v>
+        <v>3.41522979736328</v>
       </c>
       <c r="H459" t="s">
         <v>8</v>
@@ -12381,7 +12381,7 @@
         <v>4.63399982452393</v>
       </c>
       <c r="G462" t="n">
-        <v>3.38455414772034</v>
+        <v>3.38455390930176</v>
       </c>
       <c r="H462" t="s">
         <v>8</v>
@@ -12433,7 +12433,7 @@
         <v>4.68599987030029</v>
       </c>
       <c r="G464" t="n">
-        <v>3.42253351211548</v>
+        <v>3.42253398895264</v>
       </c>
       <c r="H464" t="s">
         <v>8</v>
@@ -12459,7 +12459,7 @@
         <v>4.72399997711182</v>
       </c>
       <c r="G465" t="n">
-        <v>3.45028805732727</v>
+        <v>3.45028758049011</v>
       </c>
       <c r="H465" t="s">
         <v>8</v>
@@ -12485,7 +12485,7 @@
         <v>4.63199996948242</v>
       </c>
       <c r="G466" t="n">
-        <v>3.3830931186676</v>
+        <v>3.38309335708618</v>
       </c>
       <c r="H466" t="s">
         <v>8</v>
@@ -12511,7 +12511,7 @@
         <v>4.69600009918213</v>
       </c>
       <c r="G467" t="n">
-        <v>3.42983675003052</v>
+        <v>3.42983722686768</v>
       </c>
       <c r="H467" t="s">
         <v>8</v>
@@ -12537,7 +12537,7 @@
         <v>4.67799997329712</v>
       </c>
       <c r="G468" t="n">
-        <v>3.41669082641602</v>
+        <v>3.41669058799744</v>
       </c>
       <c r="H468" t="s">
         <v>8</v>
@@ -12615,7 +12615,7 @@
         <v>4.87799978256226</v>
       </c>
       <c r="G471" t="n">
-        <v>3.56276512145996</v>
+        <v>3.56276535987854</v>
       </c>
       <c r="H471" t="s">
         <v>8</v>
@@ -12641,7 +12641,7 @@
         <v>4.88800001144409</v>
       </c>
       <c r="G472" t="n">
-        <v>3.57006907463074</v>
+        <v>3.57006931304932</v>
       </c>
       <c r="H472" t="s">
         <v>8</v>
@@ -12693,7 +12693,7 @@
         <v>4.72599983215332</v>
       </c>
       <c r="G474" t="n">
-        <v>3.45174837112427</v>
+        <v>3.45174884796143</v>
       </c>
       <c r="H474" t="s">
         <v>8</v>
@@ -12719,7 +12719,7 @@
         <v>4.72399997711182</v>
       </c>
       <c r="G475" t="n">
-        <v>3.45028805732727</v>
+        <v>3.45028758049011</v>
       </c>
       <c r="H475" t="s">
         <v>8</v>
@@ -12745,7 +12745,7 @@
         <v>4.25400018692017</v>
       </c>
       <c r="G476" t="n">
-        <v>3.10701179504395</v>
+        <v>3.10701203346252</v>
       </c>
       <c r="H476" t="s">
         <v>8</v>
@@ -12797,7 +12797,7 @@
         <v>4.28399991989136</v>
       </c>
       <c r="G478" t="n">
-        <v>3.12892293930054</v>
+        <v>3.12892270088196</v>
       </c>
       <c r="H478" t="s">
         <v>8</v>
@@ -12901,7 +12901,7 @@
         <v>4.07000017166138</v>
       </c>
       <c r="G482" t="n">
-        <v>2.97262334823608</v>
+        <v>2.9726231098175</v>
       </c>
       <c r="H482" t="s">
         <v>8</v>
@@ -12927,7 +12927,7 @@
         <v>4.07000017166138</v>
       </c>
       <c r="G483" t="n">
-        <v>2.97262334823608</v>
+        <v>2.9726231098175</v>
       </c>
       <c r="H483" t="s">
         <v>8</v>
@@ -12953,7 +12953,7 @@
         <v>4.16800022125244</v>
       </c>
       <c r="G484" t="n">
-        <v>3.04419994354248</v>
+        <v>3.0441997051239</v>
       </c>
       <c r="H484" t="s">
         <v>8</v>
@@ -12979,7 +12979,7 @@
         <v>4.15399980545044</v>
       </c>
       <c r="G485" t="n">
-        <v>3.03397440910339</v>
+        <v>3.03397417068481</v>
       </c>
       <c r="H485" t="s">
         <v>8</v>
@@ -13005,7 +13005,7 @@
         <v>4.19600009918213</v>
       </c>
       <c r="G486" t="n">
-        <v>3.06465005874634</v>
+        <v>3.06465077400208</v>
       </c>
       <c r="H486" t="s">
         <v>8</v>
@@ -13031,7 +13031,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G487" t="n">
-        <v>3.09678626060486</v>
+        <v>3.09678649902344</v>
       </c>
       <c r="H487" t="s">
         <v>8</v>
@@ -13057,7 +13057,7 @@
         <v>4.24399995803833</v>
       </c>
       <c r="G488" t="n">
-        <v>3.09970855712891</v>
+        <v>3.09970831871033</v>
       </c>
       <c r="H488" t="s">
         <v>8</v>
@@ -13109,7 +13109,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G490" t="n">
-        <v>2.88497805595398</v>
+        <v>2.88497853279114</v>
       </c>
       <c r="H490" t="s">
         <v>8</v>
@@ -13135,7 +13135,7 @@
         <v>3.73399996757507</v>
       </c>
       <c r="G491" t="n">
-        <v>2.72721743583679</v>
+        <v>2.72721719741821</v>
       </c>
       <c r="H491" t="s">
         <v>8</v>
@@ -13213,7 +13213,7 @@
         <v>3.86800003051758</v>
       </c>
       <c r="G494" t="n">
-        <v>2.82508754730225</v>
+        <v>2.82508778572083</v>
       </c>
       <c r="H494" t="s">
         <v>8</v>
@@ -13265,7 +13265,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G496" t="n">
-        <v>2.73159956932068</v>
+        <v>2.7315993309021</v>
       </c>
       <c r="H496" t="s">
         <v>8</v>
@@ -13395,7 +13395,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G501" t="n">
-        <v>2.84845972061157</v>
+        <v>2.84845948219299</v>
       </c>
       <c r="H501" t="s">
         <v>8</v>
@@ -13447,7 +13447,7 @@
         <v>4.05800008773804</v>
       </c>
       <c r="G503" t="n">
-        <v>2.96385884284973</v>
+        <v>2.96385860443115</v>
       </c>
       <c r="H503" t="s">
         <v>8</v>
@@ -13499,7 +13499,7 @@
         <v>4.07000017166138</v>
       </c>
       <c r="G505" t="n">
-        <v>2.97262334823608</v>
+        <v>2.9726231098175</v>
       </c>
       <c r="H505" t="s">
         <v>8</v>
@@ -13577,7 +13577,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G508" t="n">
-        <v>3.09678626060486</v>
+        <v>3.09678649902344</v>
       </c>
       <c r="H508" t="s">
         <v>8</v>
@@ -13629,7 +13629,7 @@
         <v>4.35799980163574</v>
       </c>
       <c r="G510" t="n">
-        <v>3.18297100067139</v>
+        <v>3.18297052383423</v>
       </c>
       <c r="H510" t="s">
         <v>8</v>
@@ -13655,7 +13655,7 @@
         <v>4.31799983978271</v>
       </c>
       <c r="G511" t="n">
-        <v>3.15375566482544</v>
+        <v>3.15375590324402</v>
       </c>
       <c r="H511" t="s">
         <v>8</v>
@@ -13733,7 +13733,7 @@
         <v>4.37599992752075</v>
       </c>
       <c r="G514" t="n">
-        <v>3.19611716270447</v>
+        <v>3.19611763954163</v>
       </c>
       <c r="H514" t="s">
         <v>8</v>
@@ -13785,7 +13785,7 @@
         <v>4.3600001335144</v>
       </c>
       <c r="G516" t="n">
-        <v>3.18443131446838</v>
+        <v>3.18443179130554</v>
       </c>
       <c r="H516" t="s">
         <v>8</v>
@@ -13811,7 +13811,7 @@
         <v>4.35400009155273</v>
       </c>
       <c r="G517" t="n">
-        <v>3.18004941940308</v>
+        <v>3.1800491809845</v>
       </c>
       <c r="H517" t="s">
         <v>8</v>
@@ -13837,7 +13837,7 @@
         <v>4.41400003433228</v>
       </c>
       <c r="G518" t="n">
-        <v>3.22387170791626</v>
+        <v>3.22387194633484</v>
       </c>
       <c r="H518" t="s">
         <v>8</v>
@@ -13863,7 +13863,7 @@
         <v>4.46199989318848</v>
       </c>
       <c r="G519" t="n">
-        <v>3.25892949104309</v>
+        <v>3.25892996788025</v>
       </c>
       <c r="H519" t="s">
         <v>8</v>
@@ -13889,7 +13889,7 @@
         <v>4.46199989318848</v>
       </c>
       <c r="G520" t="n">
-        <v>3.25892949104309</v>
+        <v>3.25892996788025</v>
       </c>
       <c r="H520" t="s">
         <v>8</v>
@@ -13915,7 +13915,7 @@
         <v>4.47200012207031</v>
       </c>
       <c r="G521" t="n">
-        <v>3.26623344421387</v>
+        <v>3.26623368263245</v>
       </c>
       <c r="H521" t="s">
         <v>8</v>
@@ -13941,7 +13941,7 @@
         <v>4.44999980926514</v>
       </c>
       <c r="G522" t="n">
-        <v>3.25016522407532</v>
+        <v>3.2501654624939</v>
       </c>
       <c r="H522" t="s">
         <v>8</v>
@@ -14045,7 +14045,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G526" t="n">
-        <v>3.25746917724609</v>
+        <v>3.25746941566467</v>
       </c>
       <c r="H526" t="s">
         <v>8</v>
@@ -14149,7 +14149,7 @@
         <v>4.34800004959106</v>
       </c>
       <c r="G530" t="n">
-        <v>3.17566680908203</v>
+        <v>3.17566704750061</v>
       </c>
       <c r="H530" t="s">
         <v>8</v>
@@ -14201,7 +14201,7 @@
         <v>4.16200017929077</v>
       </c>
       <c r="G532" t="n">
-        <v>3.03981781005859</v>
+        <v>3.03981757164001</v>
       </c>
       <c r="H532" t="s">
         <v>8</v>
@@ -14253,7 +14253,7 @@
         <v>4.19000005722046</v>
       </c>
       <c r="G534" t="n">
-        <v>3.06026840209961</v>
+        <v>3.06026768684387</v>
       </c>
       <c r="H534" t="s">
         <v>8</v>
@@ -14383,7 +14383,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G539" t="n">
-        <v>2.73159956932068</v>
+        <v>2.7315993309021</v>
       </c>
       <c r="H539" t="s">
         <v>8</v>
@@ -14435,7 +14435,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G541" t="n">
-        <v>2.73159956932068</v>
+        <v>2.7315993309021</v>
       </c>
       <c r="H541" t="s">
         <v>8</v>
@@ -14539,7 +14539,7 @@
         <v>3.77600002288818</v>
       </c>
       <c r="G545" t="n">
-        <v>2.75789308547974</v>
+        <v>2.75789284706116</v>
       </c>
       <c r="H545" t="s">
         <v>8</v>
@@ -14617,7 +14617,7 @@
         <v>3.78200006484985</v>
       </c>
       <c r="G548" t="n">
-        <v>2.76227521896362</v>
+        <v>2.7622754573822</v>
       </c>
       <c r="H548" t="s">
         <v>8</v>
@@ -14643,7 +14643,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G549" t="n">
-        <v>2.70238447189331</v>
+        <v>2.70238471031189</v>
       </c>
       <c r="H549" t="s">
         <v>8</v>
@@ -14721,7 +14721,7 @@
         <v>3.97000002861023</v>
       </c>
       <c r="G552" t="n">
-        <v>2.89958524703979</v>
+        <v>2.89958572387695</v>
       </c>
       <c r="H552" t="s">
         <v>8</v>
@@ -14747,7 +14747,7 @@
         <v>4</v>
       </c>
       <c r="G553" t="n">
-        <v>2.92149662971497</v>
+        <v>2.92149639129639</v>
       </c>
       <c r="H553" t="s">
         <v>8</v>
@@ -14773,7 +14773,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G554" t="n">
-        <v>2.84845972061157</v>
+        <v>2.84845948219299</v>
       </c>
       <c r="H554" t="s">
         <v>8</v>
@@ -14877,7 +14877,7 @@
         <v>3.87199997901917</v>
       </c>
       <c r="G558" t="n">
-        <v>2.82800889015198</v>
+        <v>2.8280086517334</v>
       </c>
       <c r="H558" t="s">
         <v>8</v>
@@ -14903,7 +14903,7 @@
         <v>3.90400004386902</v>
       </c>
       <c r="G559" t="n">
-        <v>2.85138058662415</v>
+        <v>2.85138082504272</v>
       </c>
       <c r="H559" t="s">
         <v>8</v>
@@ -14929,7 +14929,7 @@
         <v>3.9760000705719</v>
       </c>
       <c r="G560" t="n">
-        <v>2.90396809577942</v>
+        <v>2.90396785736084</v>
       </c>
       <c r="H560" t="s">
         <v>8</v>
@@ -14955,7 +14955,7 @@
         <v>4.01000022888184</v>
       </c>
       <c r="G561" t="n">
-        <v>2.92880082130432</v>
+        <v>2.92880058288574</v>
       </c>
       <c r="H561" t="s">
         <v>8</v>
@@ -14981,7 +14981,7 @@
         <v>3.94400000572205</v>
       </c>
       <c r="G562" t="n">
-        <v>2.88059592247009</v>
+        <v>2.88059568405151</v>
       </c>
       <c r="H562" t="s">
         <v>8</v>
@@ -15007,7 +15007,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G563" t="n">
-        <v>2.81194019317627</v>
+        <v>2.81194067001343</v>
       </c>
       <c r="H563" t="s">
         <v>8</v>
@@ -15059,7 +15059,7 @@
         <v>4.32000017166138</v>
       </c>
       <c r="G565" t="n">
-        <v>3.15521717071533</v>
+        <v>3.15521693229675</v>
       </c>
       <c r="H565" t="s">
         <v>8</v>
@@ -15085,7 +15085,7 @@
         <v>4.32200002670288</v>
       </c>
       <c r="G566" t="n">
-        <v>3.15667724609375</v>
+        <v>3.15667748451233</v>
       </c>
       <c r="H566" t="s">
         <v>8</v>
@@ -15111,7 +15111,7 @@
         <v>4.2960000038147</v>
       </c>
       <c r="G567" t="n">
-        <v>3.13768768310547</v>
+        <v>3.13768792152405</v>
       </c>
       <c r="H567" t="s">
         <v>8</v>
@@ -15215,7 +15215,7 @@
         <v>4.08400011062622</v>
       </c>
       <c r="G571" t="n">
-        <v>2.98284840583801</v>
+        <v>2.98284864425659</v>
       </c>
       <c r="H571" t="s">
         <v>8</v>
@@ -15241,7 +15241,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G572" t="n">
-        <v>2.9945342540741</v>
+        <v>2.99453377723694</v>
       </c>
       <c r="H572" t="s">
         <v>8</v>
@@ -15267,7 +15267,7 @@
         <v>4.09200000762939</v>
       </c>
       <c r="G573" t="n">
-        <v>2.98869109153748</v>
+        <v>2.98869132995605</v>
       </c>
       <c r="H573" t="s">
         <v>8</v>
@@ -15319,7 +15319,7 @@
         <v>4.18400001525879</v>
       </c>
       <c r="G575" t="n">
-        <v>3.05588579177856</v>
+        <v>3.05588555335999</v>
       </c>
       <c r="H575" t="s">
         <v>8</v>
@@ -15345,7 +15345,7 @@
         <v>4.14200019836426</v>
       </c>
       <c r="G576" t="n">
-        <v>3.02520990371704</v>
+        <v>3.0252103805542</v>
       </c>
       <c r="H576" t="s">
         <v>8</v>
@@ -15371,7 +15371,7 @@
         <v>4.2020001411438</v>
       </c>
       <c r="G577" t="n">
-        <v>3.0690324306488</v>
+        <v>3.06903266906738</v>
       </c>
       <c r="H577" t="s">
         <v>8</v>
@@ -15423,7 +15423,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G579" t="n">
-        <v>3.09678626060486</v>
+        <v>3.09678649902344</v>
       </c>
       <c r="H579" t="s">
         <v>8</v>
@@ -15501,7 +15501,7 @@
         <v>4.08599996566772</v>
       </c>
       <c r="G582" t="n">
-        <v>2.98430919647217</v>
+        <v>2.98430895805359</v>
       </c>
       <c r="H582" t="s">
         <v>8</v>
@@ -15553,7 +15553,7 @@
         <v>4.18599987030029</v>
       </c>
       <c r="G584" t="n">
-        <v>3.05734634399414</v>
+        <v>3.05734610557556</v>
       </c>
       <c r="H584" t="s">
         <v>8</v>
@@ -15579,7 +15579,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G585" t="n">
-        <v>3.09678626060486</v>
+        <v>3.09678649902344</v>
       </c>
       <c r="H585" t="s">
         <v>8</v>
@@ -15605,7 +15605,7 @@
         <v>4.21799993515015</v>
       </c>
       <c r="G586" t="n">
-        <v>3.08071804046631</v>
+        <v>3.08071851730347</v>
       </c>
       <c r="H586" t="s">
         <v>8</v>
@@ -15631,7 +15631,7 @@
         <v>4.38000011444092</v>
       </c>
       <c r="G587" t="n">
-        <v>3.19903922080994</v>
+        <v>3.19903898239136</v>
       </c>
       <c r="H587" t="s">
         <v>8</v>
@@ -15657,7 +15657,7 @@
         <v>4.32600021362305</v>
       </c>
       <c r="G588" t="n">
-        <v>3.15959858894348</v>
+        <v>3.15959882736206</v>
       </c>
       <c r="H588" t="s">
         <v>8</v>
@@ -15683,7 +15683,7 @@
         <v>4.36600017547607</v>
       </c>
       <c r="G589" t="n">
-        <v>3.18881392478943</v>
+        <v>3.18881416320801</v>
       </c>
       <c r="H589" t="s">
         <v>8</v>
@@ -15709,7 +15709,7 @@
         <v>4.2979998588562</v>
       </c>
       <c r="G590" t="n">
-        <v>3.13914847373962</v>
+        <v>3.13914823532104</v>
       </c>
       <c r="H590" t="s">
         <v>8</v>
@@ -15735,7 +15735,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G591" t="n">
-        <v>3.1406090259552</v>
+        <v>3.14060950279236</v>
       </c>
       <c r="H591" t="s">
         <v>8</v>
@@ -15761,7 +15761,7 @@
         <v>4.3899998664856</v>
       </c>
       <c r="G592" t="n">
-        <v>3.20634269714355</v>
+        <v>3.20634293556213</v>
       </c>
       <c r="H592" t="s">
         <v>8</v>
@@ -15787,7 +15787,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G593" t="n">
-        <v>3.1406090259552</v>
+        <v>3.14060950279236</v>
       </c>
       <c r="H593" t="s">
         <v>8</v>
@@ -15813,7 +15813,7 @@
         <v>4.22200012207031</v>
       </c>
       <c r="G594" t="n">
-        <v>3.17824864387512</v>
+        <v>3.17824840545654</v>
       </c>
       <c r="H594" t="s">
         <v>8</v>
@@ -15891,7 +15891,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G597" t="n">
-        <v>3.42516112327576</v>
+        <v>3.42516088485718</v>
       </c>
       <c r="H597" t="s">
         <v>8</v>
@@ -15917,7 +15917,7 @@
         <v>4.65399980545044</v>
       </c>
       <c r="G598" t="n">
-        <v>3.50345039367676</v>
+        <v>3.50345063209534</v>
       </c>
       <c r="H598" t="s">
         <v>8</v>
@@ -15943,7 +15943,7 @@
         <v>4.5</v>
       </c>
       <c r="G599" t="n">
-        <v>3.38752174377441</v>
+        <v>3.38752150535583</v>
       </c>
       <c r="H599" t="s">
         <v>8</v>
@@ -16047,7 +16047,7 @@
         <v>4.39400005340576</v>
       </c>
       <c r="G603" t="n">
-        <v>3.30772686004639</v>
+        <v>3.30772709846497</v>
       </c>
       <c r="H603" t="s">
         <v>8</v>
@@ -16099,7 +16099,7 @@
         <v>4.2480001449585</v>
       </c>
       <c r="G605" t="n">
-        <v>3.19782042503357</v>
+        <v>3.19782066345215</v>
       </c>
       <c r="H605" t="s">
         <v>8</v>
@@ -16125,7 +16125,7 @@
         <v>4.29199981689453</v>
       </c>
       <c r="G606" t="n">
-        <v>3.23094296455383</v>
+        <v>3.23094320297241</v>
       </c>
       <c r="H606" t="s">
         <v>8</v>
@@ -16177,7 +16177,7 @@
         <v>4.14200019836426</v>
       </c>
       <c r="G608" t="n">
-        <v>3.11802554130554</v>
+        <v>3.1180260181427</v>
       </c>
       <c r="H608" t="s">
         <v>8</v>
@@ -16203,7 +16203,7 @@
         <v>4.21000003814697</v>
       </c>
       <c r="G609" t="n">
-        <v>3.16921520233154</v>
+        <v>3.16921448707581</v>
       </c>
       <c r="H609" t="s">
         <v>8</v>
@@ -16359,7 +16359,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G615" t="n">
-        <v>2.96596384048462</v>
+        <v>2.96596360206604</v>
       </c>
       <c r="H615" t="s">
         <v>8</v>
@@ -16385,7 +16385,7 @@
         <v>3.87800002098083</v>
       </c>
       <c r="G616" t="n">
-        <v>2.9192910194397</v>
+        <v>2.91929125785828</v>
       </c>
       <c r="H616" t="s">
         <v>8</v>
@@ -16411,7 +16411,7 @@
         <v>4.03399991989136</v>
       </c>
       <c r="G617" t="n">
-        <v>3.03672504425049</v>
+        <v>3.03672528266907</v>
       </c>
       <c r="H617" t="s">
         <v>8</v>
@@ -16437,7 +16437,7 @@
         <v>3.98600006103516</v>
       </c>
       <c r="G618" t="n">
-        <v>3.00059151649475</v>
+        <v>3.00059175491333</v>
       </c>
       <c r="H618" t="s">
         <v>8</v>
@@ -16489,7 +16489,7 @@
         <v>4.08799982070923</v>
       </c>
       <c r="G620" t="n">
-        <v>3.07737565040588</v>
+        <v>3.07737517356873</v>
       </c>
       <c r="H620" t="s">
         <v>8</v>
@@ -16541,7 +16541,7 @@
         <v>4.11399984359741</v>
       </c>
       <c r="G622" t="n">
-        <v>3.09694766998291</v>
+        <v>3.09694743156433</v>
       </c>
       <c r="H622" t="s">
         <v>8</v>
@@ -16619,7 +16619,7 @@
         <v>4.19600009918213</v>
       </c>
       <c r="G625" t="n">
-        <v>3.15867590904236</v>
+        <v>3.15867614746094</v>
       </c>
       <c r="H625" t="s">
         <v>8</v>
@@ -16645,7 +16645,7 @@
         <v>4.18599987030029</v>
       </c>
       <c r="G626" t="n">
-        <v>3.15114808082581</v>
+        <v>3.15114784240723</v>
       </c>
       <c r="H626" t="s">
         <v>8</v>
@@ -16671,7 +16671,7 @@
         <v>4.14200019836426</v>
       </c>
       <c r="G627" t="n">
-        <v>3.11802554130554</v>
+        <v>3.1180260181427</v>
       </c>
       <c r="H627" t="s">
         <v>8</v>
@@ -16697,7 +16697,7 @@
         <v>4.16200017929077</v>
       </c>
       <c r="G628" t="n">
-        <v>3.13308167457581</v>
+        <v>3.13308143615723</v>
       </c>
       <c r="H628" t="s">
         <v>8</v>
@@ -16723,7 +16723,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G629" t="n">
-        <v>3.16168713569641</v>
+        <v>3.16168689727783</v>
       </c>
       <c r="H629" t="s">
         <v>8</v>
@@ -16775,7 +16775,7 @@
         <v>3.93400001525879</v>
       </c>
       <c r="G631" t="n">
-        <v>2.96144700050354</v>
+        <v>2.96144676208496</v>
       </c>
       <c r="H631" t="s">
         <v>8</v>
@@ -16801,7 +16801,7 @@
         <v>3.96199989318848</v>
       </c>
       <c r="G632" t="n">
-        <v>2.98252439498901</v>
+        <v>2.98252463340759</v>
       </c>
       <c r="H632" t="s">
         <v>8</v>
@@ -16827,7 +16827,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G633" t="n">
-        <v>2.90574097633362</v>
+        <v>2.90574073791504</v>
       </c>
       <c r="H633" t="s">
         <v>8</v>
@@ -16879,7 +16879,7 @@
         <v>3.83400011062622</v>
       </c>
       <c r="G635" t="n">
-        <v>2.88616847991943</v>
+        <v>2.88616871833801</v>
       </c>
       <c r="H635" t="s">
         <v>8</v>
@@ -16931,7 +16931,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G637" t="n">
-        <v>2.89821290969849</v>
+        <v>2.89821314811707</v>
       </c>
       <c r="H637" t="s">
         <v>8</v>
@@ -17009,7 +17009,7 @@
         <v>4.16599988937378</v>
       </c>
       <c r="G640" t="n">
-        <v>3.1360924243927</v>
+        <v>3.13609218597412</v>
       </c>
       <c r="H640" t="s">
         <v>8</v>
@@ -17035,7 +17035,7 @@
         <v>4.24399995803833</v>
       </c>
       <c r="G641" t="n">
-        <v>3.1948094367981</v>
+        <v>3.19480967521667</v>
       </c>
       <c r="H641" t="s">
         <v>8</v>
@@ -17061,7 +17061,7 @@
         <v>4.2480001449585</v>
       </c>
       <c r="G642" t="n">
-        <v>3.19782042503357</v>
+        <v>3.19782066345215</v>
       </c>
       <c r="H642" t="s">
         <v>8</v>
@@ -17087,7 +17087,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G643" t="n">
-        <v>3.23696517944336</v>
+        <v>3.23696565628052</v>
       </c>
       <c r="H643" t="s">
         <v>8</v>
@@ -17113,7 +17113,7 @@
         <v>4.34200000762939</v>
       </c>
       <c r="G644" t="n">
-        <v>3.26858234405518</v>
+        <v>3.2685821056366</v>
       </c>
       <c r="H644" t="s">
         <v>8</v>
@@ -17139,7 +17139,7 @@
         <v>4.26999998092651</v>
       </c>
       <c r="G645" t="n">
-        <v>3.2143816947937</v>
+        <v>3.21438193321228</v>
       </c>
       <c r="H645" t="s">
         <v>8</v>
@@ -17191,7 +17191,7 @@
         <v>4.30600023269653</v>
       </c>
       <c r="G647" t="n">
-        <v>3.2414824962616</v>
+        <v>3.24148201942444</v>
       </c>
       <c r="H647" t="s">
         <v>8</v>
@@ -17217,7 +17217,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G648" t="n">
-        <v>3.17674255371094</v>
+        <v>3.17674279212952</v>
       </c>
       <c r="H648" t="s">
         <v>8</v>
@@ -17347,7 +17347,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G653" t="n">
-        <v>3.16168713569641</v>
+        <v>3.16168689727783</v>
       </c>
       <c r="H653" t="s">
         <v>8</v>
@@ -17373,7 +17373,7 @@
         <v>4.25</v>
       </c>
       <c r="G654" t="n">
-        <v>3.19932579994202</v>
+        <v>3.1993260383606</v>
       </c>
       <c r="H654" t="s">
         <v>8</v>
@@ -17451,7 +17451,7 @@
         <v>4.48400020599365</v>
       </c>
       <c r="G657" t="n">
-        <v>3.37547731399536</v>
+        <v>3.37547779083252</v>
       </c>
       <c r="H657" t="s">
         <v>8</v>
@@ -17529,7 +17529,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G660" t="n">
-        <v>3.23696517944336</v>
+        <v>3.23696565628052</v>
       </c>
       <c r="H660" t="s">
         <v>8</v>
@@ -17581,7 +17581,7 @@
         <v>4.16400003433228</v>
       </c>
       <c r="G662" t="n">
-        <v>3.13458704948425</v>
+        <v>3.13458681106567</v>
       </c>
       <c r="H662" t="s">
         <v>8</v>
@@ -17607,7 +17607,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G663" t="n">
-        <v>3.09393644332886</v>
+        <v>3.09393668174744</v>
       </c>
       <c r="H663" t="s">
         <v>8</v>
@@ -17659,7 +17659,7 @@
         <v>4.14200019836426</v>
       </c>
       <c r="G665" t="n">
-        <v>3.11802554130554</v>
+        <v>3.1180260181427</v>
       </c>
       <c r="H665" t="s">
         <v>8</v>
@@ -17711,7 +17711,7 @@
         <v>4.09200000762939</v>
       </c>
       <c r="G667" t="n">
-        <v>3.08038640022278</v>
+        <v>3.08038687705994</v>
       </c>
       <c r="H667" t="s">
         <v>8</v>
@@ -17737,7 +17737,7 @@
         <v>4.01000022888184</v>
       </c>
       <c r="G668" t="n">
-        <v>3.01865863800049</v>
+        <v>3.01865839958191</v>
       </c>
       <c r="H668" t="s">
         <v>8</v>
@@ -17789,7 +17789,7 @@
         <v>3.89599990844727</v>
       </c>
       <c r="G670" t="n">
-        <v>2.9328408241272</v>
+        <v>2.93284106254578</v>
       </c>
       <c r="H670" t="s">
         <v>8</v>
@@ -17815,7 +17815,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G671" t="n">
-        <v>2.89068531990051</v>
+        <v>2.89068508148193</v>
       </c>
       <c r="H671" t="s">
         <v>8</v>
@@ -17971,7 +17971,7 @@
         <v>3.83800005912781</v>
       </c>
       <c r="G677" t="n">
-        <v>2.88917970657349</v>
+        <v>2.88917994499207</v>
       </c>
       <c r="H677" t="s">
         <v>8</v>
@@ -17997,7 +17997,7 @@
         <v>3.93400001525879</v>
       </c>
       <c r="G678" t="n">
-        <v>2.96144700050354</v>
+        <v>2.96144676208496</v>
       </c>
       <c r="H678" t="s">
         <v>8</v>
@@ -18023,7 +18023,7 @@
         <v>4.11800003051758</v>
       </c>
       <c r="G679" t="n">
-        <v>3.09995889663696</v>
+        <v>3.09995913505554</v>
       </c>
       <c r="H679" t="s">
         <v>8</v>
@@ -18049,7 +18049,7 @@
         <v>4.09200000762939</v>
       </c>
       <c r="G680" t="n">
-        <v>3.08038640022278</v>
+        <v>3.08038687705994</v>
       </c>
       <c r="H680" t="s">
         <v>8</v>
@@ -18075,7 +18075,7 @@
         <v>3.99799990653992</v>
       </c>
       <c r="G681" t="n">
-        <v>3.00962495803833</v>
+        <v>3.00962471961975</v>
       </c>
       <c r="H681" t="s">
         <v>8</v>
@@ -18179,7 +18179,7 @@
         <v>4.05200004577637</v>
       </c>
       <c r="G685" t="n">
-        <v>3.05027556419373</v>
+        <v>3.05027508735657</v>
       </c>
       <c r="H685" t="s">
         <v>8</v>
@@ -18205,7 +18205,7 @@
         <v>4.06599998474121</v>
       </c>
       <c r="G686" t="n">
-        <v>3.06081438064575</v>
+        <v>3.06081414222717</v>
       </c>
       <c r="H686" t="s">
         <v>8</v>
@@ -18231,7 +18231,7 @@
         <v>4.0939998626709</v>
       </c>
       <c r="G687" t="n">
-        <v>3.0818920135498</v>
+        <v>3.08189225196838</v>
       </c>
       <c r="H687" t="s">
         <v>8</v>
@@ -18283,7 +18283,7 @@
         <v>4.06199979782104</v>
       </c>
       <c r="G689" t="n">
-        <v>3.0578031539917</v>
+        <v>3.05780291557312</v>
       </c>
       <c r="H689" t="s">
         <v>8</v>
@@ -18309,7 +18309,7 @@
         <v>4.05800008773804</v>
       </c>
       <c r="G690" t="n">
-        <v>3.0547924041748</v>
+        <v>3.05479192733765</v>
       </c>
       <c r="H690" t="s">
         <v>8</v>
@@ -18335,7 +18335,7 @@
         <v>4.07200002670288</v>
       </c>
       <c r="G691" t="n">
-        <v>3.06533098220825</v>
+        <v>3.06533074378967</v>
       </c>
       <c r="H691" t="s">
         <v>8</v>
@@ -18361,7 +18361,7 @@
         <v>4.10200023651123</v>
       </c>
       <c r="G692" t="n">
-        <v>3.08791422843933</v>
+        <v>3.08791446685791</v>
       </c>
       <c r="H692" t="s">
         <v>8</v>
@@ -18413,7 +18413,7 @@
         <v>4.06599998474121</v>
       </c>
       <c r="G694" t="n">
-        <v>3.06081438064575</v>
+        <v>3.06081414222717</v>
       </c>
       <c r="H694" t="s">
         <v>8</v>
@@ -18439,7 +18439,7 @@
         <v>4.08799982070923</v>
       </c>
       <c r="G695" t="n">
-        <v>3.07737565040588</v>
+        <v>3.07737517356873</v>
       </c>
       <c r="H695" t="s">
         <v>8</v>
@@ -18517,7 +18517,7 @@
         <v>4.05999994277954</v>
       </c>
       <c r="G698" t="n">
-        <v>3.05629754066467</v>
+        <v>3.05629730224609</v>
       </c>
       <c r="H698" t="s">
         <v>8</v>
@@ -18569,7 +18569,7 @@
         <v>3.97399997711182</v>
       </c>
       <c r="G700" t="n">
-        <v>2.99155783653259</v>
+        <v>2.99155807495117</v>
       </c>
       <c r="H700" t="s">
         <v>8</v>
@@ -18595,7 +18595,7 @@
         <v>3.87800002098083</v>
       </c>
       <c r="G701" t="n">
-        <v>2.9192910194397</v>
+        <v>2.91929125785828</v>
       </c>
       <c r="H701" t="s">
         <v>8</v>
@@ -18621,7 +18621,7 @@
         <v>3.87199997901917</v>
       </c>
       <c r="G702" t="n">
-        <v>2.91477417945862</v>
+        <v>2.91477394104004</v>
       </c>
       <c r="H702" t="s">
         <v>8</v>
@@ -18647,7 +18647,7 @@
         <v>3.84200000762939</v>
       </c>
       <c r="G703" t="n">
-        <v>2.89219069480896</v>
+        <v>2.89219093322754</v>
       </c>
       <c r="H703" t="s">
         <v>8</v>
@@ -18725,7 +18725,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G706" t="n">
-        <v>2.79282355308533</v>
+        <v>2.79282379150391</v>
       </c>
       <c r="H706" t="s">
         <v>8</v>
@@ -18751,7 +18751,7 @@
         <v>3.68400001525879</v>
       </c>
       <c r="G707" t="n">
-        <v>2.77325081825256</v>
+        <v>2.77325129508972</v>
       </c>
       <c r="H707" t="s">
         <v>8</v>
@@ -18777,7 +18777,7 @@
         <v>3.71199989318848</v>
       </c>
       <c r="G708" t="n">
-        <v>2.79432916641235</v>
+        <v>2.79432892799377</v>
       </c>
       <c r="H708" t="s">
         <v>8</v>
@@ -18803,7 +18803,7 @@
         <v>3.71799993515015</v>
       </c>
       <c r="G709" t="n">
-        <v>2.79884600639343</v>
+        <v>2.79884576797485</v>
       </c>
       <c r="H709" t="s">
         <v>8</v>
@@ -18829,7 +18829,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G710" t="n">
-        <v>2.7852954864502</v>
+        <v>2.78529596328735</v>
       </c>
       <c r="H710" t="s">
         <v>8</v>
@@ -18855,7 +18855,7 @@
         <v>3.71600008010864</v>
       </c>
       <c r="G711" t="n">
-        <v>2.79734039306641</v>
+        <v>2.79734063148499</v>
       </c>
       <c r="H711" t="s">
         <v>8</v>
@@ -18985,7 +18985,7 @@
         <v>3.79399991035461</v>
       </c>
       <c r="G716" t="n">
-        <v>2.85605764389038</v>
+        <v>2.8560574054718</v>
       </c>
       <c r="H716" t="s">
         <v>8</v>
@@ -19011,7 +19011,7 @@
         <v>3.77800011634827</v>
       </c>
       <c r="G717" t="n">
-        <v>2.84401321411133</v>
+        <v>2.84401297569275</v>
       </c>
       <c r="H717" t="s">
         <v>8</v>
@@ -19089,7 +19089,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G720" t="n">
-        <v>2.86057424545288</v>
+        <v>2.8605740070343</v>
       </c>
       <c r="H720" t="s">
         <v>8</v>
@@ -19115,7 +19115,7 @@
         <v>3.71799993515015</v>
       </c>
       <c r="G721" t="n">
-        <v>2.79884600639343</v>
+        <v>2.79884576797485</v>
       </c>
       <c r="H721" t="s">
         <v>8</v>
@@ -19141,7 +19141,7 @@
         <v>3.83400011062622</v>
       </c>
       <c r="G722" t="n">
-        <v>2.88616847991943</v>
+        <v>2.88616871833801</v>
       </c>
       <c r="H722" t="s">
         <v>8</v>
@@ -19167,7 +19167,7 @@
         <v>3.84400010108948</v>
       </c>
       <c r="G723" t="n">
-        <v>2.89369654655457</v>
+        <v>2.89369630813599</v>
       </c>
       <c r="H723" t="s">
         <v>8</v>
@@ -19245,7 +19245,7 @@
         <v>3.87800002098083</v>
       </c>
       <c r="G726" t="n">
-        <v>2.9192910194397</v>
+        <v>2.91929125785828</v>
       </c>
       <c r="H726" t="s">
         <v>8</v>
@@ -19375,7 +19375,7 @@
         <v>3.43400001525879</v>
       </c>
       <c r="G731" t="n">
-        <v>2.58505535125732</v>
+        <v>2.58505582809448</v>
       </c>
       <c r="H731" t="s">
         <v>8</v>
@@ -19401,7 +19401,7 @@
         <v>3.32399988174438</v>
       </c>
       <c r="G732" t="n">
-        <v>2.50224924087524</v>
+        <v>2.50224947929382</v>
       </c>
       <c r="H732" t="s">
         <v>8</v>
@@ -19427,7 +19427,7 @@
         <v>3.26200008392334</v>
       </c>
       <c r="G733" t="n">
-        <v>2.45557713508606</v>
+        <v>2.45557689666748</v>
       </c>
       <c r="H733" t="s">
         <v>8</v>
@@ -19505,7 +19505,7 @@
         <v>3.2279999256134</v>
       </c>
       <c r="G736" t="n">
-        <v>2.42998218536377</v>
+        <v>2.42998242378235</v>
       </c>
       <c r="H736" t="s">
         <v>8</v>
@@ -19557,7 +19557,7 @@
         <v>3.06399989128113</v>
       </c>
       <c r="G738" t="n">
-        <v>2.30652594566345</v>
+        <v>2.30652618408203</v>
       </c>
       <c r="H738" t="s">
         <v>8</v>
@@ -19609,7 +19609,7 @@
         <v>3.25600004196167</v>
       </c>
       <c r="G740" t="n">
-        <v>2.45106053352356</v>
+        <v>2.4510600566864</v>
       </c>
       <c r="H740" t="s">
         <v>8</v>
@@ -19635,7 +19635,7 @@
         <v>3.2279999256134</v>
       </c>
       <c r="G741" t="n">
-        <v>2.42998218536377</v>
+        <v>2.42998242378235</v>
       </c>
       <c r="H741" t="s">
         <v>8</v>
@@ -19661,7 +19661,7 @@
         <v>3.30599999427795</v>
       </c>
       <c r="G742" t="n">
-        <v>2.48869919776917</v>
+        <v>2.48869943618774</v>
       </c>
       <c r="H742" t="s">
         <v>8</v>
@@ -19687,7 +19687,7 @@
         <v>3.28999996185303</v>
       </c>
       <c r="G743" t="n">
-        <v>2.47665476799011</v>
+        <v>2.47665500640869</v>
       </c>
       <c r="H743" t="s">
         <v>8</v>
@@ -19713,7 +19713,7 @@
         <v>3.39599990844727</v>
       </c>
       <c r="G744" t="n">
-        <v>2.55644989013672</v>
+        <v>2.55644965171814</v>
       </c>
       <c r="H744" t="s">
         <v>8</v>
@@ -19739,7 +19739,7 @@
         <v>3.39599990844727</v>
       </c>
       <c r="G745" t="n">
-        <v>2.55644989013672</v>
+        <v>2.55644965171814</v>
       </c>
       <c r="H745" t="s">
         <v>8</v>
@@ -19869,7 +19869,7 @@
         <v>3.28999996185303</v>
       </c>
       <c r="G750" t="n">
-        <v>2.47665476799011</v>
+        <v>2.47665500640869</v>
       </c>
       <c r="H750" t="s">
         <v>8</v>
@@ -19895,7 +19895,7 @@
         <v>3.25600004196167</v>
       </c>
       <c r="G751" t="n">
-        <v>2.45106053352356</v>
+        <v>2.4510600566864</v>
       </c>
       <c r="H751" t="s">
         <v>8</v>
@@ -19921,7 +19921,7 @@
         <v>3.14400005340576</v>
       </c>
       <c r="G752" t="n">
-        <v>2.36674857139587</v>
+        <v>2.36674880981445</v>
       </c>
       <c r="H752" t="s">
         <v>8</v>
@@ -19973,7 +19973,7 @@
         <v>3.15199995040894</v>
       </c>
       <c r="G754" t="n">
-        <v>2.3727707862854</v>
+        <v>2.37277102470398</v>
       </c>
       <c r="H754" t="s">
         <v>8</v>
@@ -19999,7 +19999,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G755" t="n">
-        <v>2.42396020889282</v>
+        <v>2.42395997047424</v>
       </c>
       <c r="H755" t="s">
         <v>8</v>
@@ -20025,7 +20025,7 @@
         <v>3.18199992179871</v>
       </c>
       <c r="G756" t="n">
-        <v>2.39535403251648</v>
+        <v>2.39535427093506</v>
       </c>
       <c r="H756" t="s">
         <v>8</v>
@@ -20077,7 +20077,7 @@
         <v>3.10999989509583</v>
       </c>
       <c r="G758" t="n">
-        <v>2.34115409851074</v>
+        <v>2.34115386009216</v>
       </c>
       <c r="H758" t="s">
         <v>8</v>
@@ -20103,7 +20103,7 @@
         <v>3.10599994659424</v>
       </c>
       <c r="G759" t="n">
-        <v>2.33814263343811</v>
+        <v>2.33814287185669</v>
       </c>
       <c r="H759" t="s">
         <v>8</v>
@@ -20129,7 +20129,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G760" t="n">
-        <v>2.3185703754425</v>
+        <v>2.31857061386108</v>
       </c>
       <c r="H760" t="s">
         <v>8</v>
@@ -20207,7 +20207,7 @@
         <v>3.21000003814697</v>
       </c>
       <c r="G763" t="n">
-        <v>2.41643238067627</v>
+        <v>2.41643214225769</v>
       </c>
       <c r="H763" t="s">
         <v>8</v>
@@ -20259,7 +20259,7 @@
         <v>3.24200010299683</v>
       </c>
       <c r="G765" t="n">
-        <v>2.44052147865295</v>
+        <v>2.44052124023438</v>
       </c>
       <c r="H765" t="s">
         <v>8</v>
@@ -20311,7 +20311,7 @@
         <v>3.36199998855591</v>
       </c>
       <c r="G767" t="n">
-        <v>2.53085541725159</v>
+        <v>2.53085517883301</v>
       </c>
       <c r="H767" t="s">
         <v>8</v>
@@ -20337,7 +20337,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G768" t="n">
-        <v>2.57451677322388</v>
+        <v>2.5745165348053</v>
       </c>
       <c r="H768" t="s">
         <v>8</v>
@@ -20363,7 +20363,7 @@
         <v>3.39400005340576</v>
       </c>
       <c r="G769" t="n">
-        <v>2.55494451522827</v>
+        <v>2.55494427680969</v>
       </c>
       <c r="H769" t="s">
         <v>8</v>
@@ -20415,7 +20415,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G771" t="n">
-        <v>2.55946087837219</v>
+        <v>2.55946111679077</v>
       </c>
       <c r="H771" t="s">
         <v>8</v>
@@ -20441,7 +20441,7 @@
         <v>3.39599990844727</v>
       </c>
       <c r="G772" t="n">
-        <v>2.55644989013672</v>
+        <v>2.55644965171814</v>
       </c>
       <c r="H772" t="s">
         <v>8</v>
@@ -20467,7 +20467,7 @@
         <v>3.41400003433228</v>
       </c>
       <c r="G773" t="n">
-        <v>2.5699999332428</v>
+        <v>2.57000017166138</v>
       </c>
       <c r="H773" t="s">
         <v>8</v>
@@ -20493,7 +20493,7 @@
         <v>3.49000000953674</v>
       </c>
       <c r="G774" t="n">
-        <v>2.62721157073975</v>
+        <v>2.62721133232117</v>
       </c>
       <c r="H774" t="s">
         <v>8</v>
@@ -20545,7 +20545,7 @@
         <v>3.59800004959106</v>
       </c>
       <c r="G776" t="n">
-        <v>2.70851159095764</v>
+        <v>2.70851182937622</v>
       </c>
       <c r="H776" t="s">
         <v>8</v>
@@ -20597,7 +20597,7 @@
         <v>3.45600008964539</v>
       </c>
       <c r="G778" t="n">
-        <v>2.60161662101746</v>
+        <v>2.60161685943604</v>
       </c>
       <c r="H778" t="s">
         <v>8</v>
@@ -20623,7 +20623,7 @@
         <v>3.38199996948242</v>
       </c>
       <c r="G779" t="n">
-        <v>2.54591107368469</v>
+        <v>2.54591083526611</v>
       </c>
       <c r="H779" t="s">
         <v>8</v>
@@ -20649,7 +20649,7 @@
         <v>3.41599988937378</v>
       </c>
       <c r="G780" t="n">
-        <v>2.57150530815125</v>
+        <v>2.57150554656982</v>
       </c>
       <c r="H780" t="s">
         <v>8</v>
@@ -20701,7 +20701,7 @@
         <v>3.53399991989136</v>
       </c>
       <c r="G782" t="n">
-        <v>2.66033387184143</v>
+        <v>2.66033363342285</v>
       </c>
       <c r="H782" t="s">
         <v>8</v>
@@ -20779,7 +20779,7 @@
         <v>3.50399994850159</v>
       </c>
       <c r="G785" t="n">
-        <v>2.63775062561035</v>
+        <v>2.63775038719177</v>
       </c>
       <c r="H785" t="s">
         <v>8</v>
@@ -20805,7 +20805,7 @@
         <v>3.49600005149841</v>
       </c>
       <c r="G786" t="n">
-        <v>2.63172841072083</v>
+        <v>2.63172817230225</v>
       </c>
       <c r="H786" t="s">
         <v>8</v>
@@ -20831,7 +20831,7 @@
         <v>3.53200006484985</v>
       </c>
       <c r="G787" t="n">
-        <v>2.6588282585144</v>
+        <v>2.65882802009583</v>
       </c>
       <c r="H787" t="s">
         <v>8</v>
@@ -20883,7 +20883,7 @@
         <v>3.53600001335144</v>
       </c>
       <c r="G789" t="n">
-        <v>2.66183948516846</v>
+        <v>2.66183924674988</v>
       </c>
       <c r="H789" t="s">
         <v>8</v>
@@ -20935,7 +20935,7 @@
         <v>3.48399996757507</v>
       </c>
       <c r="G791" t="n">
-        <v>2.62269473075867</v>
+        <v>2.62269449234009</v>
       </c>
       <c r="H791" t="s">
         <v>8</v>
@@ -20961,7 +20961,7 @@
         <v>3.44400000572205</v>
       </c>
       <c r="G792" t="n">
-        <v>2.59258365631104</v>
+        <v>2.59258341789246</v>
       </c>
       <c r="H792" t="s">
         <v>8</v>
@@ -21039,7 +21039,7 @@
         <v>3.49799990653992</v>
       </c>
       <c r="G795" t="n">
-        <v>2.63323378562927</v>
+        <v>2.63323354721069</v>
       </c>
       <c r="H795" t="s">
         <v>8</v>
@@ -21065,7 +21065,7 @@
         <v>3.6159999370575</v>
       </c>
       <c r="G796" t="n">
-        <v>2.7220618724823</v>
+        <v>2.72206211090088</v>
       </c>
       <c r="H796" t="s">
         <v>8</v>
@@ -21117,7 +21117,7 @@
         <v>3.46399998664856</v>
       </c>
       <c r="G798" t="n">
-        <v>2.60763883590698</v>
+        <v>2.60763931274414</v>
       </c>
       <c r="H798" t="s">
         <v>8</v>
@@ -21143,7 +21143,7 @@
         <v>3.47000002861023</v>
       </c>
       <c r="G799" t="n">
-        <v>2.61215567588806</v>
+        <v>2.61215543746948</v>
       </c>
       <c r="H799" t="s">
         <v>8</v>
@@ -21169,7 +21169,7 @@
         <v>3.49000000953674</v>
       </c>
       <c r="G800" t="n">
-        <v>2.62721157073975</v>
+        <v>2.62721133232117</v>
       </c>
       <c r="H800" t="s">
         <v>8</v>
@@ -21195,7 +21195,7 @@
         <v>3.50399994850159</v>
       </c>
       <c r="G801" t="n">
-        <v>2.63775062561035</v>
+        <v>2.63775038719177</v>
       </c>
       <c r="H801" t="s">
         <v>8</v>
@@ -21221,7 +21221,7 @@
         <v>3.52600002288818</v>
       </c>
       <c r="G802" t="n">
-        <v>2.6543116569519</v>
+        <v>2.65431141853333</v>
       </c>
       <c r="H802" t="s">
         <v>8</v>
@@ -21273,7 +21273,7 @@
         <v>3.53800010681152</v>
       </c>
       <c r="G804" t="n">
-        <v>2.6633448600769</v>
+        <v>2.66334509849548</v>
       </c>
       <c r="H804" t="s">
         <v>8</v>
@@ -21325,7 +21325,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G806" t="n">
-        <v>2.73260092735291</v>
+        <v>2.73260116577148</v>
       </c>
       <c r="H806" t="s">
         <v>8</v>
@@ -21351,7 +21351,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G807" t="n">
-        <v>2.72507333755493</v>
+        <v>2.72507286071777</v>
       </c>
       <c r="H807" t="s">
         <v>8</v>
@@ -21403,7 +21403,7 @@
         <v>3.55800008773804</v>
       </c>
       <c r="G809" t="n">
-        <v>2.67840051651001</v>
+        <v>2.67840075492859</v>
       </c>
       <c r="H809" t="s">
         <v>8</v>
@@ -21507,7 +21507,7 @@
         <v>3.50399994850159</v>
       </c>
       <c r="G813" t="n">
-        <v>2.63775062561035</v>
+        <v>2.63775038719177</v>
       </c>
       <c r="H813" t="s">
         <v>8</v>
@@ -21559,7 +21559,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G815" t="n">
-        <v>2.55946087837219</v>
+        <v>2.55946111679077</v>
       </c>
       <c r="H815" t="s">
         <v>8</v>
@@ -21585,7 +21585,7 @@
         <v>3.48399996757507</v>
       </c>
       <c r="G816" t="n">
-        <v>2.62269473075867</v>
+        <v>2.62269449234009</v>
       </c>
       <c r="H816" t="s">
         <v>8</v>
@@ -21637,7 +21637,7 @@
         <v>3.57200002670288</v>
       </c>
       <c r="G818" t="n">
-        <v>2.68893957138062</v>
+        <v>2.68893980979919</v>
       </c>
       <c r="H818" t="s">
         <v>8</v>
@@ -21715,7 +21715,7 @@
         <v>3.51399993896484</v>
       </c>
       <c r="G821" t="n">
-        <v>2.6452784538269</v>
+        <v>2.64527821540833</v>
       </c>
       <c r="H821" t="s">
         <v>8</v>
@@ -21741,7 +21741,7 @@
         <v>3.41400003433228</v>
       </c>
       <c r="G822" t="n">
-        <v>2.5699999332428</v>
+        <v>2.57000017166138</v>
       </c>
       <c r="H822" t="s">
         <v>8</v>
@@ -21767,7 +21767,7 @@
         <v>3.36199998855591</v>
       </c>
       <c r="G823" t="n">
-        <v>2.53085541725159</v>
+        <v>2.53085517883301</v>
       </c>
       <c r="H823" t="s">
         <v>8</v>
@@ -21819,7 +21819,7 @@
         <v>3.31200003623962</v>
       </c>
       <c r="G825" t="n">
-        <v>2.49321579933167</v>
+        <v>2.49321603775024</v>
       </c>
       <c r="H825" t="s">
         <v>8</v>
@@ -21845,7 +21845,7 @@
         <v>3.39599990844727</v>
       </c>
       <c r="G826" t="n">
-        <v>2.55644989013672</v>
+        <v>2.55644965171814</v>
       </c>
       <c r="H826" t="s">
         <v>8</v>
@@ -21949,7 +21949,7 @@
         <v>3.55200004577637</v>
       </c>
       <c r="G830" t="n">
-        <v>2.67388367652893</v>
+        <v>2.67388391494751</v>
       </c>
       <c r="H830" t="s">
         <v>8</v>
@@ -21975,7 +21975,7 @@
         <v>3.55200004577637</v>
       </c>
       <c r="G831" t="n">
-        <v>2.67388367652893</v>
+        <v>2.67388391494751</v>
       </c>
       <c r="H831" t="s">
         <v>8</v>
@@ -22157,7 +22157,7 @@
         <v>3.27600002288818</v>
       </c>
       <c r="G838" t="n">
-        <v>2.46611595153809</v>
+        <v>2.46611618995667</v>
       </c>
       <c r="H838" t="s">
         <v>8</v>
@@ -22209,7 +22209,7 @@
         <v>3.29399991035461</v>
       </c>
       <c r="G840" t="n">
-        <v>2.47966575622559</v>
+        <v>2.47966599464417</v>
       </c>
       <c r="H840" t="s">
         <v>8</v>
@@ -22235,7 +22235,7 @@
         <v>3.26200008392334</v>
       </c>
       <c r="G841" t="n">
-        <v>2.45557713508606</v>
+        <v>2.45557689666748</v>
       </c>
       <c r="H841" t="s">
         <v>8</v>
@@ -22339,7 +22339,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G845" t="n">
-        <v>2.42396020889282</v>
+        <v>2.42395997047424</v>
       </c>
       <c r="H845" t="s">
         <v>8</v>
@@ -22365,7 +22365,7 @@
         <v>3.18199992179871</v>
       </c>
       <c r="G846" t="n">
-        <v>2.39535403251648</v>
+        <v>2.39535427093506</v>
       </c>
       <c r="H846" t="s">
         <v>8</v>
@@ -22391,7 +22391,7 @@
         <v>3.26399993896484</v>
       </c>
       <c r="G847" t="n">
-        <v>2.45708227157593</v>
+        <v>2.45708250999451</v>
       </c>
       <c r="H847" t="s">
         <v>8</v>
@@ -22417,7 +22417,7 @@
         <v>3.21199989318848</v>
       </c>
       <c r="G848" t="n">
-        <v>2.50942707061768</v>
+        <v>2.5094268321991</v>
       </c>
       <c r="H848" t="s">
         <v>8</v>
@@ -22443,7 +22443,7 @@
         <v>3.04800009727478</v>
       </c>
       <c r="G849" t="n">
-        <v>2.3812997341156</v>
+        <v>2.38129949569702</v>
       </c>
       <c r="H849" t="s">
         <v>8</v>
@@ -22469,7 +22469,7 @@
         <v>2.99399995803833</v>
       </c>
       <c r="G850" t="n">
-        <v>2.339111328125</v>
+        <v>2.33911085128784</v>
       </c>
       <c r="H850" t="s">
         <v>8</v>
@@ -22495,7 +22495,7 @@
         <v>2.98799991607666</v>
       </c>
       <c r="G851" t="n">
-        <v>2.33442378044128</v>
+        <v>2.33442354202271</v>
       </c>
       <c r="H851" t="s">
         <v>8</v>
@@ -22547,7 +22547,7 @@
         <v>2.68799996376038</v>
       </c>
       <c r="G853" t="n">
-        <v>2.10004353523254</v>
+        <v>2.10004377365112</v>
       </c>
       <c r="H853" t="s">
         <v>8</v>
@@ -22573,7 +22573,7 @@
         <v>2.68400001525879</v>
       </c>
       <c r="G854" t="n">
-        <v>2.09691905975342</v>
+        <v>2.09691882133484</v>
       </c>
       <c r="H854" t="s">
         <v>8</v>
@@ -22599,7 +22599,7 @@
         <v>2.73600006103516</v>
       </c>
       <c r="G855" t="n">
-        <v>2.13754439353943</v>
+        <v>2.13754463195801</v>
       </c>
       <c r="H855" t="s">
         <v>8</v>
@@ -22625,7 +22625,7 @@
         <v>2.61800003051758</v>
       </c>
       <c r="G856" t="n">
-        <v>2.04535484313965</v>
+        <v>2.04535508155823</v>
       </c>
       <c r="H856" t="s">
         <v>8</v>
@@ -22651,7 +22651,7 @@
         <v>2.75200009346008</v>
       </c>
       <c r="G857" t="n">
-        <v>2.1500449180603</v>
+        <v>2.15004467964172</v>
       </c>
       <c r="H857" t="s">
         <v>8</v>
@@ -22677,7 +22677,7 @@
         <v>2.75200009346008</v>
       </c>
       <c r="G858" t="n">
-        <v>2.1500449180603</v>
+        <v>2.15004467964172</v>
       </c>
       <c r="H858" t="s">
         <v>8</v>
@@ -22755,7 +22755,7 @@
         <v>2.58400011062622</v>
       </c>
       <c r="G861" t="n">
-        <v>2.01879191398621</v>
+        <v>2.01879215240479</v>
       </c>
       <c r="H861" t="s">
         <v>8</v>
@@ -22833,7 +22833,7 @@
         <v>2.62199997901917</v>
       </c>
       <c r="G864" t="n">
-        <v>2.04848027229309</v>
+        <v>2.04848003387451</v>
       </c>
       <c r="H864" t="s">
         <v>8</v>
@@ -22885,7 +22885,7 @@
         <v>2.51600003242493</v>
       </c>
       <c r="G866" t="n">
-        <v>1.96566581726074</v>
+        <v>1.96566605567932</v>
       </c>
       <c r="H866" t="s">
         <v>8</v>
@@ -22937,7 +22937,7 @@
         <v>2.58200001716614</v>
       </c>
       <c r="G868" t="n">
-        <v>2.01722931861877</v>
+        <v>2.01722955703735</v>
       </c>
       <c r="H868" t="s">
         <v>8</v>
@@ -23015,7 +23015,7 @@
         <v>2.73399996757507</v>
       </c>
       <c r="G871" t="n">
-        <v>2.13598203659058</v>
+        <v>2.13598227500916</v>
       </c>
       <c r="H871" t="s">
         <v>8</v>
@@ -23093,7 +23093,7 @@
         <v>3</v>
       </c>
       <c r="G874" t="n">
-        <v>2.34379887580872</v>
+        <v>2.34379863739014</v>
       </c>
       <c r="H874" t="s">
         <v>8</v>
@@ -23145,7 +23145,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G876" t="n">
-        <v>2.2500467300415</v>
+        <v>2.25004696846008</v>
       </c>
       <c r="H876" t="s">
         <v>8</v>
@@ -23301,7 +23301,7 @@
         <v>2.91000008583069</v>
       </c>
       <c r="G882" t="n">
-        <v>2.27348470687866</v>
+        <v>2.27348518371582</v>
       </c>
       <c r="H882" t="s">
         <v>8</v>
@@ -23327,7 +23327,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G883" t="n">
-        <v>2.28129744529724</v>
+        <v>2.28129768371582</v>
       </c>
       <c r="H883" t="s">
         <v>8</v>
@@ -23431,7 +23431,7 @@
         <v>2.80599999427795</v>
       </c>
       <c r="G887" t="n">
-        <v>2.1922333240509</v>
+        <v>2.19223308563232</v>
       </c>
       <c r="H887" t="s">
         <v>8</v>
@@ -23483,7 +23483,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G889" t="n">
-        <v>2.2500467300415</v>
+        <v>2.25004696846008</v>
       </c>
       <c r="H889" t="s">
         <v>8</v>
@@ -23509,7 +23509,7 @@
         <v>2.8659999370575</v>
       </c>
       <c r="G890" t="n">
-        <v>2.23910927772522</v>
+        <v>2.23910903930664</v>
       </c>
       <c r="H890" t="s">
         <v>8</v>
@@ -23587,7 +23587,7 @@
         <v>2.88599991798401</v>
       </c>
       <c r="G893" t="n">
-        <v>2.25473427772522</v>
+        <v>2.2547345161438</v>
       </c>
       <c r="H893" t="s">
         <v>8</v>
@@ -23639,7 +23639,7 @@
         <v>2.74600005149841</v>
       </c>
       <c r="G895" t="n">
-        <v>2.14535737037659</v>
+        <v>2.14535713195801</v>
       </c>
       <c r="H895" t="s">
         <v>8</v>
@@ -23665,7 +23665,7 @@
         <v>2.68400001525879</v>
       </c>
       <c r="G896" t="n">
-        <v>2.09691905975342</v>
+        <v>2.09691882133484</v>
       </c>
       <c r="H896" t="s">
         <v>8</v>
@@ -23691,7 +23691,7 @@
         <v>2.69199991226196</v>
       </c>
       <c r="G897" t="n">
-        <v>2.10316872596741</v>
+        <v>2.10316896438599</v>
       </c>
       <c r="H897" t="s">
         <v>8</v>
@@ -23743,7 +23743,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G899" t="n">
-        <v>2.04691743850708</v>
+        <v>2.04691767692566</v>
       </c>
       <c r="H899" t="s">
         <v>8</v>
@@ -23795,7 +23795,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G901" t="n">
-        <v>1.96879100799561</v>
+        <v>1.96879124641418</v>
       </c>
       <c r="H901" t="s">
         <v>8</v>
@@ -23847,7 +23847,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G903" t="n">
-        <v>1.86722648143768</v>
+        <v>1.86722660064697</v>
       </c>
       <c r="H903" t="s">
         <v>8</v>
@@ -23873,7 +23873,7 @@
         <v>2.41799998283386</v>
       </c>
       <c r="G904" t="n">
-        <v>1.88910186290741</v>
+        <v>1.8891019821167</v>
       </c>
       <c r="H904" t="s">
         <v>8</v>
@@ -23899,7 +23899,7 @@
         <v>2.43600010871887</v>
       </c>
       <c r="G905" t="n">
-        <v>1.90316474437714</v>
+        <v>1.90316462516785</v>
       </c>
       <c r="H905" t="s">
         <v>8</v>
@@ -24003,7 +24003,7 @@
         <v>2.2279999256134</v>
       </c>
       <c r="G909" t="n">
-        <v>1.74066150188446</v>
+        <v>1.74066138267517</v>
       </c>
       <c r="H909" t="s">
         <v>8</v>
@@ -24055,7 +24055,7 @@
         <v>2.18600010871887</v>
       </c>
       <c r="G911" t="n">
-        <v>1.707848072052</v>
+        <v>1.70784819126129</v>
       </c>
       <c r="H911" t="s">
         <v>8</v>
@@ -24107,7 +24107,7 @@
         <v>2.22199988365173</v>
       </c>
       <c r="G913" t="n">
-        <v>1.73597383499146</v>
+        <v>1.73597359657288</v>
       </c>
       <c r="H913" t="s">
         <v>8</v>
@@ -24133,7 +24133,7 @@
         <v>2.21199989318848</v>
       </c>
       <c r="G914" t="n">
-        <v>1.7281608581543</v>
+        <v>1.72816097736359</v>
       </c>
       <c r="H914" t="s">
         <v>8</v>
@@ -24159,7 +24159,7 @@
         <v>2.19400000572205</v>
       </c>
       <c r="G915" t="n">
-        <v>1.71409821510315</v>
+        <v>1.71409833431244</v>
       </c>
       <c r="H915" t="s">
         <v>8</v>
@@ -24185,7 +24185,7 @@
         <v>2.20199990272522</v>
       </c>
       <c r="G916" t="n">
-        <v>1.72034823894501</v>
+        <v>1.7203483581543</v>
       </c>
       <c r="H916" t="s">
         <v>8</v>
@@ -24211,7 +24211,7 @@
         <v>2.22399997711182</v>
       </c>
       <c r="G917" t="n">
-        <v>1.73753619194031</v>
+        <v>1.7375363111496</v>
       </c>
       <c r="H917" t="s">
         <v>8</v>
@@ -24237,7 +24237,7 @@
         <v>2.13599991798401</v>
       </c>
       <c r="G918" t="n">
-        <v>1.66878473758698</v>
+        <v>1.66878485679626</v>
       </c>
       <c r="H918" t="s">
         <v>8</v>
@@ -24289,7 +24289,7 @@
         <v>2.06599998474121</v>
       </c>
       <c r="G920" t="n">
-        <v>1.61409604549408</v>
+        <v>1.61409616470337</v>
       </c>
       <c r="H920" t="s">
         <v>8</v>
@@ -24315,7 +24315,7 @@
         <v>2.01200008392334</v>
       </c>
       <c r="G921" t="n">
-        <v>1.57190787792206</v>
+        <v>1.57190775871277</v>
       </c>
       <c r="H921" t="s">
         <v>8</v>
@@ -24367,7 +24367,7 @@
         <v>2.06800007820129</v>
       </c>
       <c r="G923" t="n">
-        <v>1.6156587600708</v>
+        <v>1.61565887928009</v>
       </c>
       <c r="H923" t="s">
         <v>8</v>
@@ -24393,7 +24393,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G924" t="n">
-        <v>1.60940849781036</v>
+        <v>1.60940861701965</v>
       </c>
       <c r="H924" t="s">
         <v>8</v>
@@ -24445,7 +24445,7 @@
         <v>2.17400002479553</v>
       </c>
       <c r="G926" t="n">
-        <v>1.69847285747528</v>
+        <v>1.69847297668457</v>
       </c>
       <c r="H926" t="s">
         <v>8</v>
@@ -24497,7 +24497,7 @@
         <v>2.16199994087219</v>
       </c>
       <c r="G928" t="n">
-        <v>1.68909752368927</v>
+        <v>1.68909776210785</v>
       </c>
       <c r="H928" t="s">
         <v>8</v>
@@ -24549,7 +24549,7 @@
         <v>2.16199994087219</v>
       </c>
       <c r="G930" t="n">
-        <v>1.68909752368927</v>
+        <v>1.68909776210785</v>
       </c>
       <c r="H930" t="s">
         <v>8</v>
@@ -24575,7 +24575,7 @@
         <v>2.25200009346008</v>
       </c>
       <c r="G931" t="n">
-        <v>1.75941181182861</v>
+        <v>1.75941169261932</v>
       </c>
       <c r="H931" t="s">
         <v>8</v>
@@ -24601,7 +24601,7 @@
         <v>2.21600008010864</v>
       </c>
       <c r="G932" t="n">
-        <v>1.73128628730774</v>
+        <v>1.73128616809845</v>
       </c>
       <c r="H932" t="s">
         <v>8</v>
@@ -24627,7 +24627,7 @@
         <v>2.19600009918213</v>
       </c>
       <c r="G933" t="n">
-        <v>1.71566069126129</v>
+        <v>1.71566092967987</v>
       </c>
       <c r="H933" t="s">
         <v>8</v>
@@ -24653,7 +24653,7 @@
         <v>2.20199990272522</v>
       </c>
       <c r="G934" t="n">
-        <v>1.72034823894501</v>
+        <v>1.7203483581543</v>
       </c>
       <c r="H934" t="s">
         <v>8</v>
@@ -24705,7 +24705,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G936" t="n">
-        <v>1.78128695487976</v>
+        <v>1.78128707408905</v>
       </c>
       <c r="H936" t="s">
         <v>8</v>
@@ -24757,7 +24757,7 @@
         <v>2.31200003623962</v>
       </c>
       <c r="G938" t="n">
-        <v>1.80628788471222</v>
+        <v>1.80628776550293</v>
       </c>
       <c r="H938" t="s">
         <v>8</v>
@@ -24783,7 +24783,7 @@
         <v>2.35800004005432</v>
       </c>
       <c r="G939" t="n">
-        <v>1.84222567081451</v>
+        <v>1.84222590923309</v>
       </c>
       <c r="H939" t="s">
         <v>8</v>
@@ -24835,7 +24835,7 @@
         <v>2.33800005912781</v>
       </c>
       <c r="G941" t="n">
-        <v>1.8266007900238</v>
+        <v>1.82660067081451</v>
       </c>
       <c r="H941" t="s">
         <v>8</v>
@@ -24861,7 +24861,7 @@
         <v>2.39199995994568</v>
       </c>
       <c r="G942" t="n">
-        <v>1.86878895759583</v>
+        <v>1.86878907680511</v>
       </c>
       <c r="H942" t="s">
         <v>8</v>
@@ -24913,7 +24913,7 @@
         <v>2.3840000629425</v>
       </c>
       <c r="G944" t="n">
-        <v>1.86253881454468</v>
+        <v>1.86253905296326</v>
       </c>
       <c r="H944" t="s">
         <v>8</v>
@@ -24939,7 +24939,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G945" t="n">
-        <v>1.86722648143768</v>
+        <v>1.86722660064697</v>
       </c>
       <c r="H945" t="s">
         <v>8</v>
@@ -24965,7 +24965,7 @@
         <v>2.40199995040894</v>
       </c>
       <c r="G946" t="n">
-        <v>1.87660145759583</v>
+        <v>1.87660157680511</v>
       </c>
       <c r="H946" t="s">
         <v>8</v>
@@ -24991,7 +24991,7 @@
         <v>2.39199995994568</v>
       </c>
       <c r="G947" t="n">
-        <v>1.86878895759583</v>
+        <v>1.86878907680511</v>
       </c>
       <c r="H947" t="s">
         <v>8</v>
@@ -25017,7 +25017,7 @@
         <v>2.31200003623962</v>
       </c>
       <c r="G948" t="n">
-        <v>1.80628788471222</v>
+        <v>1.80628776550293</v>
       </c>
       <c r="H948" t="s">
         <v>8</v>
@@ -25043,7 +25043,7 @@
         <v>2.26799988746643</v>
       </c>
       <c r="G949" t="n">
-        <v>1.77191174030304</v>
+        <v>1.77191162109375</v>
       </c>
       <c r="H949" t="s">
         <v>8</v>
@@ -25095,7 +25095,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G951" t="n">
-        <v>1.7500364780426</v>
+        <v>1.75003623962402</v>
       </c>
       <c r="H951" t="s">
         <v>8</v>
@@ -25121,7 +25121,7 @@
         <v>2.2279999256134</v>
       </c>
       <c r="G952" t="n">
-        <v>1.74066150188446</v>
+        <v>1.74066138267517</v>
       </c>
       <c r="H952" t="s">
         <v>8</v>
@@ -25173,7 +25173,7 @@
         <v>2.35599994659424</v>
       </c>
       <c r="G954" t="n">
-        <v>1.84066331386566</v>
+        <v>1.84066319465637</v>
       </c>
       <c r="H954" t="s">
         <v>8</v>
@@ -25199,7 +25199,7 @@
         <v>2.25799989700317</v>
       </c>
       <c r="G955" t="n">
-        <v>1.76409935951233</v>
+        <v>1.76409912109375</v>
       </c>
       <c r="H955" t="s">
         <v>8</v>
@@ -25225,7 +25225,7 @@
         <v>2.21199989318848</v>
       </c>
       <c r="G956" t="n">
-        <v>1.7281608581543</v>
+        <v>1.72816097736359</v>
       </c>
       <c r="H956" t="s">
         <v>8</v>
@@ -25251,7 +25251,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G957" t="n">
-        <v>1.703160405159</v>
+        <v>1.70316064357758</v>
       </c>
       <c r="H957" t="s">
         <v>8</v>
@@ -25277,7 +25277,7 @@
         <v>2.21600008010864</v>
       </c>
       <c r="G958" t="n">
-        <v>1.73128628730774</v>
+        <v>1.73128616809845</v>
       </c>
       <c r="H958" t="s">
         <v>8</v>
@@ -25303,7 +25303,7 @@
         <v>2.19199991226196</v>
       </c>
       <c r="G959" t="n">
-        <v>1.7125358581543</v>
+        <v>1.71253573894501</v>
       </c>
       <c r="H959" t="s">
         <v>8</v>
@@ -25329,7 +25329,7 @@
         <v>2.2260000705719</v>
       </c>
       <c r="G960" t="n">
-        <v>1.73909878730774</v>
+        <v>1.73909890651703</v>
       </c>
       <c r="H960" t="s">
         <v>8</v>
@@ -25355,7 +25355,7 @@
         <v>2.26200008392334</v>
       </c>
       <c r="G961" t="n">
-        <v>1.76722455024719</v>
+        <v>1.7672244310379</v>
       </c>
       <c r="H961" t="s">
         <v>8</v>
@@ -25381,7 +25381,7 @@
         <v>2.30599999427795</v>
       </c>
       <c r="G962" t="n">
-        <v>1.80160021781921</v>
+        <v>1.80160009860992</v>
       </c>
       <c r="H962" t="s">
         <v>8</v>
@@ -25433,7 +25433,7 @@
         <v>2.31200003623962</v>
       </c>
       <c r="G964" t="n">
-        <v>1.80628788471222</v>
+        <v>1.80628776550293</v>
       </c>
       <c r="H964" t="s">
         <v>8</v>
@@ -25459,7 +25459,7 @@
         <v>2.35199999809265</v>
       </c>
       <c r="G965" t="n">
-        <v>1.83753836154938</v>
+        <v>1.83753824234009</v>
       </c>
       <c r="H965" t="s">
         <v>8</v>
@@ -25485,7 +25485,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G966" t="n">
-        <v>1.82816302776337</v>
+        <v>1.82816290855408</v>
       </c>
       <c r="H966" t="s">
         <v>8</v>
@@ -25511,7 +25511,7 @@
         <v>2.34400010108948</v>
       </c>
       <c r="G967" t="n">
-        <v>1.83128798007965</v>
+        <v>1.83128809928894</v>
       </c>
       <c r="H967" t="s">
         <v>8</v>
@@ -25537,7 +25537,7 @@
         <v>2.37199997901917</v>
       </c>
       <c r="G968" t="n">
-        <v>1.85316371917725</v>
+        <v>1.85316336154938</v>
       </c>
       <c r="H968" t="s">
         <v>8</v>
@@ -25563,7 +25563,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G969" t="n">
-        <v>1.89847707748413</v>
+        <v>1.89847719669342</v>
       </c>
       <c r="H969" t="s">
         <v>8</v>
@@ -25615,7 +25615,7 @@
         <v>2.35400009155273</v>
       </c>
       <c r="G971" t="n">
-        <v>1.83910095691681</v>
+        <v>1.83910071849823</v>
       </c>
       <c r="H971" t="s">
         <v>8</v>
@@ -25641,7 +25641,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G972" t="n">
-        <v>1.89847707748413</v>
+        <v>1.89847719669342</v>
       </c>
       <c r="H972" t="s">
         <v>8</v>
@@ -25667,7 +25667,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G973" t="n">
-        <v>1.89847707748413</v>
+        <v>1.89847719669342</v>
       </c>
       <c r="H973" t="s">
         <v>8</v>
@@ -25745,7 +25745,7 @@
         <v>2.34599995613098</v>
       </c>
       <c r="G976" t="n">
-        <v>1.83285069465637</v>
+        <v>1.83285057544708</v>
       </c>
       <c r="H976" t="s">
         <v>8</v>
@@ -25771,7 +25771,7 @@
         <v>2.35599994659424</v>
       </c>
       <c r="G977" t="n">
-        <v>1.84066331386566</v>
+        <v>1.84066319465637</v>
       </c>
       <c r="H977" t="s">
         <v>8</v>
@@ -25797,7 +25797,7 @@
         <v>2.44600009918213</v>
       </c>
       <c r="G978" t="n">
-        <v>1.91097724437714</v>
+        <v>1.910977602005</v>
       </c>
       <c r="H978" t="s">
         <v>8</v>
@@ -25927,7 +25927,7 @@
         <v>2.40199995040894</v>
       </c>
       <c r="G983" t="n">
-        <v>1.87660145759583</v>
+        <v>1.87660157680511</v>
       </c>
       <c r="H983" t="s">
         <v>8</v>
@@ -25979,7 +25979,7 @@
         <v>2.35400009155273</v>
       </c>
       <c r="G985" t="n">
-        <v>1.83910095691681</v>
+        <v>1.83910071849823</v>
       </c>
       <c r="H985" t="s">
         <v>8</v>
@@ -26031,7 +26031,7 @@
         <v>2.37400007247925</v>
       </c>
       <c r="G987" t="n">
-        <v>1.85472643375397</v>
+        <v>1.85472631454468</v>
       </c>
       <c r="H987" t="s">
         <v>8</v>
@@ -26057,7 +26057,7 @@
         <v>2.34400010108948</v>
       </c>
       <c r="G988" t="n">
-        <v>1.83128798007965</v>
+        <v>1.83128809928894</v>
       </c>
       <c r="H988" t="s">
         <v>8</v>
@@ -26083,7 +26083,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G989" t="n">
-        <v>1.85941410064697</v>
+        <v>1.85941398143768</v>
       </c>
       <c r="H989" t="s">
         <v>8</v>
@@ -26109,7 +26109,7 @@
         <v>2.35400009155273</v>
       </c>
       <c r="G990" t="n">
-        <v>1.83910095691681</v>
+        <v>1.83910071849823</v>
       </c>
       <c r="H990" t="s">
         <v>8</v>
@@ -26135,7 +26135,7 @@
         <v>2.36400008201599</v>
       </c>
       <c r="G991" t="n">
-        <v>1.84691345691681</v>
+        <v>1.8469135761261</v>
       </c>
       <c r="H991" t="s">
         <v>8</v>
@@ -26161,7 +26161,7 @@
         <v>2.35800004005432</v>
       </c>
       <c r="G992" t="n">
-        <v>1.84222567081451</v>
+        <v>1.84222590923309</v>
       </c>
       <c r="H992" t="s">
         <v>8</v>
@@ -26187,7 +26187,7 @@
         <v>2.4539999961853</v>
       </c>
       <c r="G993" t="n">
-        <v>1.9172271490097</v>
+        <v>1.91722750663757</v>
       </c>
       <c r="H993" t="s">
         <v>8</v>
@@ -26213,7 +26213,7 @@
         <v>2.45199990272522</v>
       </c>
       <c r="G994" t="n">
-        <v>1.91566479206085</v>
+        <v>1.91566503047943</v>
       </c>
       <c r="H994" t="s">
         <v>8</v>
@@ -26265,7 +26265,7 @@
         <v>2.50399994850159</v>
       </c>
       <c r="G996" t="n">
-        <v>1.95629072189331</v>
+        <v>1.95629048347473</v>
       </c>
       <c r="H996" t="s">
         <v>8</v>
@@ -26291,7 +26291,7 @@
         <v>2.51200008392334</v>
       </c>
       <c r="G997" t="n">
-        <v>1.96254086494446</v>
+        <v>1.96254062652588</v>
       </c>
       <c r="H997" t="s">
         <v>8</v>
@@ -26317,7 +26317,7 @@
         <v>2.4539999961853</v>
       </c>
       <c r="G998" t="n">
-        <v>1.9172271490097</v>
+        <v>1.91722750663757</v>
       </c>
       <c r="H998" t="s">
         <v>8</v>
@@ -26395,7 +26395,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G1001" t="n">
-        <v>2.00004172325134</v>
+        <v>2.00004148483276</v>
       </c>
       <c r="H1001" t="s">
         <v>8</v>
@@ -26447,7 +26447,7 @@
         <v>2.53600001335144</v>
       </c>
       <c r="G1003" t="n">
-        <v>1.9812912940979</v>
+        <v>1.98129105567932</v>
       </c>
       <c r="H1003" t="s">
         <v>8</v>
@@ -26525,7 +26525,7 @@
         <v>2.5239999294281</v>
       </c>
       <c r="G1006" t="n">
-        <v>1.97191643714905</v>
+        <v>1.97191619873047</v>
       </c>
       <c r="H1006" t="s">
         <v>8</v>
@@ -26551,7 +26551,7 @@
         <v>2.50200009346008</v>
       </c>
       <c r="G1007" t="n">
-        <v>1.95472848415375</v>
+        <v>1.95472824573517</v>
       </c>
       <c r="H1007" t="s">
         <v>8</v>
@@ -26577,7 +26577,7 @@
         <v>2.50999999046326</v>
       </c>
       <c r="G1008" t="n">
-        <v>1.9609786272049</v>
+        <v>1.96097815036774</v>
       </c>
       <c r="H1008" t="s">
         <v>8</v>
@@ -26603,7 +26603,7 @@
         <v>2.50999999046326</v>
       </c>
       <c r="G1009" t="n">
-        <v>1.9609786272049</v>
+        <v>1.96097815036774</v>
       </c>
       <c r="H1009" t="s">
         <v>8</v>
@@ -26629,7 +26629,7 @@
         <v>2.46600008010864</v>
       </c>
       <c r="G1010" t="n">
-        <v>1.926602602005</v>
+        <v>1.92660284042358</v>
       </c>
       <c r="H1010" t="s">
         <v>8</v>
@@ -26655,7 +26655,7 @@
         <v>2.46199989318848</v>
       </c>
       <c r="G1011" t="n">
-        <v>1.92347753047943</v>
+        <v>1.92347741127014</v>
       </c>
       <c r="H1011" t="s">
         <v>8</v>
@@ -26759,7 +26759,7 @@
         <v>2.47399997711182</v>
       </c>
       <c r="G1015" t="n">
-        <v>1.93285286426544</v>
+        <v>1.93285262584686</v>
       </c>
       <c r="H1015" t="s">
         <v>8</v>
@@ -26889,7 +26889,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G1020" t="n">
-        <v>1.89847707748413</v>
+        <v>1.89847719669342</v>
       </c>
       <c r="H1020" t="s">
         <v>8</v>
@@ -27019,7 +27019,7 @@
         <v>2.57599997520447</v>
       </c>
       <c r="G1025" t="n">
-        <v>2.01254153251648</v>
+        <v>2.01254177093506</v>
       </c>
       <c r="H1025" t="s">
         <v>8</v>
@@ -27045,7 +27045,7 @@
         <v>2.63000011444092</v>
       </c>
       <c r="G1026" t="n">
-        <v>2.05473017692566</v>
+        <v>2.05473041534424</v>
       </c>
       <c r="H1026" t="s">
         <v>8</v>
@@ -27071,7 +27071,7 @@
         <v>2.61199998855591</v>
       </c>
       <c r="G1027" t="n">
-        <v>2.04066729545593</v>
+        <v>2.04066753387451</v>
       </c>
       <c r="H1027" t="s">
         <v>8</v>
@@ -27227,7 +27227,7 @@
         <v>2.55599999427795</v>
       </c>
       <c r="G1033" t="n">
-        <v>1.99691665172577</v>
+        <v>1.99691677093506</v>
       </c>
       <c r="H1033" t="s">
         <v>8</v>
@@ -27253,7 +27253,7 @@
         <v>2.55200004577637</v>
       </c>
       <c r="G1034" t="n">
-        <v>1.9937915802002</v>
+        <v>1.99379181861877</v>
       </c>
       <c r="H1034" t="s">
         <v>8</v>
@@ -27279,7 +27279,7 @@
         <v>2.51200008392334</v>
       </c>
       <c r="G1035" t="n">
-        <v>1.96254086494446</v>
+        <v>1.96254062652588</v>
       </c>
       <c r="H1035" t="s">
         <v>8</v>
@@ -27305,7 +27305,7 @@
         <v>2.3840000629425</v>
       </c>
       <c r="G1036" t="n">
-        <v>1.86253881454468</v>
+        <v>1.86253905296326</v>
       </c>
       <c r="H1036" t="s">
         <v>8</v>
@@ -27331,7 +27331,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G1037" t="n">
-        <v>1.82035028934479</v>
+        <v>1.82035064697266</v>
       </c>
       <c r="H1037" t="s">
         <v>8</v>
@@ -27383,7 +27383,7 @@
         <v>2.35400009155273</v>
       </c>
       <c r="G1039" t="n">
-        <v>1.83910095691681</v>
+        <v>1.83910071849823</v>
       </c>
       <c r="H1039" t="s">
         <v>8</v>
@@ -27409,7 +27409,7 @@
         <v>2.56599998474121</v>
       </c>
       <c r="G1040" t="n">
-        <v>2.00472950935364</v>
+        <v>2.00472927093506</v>
       </c>
       <c r="H1040" t="s">
         <v>8</v>
@@ -27435,7 +27435,7 @@
         <v>2.61199998855591</v>
       </c>
       <c r="G1041" t="n">
-        <v>2.04066729545593</v>
+        <v>2.04066753387451</v>
       </c>
       <c r="H1041" t="s">
         <v>8</v>
@@ -27461,7 +27461,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G1042" t="n">
-        <v>2.00004172325134</v>
+        <v>2.00004148483276</v>
       </c>
       <c r="H1042" t="s">
         <v>8</v>
@@ -27487,7 +27487,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G1043" t="n">
-        <v>1.94535315036774</v>
+        <v>1.94535291194916</v>
       </c>
       <c r="H1043" t="s">
         <v>8</v>
@@ -27539,7 +27539,7 @@
         <v>2.62199997901917</v>
       </c>
       <c r="G1045" t="n">
-        <v>2.04848027229309</v>
+        <v>2.04848003387451</v>
       </c>
       <c r="H1045" t="s">
         <v>8</v>
@@ -27565,7 +27565,7 @@
         <v>2.62599992752075</v>
       </c>
       <c r="G1046" t="n">
-        <v>2.0516049861908</v>
+        <v>2.05160522460938</v>
       </c>
       <c r="H1046" t="s">
         <v>8</v>
@@ -27617,7 +27617,7 @@
         <v>2.63000011444092</v>
       </c>
       <c r="G1048" t="n">
-        <v>2.05473017692566</v>
+        <v>2.05473041534424</v>
       </c>
       <c r="H1048" t="s">
         <v>8</v>
@@ -27669,7 +27669,7 @@
         <v>2.67199993133545</v>
       </c>
       <c r="G1050" t="n">
-        <v>2.08754372596741</v>
+        <v>2.08754348754883</v>
       </c>
       <c r="H1050" t="s">
         <v>8</v>
@@ -27695,7 +27695,7 @@
         <v>2.69799995422363</v>
       </c>
       <c r="G1051" t="n">
-        <v>2.10785627365112</v>
+        <v>2.1078565120697</v>
       </c>
       <c r="H1051" t="s">
         <v>8</v>
@@ -27825,7 +27825,7 @@
         <v>2.44799995422363</v>
       </c>
       <c r="G1056" t="n">
-        <v>1.91253995895386</v>
+        <v>1.91254007816315</v>
       </c>
       <c r="H1056" t="s">
         <v>8</v>
@@ -27851,7 +27851,7 @@
         <v>2.31800007820129</v>
       </c>
       <c r="G1057" t="n">
-        <v>1.81097543239594</v>
+        <v>1.81097531318665</v>
       </c>
       <c r="H1057" t="s">
         <v>8</v>
@@ -27929,7 +27929,7 @@
         <v>2.23600006103516</v>
       </c>
       <c r="G1060" t="n">
-        <v>1.74691152572632</v>
+        <v>1.74691128730774</v>
       </c>
       <c r="H1060" t="s">
         <v>8</v>
@@ -27955,7 +27955,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G1061" t="n">
-        <v>1.67190992832184</v>
+        <v>1.67191004753113</v>
       </c>
       <c r="H1061" t="s">
         <v>8</v>
@@ -27981,7 +27981,7 @@
         <v>2.0239999294281</v>
       </c>
       <c r="G1062" t="n">
-        <v>1.58128273487091</v>
+        <v>1.5812828540802</v>
       </c>
       <c r="H1062" t="s">
         <v>8</v>
@@ -28033,7 +28033,7 @@
         <v>1.87100005149841</v>
       </c>
       <c r="G1064" t="n">
-        <v>1.46174931526184</v>
+        <v>1.46174919605255</v>
       </c>
       <c r="H1064" t="s">
         <v>8</v>
@@ -28085,7 +28085,7 @@
         <v>1.69799995422363</v>
       </c>
       <c r="G1066" t="n">
-        <v>1.32659006118774</v>
+        <v>1.32659018039703</v>
       </c>
       <c r="H1066" t="s">
         <v>8</v>
@@ -28111,7 +28111,7 @@
         <v>1.67299997806549</v>
       </c>
       <c r="G1067" t="n">
-        <v>1.30705857276917</v>
+        <v>1.30705845355988</v>
       </c>
       <c r="H1067" t="s">
         <v>8</v>
@@ -28163,7 +28163,7 @@
         <v>1.47099995613098</v>
       </c>
       <c r="G1069" t="n">
-        <v>1.14924263954163</v>
+        <v>1.14924275875092</v>
       </c>
       <c r="H1069" t="s">
         <v>8</v>
@@ -28215,7 +28215,7 @@
         <v>1.58800005912781</v>
       </c>
       <c r="G1071" t="n">
-        <v>1.24065089225769</v>
+        <v>1.2406507730484</v>
       </c>
       <c r="H1071" t="s">
         <v>8</v>
@@ -28241,7 +28241,7 @@
         <v>1.60500001907349</v>
       </c>
       <c r="G1072" t="n">
-        <v>1.2539324760437</v>
+        <v>1.25393235683441</v>
       </c>
       <c r="H1072" t="s">
         <v>8</v>
@@ -28267,7 +28267,7 @@
         <v>1.48399996757507</v>
       </c>
       <c r="G1073" t="n">
-        <v>1.15939927101135</v>
+        <v>1.15939903259277</v>
       </c>
       <c r="H1073" t="s">
         <v>8</v>
@@ -28293,7 +28293,7 @@
         <v>1.50100004673004</v>
       </c>
       <c r="G1074" t="n">
-        <v>1.17268073558807</v>
+        <v>1.17268049716949</v>
       </c>
       <c r="H1074" t="s">
         <v>8</v>
@@ -28345,7 +28345,7 @@
         <v>1.46099996566772</v>
       </c>
       <c r="G1076" t="n">
-        <v>1.14142990112305</v>
+        <v>1.14143013954163</v>
       </c>
       <c r="H1076" t="s">
         <v>8</v>
@@ -28423,7 +28423,7 @@
         <v>1.44500005245209</v>
       </c>
       <c r="G1079" t="n">
-        <v>1.12892997264862</v>
+        <v>1.12892985343933</v>
       </c>
       <c r="H1079" t="s">
         <v>8</v>
@@ -28475,7 +28475,7 @@
         <v>1.53400003910065</v>
       </c>
       <c r="G1081" t="n">
-        <v>1.1984623670578</v>
+        <v>1.19846248626709</v>
       </c>
       <c r="H1081" t="s">
         <v>8</v>
@@ -28527,7 +28527,7 @@
         <v>1.6360000371933</v>
       </c>
       <c r="G1083" t="n">
-        <v>1.27815175056458</v>
+        <v>1.27815163135529</v>
       </c>
       <c r="H1083" t="s">
         <v>8</v>
@@ -28553,7 +28553,7 @@
         <v>1.68599998950958</v>
       </c>
       <c r="G1084" t="n">
-        <v>1.31721472740173</v>
+        <v>1.31721496582031</v>
       </c>
       <c r="H1084" t="s">
         <v>8</v>
@@ -28579,7 +28579,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G1085" t="n">
-        <v>1.39065408706665</v>
+        <v>1.39065396785736</v>
       </c>
       <c r="H1085" t="s">
         <v>8</v>
@@ -28605,7 +28605,7 @@
         <v>1.85300004482269</v>
       </c>
       <c r="G1086" t="n">
-        <v>1.4476865530014</v>
+        <v>1.44768643379211</v>
       </c>
       <c r="H1086" t="s">
         <v>8</v>
@@ -28709,7 +28709,7 @@
         <v>1.71099996566772</v>
       </c>
       <c r="G1090" t="n">
-        <v>1.33674657344818</v>
+        <v>1.33674645423889</v>
       </c>
       <c r="H1090" t="s">
         <v>8</v>
@@ -28735,7 +28735,7 @@
         <v>1.74399995803833</v>
       </c>
       <c r="G1091" t="n">
-        <v>1.36252844333649</v>
+        <v>1.3625283241272</v>
       </c>
       <c r="H1091" t="s">
         <v>8</v>
@@ -28761,7 +28761,7 @@
         <v>1.72099995613098</v>
       </c>
       <c r="G1092" t="n">
-        <v>1.34455919265747</v>
+        <v>1.34455931186676</v>
       </c>
       <c r="H1092" t="s">
         <v>8</v>
@@ -28813,7 +28813,7 @@
         <v>1.75600004196167</v>
       </c>
       <c r="G1094" t="n">
-        <v>1.37190365791321</v>
+        <v>1.37190353870392</v>
       </c>
       <c r="H1094" t="s">
         <v>8</v>
@@ -28891,7 +28891,7 @@
         <v>1.83000004291534</v>
       </c>
       <c r="G1097" t="n">
-        <v>1.42971730232239</v>
+        <v>1.42971742153168</v>
       </c>
       <c r="H1097" t="s">
         <v>8</v>
@@ -28917,7 +28917,7 @@
         <v>1.80499994754791</v>
       </c>
       <c r="G1098" t="n">
-        <v>1.41018557548523</v>
+        <v>1.41018569469452</v>
       </c>
       <c r="H1098" t="s">
         <v>8</v>
@@ -29021,7 +29021,7 @@
         <v>1.74000000953674</v>
       </c>
       <c r="G1102" t="n">
-        <v>1.35940337181091</v>
+        <v>1.35940325260162</v>
       </c>
       <c r="H1102" t="s">
         <v>8</v>
@@ -29047,7 +29047,7 @@
         <v>1.56900000572205</v>
       </c>
       <c r="G1103" t="n">
-        <v>1.22580671310425</v>
+        <v>1.22580695152283</v>
       </c>
       <c r="H1103" t="s">
         <v>8</v>
@@ -29099,7 +29099,7 @@
         <v>1.49300003051758</v>
       </c>
       <c r="G1105" t="n">
-        <v>1.16643047332764</v>
+        <v>1.16643059253693</v>
       </c>
       <c r="H1105" t="s">
         <v>8</v>
@@ -29125,7 +29125,7 @@
         <v>1.47000002861023</v>
       </c>
       <c r="G1106" t="n">
-        <v>1.14846158027649</v>
+        <v>1.1484614610672</v>
       </c>
       <c r="H1106" t="s">
         <v>8</v>
@@ -29151,7 +29151,7 @@
         <v>1.46000003814697</v>
       </c>
       <c r="G1107" t="n">
-        <v>1.14064872264862</v>
+        <v>1.14064884185791</v>
       </c>
       <c r="H1107" t="s">
         <v>8</v>
@@ -29177,7 +29177,7 @@
         <v>1.41600000858307</v>
       </c>
       <c r="G1108" t="n">
-        <v>1.1062730550766</v>
+        <v>1.10627317428589</v>
       </c>
       <c r="H1108" t="s">
         <v>8</v>
@@ -29229,7 +29229,7 @@
         <v>1.43599998950958</v>
       </c>
       <c r="G1110" t="n">
-        <v>1.12189829349518</v>
+        <v>1.12189841270447</v>
       </c>
       <c r="H1110" t="s">
         <v>8</v>
@@ -29255,7 +29255,7 @@
         <v>1.36000001430511</v>
       </c>
       <c r="G1111" t="n">
-        <v>1.06252217292786</v>
+        <v>1.06252205371857</v>
       </c>
       <c r="H1111" t="s">
         <v>8</v>
@@ -29281,7 +29281,7 @@
         <v>1.375</v>
       </c>
       <c r="G1112" t="n">
-        <v>1.07424116134644</v>
+        <v>1.07424104213715</v>
       </c>
       <c r="H1112" t="s">
         <v>8</v>
@@ -29437,7 +29437,7 @@
         <v>1.43700003623962</v>
       </c>
       <c r="G1118" t="n">
-        <v>1.12267971038818</v>
+        <v>1.12267982959747</v>
       </c>
       <c r="H1118" t="s">
         <v>8</v>
@@ -29463,7 +29463,7 @@
         <v>1.41600000858307</v>
       </c>
       <c r="G1119" t="n">
-        <v>1.1062730550766</v>
+        <v>1.10627317428589</v>
       </c>
       <c r="H1119" t="s">
         <v>8</v>
@@ -29489,7 +29489,7 @@
         <v>1.43799996376038</v>
       </c>
       <c r="G1120" t="n">
-        <v>1.1234610080719</v>
+        <v>1.12346088886261</v>
       </c>
       <c r="H1120" t="s">
         <v>8</v>
@@ -29697,7 +29697,7 @@
         <v>1.58800005912781</v>
       </c>
       <c r="G1128" t="n">
-        <v>1.24065089225769</v>
+        <v>1.2406507730484</v>
       </c>
       <c r="H1128" t="s">
         <v>8</v>
@@ -29749,7 +29749,7 @@
         <v>1.61800003051758</v>
       </c>
       <c r="G1130" t="n">
-        <v>1.26408886909485</v>
+        <v>1.26408874988556</v>
       </c>
       <c r="H1130" t="s">
         <v>8</v>
@@ -29801,7 +29801,7 @@
         <v>1.6710000038147</v>
       </c>
       <c r="G1132" t="n">
-        <v>1.30549585819244</v>
+        <v>1.30549597740173</v>
       </c>
       <c r="H1132" t="s">
         <v>8</v>
@@ -29827,7 +29827,7 @@
         <v>1.71000003814697</v>
       </c>
       <c r="G1133" t="n">
-        <v>1.33596539497375</v>
+        <v>1.33596515655518</v>
       </c>
       <c r="H1133" t="s">
         <v>8</v>
@@ -29879,7 +29879,7 @@
         <v>1.6710000038147</v>
       </c>
       <c r="G1135" t="n">
-        <v>1.30549585819244</v>
+        <v>1.30549597740173</v>
       </c>
       <c r="H1135" t="s">
         <v>8</v>
@@ -29931,7 +29931,7 @@
         <v>1.67299997806549</v>
       </c>
       <c r="G1137" t="n">
-        <v>1.30705857276917</v>
+        <v>1.30705845355988</v>
       </c>
       <c r="H1137" t="s">
         <v>8</v>
@@ -29957,7 +29957,7 @@
         <v>1.64400005340576</v>
       </c>
       <c r="G1138" t="n">
-        <v>1.28440177440643</v>
+        <v>1.28440189361572</v>
       </c>
       <c r="H1138" t="s">
         <v>8</v>
@@ -29983,7 +29983,7 @@
         <v>1.60599994659424</v>
       </c>
       <c r="G1139" t="n">
-        <v>1.25471353530884</v>
+        <v>1.25471341609955</v>
       </c>
       <c r="H1139" t="s">
         <v>8</v>
@@ -30009,7 +30009,7 @@
         <v>1.66799998283386</v>
       </c>
       <c r="G1140" t="n">
-        <v>1.30315208435059</v>
+        <v>1.30315220355988</v>
       </c>
       <c r="H1140" t="s">
         <v>8</v>
@@ -30035,7 +30035,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G1141" t="n">
-        <v>1.34377801418304</v>
+        <v>1.34377813339233</v>
       </c>
       <c r="H1141" t="s">
         <v>8</v>
@@ -30061,7 +30061,7 @@
         <v>1.682000041008</v>
       </c>
       <c r="G1142" t="n">
-        <v>1.31408989429474</v>
+        <v>1.31409001350403</v>
       </c>
       <c r="H1142" t="s">
         <v>8</v>
@@ -30087,7 +30087,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G1143" t="n">
-        <v>1.34377801418304</v>
+        <v>1.34377813339233</v>
       </c>
       <c r="H1143" t="s">
         <v>8</v>
@@ -30165,7 +30165,7 @@
         <v>1.72699999809265</v>
       </c>
       <c r="G1146" t="n">
-        <v>1.34924685955048</v>
+        <v>1.34924674034119</v>
       </c>
       <c r="H1146" t="s">
         <v>8</v>
@@ -30217,7 +30217,7 @@
         <v>1.64999997615814</v>
       </c>
       <c r="G1148" t="n">
-        <v>1.28908932209015</v>
+        <v>1.28908944129944</v>
       </c>
       <c r="H1148" t="s">
         <v>8</v>
@@ -30451,7 +30451,7 @@
         <v>1.6599999666214</v>
       </c>
       <c r="G1157" t="n">
-        <v>1.29690206050873</v>
+        <v>1.29690194129944</v>
       </c>
       <c r="H1157" t="s">
         <v>8</v>
@@ -30477,7 +30477,7 @@
         <v>1.63499999046326</v>
       </c>
       <c r="G1158" t="n">
-        <v>1.27737045288086</v>
+        <v>1.27737021446228</v>
       </c>
       <c r="H1158" t="s">
         <v>8</v>
@@ -30581,7 +30581,7 @@
         <v>1.50399994850159</v>
       </c>
       <c r="G1162" t="n">
-        <v>1.17502439022064</v>
+        <v>1.17502450942993</v>
       </c>
       <c r="H1162" t="s">
         <v>8</v>
@@ -30607,7 +30607,7 @@
         <v>1.51600003242493</v>
       </c>
       <c r="G1163" t="n">
-        <v>1.18439960479736</v>
+        <v>1.18439972400665</v>
       </c>
       <c r="H1163" t="s">
         <v>8</v>
@@ -30763,7 +30763,7 @@
         <v>1.57000005245209</v>
       </c>
       <c r="G1169" t="n">
-        <v>1.22658824920654</v>
+        <v>1.22658812999725</v>
       </c>
       <c r="H1169" t="s">
         <v>8</v>
@@ -30789,7 +30789,7 @@
         <v>1.60500001907349</v>
       </c>
       <c r="G1170" t="n">
-        <v>1.2539324760437</v>
+        <v>1.25393235683441</v>
       </c>
       <c r="H1170" t="s">
         <v>8</v>
@@ -30815,7 +30815,7 @@
         <v>1.67599999904633</v>
       </c>
       <c r="G1171" t="n">
-        <v>1.30940234661102</v>
+        <v>1.30940222740173</v>
       </c>
       <c r="H1171" t="s">
         <v>8</v>
@@ -30867,7 +30867,7 @@
         <v>1.67999994754791</v>
       </c>
       <c r="G1173" t="n">
-        <v>1.31252729892731</v>
+        <v>1.3125274181366</v>
       </c>
       <c r="H1173" t="s">
         <v>8</v>
@@ -30997,7 +30997,7 @@
         <v>1.60800004005432</v>
       </c>
       <c r="G1178" t="n">
-        <v>1.25627624988556</v>
+        <v>1.25627601146698</v>
       </c>
       <c r="H1178" t="s">
         <v>8</v>
@@ -31075,7 +31075,7 @@
         <v>1.5900000333786</v>
       </c>
       <c r="G1181" t="n">
-        <v>1.24221336841583</v>
+        <v>1.24221324920654</v>
       </c>
       <c r="H1181" t="s">
         <v>8</v>
@@ -31101,7 +31101,7 @@
         <v>1.57799994945526</v>
       </c>
       <c r="G1182" t="n">
-        <v>1.23283815383911</v>
+        <v>1.2328382730484</v>
       </c>
       <c r="H1182" t="s">
         <v>8</v>
@@ -31127,7 +31127,7 @@
         <v>1.57000005245209</v>
       </c>
       <c r="G1183" t="n">
-        <v>1.22658824920654</v>
+        <v>1.22658812999725</v>
       </c>
       <c r="H1183" t="s">
         <v>8</v>
@@ -31257,7 +31257,7 @@
         <v>1.48000001907349</v>
       </c>
       <c r="G1188" t="n">
-        <v>1.15627419948578</v>
+        <v>1.15627408027649</v>
       </c>
       <c r="H1188" t="s">
         <v>8</v>
@@ -31309,7 +31309,7 @@
         <v>1.48399996757507</v>
       </c>
       <c r="G1190" t="n">
-        <v>1.15939927101135</v>
+        <v>1.15939903259277</v>
       </c>
       <c r="H1190" t="s">
         <v>8</v>
@@ -31335,7 +31335,7 @@
         <v>1.48800003528595</v>
       </c>
       <c r="G1191" t="n">
-        <v>1.16252422332764</v>
+        <v>1.16252434253693</v>
       </c>
       <c r="H1191" t="s">
         <v>8</v>
@@ -31361,7 +31361,7 @@
         <v>1.51199996471405</v>
       </c>
       <c r="G1192" t="n">
-        <v>1.18127465248108</v>
+        <v>1.18127453327179</v>
       </c>
       <c r="H1192" t="s">
         <v>8</v>
@@ -31387,7 +31387,7 @@
         <v>1.49300003051758</v>
       </c>
       <c r="G1193" t="n">
-        <v>1.16643047332764</v>
+        <v>1.16643059253693</v>
       </c>
       <c r="H1193" t="s">
         <v>8</v>
@@ -31465,7 +31465,7 @@
         <v>1.43900001049042</v>
       </c>
       <c r="G1196" t="n">
-        <v>1.12424218654633</v>
+        <v>1.12424230575562</v>
       </c>
       <c r="H1196" t="s">
         <v>8</v>
@@ -31491,7 +31491,7 @@
         <v>1.43599998950958</v>
       </c>
       <c r="G1197" t="n">
-        <v>1.12189829349518</v>
+        <v>1.12189841270447</v>
       </c>
       <c r="H1197" t="s">
         <v>8</v>
@@ -31517,7 +31517,7 @@
         <v>1.49699997901917</v>
       </c>
       <c r="G1198" t="n">
-        <v>1.1695556640625</v>
+        <v>1.16955542564392</v>
       </c>
       <c r="H1198" t="s">
         <v>8</v>
@@ -31621,7 +31621,7 @@
         <v>1.41600000858307</v>
       </c>
       <c r="G1202" t="n">
-        <v>1.1062730550766</v>
+        <v>1.10627317428589</v>
       </c>
       <c r="H1202" t="s">
         <v>8</v>
@@ -31673,7 +31673,7 @@
         <v>1.39699995517731</v>
       </c>
       <c r="G1204" t="n">
-        <v>1.09142899513245</v>
+        <v>1.09142887592316</v>
       </c>
       <c r="H1204" t="s">
         <v>8</v>
@@ -31699,7 +31699,7 @@
         <v>1.41799998283386</v>
       </c>
       <c r="G1205" t="n">
-        <v>1.10783565044403</v>
+        <v>1.10783553123474</v>
       </c>
       <c r="H1205" t="s">
         <v>8</v>
@@ -31777,7 +31777,7 @@
         <v>1.43599998950958</v>
       </c>
       <c r="G1208" t="n">
-        <v>1.12189829349518</v>
+        <v>1.12189841270447</v>
       </c>
       <c r="H1208" t="s">
         <v>8</v>
@@ -31829,7 +31829,7 @@
         <v>1.442999958992</v>
       </c>
       <c r="G1210" t="n">
-        <v>1.12736713886261</v>
+        <v>1.1273672580719</v>
       </c>
       <c r="H1210" t="s">
         <v>8</v>
@@ -31933,7 +31933,7 @@
         <v>1.4559999704361</v>
       </c>
       <c r="G1214" t="n">
-        <v>1.13752377033234</v>
+        <v>1.13752365112305</v>
       </c>
       <c r="H1214" t="s">
         <v>8</v>
@@ -32011,7 +32011,7 @@
         <v>1.35699999332428</v>
       </c>
       <c r="G1217" t="n">
-        <v>1.06017851829529</v>
+        <v>1.06017827987671</v>
       </c>
       <c r="H1217" t="s">
         <v>8</v>
@@ -32063,7 +32063,7 @@
         <v>1.33800005912781</v>
       </c>
       <c r="G1219" t="n">
-        <v>1.04533445835114</v>
+        <v>1.04533433914185</v>
       </c>
       <c r="H1219" t="s">
         <v>8</v>
@@ -32115,7 +32115,7 @@
         <v>1.33800005912781</v>
       </c>
       <c r="G1221" t="n">
-        <v>1.04533445835114</v>
+        <v>1.04533433914185</v>
       </c>
       <c r="H1221" t="s">
         <v>8</v>
@@ -32141,7 +32141,7 @@
         <v>1.31099998950958</v>
       </c>
       <c r="G1222" t="n">
-        <v>1.02424013614655</v>
+        <v>1.02424001693726</v>
       </c>
       <c r="H1222" t="s">
         <v>8</v>
@@ -32219,7 +32219,7 @@
         <v>1.25100004673004</v>
       </c>
       <c r="G1225" t="n">
-        <v>0.977364242076874</v>
+        <v>0.977364122867584</v>
       </c>
       <c r="H1225" t="s">
         <v>8</v>
@@ -32245,7 +32245,7 @@
         <v>1.20000004768372</v>
       </c>
       <c r="G1226" t="n">
-        <v>0.937519609928131</v>
+        <v>0.937519550323486</v>
       </c>
       <c r="H1226" t="s">
         <v>8</v>
@@ -32271,7 +32271,7 @@
         <v>1.11500000953674</v>
       </c>
       <c r="G1227" t="n">
-        <v>0.871111929416656</v>
+        <v>0.871112048625946</v>
       </c>
       <c r="H1227" t="s">
         <v>8</v>
@@ -32297,7 +32297,7 @@
         <v>1.09099996089935</v>
       </c>
       <c r="G1228" t="n">
-        <v>0.852361381053925</v>
+        <v>0.852361500263214</v>
       </c>
       <c r="H1228" t="s">
         <v>8</v>
@@ -32323,7 +32323,7 @@
         <v>1.16199994087219</v>
       </c>
       <c r="G1229" t="n">
-        <v>0.907831430435181</v>
+        <v>0.907831311225891</v>
       </c>
       <c r="H1229" t="s">
         <v>8</v>
@@ -32375,7 +32375,7 @@
         <v>1.16199994087219</v>
       </c>
       <c r="G1231" t="n">
-        <v>0.907831430435181</v>
+        <v>0.907831311225891</v>
       </c>
       <c r="H1231" t="s">
         <v>8</v>
@@ -32427,7 +32427,7 @@
         <v>1.14600002765656</v>
       </c>
       <c r="G1233" t="n">
-        <v>0.895331144332886</v>
+        <v>0.895331084728241</v>
       </c>
       <c r="H1233" t="s">
         <v>8</v>
@@ -32453,7 +32453,7 @@
         <v>1.13399994373322</v>
       </c>
       <c r="G1234" t="n">
-        <v>0.88595587015152</v>
+        <v>0.885955810546875</v>
       </c>
       <c r="H1234" t="s">
         <v>8</v>
@@ -32505,7 +32505,7 @@
         <v>1.39800000190735</v>
       </c>
       <c r="G1236" t="n">
-        <v>1.09221029281616</v>
+        <v>1.09221041202545</v>
       </c>
       <c r="H1236" t="s">
         <v>8</v>
@@ -32557,7 +32557,7 @@
         <v>1.26199996471405</v>
       </c>
       <c r="G1238" t="n">
-        <v>0.985958218574524</v>
+        <v>0.985958099365234</v>
       </c>
       <c r="H1238" t="s">
         <v>8</v>
@@ -32583,7 +32583,7 @@
         <v>1.33899998664856</v>
       </c>
       <c r="G1239" t="n">
-        <v>1.04611563682556</v>
+        <v>1.04611551761627</v>
       </c>
       <c r="H1239" t="s">
         <v>8</v>
@@ -32609,7 +32609,7 @@
         <v>1.4539999961853</v>
       </c>
       <c r="G1240" t="n">
-        <v>1.13596105575562</v>
+        <v>1.1359611749649</v>
       </c>
       <c r="H1240" t="s">
         <v>8</v>
@@ -32635,7 +32635,7 @@
         <v>1.44000005722046</v>
       </c>
       <c r="G1241" t="n">
-        <v>1.12502336502075</v>
+        <v>1.12502348423004</v>
       </c>
       <c r="H1241" t="s">
         <v>8</v>
@@ -32661,7 +32661,7 @@
         <v>1.46000003814697</v>
       </c>
       <c r="G1242" t="n">
-        <v>1.14064872264862</v>
+        <v>1.14064884185791</v>
       </c>
       <c r="H1242" t="s">
         <v>8</v>
@@ -32687,7 +32687,7 @@
         <v>1.47899997234344</v>
       </c>
       <c r="G1243" t="n">
-        <v>1.15549278259277</v>
+        <v>1.15549266338348</v>
       </c>
       <c r="H1243" t="s">
         <v>8</v>
@@ -32739,7 +32739,7 @@
         <v>1.58000004291534</v>
       </c>
       <c r="G1245" t="n">
-        <v>1.23440074920654</v>
+        <v>1.23440086841583</v>
       </c>
       <c r="H1245" t="s">
         <v>8</v>
@@ -32765,7 +32765,7 @@
         <v>1.58000004291534</v>
       </c>
       <c r="G1246" t="n">
-        <v>1.23440074920654</v>
+        <v>1.23440086841583</v>
       </c>
       <c r="H1246" t="s">
         <v>8</v>
@@ -32817,7 +32817,7 @@
         <v>1.60599994659424</v>
       </c>
       <c r="G1248" t="n">
-        <v>1.25471353530884</v>
+        <v>1.25471341609955</v>
       </c>
       <c r="H1248" t="s">
         <v>8</v>
@@ -32895,7 +32895,7 @@
         <v>1.58700001239777</v>
       </c>
       <c r="G1251" t="n">
-        <v>1.23986947536469</v>
+        <v>1.23986959457397</v>
       </c>
       <c r="H1251" t="s">
         <v>8</v>
@@ -32921,7 +32921,7 @@
         <v>1.55900001525879</v>
       </c>
       <c r="G1252" t="n">
-        <v>1.21799409389496</v>
+        <v>1.21799421310425</v>
       </c>
       <c r="H1252" t="s">
         <v>8</v>
@@ -33051,7 +33051,7 @@
         <v>1.69799995422363</v>
       </c>
       <c r="G1257" t="n">
-        <v>1.32659006118774</v>
+        <v>1.32659018039703</v>
       </c>
       <c r="H1257" t="s">
         <v>8</v>
@@ -33077,7 +33077,7 @@
         <v>1.68599998950958</v>
       </c>
       <c r="G1258" t="n">
-        <v>1.31721472740173</v>
+        <v>1.31721496582031</v>
       </c>
       <c r="H1258" t="s">
         <v>8</v>
@@ -33103,7 +33103,7 @@
         <v>1.74300003051758</v>
       </c>
       <c r="G1259" t="n">
-        <v>1.36174714565277</v>
+        <v>1.36174702644348</v>
       </c>
       <c r="H1259" t="s">
         <v>8</v>
@@ -33181,7 +33181,7 @@
         <v>1.7849999666214</v>
       </c>
       <c r="G1262" t="n">
-        <v>1.39456021785736</v>
+        <v>1.39456033706665</v>
       </c>
       <c r="H1262" t="s">
         <v>8</v>
@@ -33233,7 +33233,7 @@
         <v>1.76199996471405</v>
       </c>
       <c r="G1264" t="n">
-        <v>1.37659108638763</v>
+        <v>1.37659120559692</v>
       </c>
       <c r="H1264" t="s">
         <v>8</v>
@@ -33311,7 +33311,7 @@
         <v>1.72099995613098</v>
       </c>
       <c r="G1267" t="n">
-        <v>1.34455919265747</v>
+        <v>1.34455931186676</v>
       </c>
       <c r="H1267" t="s">
         <v>8</v>
@@ -33337,7 +33337,7 @@
         <v>1.82700002193451</v>
       </c>
       <c r="G1268" t="n">
-        <v>1.42737340927124</v>
+        <v>1.42737352848053</v>
       </c>
       <c r="H1268" t="s">
         <v>8</v>
@@ -33441,7 +33441,7 @@
         <v>1.85300004482269</v>
       </c>
       <c r="G1272" t="n">
-        <v>1.4476865530014</v>
+        <v>1.44768643379211</v>
       </c>
       <c r="H1272" t="s">
         <v>8</v>
@@ -33519,7 +33519,7 @@
         <v>2.00799989700317</v>
       </c>
       <c r="G1275" t="n">
-        <v>1.56878268718719</v>
+        <v>1.56878256797791</v>
       </c>
       <c r="H1275" t="s">
         <v>8</v>
@@ -33545,7 +33545,7 @@
         <v>2.00799989700317</v>
       </c>
       <c r="G1276" t="n">
-        <v>1.56878268718719</v>
+        <v>1.56878256797791</v>
       </c>
       <c r="H1276" t="s">
         <v>8</v>
@@ -33571,7 +33571,7 @@
         <v>2</v>
       </c>
       <c r="G1277" t="n">
-        <v>1.56253254413605</v>
+        <v>1.56253266334534</v>
       </c>
       <c r="H1277" t="s">
         <v>8</v>
@@ -33623,7 +33623,7 @@
         <v>2.02800011634827</v>
       </c>
       <c r="G1279" t="n">
-        <v>1.58440804481506</v>
+        <v>1.58440816402435</v>
       </c>
       <c r="H1279" t="s">
         <v>8</v>
@@ -33649,7 +33649,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G1280" t="n">
-        <v>1.55471980571747</v>
+        <v>1.55471992492676</v>
       </c>
       <c r="H1280" t="s">
         <v>8</v>
@@ -33675,7 +33675,7 @@
         <v>1.97599995136261</v>
       </c>
       <c r="G1281" t="n">
-        <v>1.54378223419189</v>
+        <v>1.5437821149826</v>
       </c>
       <c r="H1281" t="s">
         <v>8</v>
@@ -33753,7 +33753,7 @@
         <v>1.97899997234344</v>
       </c>
       <c r="G1284" t="n">
-        <v>1.54612588882446</v>
+        <v>1.54612600803375</v>
       </c>
       <c r="H1284" t="s">
         <v>8</v>
@@ -33831,7 +33831,7 @@
         <v>1.90100002288818</v>
       </c>
       <c r="G1287" t="n">
-        <v>1.485187292099</v>
+        <v>1.48518717288971</v>
       </c>
       <c r="H1287" t="s">
         <v>8</v>
@@ -33857,7 +33857,7 @@
         <v>1.87600004673004</v>
       </c>
       <c r="G1288" t="n">
-        <v>1.46565544605255</v>
+        <v>1.46565556526184</v>
       </c>
       <c r="H1288" t="s">
         <v>8</v>
@@ -33883,7 +33883,7 @@
         <v>1.93400001525879</v>
       </c>
       <c r="G1289" t="n">
-        <v>1.51096904277802</v>
+        <v>1.5109691619873</v>
       </c>
       <c r="H1289" t="s">
         <v>8</v>
@@ -33935,7 +33935,7 @@
         <v>1.93400001525879</v>
       </c>
       <c r="G1291" t="n">
-        <v>1.51096904277802</v>
+        <v>1.5109691619873</v>
       </c>
       <c r="H1291" t="s">
         <v>8</v>
@@ -33961,7 +33961,7 @@
         <v>1.97000002861023</v>
       </c>
       <c r="G1292" t="n">
-        <v>1.53909468650818</v>
+        <v>1.53909456729889</v>
       </c>
       <c r="H1292" t="s">
         <v>8</v>
@@ -34039,7 +34039,7 @@
         <v>2.10400009155273</v>
       </c>
       <c r="G1295" t="n">
-        <v>1.64378428459167</v>
+        <v>1.64378440380096</v>
       </c>
       <c r="H1295" t="s">
         <v>8</v>
@@ -34117,7 +34117,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G1298" t="n">
-        <v>1.7500364780426</v>
+        <v>1.75003623962402</v>
       </c>
       <c r="H1298" t="s">
         <v>8</v>
@@ -34143,7 +34143,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G1299" t="n">
-        <v>1.7500364780426</v>
+        <v>1.75003623962402</v>
       </c>
       <c r="H1299" t="s">
         <v>8</v>
@@ -34169,7 +34169,7 @@
         <v>2.24200010299683</v>
       </c>
       <c r="G1300" t="n">
-        <v>1.75159895420074</v>
+        <v>1.75159919261932</v>
       </c>
       <c r="H1300" t="s">
         <v>8</v>
@@ -34195,7 +34195,7 @@
         <v>2.30599999427795</v>
       </c>
       <c r="G1301" t="n">
-        <v>1.80160021781921</v>
+        <v>1.80160009860992</v>
       </c>
       <c r="H1301" t="s">
         <v>8</v>
@@ -34247,7 +34247,7 @@
         <v>2.25</v>
       </c>
       <c r="G1303" t="n">
-        <v>1.75784909725189</v>
+        <v>1.7578489780426</v>
       </c>
       <c r="H1303" t="s">
         <v>8</v>
@@ -34429,7 +34429,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G1310" t="n">
-        <v>1.68753552436829</v>
+        <v>1.68753528594971</v>
       </c>
       <c r="H1310" t="s">
         <v>8</v>
@@ -34507,7 +34507,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G1313" t="n">
-        <v>1.67972254753113</v>
+        <v>1.67972266674042</v>
       </c>
       <c r="H1313" t="s">
         <v>8</v>
@@ -34533,7 +34533,7 @@
         <v>2.20799994468689</v>
       </c>
       <c r="G1314" t="n">
-        <v>1.72503590583801</v>
+        <v>1.7250360250473</v>
       </c>
       <c r="H1314" t="s">
         <v>8</v>
@@ -34637,7 +34637,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G1318" t="n">
-        <v>1.83597576618195</v>
+        <v>1.83597564697266</v>
       </c>
       <c r="H1318" t="s">
         <v>8</v>
@@ -34767,7 +34767,7 @@
         <v>2.50399994850159</v>
       </c>
       <c r="G1323" t="n">
-        <v>1.95629072189331</v>
+        <v>1.95629048347473</v>
       </c>
       <c r="H1323" t="s">
         <v>8</v>
@@ -34845,7 +34845,7 @@
         <v>2.50999999046326</v>
       </c>
       <c r="G1326" t="n">
-        <v>1.9609786272049</v>
+        <v>1.96097815036774</v>
       </c>
       <c r="H1326" t="s">
         <v>8</v>
@@ -34871,7 +34871,7 @@
         <v>2.42799997329712</v>
       </c>
       <c r="G1327" t="n">
-        <v>1.89691472053528</v>
+        <v>1.8969144821167</v>
       </c>
       <c r="H1327" t="s">
         <v>8</v>
@@ -34923,7 +34923,7 @@
         <v>2.43600010871887</v>
       </c>
       <c r="G1329" t="n">
-        <v>1.90316474437714</v>
+        <v>1.90316462516785</v>
       </c>
       <c r="H1329" t="s">
         <v>8</v>
@@ -34949,7 +34949,7 @@
         <v>2.50200009346008</v>
       </c>
       <c r="G1330" t="n">
-        <v>1.95472848415375</v>
+        <v>1.95472824573517</v>
       </c>
       <c r="H1330" t="s">
         <v>8</v>
@@ -35053,7 +35053,7 @@
         <v>2.54200005531311</v>
       </c>
       <c r="G1334" t="n">
-        <v>1.98597896099091</v>
+        <v>1.98597872257233</v>
       </c>
       <c r="H1334" t="s">
         <v>8</v>
@@ -35079,7 +35079,7 @@
         <v>2.65599989891052</v>
       </c>
       <c r="G1335" t="n">
-        <v>2.07504320144653</v>
+        <v>2.07504343986511</v>
       </c>
       <c r="H1335" t="s">
         <v>8</v>
@@ -35105,7 +35105,7 @@
         <v>2.57599997520447</v>
       </c>
       <c r="G1336" t="n">
-        <v>2.01254153251648</v>
+        <v>2.01254177093506</v>
       </c>
       <c r="H1336" t="s">
         <v>8</v>
@@ -35131,7 +35131,7 @@
         <v>2.58400011062622</v>
       </c>
       <c r="G1337" t="n">
-        <v>2.01879191398621</v>
+        <v>2.01879215240479</v>
       </c>
       <c r="H1337" t="s">
         <v>8</v>
@@ -35235,7 +35235,7 @@
         <v>2.61199998855591</v>
       </c>
       <c r="G1341" t="n">
-        <v>2.04066729545593</v>
+        <v>2.04066753387451</v>
       </c>
       <c r="H1341" t="s">
         <v>8</v>
@@ -35261,7 +35261,7 @@
         <v>2.62599992752075</v>
       </c>
       <c r="G1342" t="n">
-        <v>2.0516049861908</v>
+        <v>2.05160522460938</v>
       </c>
       <c r="H1342" t="s">
         <v>8</v>
@@ -35287,7 +35287,7 @@
         <v>2.68799996376038</v>
       </c>
       <c r="G1343" t="n">
-        <v>2.10004353523254</v>
+        <v>2.10004377365112</v>
       </c>
       <c r="H1343" t="s">
         <v>8</v>
@@ -35313,7 +35313,7 @@
         <v>2.58200001716614</v>
       </c>
       <c r="G1344" t="n">
-        <v>2.10820865631104</v>
+        <v>2.10820889472961</v>
       </c>
       <c r="H1344" t="s">
         <v>8</v>
@@ -35339,7 +35339,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G1345" t="n">
-        <v>1.99226534366608</v>
+        <v>1.99226558208466</v>
       </c>
       <c r="H1345" t="s">
         <v>8</v>
@@ -35443,7 +35443,7 @@
         <v>2.69400000572205</v>
       </c>
       <c r="G1349" t="n">
-        <v>2.19965696334839</v>
+        <v>2.19965720176697</v>
       </c>
       <c r="H1349" t="s">
         <v>8</v>
@@ -35521,7 +35521,7 @@
         <v>2.62800002098083</v>
       </c>
       <c r="G1352" t="n">
-        <v>2.14576816558838</v>
+        <v>2.1457679271698</v>
       </c>
       <c r="H1352" t="s">
         <v>8</v>
@@ -35547,7 +35547,7 @@
         <v>2.66199994087219</v>
       </c>
       <c r="G1353" t="n">
-        <v>2.17352890968323</v>
+        <v>2.17352867126465</v>
       </c>
       <c r="H1353" t="s">
         <v>8</v>
@@ -35573,7 +35573,7 @@
         <v>2.69199991226196</v>
       </c>
       <c r="G1354" t="n">
-        <v>2.19802403450012</v>
+        <v>2.19802379608154</v>
       </c>
       <c r="H1354" t="s">
         <v>8</v>
@@ -35599,7 +35599,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G1355" t="n">
-        <v>2.15556621551514</v>
+        <v>2.15556597709656</v>
       </c>
       <c r="H1355" t="s">
         <v>8</v>
@@ -35625,7 +35625,7 @@
         <v>2.67600011825562</v>
       </c>
       <c r="G1356" t="n">
-        <v>2.18496036529541</v>
+        <v>2.18496012687683</v>
       </c>
       <c r="H1356" t="s">
         <v>8</v>
@@ -35859,7 +35859,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G1365" t="n">
-        <v>2.35969185829163</v>
+        <v>2.35969161987305</v>
       </c>
       <c r="H1365" t="s">
         <v>8</v>
@@ -35989,7 +35989,7 @@
         <v>2.85400009155273</v>
       </c>
       <c r="G1370" t="n">
-        <v>2.33029747009277</v>
+        <v>2.33029723167419</v>
       </c>
       <c r="H1370" t="s">
         <v>8</v>
@@ -36041,7 +36041,7 @@
         <v>2.93400001525879</v>
       </c>
       <c r="G1372" t="n">
-        <v>2.39561748504639</v>
+        <v>2.39561772346497</v>
       </c>
       <c r="H1372" t="s">
         <v>8</v>
@@ -36119,7 +36119,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G1375" t="n">
-        <v>2.50666165351868</v>
+        <v>2.50666189193726</v>
       </c>
       <c r="H1375" t="s">
         <v>8</v>
@@ -36171,7 +36171,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G1377" t="n">
-        <v>2.61280727386475</v>
+        <v>2.61280703544617</v>
       </c>
       <c r="H1377" t="s">
         <v>8</v>
@@ -36197,7 +36197,7 @@
         <v>3.21000003814697</v>
       </c>
       <c r="G1378" t="n">
-        <v>2.62097239494324</v>
+        <v>2.62097215652466</v>
       </c>
       <c r="H1378" t="s">
         <v>8</v>
@@ -36249,7 +36249,7 @@
         <v>3.29800009727478</v>
       </c>
       <c r="G1380" t="n">
-        <v>2.69282484054565</v>
+        <v>2.69282460212708</v>
       </c>
       <c r="H1380" t="s">
         <v>8</v>
@@ -36275,7 +36275,7 @@
         <v>3.26999998092651</v>
       </c>
       <c r="G1381" t="n">
-        <v>2.66996240615845</v>
+        <v>2.66996216773987</v>
       </c>
       <c r="H1381" t="s">
         <v>8</v>
@@ -36301,7 +36301,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G1382" t="n">
-        <v>2.62913703918457</v>
+        <v>2.62913727760315</v>
       </c>
       <c r="H1382" t="s">
         <v>8</v>
@@ -36327,7 +36327,7 @@
         <v>3.25</v>
       </c>
       <c r="G1383" t="n">
-        <v>2.65363240242004</v>
+        <v>2.65363216400146</v>
       </c>
       <c r="H1383" t="s">
         <v>8</v>
@@ -36379,7 +36379,7 @@
         <v>3.25399994850159</v>
       </c>
       <c r="G1385" t="n">
-        <v>2.65689826011658</v>
+        <v>2.65689849853516</v>
       </c>
       <c r="H1385" t="s">
         <v>8</v>
@@ -36405,7 +36405,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G1386" t="n">
-        <v>2.59647727012634</v>
+        <v>2.59647703170776</v>
       </c>
       <c r="H1386" t="s">
         <v>8</v>
@@ -36535,7 +36535,7 @@
         <v>3.04999995231628</v>
       </c>
       <c r="G1391" t="n">
-        <v>2.49033164978027</v>
+        <v>2.49033188819885</v>
       </c>
       <c r="H1391" t="s">
         <v>8</v>
@@ -36561,7 +36561,7 @@
         <v>3.08400011062622</v>
       </c>
       <c r="G1392" t="n">
-        <v>2.51809310913086</v>
+        <v>2.51809287071228</v>
       </c>
       <c r="H1392" t="s">
         <v>8</v>
@@ -36613,7 +36613,7 @@
         <v>3.04999995231628</v>
       </c>
       <c r="G1394" t="n">
-        <v>2.49033164978027</v>
+        <v>2.49033188819885</v>
       </c>
       <c r="H1394" t="s">
         <v>8</v>
@@ -36639,7 +36639,7 @@
         <v>3.08400011062622</v>
       </c>
       <c r="G1395" t="n">
-        <v>2.51809310913086</v>
+        <v>2.51809287071228</v>
       </c>
       <c r="H1395" t="s">
         <v>8</v>
@@ -36665,7 +36665,7 @@
         <v>3.08400011062622</v>
       </c>
       <c r="G1396" t="n">
-        <v>2.51809310913086</v>
+        <v>2.51809287071228</v>
       </c>
       <c r="H1396" t="s">
         <v>8</v>
@@ -36743,7 +36743,7 @@
         <v>3.28999996185303</v>
       </c>
       <c r="G1399" t="n">
-        <v>2.68629217147827</v>
+        <v>2.68629240989685</v>
       </c>
       <c r="H1399" t="s">
         <v>8</v>
@@ -36769,7 +36769,7 @@
         <v>3.21399998664856</v>
       </c>
       <c r="G1400" t="n">
-        <v>2.62423801422119</v>
+        <v>2.62423849105835</v>
       </c>
       <c r="H1400" t="s">
         <v>8</v>
@@ -36795,7 +36795,7 @@
         <v>3.20199990272522</v>
       </c>
       <c r="G1401" t="n">
-        <v>2.61444020271301</v>
+        <v>2.61444044113159</v>
       </c>
       <c r="H1401" t="s">
         <v>8</v>
@@ -36821,7 +36821,7 @@
         <v>3.04999995231628</v>
       </c>
       <c r="G1402" t="n">
-        <v>2.49033164978027</v>
+        <v>2.49033188819885</v>
       </c>
       <c r="H1402" t="s">
         <v>8</v>
@@ -36847,7 +36847,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G1403" t="n">
-        <v>2.54748702049255</v>
+        <v>2.54748725891113</v>
       </c>
       <c r="H1403" t="s">
         <v>8</v>
@@ -36873,7 +36873,7 @@
         <v>3.14800000190735</v>
       </c>
       <c r="G1404" t="n">
-        <v>2.57034921646118</v>
+        <v>2.5703489780426</v>
       </c>
       <c r="H1404" t="s">
         <v>8</v>
@@ -36925,7 +36925,7 @@
         <v>3.10400009155273</v>
       </c>
       <c r="G1406" t="n">
-        <v>2.53442335128784</v>
+        <v>2.53442311286926</v>
       </c>
       <c r="H1406" t="s">
         <v>8</v>
@@ -37081,7 +37081,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G1412" t="n">
-        <v>2.40051674842834</v>
+        <v>2.40051651000977</v>
       </c>
       <c r="H1412" t="s">
         <v>8</v>
@@ -37185,7 +37185,7 @@
         <v>3.09400010108948</v>
       </c>
       <c r="G1416" t="n">
-        <v>2.52625799179077</v>
+        <v>2.52625823020935</v>
       </c>
       <c r="H1416" t="s">
         <v>8</v>
@@ -37211,7 +37211,7 @@
         <v>3.08200001716614</v>
       </c>
       <c r="G1417" t="n">
-        <v>2.51645970344543</v>
+        <v>2.51645994186401</v>
       </c>
       <c r="H1417" t="s">
         <v>8</v>
@@ -37237,7 +37237,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G1418" t="n">
-        <v>2.54748702049255</v>
+        <v>2.54748725891113</v>
       </c>
       <c r="H1418" t="s">
         <v>8</v>
@@ -37289,7 +37289,7 @@
         <v>3.14400005340576</v>
       </c>
       <c r="G1420" t="n">
-        <v>2.56708288192749</v>
+        <v>2.56708312034607</v>
       </c>
       <c r="H1420" t="s">
         <v>8</v>
@@ -37341,7 +37341,7 @@
         <v>3.1340000629425</v>
       </c>
       <c r="G1422" t="n">
-        <v>2.55891823768616</v>
+        <v>2.55891799926758</v>
       </c>
       <c r="H1422" t="s">
         <v>8</v>
@@ -37393,7 +37393,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G1424" t="n">
-        <v>2.69445729255676</v>
+        <v>2.69445705413818</v>
       </c>
       <c r="H1424" t="s">
         <v>8</v>
@@ -37549,7 +37549,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G1430" t="n">
-        <v>2.77610778808594</v>
+        <v>2.77610802650452</v>
       </c>
       <c r="H1430" t="s">
         <v>8</v>
@@ -37653,7 +37653,7 @@
         <v>3.33800005912781</v>
       </c>
       <c r="G1434" t="n">
-        <v>2.72548460960388</v>
+        <v>2.72548484802246</v>
       </c>
       <c r="H1434" t="s">
         <v>8</v>
@@ -37679,7 +37679,7 @@
         <v>3.32999992370605</v>
       </c>
       <c r="G1435" t="n">
-        <v>2.71895241737366</v>
+        <v>2.71895265579224</v>
       </c>
       <c r="H1435" t="s">
         <v>8</v>
@@ -37731,7 +37731,7 @@
         <v>3.32200002670288</v>
       </c>
       <c r="G1437" t="n">
-        <v>2.71242046356201</v>
+        <v>2.71242022514343</v>
       </c>
       <c r="H1437" t="s">
         <v>8</v>
@@ -37757,7 +37757,7 @@
         <v>3.36999988555908</v>
       </c>
       <c r="G1438" t="n">
-        <v>2.75161266326904</v>
+        <v>2.75161242485046</v>
       </c>
       <c r="H1438" t="s">
         <v>8</v>
@@ -37783,7 +37783,7 @@
         <v>3.32800006866455</v>
       </c>
       <c r="G1439" t="n">
-        <v>2.71731948852539</v>
+        <v>2.71731996536255</v>
       </c>
       <c r="H1439" t="s">
         <v>8</v>
@@ -37809,7 +37809,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G1440" t="n">
-        <v>2.69445729255676</v>
+        <v>2.69445705413818</v>
       </c>
       <c r="H1440" t="s">
         <v>8</v>
@@ -37835,7 +37835,7 @@
         <v>3.32200002670288</v>
       </c>
       <c r="G1441" t="n">
-        <v>2.71242046356201</v>
+        <v>2.71242022514343</v>
       </c>
       <c r="H1441" t="s">
         <v>8</v>
@@ -37861,7 +37861,7 @@
         <v>3.33800005912781</v>
       </c>
       <c r="G1442" t="n">
-        <v>2.72548460960388</v>
+        <v>2.72548484802246</v>
       </c>
       <c r="H1442" t="s">
         <v>8</v>
@@ -37887,7 +37887,7 @@
         <v>3.35400009155273</v>
       </c>
       <c r="G1443" t="n">
-        <v>2.73854851722717</v>
+        <v>2.73854875564575</v>
       </c>
       <c r="H1443" t="s">
         <v>8</v>
@@ -37991,7 +37991,7 @@
         <v>3.25</v>
       </c>
       <c r="G1447" t="n">
-        <v>2.65363240242004</v>
+        <v>2.65363216400146</v>
       </c>
       <c r="H1447" t="s">
         <v>8</v>
@@ -38043,7 +38043,7 @@
         <v>3.28399991989136</v>
       </c>
       <c r="G1449" t="n">
-        <v>2.68139362335205</v>
+        <v>2.68139314651489</v>
       </c>
       <c r="H1449" t="s">
         <v>8</v>
@@ -38095,7 +38095,7 @@
         <v>3.27600002288818</v>
       </c>
       <c r="G1451" t="n">
-        <v>2.67486143112183</v>
+        <v>2.67486166954041</v>
       </c>
       <c r="H1451" t="s">
         <v>8</v>
@@ -38121,7 +38121,7 @@
         <v>3.37199997901917</v>
       </c>
       <c r="G1452" t="n">
-        <v>2.75324535369873</v>
+        <v>2.75324583053589</v>
       </c>
       <c r="H1452" t="s">
         <v>8</v>
@@ -38173,7 +38173,7 @@
         <v>3.25</v>
       </c>
       <c r="G1454" t="n">
-        <v>2.65363240242004</v>
+        <v>2.65363216400146</v>
       </c>
       <c r="H1454" t="s">
         <v>8</v>
@@ -38225,7 +38225,7 @@
         <v>3.36199998855591</v>
       </c>
       <c r="G1456" t="n">
-        <v>2.7450807094574</v>
+        <v>2.74508047103882</v>
       </c>
       <c r="H1456" t="s">
         <v>8</v>
@@ -38251,7 +38251,7 @@
         <v>3.36999988555908</v>
       </c>
       <c r="G1457" t="n">
-        <v>2.75161266326904</v>
+        <v>2.75161242485046</v>
       </c>
       <c r="H1457" t="s">
         <v>8</v>
@@ -38277,7 +38277,7 @@
         <v>3.37800002098083</v>
       </c>
       <c r="G1458" t="n">
-        <v>2.75814437866211</v>
+        <v>2.75814461708069</v>
       </c>
       <c r="H1458" t="s">
         <v>8</v>
@@ -38407,7 +38407,7 @@
         <v>3.37400007247925</v>
       </c>
       <c r="G1463" t="n">
-        <v>2.75487875938416</v>
+        <v>2.75487852096558</v>
       </c>
       <c r="H1463" t="s">
         <v>8</v>
@@ -38459,7 +38459,7 @@
         <v>3.40199995040894</v>
       </c>
       <c r="G1465" t="n">
-        <v>2.7777407169342</v>
+        <v>2.77774095535278</v>
       </c>
       <c r="H1465" t="s">
         <v>8</v>
@@ -38537,7 +38537,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G1468" t="n">
-        <v>2.75977778434753</v>
+        <v>2.75977802276611</v>
       </c>
       <c r="H1468" t="s">
         <v>8</v>
@@ -38563,7 +38563,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G1469" t="n">
-        <v>2.75977778434753</v>
+        <v>2.75977802276611</v>
       </c>
       <c r="H1469" t="s">
         <v>8</v>
@@ -38693,7 +38693,7 @@
         <v>3.51399993896484</v>
       </c>
       <c r="G1474" t="n">
-        <v>2.86918878555298</v>
+        <v>2.86918902397156</v>
       </c>
       <c r="H1474" t="s">
         <v>8</v>
@@ -38745,7 +38745,7 @@
         <v>3.63800001144409</v>
       </c>
       <c r="G1476" t="n">
-        <v>2.97043514251709</v>
+        <v>2.97043538093567</v>
       </c>
       <c r="H1476" t="s">
         <v>8</v>
@@ -38771,7 +38771,7 @@
         <v>3.75</v>
       </c>
       <c r="G1477" t="n">
-        <v>3.06188321113586</v>
+        <v>3.06188344955444</v>
       </c>
       <c r="H1477" t="s">
         <v>8</v>
@@ -38823,7 +38823,7 @@
         <v>3.73600006103516</v>
       </c>
       <c r="G1479" t="n">
-        <v>3.05045247077942</v>
+        <v>3.050452709198</v>
       </c>
       <c r="H1479" t="s">
         <v>8</v>
@@ -38849,7 +38849,7 @@
         <v>3.72399997711182</v>
       </c>
       <c r="G1480" t="n">
-        <v>3.04065442085266</v>
+        <v>3.04065465927124</v>
       </c>
       <c r="H1480" t="s">
         <v>8</v>
@@ -38875,7 +38875,7 @@
         <v>3.74399995803833</v>
       </c>
       <c r="G1481" t="n">
-        <v>3.05698418617249</v>
+        <v>3.05698442459106</v>
       </c>
       <c r="H1481" t="s">
         <v>8</v>
@@ -38979,7 +38979,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G1485" t="n">
-        <v>3.07004857063293</v>
+        <v>3.07004833221436</v>
       </c>
       <c r="H1485" t="s">
         <v>8</v>
@@ -39083,7 +39083,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G1489" t="n">
-        <v>3.35582423210144</v>
+        <v>3.35582447052002</v>
       </c>
       <c r="H1489" t="s">
         <v>8</v>
@@ -39109,7 +39109,7 @@
         <v>3.85199999809265</v>
       </c>
       <c r="G1490" t="n">
-        <v>3.14516711235046</v>
+        <v>3.14516663551331</v>
       </c>
       <c r="H1490" t="s">
         <v>8</v>
@@ -39135,7 +39135,7 @@
         <v>3.85199999809265</v>
       </c>
       <c r="G1491" t="n">
-        <v>3.14516711235046</v>
+        <v>3.14516663551331</v>
       </c>
       <c r="H1491" t="s">
         <v>8</v>
@@ -39213,7 +39213,7 @@
         <v>3.9539999961853</v>
       </c>
       <c r="G1494" t="n">
-        <v>3.22845005989075</v>
+        <v>3.22844982147217</v>
       </c>
       <c r="H1494" t="s">
         <v>8</v>
@@ -39239,7 +39239,7 @@
         <v>4.09600019454956</v>
       </c>
       <c r="G1495" t="n">
-        <v>3.34439325332642</v>
+        <v>3.344393491745</v>
       </c>
       <c r="H1495" t="s">
         <v>8</v>
@@ -39369,7 +39369,7 @@
         <v>3.97399997711182</v>
       </c>
       <c r="G1500" t="n">
-        <v>3.24478006362915</v>
+        <v>3.24477982521057</v>
       </c>
       <c r="H1500" t="s">
         <v>8</v>
@@ -39421,7 +39421,7 @@
         <v>3.99000000953674</v>
       </c>
       <c r="G1502" t="n">
-        <v>3.25784397125244</v>
+        <v>3.25784373283386</v>
       </c>
       <c r="H1502" t="s">
         <v>8</v>
@@ -39499,7 +39499,7 @@
         <v>3.90599989891052</v>
       </c>
       <c r="G1505" t="n">
-        <v>3.18925786018372</v>
+        <v>3.18925762176514</v>
       </c>
       <c r="H1505" t="s">
         <v>8</v>
@@ -39551,7 +39551,7 @@
         <v>3.9760000705719</v>
       </c>
       <c r="G1507" t="n">
-        <v>3.246413230896</v>
+        <v>3.24641299247742</v>
       </c>
       <c r="H1507" t="s">
         <v>8</v>
@@ -39577,7 +39577,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G1508" t="n">
-        <v>3.22518372535706</v>
+        <v>3.22518396377563</v>
       </c>
       <c r="H1508" t="s">
         <v>8</v>
@@ -39603,7 +39603,7 @@
         <v>4.03399991989136</v>
       </c>
       <c r="G1509" t="n">
-        <v>3.29376983642578</v>
+        <v>3.29377007484436</v>
       </c>
       <c r="H1509" t="s">
         <v>8</v>
@@ -39681,7 +39681,7 @@
         <v>4.04199981689453</v>
       </c>
       <c r="G1512" t="n">
-        <v>3.30030202865601</v>
+        <v>3.30030179023743</v>
       </c>
       <c r="H1512" t="s">
         <v>8</v>
@@ -39707,7 +39707,7 @@
         <v>3.99000000953674</v>
       </c>
       <c r="G1513" t="n">
-        <v>3.25784397125244</v>
+        <v>3.25784373283386</v>
       </c>
       <c r="H1513" t="s">
         <v>8</v>
@@ -39759,7 +39759,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G1515" t="n">
-        <v>3.22518372535706</v>
+        <v>3.22518396377563</v>
       </c>
       <c r="H1515" t="s">
         <v>8</v>
@@ -39837,7 +39837,7 @@
         <v>4.00799989700317</v>
       </c>
       <c r="G1518" t="n">
-        <v>3.272540807724</v>
+        <v>3.27254104614258</v>
       </c>
       <c r="H1518" t="s">
         <v>8</v>
@@ -39863,7 +39863,7 @@
         <v>3.94600009918213</v>
       </c>
       <c r="G1519" t="n">
-        <v>3.22191786766052</v>
+        <v>3.2219181060791</v>
       </c>
       <c r="H1519" t="s">
         <v>8</v>
@@ -39889,7 +39889,7 @@
         <v>4.03000020980835</v>
       </c>
       <c r="G1520" t="n">
-        <v>3.29050445556641</v>
+        <v>3.29050421714783</v>
       </c>
       <c r="H1520" t="s">
         <v>8</v>
@@ -39941,7 +39941,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G1522" t="n">
-        <v>3.372154712677</v>
+        <v>3.37215423583984</v>
       </c>
       <c r="H1522" t="s">
         <v>8</v>
@@ -40019,7 +40019,7 @@
         <v>4.15799999237061</v>
       </c>
       <c r="G1525" t="n">
-        <v>3.39501595497131</v>
+        <v>3.39501643180847</v>
       </c>
       <c r="H1525" t="s">
         <v>8</v>
@@ -40097,7 +40097,7 @@
         <v>4.21199989318848</v>
       </c>
       <c r="G1528" t="n">
-        <v>3.43910717964172</v>
+        <v>3.4391074180603</v>
       </c>
       <c r="H1528" t="s">
         <v>8</v>
@@ -40123,7 +40123,7 @@
         <v>4.25600004196167</v>
       </c>
       <c r="G1529" t="n">
-        <v>3.47503328323364</v>
+        <v>3.47503352165222</v>
       </c>
       <c r="H1529" t="s">
         <v>8</v>
@@ -40149,7 +40149,7 @@
         <v>4.34999990463257</v>
       </c>
       <c r="G1530" t="n">
-        <v>3.55178451538086</v>
+        <v>3.55178475379944</v>
       </c>
       <c r="H1530" t="s">
         <v>8</v>
@@ -40227,7 +40227,7 @@
         <v>4.46600008010864</v>
       </c>
       <c r="G1533" t="n">
-        <v>3.6464991569519</v>
+        <v>3.64649891853333</v>
       </c>
       <c r="H1533" t="s">
         <v>8</v>
@@ -40253,7 +40253,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G1534" t="n">
-        <v>3.71508526802063</v>
+        <v>3.71508550643921</v>
       </c>
       <c r="H1534" t="s">
         <v>8</v>
@@ -40279,7 +40279,7 @@
         <v>4.61999988555908</v>
       </c>
       <c r="G1535" t="n">
-        <v>3.77224016189575</v>
+        <v>3.77224063873291</v>
       </c>
       <c r="H1535" t="s">
         <v>8</v>
@@ -40305,7 +40305,7 @@
         <v>4.67000007629395</v>
       </c>
       <c r="G1536" t="n">
-        <v>3.81306529045105</v>
+        <v>3.81306576728821</v>
       </c>
       <c r="H1536" t="s">
         <v>8</v>
@@ -40357,7 +40357,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G1538" t="n">
-        <v>3.83756065368652</v>
+        <v>3.83756041526794</v>
       </c>
       <c r="H1538" t="s">
         <v>8</v>
@@ -40383,7 +40383,7 @@
         <v>4.46799993515015</v>
       </c>
       <c r="G1539" t="n">
-        <v>3.64813232421875</v>
+        <v>3.64813184738159</v>
       </c>
       <c r="H1539" t="s">
         <v>8</v>
@@ -40409,7 +40409,7 @@
         <v>4.46799993515015</v>
       </c>
       <c r="G1540" t="n">
-        <v>3.64813232421875</v>
+        <v>3.64813184738159</v>
       </c>
       <c r="H1540" t="s">
         <v>8</v>
@@ -40435,7 +40435,7 @@
         <v>4.41599988937378</v>
       </c>
       <c r="G1541" t="n">
-        <v>3.60567402839661</v>
+        <v>3.60567378997803</v>
       </c>
       <c r="H1541" t="s">
         <v>8</v>
@@ -40461,7 +40461,7 @@
         <v>4.15799999237061</v>
       </c>
       <c r="G1542" t="n">
-        <v>3.39501595497131</v>
+        <v>3.39501643180847</v>
       </c>
       <c r="H1542" t="s">
         <v>8</v>
@@ -40487,7 +40487,7 @@
         <v>4.16800022125244</v>
       </c>
       <c r="G1543" t="n">
-        <v>3.40318155288696</v>
+        <v>3.40318179130554</v>
       </c>
       <c r="H1543" t="s">
         <v>8</v>
@@ -40513,7 +40513,7 @@
         <v>4.34200000762939</v>
       </c>
       <c r="G1544" t="n">
-        <v>3.54525303840637</v>
+        <v>3.54525256156921</v>
       </c>
       <c r="H1544" t="s">
         <v>8</v>
@@ -40539,7 +40539,7 @@
         <v>4.38800001144409</v>
       </c>
       <c r="G1545" t="n">
-        <v>3.58281183242798</v>
+        <v>3.5828115940094</v>
       </c>
       <c r="H1545" t="s">
         <v>8</v>
@@ -40565,7 +40565,7 @@
         <v>4.32399988174438</v>
       </c>
       <c r="G1546" t="n">
-        <v>3.53055548667908</v>
+        <v>3.53055596351624</v>
       </c>
       <c r="H1546" t="s">
         <v>8</v>
@@ -40617,7 +40617,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G1548" t="n">
-        <v>3.46196937561035</v>
+        <v>3.46196961402893</v>
       </c>
       <c r="H1548" t="s">
         <v>8</v>
@@ -40643,7 +40643,7 @@
         <v>4.22599983215332</v>
       </c>
       <c r="G1549" t="n">
-        <v>3.45053839683533</v>
+        <v>3.45053815841675</v>
       </c>
       <c r="H1549" t="s">
         <v>8</v>
@@ -40669,7 +40669,7 @@
         <v>3.99799990653992</v>
       </c>
       <c r="G1550" t="n">
-        <v>3.26437616348267</v>
+        <v>3.26437592506409</v>
       </c>
       <c r="H1550" t="s">
         <v>8</v>
@@ -40695,7 +40695,7 @@
         <v>3.93400001525879</v>
       </c>
       <c r="G1551" t="n">
-        <v>3.21211981773376</v>
+        <v>3.21212005615234</v>
       </c>
       <c r="H1551" t="s">
         <v>8</v>
@@ -40799,7 +40799,7 @@
         <v>4.07600021362305</v>
       </c>
       <c r="G1555" t="n">
-        <v>3.32806324958801</v>
+        <v>3.32806348800659</v>
       </c>
       <c r="H1555" t="s">
         <v>8</v>
@@ -40877,7 +40877,7 @@
         <v>3.99399995803833</v>
       </c>
       <c r="G1558" t="n">
-        <v>3.26110982894897</v>
+        <v>3.26111006736755</v>
       </c>
       <c r="H1558" t="s">
         <v>8</v>
@@ -40903,7 +40903,7 @@
         <v>4.08400011062622</v>
       </c>
       <c r="G1559" t="n">
-        <v>3.33459496498108</v>
+        <v>3.33459520339966</v>
       </c>
       <c r="H1559" t="s">
         <v>8</v>
@@ -40955,7 +40955,7 @@
         <v>3.97000002861023</v>
       </c>
       <c r="G1561" t="n">
-        <v>3.24151396751404</v>
+        <v>3.24151372909546</v>
       </c>
       <c r="H1561" t="s">
         <v>8</v>
@@ -41059,7 +41059,7 @@
         <v>3.49399995803833</v>
       </c>
       <c r="G1565" t="n">
-        <v>2.85285878181458</v>
+        <v>2.85285902023315</v>
       </c>
       <c r="H1565" t="s">
         <v>8</v>
@@ -41085,7 +41085,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G1566" t="n">
-        <v>2.54748702049255</v>
+        <v>2.54748725891113</v>
       </c>
       <c r="H1566" t="s">
         <v>8</v>
@@ -41137,7 +41137,7 @@
         <v>2.76799988746643</v>
       </c>
       <c r="G1568" t="n">
-        <v>2.2600781917572</v>
+        <v>2.26007843017578</v>
       </c>
       <c r="H1568" t="s">
         <v>8</v>
@@ -41189,7 +41189,7 @@
         <v>2.88199996948242</v>
       </c>
       <c r="G1570" t="n">
-        <v>2.35315942764282</v>
+        <v>2.3531596660614</v>
       </c>
       <c r="H1570" t="s">
         <v>8</v>
@@ -41215,7 +41215,7 @@
         <v>2.69000005722046</v>
       </c>
       <c r="G1571" t="n">
-        <v>2.19639134407043</v>
+        <v>2.19639110565186</v>
       </c>
       <c r="H1571" t="s">
         <v>8</v>
@@ -41241,7 +41241,7 @@
         <v>2.65199995040894</v>
       </c>
       <c r="G1572" t="n">
-        <v>2.16536378860474</v>
+        <v>2.16536402702332</v>
       </c>
       <c r="H1572" t="s">
         <v>8</v>
@@ -41267,7 +41267,7 @@
         <v>2.85400009155273</v>
       </c>
       <c r="G1573" t="n">
-        <v>2.33029747009277</v>
+        <v>2.33029723167419</v>
       </c>
       <c r="H1573" t="s">
         <v>8</v>
@@ -41293,7 +41293,7 @@
         <v>3.00999999046326</v>
       </c>
       <c r="G1574" t="n">
-        <v>2.45767188072205</v>
+        <v>2.45767164230347</v>
       </c>
       <c r="H1574" t="s">
         <v>8</v>
@@ -41319,7 +41319,7 @@
         <v>3.03600001335144</v>
       </c>
       <c r="G1575" t="n">
-        <v>2.47890114784241</v>
+        <v>2.47890090942383</v>
       </c>
       <c r="H1575" t="s">
         <v>8</v>
@@ -41423,7 +41423,7 @@
         <v>3.14800000190735</v>
       </c>
       <c r="G1579" t="n">
-        <v>2.57034921646118</v>
+        <v>2.5703489780426</v>
       </c>
       <c r="H1579" t="s">
         <v>8</v>
@@ -41449,7 +41449,7 @@
         <v>3.13000011444092</v>
       </c>
       <c r="G1580" t="n">
-        <v>2.55565214157104</v>
+        <v>2.55565237998962</v>
       </c>
       <c r="H1580" t="s">
         <v>8</v>
@@ -41475,7 +41475,7 @@
         <v>3.07599997520447</v>
       </c>
       <c r="G1581" t="n">
-        <v>2.51156067848206</v>
+        <v>2.51156091690063</v>
       </c>
       <c r="H1581" t="s">
         <v>8</v>
@@ -41501,7 +41501,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G1582" t="n">
-        <v>2.50666165351868</v>
+        <v>2.50666189193726</v>
       </c>
       <c r="H1582" t="s">
         <v>8</v>
@@ -41579,7 +41579,7 @@
         <v>3.10400009155273</v>
       </c>
       <c r="G1585" t="n">
-        <v>2.53442335128784</v>
+        <v>2.53442311286926</v>
       </c>
       <c r="H1585" t="s">
         <v>8</v>
@@ -41631,7 +41631,7 @@
         <v>3.12400007247925</v>
       </c>
       <c r="G1587" t="n">
-        <v>2.55075287818909</v>
+        <v>2.55075311660767</v>
       </c>
       <c r="H1587" t="s">
         <v>8</v>
@@ -41683,7 +41683,7 @@
         <v>3.18799996376038</v>
       </c>
       <c r="G1589" t="n">
-        <v>2.60300922393799</v>
+        <v>2.60300898551941</v>
       </c>
       <c r="H1589" t="s">
         <v>8</v>
@@ -41709,7 +41709,7 @@
         <v>3.1340000629425</v>
       </c>
       <c r="G1590" t="n">
-        <v>2.55891823768616</v>
+        <v>2.55891799926758</v>
       </c>
       <c r="H1590" t="s">
         <v>8</v>
@@ -41735,7 +41735,7 @@
         <v>3.17000007629395</v>
       </c>
       <c r="G1591" t="n">
-        <v>2.58831238746643</v>
+        <v>2.58831214904785</v>
       </c>
       <c r="H1591" t="s">
         <v>8</v>
@@ -41761,7 +41761,7 @@
         <v>3.13599991798401</v>
       </c>
       <c r="G1592" t="n">
-        <v>2.56055092811584</v>
+        <v>2.56055068969727</v>
       </c>
       <c r="H1592" t="s">
         <v>8</v>
@@ -41891,7 +41891,7 @@
         <v>3.13599991798401</v>
       </c>
       <c r="G1597" t="n">
-        <v>2.56055092811584</v>
+        <v>2.56055068969727</v>
       </c>
       <c r="H1597" t="s">
         <v>8</v>
@@ -42073,7 +42073,7 @@
         <v>2.8840000629425</v>
       </c>
       <c r="G1604" t="n">
-        <v>2.50272512435913</v>
+        <v>2.50272488594055</v>
       </c>
       <c r="H1604" t="s">
         <v>8</v>
@@ -42125,7 +42125,7 @@
         <v>2.76999998092651</v>
       </c>
       <c r="G1606" t="n">
-        <v>2.40379595756531</v>
+        <v>2.40379619598389</v>
       </c>
       <c r="H1606" t="s">
         <v>8</v>
@@ -42177,7 +42177,7 @@
         <v>2.7960000038147</v>
       </c>
       <c r="G1608" t="n">
-        <v>2.42635869979858</v>
+        <v>2.42635893821716</v>
       </c>
       <c r="H1608" t="s">
         <v>8</v>
@@ -42333,7 +42333,7 @@
         <v>2.61400008201599</v>
       </c>
       <c r="G1614" t="n">
-        <v>2.26841998100281</v>
+        <v>2.26841974258423</v>
       </c>
       <c r="H1614" t="s">
         <v>8</v>
@@ -42463,7 +42463,7 @@
         <v>2.74200010299683</v>
       </c>
       <c r="G1619" t="n">
-        <v>2.37949776649475</v>
+        <v>2.37949800491333</v>
       </c>
       <c r="H1619" t="s">
         <v>8</v>
@@ -42489,7 +42489,7 @@
         <v>2.86199998855591</v>
       </c>
       <c r="G1620" t="n">
-        <v>2.48363327980042</v>
+        <v>2.48363351821899</v>
       </c>
       <c r="H1620" t="s">
         <v>8</v>
@@ -42619,7 +42619,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G1625" t="n">
-        <v>2.47321963310242</v>
+        <v>2.473219871521</v>
       </c>
       <c r="H1625" t="s">
         <v>8</v>
@@ -42671,7 +42671,7 @@
         <v>2.98399996757507</v>
       </c>
       <c r="G1627" t="n">
-        <v>2.58950448036194</v>
+        <v>2.58950471878052</v>
       </c>
       <c r="H1627" t="s">
         <v>8</v>
@@ -42723,7 +42723,7 @@
         <v>3.18199992179871</v>
       </c>
       <c r="G1629" t="n">
-        <v>2.76132822036743</v>
+        <v>2.76132798194885</v>
       </c>
       <c r="H1629" t="s">
         <v>8</v>
@@ -42749,7 +42749,7 @@
         <v>3.32399988174438</v>
       </c>
       <c r="G1630" t="n">
-        <v>2.88455510139465</v>
+        <v>2.88455533981323</v>
       </c>
       <c r="H1630" t="s">
         <v>8</v>
@@ -42983,7 +42983,7 @@
         <v>3.17199993133545</v>
       </c>
       <c r="G1639" t="n">
-        <v>2.75265002250671</v>
+        <v>2.75265026092529</v>
       </c>
       <c r="H1639" t="s">
         <v>8</v>
@@ -43035,7 +43035,7 @@
         <v>2.91000008583069</v>
       </c>
       <c r="G1641" t="n">
-        <v>2.52528738975525</v>
+        <v>2.52528762817383</v>
       </c>
       <c r="H1641" t="s">
         <v>8</v>
@@ -43113,7 +43113,7 @@
         <v>2.86199998855591</v>
       </c>
       <c r="G1644" t="n">
-        <v>2.48363327980042</v>
+        <v>2.48363351821899</v>
       </c>
       <c r="H1644" t="s">
         <v>8</v>
@@ -43139,7 +43139,7 @@
         <v>2.9300000667572</v>
       </c>
       <c r="G1645" t="n">
-        <v>2.54264354705811</v>
+        <v>2.54264378547668</v>
       </c>
       <c r="H1645" t="s">
         <v>8</v>
@@ -43321,7 +43321,7 @@
         <v>2.86800003051758</v>
       </c>
       <c r="G1652" t="n">
-        <v>2.48884010314941</v>
+        <v>2.48884034156799</v>
       </c>
       <c r="H1652" t="s">
         <v>8</v>
@@ -43347,7 +43347,7 @@
         <v>2.74000000953674</v>
       </c>
       <c r="G1653" t="n">
-        <v>2.37776231765747</v>
+        <v>2.37776255607605</v>
       </c>
       <c r="H1653" t="s">
         <v>8</v>
@@ -43555,7 +43555,7 @@
         <v>2.73200011253357</v>
       </c>
       <c r="G1661" t="n">
-        <v>2.37082028388977</v>
+        <v>2.37082004547119</v>
       </c>
       <c r="H1661" t="s">
         <v>8</v>
@@ -43659,7 +43659,7 @@
         <v>2.6159999370575</v>
       </c>
       <c r="G1665" t="n">
-        <v>2.27015566825867</v>
+        <v>2.27015542984009</v>
       </c>
       <c r="H1665" t="s">
         <v>8</v>
@@ -43737,7 +43737,7 @@
         <v>2.50799989700317</v>
       </c>
       <c r="G1668" t="n">
-        <v>2.17643332481384</v>
+        <v>2.17643308639526</v>
       </c>
       <c r="H1668" t="s">
         <v>8</v>
@@ -43763,7 +43763,7 @@
         <v>2.56200003623962</v>
       </c>
       <c r="G1669" t="n">
-        <v>2.22329473495483</v>
+        <v>2.22329449653625</v>
       </c>
       <c r="H1669" t="s">
         <v>8</v>
@@ -43841,7 +43841,7 @@
         <v>2.56200003623962</v>
       </c>
       <c r="G1672" t="n">
-        <v>2.22329473495483</v>
+        <v>2.22329449653625</v>
       </c>
       <c r="H1672" t="s">
         <v>8</v>
@@ -43919,7 +43919,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G1675" t="n">
-        <v>2.36040639877319</v>
+        <v>2.36040616035461</v>
       </c>
       <c r="H1675" t="s">
         <v>8</v>
@@ -43945,7 +43945,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G1676" t="n">
-        <v>2.36040639877319</v>
+        <v>2.36040616035461</v>
       </c>
       <c r="H1676" t="s">
         <v>8</v>
@@ -44023,7 +44023,7 @@
         <v>2.73600006103516</v>
       </c>
       <c r="G1679" t="n">
-        <v>2.37429094314575</v>
+        <v>2.37429118156433</v>
       </c>
       <c r="H1679" t="s">
         <v>8</v>
@@ -44049,7 +44049,7 @@
         <v>2.74200010299683</v>
       </c>
       <c r="G1680" t="n">
-        <v>2.37949776649475</v>
+        <v>2.37949800491333</v>
       </c>
       <c r="H1680" t="s">
         <v>8</v>
@@ -44075,7 +44075,7 @@
         <v>2.73200011253357</v>
       </c>
       <c r="G1681" t="n">
-        <v>2.37082028388977</v>
+        <v>2.37082004547119</v>
       </c>
       <c r="H1681" t="s">
         <v>8</v>
@@ -44101,7 +44101,7 @@
         <v>2.76999998092651</v>
       </c>
       <c r="G1682" t="n">
-        <v>2.40379595756531</v>
+        <v>2.40379619598389</v>
       </c>
       <c r="H1682" t="s">
         <v>8</v>
@@ -44231,7 +44231,7 @@
         <v>2.74000000953674</v>
       </c>
       <c r="G1687" t="n">
-        <v>2.37776231765747</v>
+        <v>2.37776255607605</v>
       </c>
       <c r="H1687" t="s">
         <v>8</v>
@@ -44283,7 +44283,7 @@
         <v>2.5699999332428</v>
       </c>
       <c r="G1689" t="n">
-        <v>2.23023676872253</v>
+        <v>2.23023700714111</v>
       </c>
       <c r="H1689" t="s">
         <v>8</v>
@@ -44413,7 +44413,7 @@
         <v>2.57800006866455</v>
       </c>
       <c r="G1694" t="n">
-        <v>2.23717927932739</v>
+        <v>2.23717951774597</v>
       </c>
       <c r="H1694" t="s">
         <v>8</v>
@@ -44465,7 +44465,7 @@
         <v>2.53800010681152</v>
       </c>
       <c r="G1696" t="n">
-        <v>2.20246767997742</v>
+        <v>2.20246744155884</v>
       </c>
       <c r="H1696" t="s">
         <v>8</v>
@@ -44517,7 +44517,7 @@
         <v>2.57599997520447</v>
       </c>
       <c r="G1698" t="n">
-        <v>2.23544335365295</v>
+        <v>2.23544359207153</v>
       </c>
       <c r="H1698" t="s">
         <v>8</v>
@@ -44543,7 +44543,7 @@
         <v>2.50999999046326</v>
       </c>
       <c r="G1699" t="n">
-        <v>2.17816925048828</v>
+        <v>2.1781690120697</v>
       </c>
       <c r="H1699" t="s">
         <v>8</v>
@@ -44595,7 +44595,7 @@
         <v>2.46799993515015</v>
       </c>
       <c r="G1701" t="n">
-        <v>2.14172148704529</v>
+        <v>2.14172172546387</v>
       </c>
       <c r="H1701" t="s">
         <v>8</v>
@@ -44673,7 +44673,7 @@
         <v>2.52800011634827</v>
       </c>
       <c r="G1704" t="n">
-        <v>2.1937894821167</v>
+        <v>2.19378972053528</v>
       </c>
       <c r="H1704" t="s">
         <v>8</v>
@@ -45037,7 +45037,7 @@
         <v>2.41799998283386</v>
       </c>
       <c r="G1718" t="n">
-        <v>2.09833168983459</v>
+        <v>2.09833192825317</v>
       </c>
       <c r="H1718" t="s">
         <v>8</v>
@@ -45167,7 +45167,7 @@
         <v>2.74200010299683</v>
       </c>
       <c r="G1723" t="n">
-        <v>2.37949776649475</v>
+        <v>2.37949800491333</v>
       </c>
       <c r="H1723" t="s">
         <v>8</v>
@@ -45193,7 +45193,7 @@
         <v>2.60599994659424</v>
       </c>
       <c r="G1724" t="n">
-        <v>2.26147723197937</v>
+        <v>2.26147747039795</v>
       </c>
       <c r="H1724" t="s">
         <v>8</v>
@@ -45245,7 +45245,7 @@
         <v>2.67799997329712</v>
       </c>
       <c r="G1726" t="n">
-        <v>2.32395911216736</v>
+        <v>2.32395887374878</v>
       </c>
       <c r="H1726" t="s">
         <v>8</v>
@@ -45479,7 +45479,7 @@
         <v>2.9300000667572</v>
       </c>
       <c r="G1735" t="n">
-        <v>2.54264354705811</v>
+        <v>2.54264378547668</v>
       </c>
       <c r="H1735" t="s">
         <v>8</v>
@@ -45557,7 +45557,7 @@
         <v>3.03800010681152</v>
       </c>
       <c r="G1738" t="n">
-        <v>2.63636565208435</v>
+        <v>2.63636589050293</v>
       </c>
       <c r="H1738" t="s">
         <v>8</v>
@@ -45583,7 +45583,7 @@
         <v>3.14199995994568</v>
       </c>
       <c r="G1739" t="n">
-        <v>2.72661638259888</v>
+        <v>2.72661662101746</v>
       </c>
       <c r="H1739" t="s">
         <v>8</v>
@@ -45609,7 +45609,7 @@
         <v>3.14199995994568</v>
       </c>
       <c r="G1740" t="n">
-        <v>2.72661638259888</v>
+        <v>2.72661662101746</v>
       </c>
       <c r="H1740" t="s">
         <v>8</v>
@@ -45635,7 +45635,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G1741" t="n">
-        <v>2.70752477645874</v>
+        <v>2.70752453804016</v>
       </c>
       <c r="H1741" t="s">
         <v>8</v>
@@ -45661,7 +45661,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G1742" t="n">
-        <v>2.67281293869019</v>
+        <v>2.67281317710876</v>
       </c>
       <c r="H1742" t="s">
         <v>8</v>
@@ -45817,7 +45817,7 @@
         <v>3.17199993133545</v>
       </c>
       <c r="G1748" t="n">
-        <v>2.75265002250671</v>
+        <v>2.75265026092529</v>
       </c>
       <c r="H1748" t="s">
         <v>8</v>
@@ -45869,7 +45869,7 @@
         <v>3.07399988174438</v>
       </c>
       <c r="G1750" t="n">
-        <v>2.66760611534119</v>
+        <v>2.66760635375977</v>
       </c>
       <c r="H1750" t="s">
         <v>8</v>
@@ -45921,7 +45921,7 @@
         <v>3.08800005912781</v>
       </c>
       <c r="G1752" t="n">
-        <v>2.67975544929504</v>
+        <v>2.67975568771362</v>
       </c>
       <c r="H1752" t="s">
         <v>8</v>
@@ -45999,7 +45999,7 @@
         <v>3.07599997520447</v>
       </c>
       <c r="G1755" t="n">
-        <v>2.66934156417847</v>
+        <v>2.66934180259705</v>
       </c>
       <c r="H1755" t="s">
         <v>8</v>
@@ -46051,7 +46051,7 @@
         <v>3.07599997520447</v>
       </c>
       <c r="G1757" t="n">
-        <v>2.66934156417847</v>
+        <v>2.66934180259705</v>
       </c>
       <c r="H1757" t="s">
         <v>8</v>
@@ -46103,7 +46103,7 @@
         <v>3.01200008392334</v>
       </c>
       <c r="G1759" t="n">
-        <v>2.61380314826965</v>
+        <v>2.61380290985107</v>
       </c>
       <c r="H1759" t="s">
         <v>8</v>
@@ -46155,7 +46155,7 @@
         <v>3.03200006484985</v>
       </c>
       <c r="G1761" t="n">
-        <v>2.63115859031677</v>
+        <v>2.63115882873535</v>
       </c>
       <c r="H1761" t="s">
         <v>8</v>
@@ -46233,7 +46233,7 @@
         <v>3.01399993896484</v>
       </c>
       <c r="G1764" t="n">
-        <v>2.61553835868835</v>
+        <v>2.61553812026978</v>
       </c>
       <c r="H1764" t="s">
         <v>8</v>
@@ -46311,7 +46311,7 @@
         <v>3.07399988174438</v>
       </c>
       <c r="G1767" t="n">
-        <v>2.66760611534119</v>
+        <v>2.66760635375977</v>
       </c>
       <c r="H1767" t="s">
         <v>8</v>
@@ -46415,7 +46415,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G1771" t="n">
-        <v>2.67281293869019</v>
+        <v>2.67281317710876</v>
       </c>
       <c r="H1771" t="s">
         <v>8</v>
@@ -46441,7 +46441,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G1772" t="n">
-        <v>2.62074518203735</v>
+        <v>2.62074542045593</v>
       </c>
       <c r="H1772" t="s">
         <v>8</v>
@@ -46545,7 +46545,7 @@
         <v>3.10400009155273</v>
       </c>
       <c r="G1776" t="n">
-        <v>2.69364047050476</v>
+        <v>2.69364023208618</v>
       </c>
       <c r="H1776" t="s">
         <v>8</v>
@@ -46571,7 +46571,7 @@
         <v>3.13800001144409</v>
       </c>
       <c r="G1777" t="n">
-        <v>2.72314500808716</v>
+        <v>2.72314524650574</v>
       </c>
       <c r="H1777" t="s">
         <v>8</v>
@@ -46623,7 +46623,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G1779" t="n">
-        <v>2.66413497924805</v>
+        <v>2.66413474082947</v>
       </c>
       <c r="H1779" t="s">
         <v>8</v>
@@ -46649,7 +46649,7 @@
         <v>3.06200003623962</v>
       </c>
       <c r="G1780" t="n">
-        <v>2.65719246864319</v>
+        <v>2.65719270706177</v>
       </c>
       <c r="H1780" t="s">
         <v>8</v>
@@ -46961,7 +46961,7 @@
         <v>3.30200004577637</v>
       </c>
       <c r="G1792" t="n">
-        <v>2.86546397209167</v>
+        <v>2.86546421051025</v>
       </c>
       <c r="H1792" t="s">
         <v>8</v>
@@ -47013,7 +47013,7 @@
         <v>3.37800002098083</v>
       </c>
       <c r="G1794" t="n">
-        <v>2.93141627311707</v>
+        <v>2.93141651153564</v>
       </c>
       <c r="H1794" t="s">
         <v>8</v>
@@ -47065,7 +47065,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G1796" t="n">
-        <v>2.98521971702576</v>
+        <v>2.98521995544434</v>
       </c>
       <c r="H1796" t="s">
         <v>8</v>
@@ -47169,7 +47169,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G1800" t="n">
-        <v>3.08935546875</v>
+        <v>3.08935523033142</v>
       </c>
       <c r="H1800" t="s">
         <v>8</v>
@@ -47247,7 +47247,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G1803" t="n">
-        <v>3.08935546875</v>
+        <v>3.08935523033142</v>
       </c>
       <c r="H1803" t="s">
         <v>8</v>
@@ -47299,7 +47299,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G1805" t="n">
-        <v>3.12406706809998</v>
+        <v>3.12406730651855</v>
       </c>
       <c r="H1805" t="s">
         <v>8</v>
@@ -47429,7 +47429,7 @@
         <v>3.63800001144409</v>
       </c>
       <c r="G1810" t="n">
-        <v>3.15704345703125</v>
+        <v>3.15704321861267</v>
       </c>
       <c r="H1810" t="s">
         <v>8</v>
@@ -47455,7 +47455,7 @@
         <v>3.68799996376038</v>
       </c>
       <c r="G1811" t="n">
-        <v>3.20043349266052</v>
+        <v>3.20043325424194</v>
       </c>
       <c r="H1811" t="s">
         <v>8</v>
@@ -47481,7 +47481,7 @@
         <v>3.64199995994568</v>
       </c>
       <c r="G1812" t="n">
-        <v>3.16051459312439</v>
+        <v>3.16051483154297</v>
       </c>
       <c r="H1812" t="s">
         <v>8</v>
@@ -47507,7 +47507,7 @@
         <v>3.70199990272522</v>
       </c>
       <c r="G1813" t="n">
-        <v>3.21258234977722</v>
+        <v>3.2125825881958</v>
       </c>
       <c r="H1813" t="s">
         <v>8</v>
@@ -47533,7 +47533,7 @@
         <v>3.73600006103516</v>
       </c>
       <c r="G1814" t="n">
-        <v>3.24208760261536</v>
+        <v>3.24208736419678</v>
       </c>
       <c r="H1814" t="s">
         <v>8</v>
@@ -47559,7 +47559,7 @@
         <v>3.75799989700317</v>
       </c>
       <c r="G1815" t="n">
-        <v>3.26117897033691</v>
+        <v>3.26117920875549</v>
       </c>
       <c r="H1815" t="s">
         <v>8</v>
@@ -47663,7 +47663,7 @@
         <v>3.78800010681152</v>
       </c>
       <c r="G1819" t="n">
-        <v>3.28721308708191</v>
+        <v>3.28721284866333</v>
       </c>
       <c r="H1819" t="s">
         <v>8</v>
@@ -47741,7 +47741,7 @@
         <v>3.74200010299683</v>
       </c>
       <c r="G1822" t="n">
-        <v>3.24729442596436</v>
+        <v>3.24729418754578</v>
       </c>
       <c r="H1822" t="s">
         <v>8</v>
@@ -47767,7 +47767,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G1823" t="n">
-        <v>3.34101629257202</v>
+        <v>3.34101605415344</v>
       </c>
       <c r="H1823" t="s">
         <v>8</v>
@@ -47819,7 +47819,7 @@
         <v>3.84200000762939</v>
       </c>
       <c r="G1825" t="n">
-        <v>3.33407378196716</v>
+        <v>3.33407402038574</v>
       </c>
       <c r="H1825" t="s">
         <v>8</v>
@@ -47845,7 +47845,7 @@
         <v>3.90599989891052</v>
       </c>
       <c r="G1826" t="n">
-        <v>3.38961315155029</v>
+        <v>3.38961291313171</v>
       </c>
       <c r="H1826" t="s">
         <v>8</v>
@@ -47897,7 +47897,7 @@
         <v>4.14200019836426</v>
       </c>
       <c r="G1828" t="n">
-        <v>3.59441304206848</v>
+        <v>3.5944128036499</v>
       </c>
       <c r="H1828" t="s">
         <v>8</v>
@@ -47949,7 +47949,7 @@
         <v>4.08799982070923</v>
       </c>
       <c r="G1830" t="n">
-        <v>3.54755187034607</v>
+        <v>3.54755163192749</v>
       </c>
       <c r="H1830" t="s">
         <v>8</v>
@@ -47975,7 +47975,7 @@
         <v>4.08799982070923</v>
       </c>
       <c r="G1831" t="n">
-        <v>3.54755187034607</v>
+        <v>3.54755163192749</v>
       </c>
       <c r="H1831" t="s">
         <v>8</v>
@@ -48001,7 +48001,7 @@
         <v>4.10400009155273</v>
       </c>
       <c r="G1832" t="n">
-        <v>3.56143665313721</v>
+        <v>3.56143689155579</v>
       </c>
       <c r="H1832" t="s">
         <v>8</v>
@@ -48079,7 +48079,7 @@
         <v>3.7039999961853</v>
       </c>
       <c r="G1835" t="n">
-        <v>3.21431803703308</v>
+        <v>3.21431827545166</v>
       </c>
       <c r="H1835" t="s">
         <v>8</v>
@@ -48235,7 +48235,7 @@
         <v>3.85199999809265</v>
       </c>
       <c r="G1841" t="n">
-        <v>3.34275221824646</v>
+        <v>3.34275197982788</v>
       </c>
       <c r="H1841" t="s">
         <v>8</v>
@@ -48287,7 +48287,7 @@
         <v>3.89800000190735</v>
       </c>
       <c r="G1843" t="n">
-        <v>3.38267087936401</v>
+        <v>3.38267064094543</v>
       </c>
       <c r="H1843" t="s">
         <v>8</v>
@@ -48313,7 +48313,7 @@
         <v>3.83400011062622</v>
       </c>
       <c r="G1844" t="n">
-        <v>3.32713150978088</v>
+        <v>3.32713174819946</v>
       </c>
       <c r="H1844" t="s">
         <v>8</v>
@@ -48417,7 +48417,7 @@
         <v>3.89800000190735</v>
       </c>
       <c r="G1848" t="n">
-        <v>3.38267087936401</v>
+        <v>3.38267064094543</v>
       </c>
       <c r="H1848" t="s">
         <v>8</v>
@@ -48495,7 +48495,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G1851" t="n">
-        <v>3.38440632820129</v>
+        <v>3.38440608978271</v>
       </c>
       <c r="H1851" t="s">
         <v>8</v>
@@ -48521,7 +48521,7 @@
         <v>3.8659999370575</v>
       </c>
       <c r="G1852" t="n">
-        <v>3.35490083694458</v>
+        <v>3.35490107536316</v>
       </c>
       <c r="H1852" t="s">
         <v>8</v>
@@ -48547,7 +48547,7 @@
         <v>3.8659999370575</v>
       </c>
       <c r="G1853" t="n">
-        <v>3.35490083694458</v>
+        <v>3.35490107536316</v>
       </c>
       <c r="H1853" t="s">
         <v>8</v>
@@ -71652,7 +71652,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="D2742" t="n">
-        <v>12.4300003051758</v>
+        <v>12.4099998474121</v>
       </c>
       <c r="E2742" t="n">
         <v>12.539999961853</v>
@@ -71664,6 +71664,32 @@
         <v>12.4099998474121</v>
       </c>
       <c r="H2742" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2743">
+      <c r="A2743" s="1" t="n">
+        <v>46310.2916666667</v>
+      </c>
+      <c r="B2743" t="n">
+        <v>1264604</v>
+      </c>
+      <c r="C2743" t="n">
+        <v>12.3500003814697</v>
+      </c>
+      <c r="D2743" t="n">
+        <v>11.8299999237061</v>
+      </c>
+      <c r="E2743" t="n">
+        <v>12.1599998474121</v>
+      </c>
+      <c r="F2743" t="n">
+        <v>12.0699996948242</v>
+      </c>
+      <c r="G2743" t="n">
+        <v>12.0699996948242</v>
+      </c>
+      <c r="H2743" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/MAIRE.MI.xlsx
+++ b/data/MAIRE.MI.xlsx
@@ -456,7 +456,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G3" t="n">
-        <v>1.66390860080719</v>
+        <v>1.66390895843506</v>
       </c>
       <c r="H3" t="n">
         <v>1131141</v>
@@ -514,7 +514,7 @@
         <v>2.33800005912781</v>
       </c>
       <c r="G5" t="n">
-        <v>1.63454568386078</v>
+        <v>1.63454580307007</v>
       </c>
       <c r="H5" t="n">
         <v>904707</v>
@@ -543,7 +543,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G6" t="n">
-        <v>1.60098779201508</v>
+        <v>1.60098803043365</v>
       </c>
       <c r="H6" t="n">
         <v>768222</v>
@@ -572,7 +572,7 @@
         <v>2.24600005149841</v>
       </c>
       <c r="G7" t="n">
-        <v>1.57022631168365</v>
+        <v>1.57022666931152</v>
       </c>
       <c r="H7" t="n">
         <v>508438</v>
@@ -601,7 +601,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G8" t="n">
-        <v>1.58001434803009</v>
+        <v>1.5800142288208</v>
       </c>
       <c r="H8" t="n">
         <v>688214</v>
@@ -630,7 +630,7 @@
         <v>2.28800010681152</v>
       </c>
       <c r="G9" t="n">
-        <v>1.59958958625793</v>
+        <v>1.59958982467651</v>
       </c>
       <c r="H9" t="n">
         <v>1057980</v>
@@ -659,7 +659,7 @@
         <v>2.24200010299683</v>
       </c>
       <c r="G10" t="n">
-        <v>1.56743013858795</v>
+        <v>1.56743025779724</v>
       </c>
       <c r="H10" t="n">
         <v>833088</v>
@@ -775,7 +775,7 @@
         <v>1.86600005626678</v>
       </c>
       <c r="G14" t="n">
-        <v>1.30456042289734</v>
+        <v>1.30456066131592</v>
       </c>
       <c r="H14" t="n">
         <v>1772928</v>
@@ -804,7 +804,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G15" t="n">
-        <v>1.3632869720459</v>
+        <v>1.36328673362732</v>
       </c>
       <c r="H15" t="n">
         <v>1900263</v>
@@ -891,7 +891,7 @@
         <v>2.05200004577637</v>
       </c>
       <c r="G18" t="n">
-        <v>1.43459689617157</v>
+        <v>1.43459713459015</v>
       </c>
       <c r="H18" t="n">
         <v>1219375</v>
@@ -949,7 +949,7 @@
         <v>2.18199992179871</v>
       </c>
       <c r="G20" t="n">
-        <v>1.52548265457153</v>
+        <v>1.52548277378082</v>
       </c>
       <c r="H20" t="n">
         <v>3293076</v>
@@ -1007,7 +1007,7 @@
         <v>2.15400004386902</v>
       </c>
       <c r="G22" t="n">
-        <v>1.50590753555298</v>
+        <v>1.5059072971344</v>
       </c>
       <c r="H22" t="n">
         <v>529660</v>
@@ -1065,7 +1065,7 @@
         <v>2.06399989128113</v>
       </c>
       <c r="G24" t="n">
-        <v>1.44298624992371</v>
+        <v>1.442986369133</v>
       </c>
       <c r="H24" t="n">
         <v>976931</v>
@@ -1094,7 +1094,7 @@
         <v>2.12199997901917</v>
       </c>
       <c r="G25" t="n">
-        <v>1.48353552818298</v>
+        <v>1.48353564739227</v>
       </c>
       <c r="H25" t="n">
         <v>326053</v>
@@ -1123,7 +1123,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G26" t="n">
-        <v>1.46815478801727</v>
+        <v>1.46815490722656</v>
       </c>
       <c r="H26" t="n">
         <v>1049740</v>
@@ -1181,7 +1181,7 @@
         <v>1.85500001907349</v>
       </c>
       <c r="G28" t="n">
-        <v>1.29687023162842</v>
+        <v>1.29686999320984</v>
       </c>
       <c r="H28" t="n">
         <v>1908033</v>
@@ -1210,7 +1210,7 @@
         <v>2.01600003242493</v>
       </c>
       <c r="G29" t="n">
-        <v>1.40942859649658</v>
+        <v>1.40942871570587</v>
       </c>
       <c r="H29" t="n">
         <v>1125595</v>
@@ -1297,7 +1297,7 @@
         <v>2.10999989509583</v>
       </c>
       <c r="G32" t="n">
-        <v>1.47514617443085</v>
+        <v>1.47514605522156</v>
       </c>
       <c r="H32" t="n">
         <v>1012139</v>
@@ -1326,7 +1326,7 @@
         <v>2.08400011062622</v>
       </c>
       <c r="G33" t="n">
-        <v>1.45696902275085</v>
+        <v>1.45696890354156</v>
       </c>
       <c r="H33" t="n">
         <v>436314</v>
@@ -1355,7 +1355,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G34" t="n">
-        <v>1.59399664402008</v>
+        <v>1.59399676322937</v>
       </c>
       <c r="H34" t="n">
         <v>2358446</v>
@@ -1442,7 +1442,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G37" t="n">
-        <v>1.58001434803009</v>
+        <v>1.5800142288208</v>
       </c>
       <c r="H37" t="n">
         <v>549717</v>
@@ -1500,7 +1500,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G39" t="n">
-        <v>1.46815478801727</v>
+        <v>1.46815490722656</v>
       </c>
       <c r="H39" t="n">
         <v>749979</v>
@@ -1529,7 +1529,7 @@
         <v>2.25399994850159</v>
       </c>
       <c r="G40" t="n">
-        <v>1.57581961154938</v>
+        <v>1.57581949234009</v>
       </c>
       <c r="H40" t="n">
         <v>570572</v>
@@ -1587,7 +1587,7 @@
         <v>2.38599991798401</v>
       </c>
       <c r="G42" t="n">
-        <v>1.66810369491577</v>
+        <v>1.6681033372879</v>
       </c>
       <c r="H42" t="n">
         <v>1693605</v>
@@ -1645,7 +1645,7 @@
         <v>2.3659999370575</v>
       </c>
       <c r="G44" t="n">
-        <v>1.65412104129791</v>
+        <v>1.6541211605072</v>
       </c>
       <c r="H44" t="n">
         <v>1399717</v>
@@ -1703,7 +1703,7 @@
         <v>2.47199988365173</v>
       </c>
       <c r="G46" t="n">
-        <v>1.72822785377502</v>
+        <v>1.72822797298431</v>
       </c>
       <c r="H46" t="n">
         <v>803965</v>
@@ -1732,7 +1732,7 @@
         <v>2.46399998664856</v>
       </c>
       <c r="G47" t="n">
-        <v>1.72263479232788</v>
+        <v>1.72263491153717</v>
       </c>
       <c r="H47" t="n">
         <v>939266</v>
@@ -1761,7 +1761,7 @@
         <v>2.44199991226196</v>
       </c>
       <c r="G48" t="n">
-        <v>1.70725429058075</v>
+        <v>1.70725417137146</v>
       </c>
       <c r="H48" t="n">
         <v>1290792</v>
@@ -1790,7 +1790,7 @@
         <v>2.58999991416931</v>
       </c>
       <c r="G49" t="n">
-        <v>1.81072425842285</v>
+        <v>1.81072402000427</v>
       </c>
       <c r="H49" t="n">
         <v>1826201</v>
@@ -1819,7 +1819,7 @@
         <v>2.50799989700317</v>
       </c>
       <c r="G50" t="n">
-        <v>1.75339603424072</v>
+        <v>1.75339663028717</v>
       </c>
       <c r="H50" t="n">
         <v>2307001</v>
@@ -1848,7 +1848,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G51" t="n">
-        <v>1.80373287200928</v>
+        <v>1.80373299121857</v>
       </c>
       <c r="H51" t="n">
         <v>1402511</v>
@@ -1877,7 +1877,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G52" t="n">
-        <v>1.81771552562714</v>
+        <v>1.81771528720856</v>
       </c>
       <c r="H52" t="n">
         <v>642693</v>
@@ -1906,7 +1906,7 @@
         <v>2.49799990653992</v>
       </c>
       <c r="G53" t="n">
-        <v>1.74640500545502</v>
+        <v>1.74640512466431</v>
       </c>
       <c r="H53" t="n">
         <v>1185560</v>
@@ -1935,7 +1935,7 @@
         <v>2.67000007629395</v>
       </c>
       <c r="G54" t="n">
-        <v>1.86665391921997</v>
+        <v>1.86665403842926</v>
       </c>
       <c r="H54" t="n">
         <v>3600932</v>
@@ -1964,7 +1964,7 @@
         <v>2.67199993133545</v>
       </c>
       <c r="G55" t="n">
-        <v>1.86805200576782</v>
+        <v>1.86805236339569</v>
       </c>
       <c r="H55" t="n">
         <v>2267726</v>
@@ -1993,7 +1993,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G56" t="n">
-        <v>1.90161001682281</v>
+        <v>1.90160989761353</v>
       </c>
       <c r="H56" t="n">
         <v>2144807</v>
@@ -2022,7 +2022,7 @@
         <v>2.69600009918213</v>
       </c>
       <c r="G57" t="n">
-        <v>1.88483119010925</v>
+        <v>1.88483130931854</v>
       </c>
       <c r="H57" t="n">
         <v>1641960</v>
@@ -2051,7 +2051,7 @@
         <v>2.68400001525879</v>
       </c>
       <c r="G58" t="n">
-        <v>1.87644171714783</v>
+        <v>1.87644159793854</v>
       </c>
       <c r="H58" t="n">
         <v>1329482</v>
@@ -2080,7 +2080,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G59" t="n">
-        <v>1.80373287200928</v>
+        <v>1.80373299121857</v>
       </c>
       <c r="H59" t="n">
         <v>2238766</v>
@@ -2109,7 +2109,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G60" t="n">
-        <v>1.80373287200928</v>
+        <v>1.80373299121857</v>
       </c>
       <c r="H60" t="n">
         <v>1591775</v>
@@ -2138,7 +2138,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G61" t="n">
-        <v>1.78275954723358</v>
+        <v>1.78275942802429</v>
       </c>
       <c r="H61" t="n">
         <v>855878</v>
@@ -2167,7 +2167,7 @@
         <v>2.61800003051758</v>
       </c>
       <c r="G62" t="n">
-        <v>1.8302994966507</v>
+        <v>1.83029985427856</v>
       </c>
       <c r="H62" t="n">
         <v>1143974</v>
@@ -2196,7 +2196,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G63" t="n">
-        <v>1.85267162322998</v>
+        <v>1.85267174243927</v>
       </c>
       <c r="H63" t="n">
         <v>1165028</v>
@@ -2225,7 +2225,7 @@
         <v>2.59200000762939</v>
       </c>
       <c r="G64" t="n">
-        <v>1.81212246417999</v>
+        <v>1.8121223449707</v>
       </c>
       <c r="H64" t="n">
         <v>733584</v>
@@ -2254,7 +2254,7 @@
         <v>2.63199996948242</v>
       </c>
       <c r="G65" t="n">
-        <v>1.84008717536926</v>
+        <v>1.84008753299713</v>
       </c>
       <c r="H65" t="n">
         <v>744372</v>
@@ -2312,7 +2312,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G67" t="n">
-        <v>1.74081206321716</v>
+        <v>1.74081218242645</v>
       </c>
       <c r="H67" t="n">
         <v>976847</v>
@@ -2341,7 +2341,7 @@
         <v>2.45199990272522</v>
       </c>
       <c r="G68" t="n">
-        <v>1.71424555778503</v>
+        <v>1.71424567699432</v>
       </c>
       <c r="H68" t="n">
         <v>683319</v>
@@ -2370,7 +2370,7 @@
         <v>2.54399991035461</v>
       </c>
       <c r="G69" t="n">
-        <v>1.778564453125</v>
+        <v>1.77856469154358</v>
       </c>
       <c r="H69" t="n">
         <v>707623</v>
@@ -2399,7 +2399,7 @@
         <v>2.61800003051758</v>
       </c>
       <c r="G70" t="n">
-        <v>1.8302994966507</v>
+        <v>1.83029985427856</v>
       </c>
       <c r="H70" t="n">
         <v>1129515</v>
@@ -2428,7 +2428,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G71" t="n">
-        <v>1.85267162322998</v>
+        <v>1.85267174243927</v>
       </c>
       <c r="H71" t="n">
         <v>710507</v>
@@ -2457,7 +2457,7 @@
         <v>2.69199991226196</v>
       </c>
       <c r="G72" t="n">
-        <v>1.88203465938568</v>
+        <v>1.88203477859497</v>
       </c>
       <c r="H72" t="n">
         <v>1152888</v>
@@ -2486,7 +2486,7 @@
         <v>2.66799998283386</v>
       </c>
       <c r="G73" t="n">
-        <v>1.86525571346283</v>
+        <v>1.86525583267212</v>
       </c>
       <c r="H73" t="n">
         <v>504840</v>
@@ -2515,7 +2515,7 @@
         <v>2.67000007629395</v>
       </c>
       <c r="G74" t="n">
-        <v>1.86665391921997</v>
+        <v>1.86665403842926</v>
       </c>
       <c r="H74" t="n">
         <v>372726</v>
@@ -2544,7 +2544,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G75" t="n">
-        <v>1.88762748241425</v>
+        <v>1.88762760162354</v>
       </c>
       <c r="H75" t="n">
         <v>782281</v>
@@ -2573,7 +2573,7 @@
         <v>2.67000007629395</v>
       </c>
       <c r="G76" t="n">
-        <v>1.86665391921997</v>
+        <v>1.86665403842926</v>
       </c>
       <c r="H76" t="n">
         <v>761754</v>
@@ -2631,7 +2631,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G78" t="n">
-        <v>1.84568059444427</v>
+        <v>1.84568023681641</v>
       </c>
       <c r="H78" t="n">
         <v>1104301</v>
@@ -2660,7 +2660,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G79" t="n">
-        <v>1.85267162322998</v>
+        <v>1.85267174243927</v>
       </c>
       <c r="H79" t="n">
         <v>680735</v>
@@ -2689,7 +2689,7 @@
         <v>2.66000008583069</v>
       </c>
       <c r="G80" t="n">
-        <v>1.85966289043427</v>
+        <v>1.85966277122498</v>
       </c>
       <c r="H80" t="n">
         <v>378271</v>
@@ -2776,7 +2776,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G83" t="n">
-        <v>1.85267162322998</v>
+        <v>1.85267174243927</v>
       </c>
       <c r="H83" t="n">
         <v>394781</v>
@@ -2834,7 +2834,7 @@
         <v>2.59599995613098</v>
       </c>
       <c r="G85" t="n">
-        <v>1.8477144241333</v>
+        <v>1.84771466255188</v>
       </c>
       <c r="H85" t="n">
         <v>679217</v>
@@ -2863,7 +2863,7 @@
         <v>2.40400004386902</v>
       </c>
       <c r="G86" t="n">
-        <v>1.71105790138245</v>
+        <v>1.71105766296387</v>
       </c>
       <c r="H86" t="n">
         <v>1865772</v>
@@ -2892,7 +2892,7 @@
         <v>2.48600006103516</v>
       </c>
       <c r="G87" t="n">
-        <v>1.76942145824432</v>
+        <v>1.76942181587219</v>
       </c>
       <c r="H87" t="n">
         <v>1057485</v>
@@ -2921,7 +2921,7 @@
         <v>2.53600001335144</v>
       </c>
       <c r="G88" t="n">
-        <v>1.80500912666321</v>
+        <v>1.80500948429108</v>
       </c>
       <c r="H88" t="n">
         <v>505960</v>
@@ -2979,7 +2979,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G90" t="n">
-        <v>1.70821070671082</v>
+        <v>1.70821094512939</v>
       </c>
       <c r="H90" t="n">
         <v>732240</v>
@@ -3008,7 +3008,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G91" t="n">
-        <v>1.74379849433899</v>
+        <v>1.7437983751297</v>
       </c>
       <c r="H91" t="n">
         <v>657528</v>
@@ -3066,7 +3066,7 @@
         <v>2.56800007820129</v>
       </c>
       <c r="G93" t="n">
-        <v>1.82778549194336</v>
+        <v>1.82778525352478</v>
       </c>
       <c r="H93" t="n">
         <v>946941</v>
@@ -3095,7 +3095,7 @@
         <v>2.59800004959106</v>
       </c>
       <c r="G94" t="n">
-        <v>1.84913790225983</v>
+        <v>1.84913814067841</v>
       </c>
       <c r="H94" t="n">
         <v>1347283</v>
@@ -3124,7 +3124,7 @@
         <v>2.60199999809265</v>
       </c>
       <c r="G95" t="n">
-        <v>1.85198509693146</v>
+        <v>1.85198533535004</v>
       </c>
       <c r="H95" t="n">
         <v>318458</v>
@@ -3153,7 +3153,7 @@
         <v>2.5699999332428</v>
       </c>
       <c r="G96" t="n">
-        <v>1.82920897006989</v>
+        <v>1.82920908927917</v>
       </c>
       <c r="H96" t="n">
         <v>1177185</v>
@@ -3182,7 +3182,7 @@
         <v>2.62599992752075</v>
       </c>
       <c r="G97" t="n">
-        <v>1.86906731128693</v>
+        <v>1.86906695365906</v>
       </c>
       <c r="H97" t="n">
         <v>1113110</v>
@@ -3211,7 +3211,7 @@
         <v>2.61800003051758</v>
       </c>
       <c r="G98" t="n">
-        <v>1.86337292194366</v>
+        <v>1.86337304115295</v>
       </c>
       <c r="H98" t="n">
         <v>457721</v>
@@ -3240,7 +3240,7 @@
         <v>2.58999991416931</v>
       </c>
       <c r="G99" t="n">
-        <v>1.84344398975372</v>
+        <v>1.84344375133514</v>
       </c>
       <c r="H99" t="n">
         <v>570097</v>
@@ -3269,7 +3269,7 @@
         <v>2.62800002098083</v>
       </c>
       <c r="G100" t="n">
-        <v>1.87049090862274</v>
+        <v>1.87049067020416</v>
       </c>
       <c r="H100" t="n">
         <v>806323</v>
@@ -3298,7 +3298,7 @@
         <v>2.63000011444092</v>
       </c>
       <c r="G101" t="n">
-        <v>1.87191414833069</v>
+        <v>1.8719140291214</v>
       </c>
       <c r="H101" t="n">
         <v>309460</v>
@@ -3327,7 +3327,7 @@
         <v>2.58400011062622</v>
       </c>
       <c r="G102" t="n">
-        <v>1.83917367458344</v>
+        <v>1.83917391300201</v>
       </c>
       <c r="H102" t="n">
         <v>786834</v>
@@ -3356,7 +3356,7 @@
         <v>2.55599999427795</v>
       </c>
       <c r="G103" t="n">
-        <v>1.81924438476562</v>
+        <v>1.81924450397491</v>
       </c>
       <c r="H103" t="n">
         <v>409748</v>
@@ -3385,7 +3385,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G104" t="n">
-        <v>1.82209146022797</v>
+        <v>1.82209134101868</v>
       </c>
       <c r="H104" t="n">
         <v>444223</v>
@@ -3414,7 +3414,7 @@
         <v>2.55399990081787</v>
       </c>
       <c r="G105" t="n">
-        <v>1.81782078742981</v>
+        <v>1.81782066822052</v>
       </c>
       <c r="H105" t="n">
         <v>360830</v>
@@ -3443,7 +3443,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G106" t="n">
-        <v>1.83632624149323</v>
+        <v>1.83632671833038</v>
       </c>
       <c r="H106" t="n">
         <v>743636</v>
@@ -3472,7 +3472,7 @@
         <v>2.5239999294281</v>
       </c>
       <c r="G107" t="n">
-        <v>1.79646837711334</v>
+        <v>1.79646801948547</v>
       </c>
       <c r="H107" t="n">
         <v>390435</v>
@@ -3501,7 +3501,7 @@
         <v>2.54399991035461</v>
       </c>
       <c r="G108" t="n">
-        <v>1.8107031583786</v>
+        <v>1.81070339679718</v>
       </c>
       <c r="H108" t="n">
         <v>689024</v>
@@ -3530,7 +3530,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G109" t="n">
-        <v>1.76515078544617</v>
+        <v>1.76515102386475</v>
       </c>
       <c r="H109" t="n">
         <v>510149</v>
@@ -3559,7 +3559,7 @@
         <v>2.46399998664856</v>
       </c>
       <c r="G110" t="n">
-        <v>1.75376272201538</v>
+        <v>1.75376296043396</v>
       </c>
       <c r="H110" t="n">
         <v>489719</v>
@@ -3617,7 +3617,7 @@
         <v>2.46600008010864</v>
       </c>
       <c r="G112" t="n">
-        <v>1.75518655776978</v>
+        <v>1.75518643856049</v>
       </c>
       <c r="H112" t="n">
         <v>326930</v>
@@ -3704,7 +3704,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G115" t="n">
-        <v>1.67974042892456</v>
+        <v>1.67974030971527</v>
       </c>
       <c r="H115" t="n">
         <v>507496</v>
@@ -3733,7 +3733,7 @@
         <v>2.31599998474121</v>
       </c>
       <c r="G116" t="n">
-        <v>1.64842295646667</v>
+        <v>1.64842343330383</v>
       </c>
       <c r="H116" t="n">
         <v>650823</v>
@@ -3820,7 +3820,7 @@
         <v>2.37800002098083</v>
       </c>
       <c r="G119" t="n">
-        <v>1.69255208969116</v>
+        <v>1.69255220890045</v>
       </c>
       <c r="H119" t="n">
         <v>1664604</v>
@@ -3849,7 +3849,7 @@
         <v>2.42400002479553</v>
       </c>
       <c r="G120" t="n">
-        <v>1.72529268264771</v>
+        <v>1.72529292106628</v>
       </c>
       <c r="H120" t="n">
         <v>880203</v>
@@ -3878,7 +3878,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G121" t="n">
-        <v>1.66550552845001</v>
+        <v>1.66550529003143</v>
       </c>
       <c r="H121" t="n">
         <v>526142</v>
@@ -3907,7 +3907,7 @@
         <v>2.33800005912781</v>
       </c>
       <c r="G122" t="n">
-        <v>1.66408181190491</v>
+        <v>1.6640819311142</v>
       </c>
       <c r="H122" t="n">
         <v>829056</v>
@@ -3936,7 +3936,7 @@
         <v>2.36400008201599</v>
       </c>
       <c r="G123" t="n">
-        <v>1.68258774280548</v>
+        <v>1.6825875043869</v>
       </c>
       <c r="H123" t="n">
         <v>661969</v>
@@ -3965,7 +3965,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G124" t="n">
-        <v>1.53027200698853</v>
+        <v>1.5302722454071</v>
       </c>
       <c r="H124" t="n">
         <v>832527</v>
@@ -3994,7 +3994,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G125" t="n">
-        <v>1.47333168983459</v>
+        <v>1.47333180904388</v>
       </c>
       <c r="H125" t="n">
         <v>1170750</v>
@@ -4023,7 +4023,7 @@
         <v>2.23000001907349</v>
       </c>
       <c r="G126" t="n">
-        <v>1.58721232414246</v>
+        <v>1.58721256256104</v>
       </c>
       <c r="H126" t="n">
         <v>1484614</v>
@@ -4052,7 +4052,7 @@
         <v>2.25200009346008</v>
       </c>
       <c r="G127" t="n">
-        <v>1.60287094116211</v>
+        <v>1.60287129878998</v>
       </c>
       <c r="H127" t="n">
         <v>498300</v>
@@ -4110,7 +4110,7 @@
         <v>2.33800005912781</v>
       </c>
       <c r="G129" t="n">
-        <v>1.66408181190491</v>
+        <v>1.6640819311142</v>
       </c>
       <c r="H129" t="n">
         <v>438412</v>
@@ -4139,7 +4139,7 @@
         <v>2.29200005531311</v>
       </c>
       <c r="G130" t="n">
-        <v>1.63134121894836</v>
+        <v>1.63134133815765</v>
       </c>
       <c r="H130" t="n">
         <v>182747</v>
@@ -4197,7 +4197,7 @@
         <v>2.14400005340576</v>
       </c>
       <c r="G132" t="n">
-        <v>1.52600145339966</v>
+        <v>1.52600157260895</v>
       </c>
       <c r="H132" t="n">
         <v>465666</v>
@@ -4226,7 +4226,7 @@
         <v>2.17199993133545</v>
       </c>
       <c r="G133" t="n">
-        <v>1.54593062400818</v>
+        <v>1.54593074321747</v>
       </c>
       <c r="H133" t="n">
         <v>162623</v>
@@ -4255,7 +4255,7 @@
         <v>2.25</v>
       </c>
       <c r="G134" t="n">
-        <v>1.60144758224487</v>
+        <v>1.60144746303558</v>
       </c>
       <c r="H134" t="n">
         <v>199141</v>
@@ -4284,7 +4284,7 @@
         <v>2.30399990081787</v>
       </c>
       <c r="G135" t="n">
-        <v>1.6398823261261</v>
+        <v>1.63988220691681</v>
       </c>
       <c r="H135" t="n">
         <v>523956</v>
@@ -4313,7 +4313,7 @@
         <v>2.28399991989136</v>
       </c>
       <c r="G136" t="n">
-        <v>1.62564706802368</v>
+        <v>1.62564718723297</v>
       </c>
       <c r="H136" t="n">
         <v>513407</v>
@@ -4342,7 +4342,7 @@
         <v>2.29200005531311</v>
       </c>
       <c r="G137" t="n">
-        <v>1.63134121894836</v>
+        <v>1.63134133815765</v>
       </c>
       <c r="H137" t="n">
         <v>556168</v>
@@ -4400,7 +4400,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G139" t="n">
-        <v>1.67262291908264</v>
+        <v>1.67262303829193</v>
       </c>
       <c r="H139" t="n">
         <v>293783</v>
@@ -4429,7 +4429,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G140" t="n">
-        <v>1.70821070671082</v>
+        <v>1.70821094512939</v>
       </c>
       <c r="H140" t="n">
         <v>385684</v>
@@ -4458,7 +4458,7 @@
         <v>2.34800004959106</v>
       </c>
       <c r="G141" t="n">
-        <v>1.67119956016541</v>
+        <v>1.67119944095612</v>
       </c>
       <c r="H141" t="n">
         <v>265660</v>
@@ -4487,7 +4487,7 @@
         <v>2.3659999370575</v>
       </c>
       <c r="G142" t="n">
-        <v>1.68401098251343</v>
+        <v>1.68401086330414</v>
       </c>
       <c r="H142" t="n">
         <v>194145</v>
@@ -4516,7 +4516,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G143" t="n">
-        <v>1.63703501224518</v>
+        <v>1.63703525066376</v>
       </c>
       <c r="H143" t="n">
         <v>287402</v>
@@ -4545,7 +4545,7 @@
         <v>2.31399989128113</v>
       </c>
       <c r="G144" t="n">
-        <v>1.64699971675873</v>
+        <v>1.64699995517731</v>
       </c>
       <c r="H144" t="n">
         <v>338828</v>
@@ -4574,7 +4574,7 @@
         <v>2.32200002670288</v>
       </c>
       <c r="G145" t="n">
-        <v>1.65269410610199</v>
+        <v>1.65269374847412</v>
       </c>
       <c r="H145" t="n">
         <v>154272</v>
@@ -4632,7 +4632,7 @@
         <v>2.32599997520447</v>
       </c>
       <c r="G147" t="n">
-        <v>1.65554070472717</v>
+        <v>1.65554082393646</v>
       </c>
       <c r="H147" t="n">
         <v>283107</v>
@@ -4690,7 +4690,7 @@
         <v>2.27600002288818</v>
       </c>
       <c r="G149" t="n">
-        <v>1.61995339393616</v>
+        <v>1.61995315551758</v>
       </c>
       <c r="H149" t="n">
         <v>609455</v>
@@ -4719,7 +4719,7 @@
         <v>2.18400001525879</v>
       </c>
       <c r="G150" t="n">
-        <v>1.55447196960449</v>
+        <v>1.55447173118591</v>
       </c>
       <c r="H150" t="n">
         <v>584750</v>
@@ -4748,7 +4748,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G151" t="n">
-        <v>1.55874216556549</v>
+        <v>1.55874252319336</v>
       </c>
       <c r="H151" t="n">
         <v>363317</v>
@@ -4806,7 +4806,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G153" t="n">
-        <v>1.54450714588165</v>
+        <v>1.54450750350952</v>
       </c>
       <c r="H153" t="n">
         <v>274389</v>
@@ -4864,7 +4864,7 @@
         <v>2.14400005340576</v>
       </c>
       <c r="G155" t="n">
-        <v>1.52600145339966</v>
+        <v>1.52600157260895</v>
       </c>
       <c r="H155" t="n">
         <v>370456</v>
@@ -4893,7 +4893,7 @@
         <v>2.13199996948242</v>
       </c>
       <c r="G156" t="n">
-        <v>1.5174605846405</v>
+        <v>1.51746034622192</v>
       </c>
       <c r="H156" t="n">
         <v>169798</v>
@@ -4922,7 +4922,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G157" t="n">
-        <v>1.49468433856964</v>
+        <v>1.49468421936035</v>
       </c>
       <c r="H157" t="n">
         <v>578131</v>
@@ -4980,7 +4980,7 @@
         <v>2.09400010108948</v>
       </c>
       <c r="G159" t="n">
-        <v>1.49041366577148</v>
+        <v>1.49041378498077</v>
       </c>
       <c r="H159" t="n">
         <v>281320</v>
@@ -5038,7 +5038,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G161" t="n">
-        <v>1.43774390220642</v>
+        <v>1.43774402141571</v>
       </c>
       <c r="H161" t="n">
         <v>456219</v>
@@ -5096,7 +5096,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G163" t="n">
-        <v>1.45197904109955</v>
+        <v>1.45197892189026</v>
       </c>
       <c r="H163" t="n">
         <v>473821</v>
@@ -5270,7 +5270,7 @@
         <v>2.04200005531311</v>
       </c>
       <c r="G169" t="n">
-        <v>1.45340275764465</v>
+        <v>1.45340263843536</v>
       </c>
       <c r="H169" t="n">
         <v>179432</v>
@@ -5299,7 +5299,7 @@
         <v>2.02800011634827</v>
       </c>
       <c r="G170" t="n">
-        <v>1.44343793392181</v>
+        <v>1.44343817234039</v>
       </c>
       <c r="H170" t="n">
         <v>818875</v>
@@ -5328,7 +5328,7 @@
         <v>2.14599990844727</v>
       </c>
       <c r="G171" t="n">
-        <v>1.52742481231689</v>
+        <v>1.52742505073547</v>
       </c>
       <c r="H171" t="n">
         <v>1620476</v>
@@ -5357,7 +5357,7 @@
         <v>2.13000011444092</v>
       </c>
       <c r="G172" t="n">
-        <v>1.51603710651398</v>
+        <v>1.51603698730469</v>
       </c>
       <c r="H172" t="n">
         <v>1255209</v>
@@ -5386,7 +5386,7 @@
         <v>2.15599989891052</v>
       </c>
       <c r="G173" t="n">
-        <v>1.53454256057739</v>
+        <v>1.5345424413681</v>
       </c>
       <c r="H173" t="n">
         <v>222233</v>
@@ -5502,7 +5502,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G177" t="n">
-        <v>1.54450714588165</v>
+        <v>1.54450750350952</v>
       </c>
       <c r="H177" t="n">
         <v>528748</v>
@@ -5531,7 +5531,7 @@
         <v>2.15599989891052</v>
       </c>
       <c r="G178" t="n">
-        <v>1.53454256057739</v>
+        <v>1.5345424413681</v>
       </c>
       <c r="H178" t="n">
         <v>263418</v>
@@ -5560,7 +5560,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G179" t="n">
-        <v>1.52315485477448</v>
+        <v>1.5231546163559</v>
       </c>
       <c r="H179" t="n">
         <v>462417</v>
@@ -5589,7 +5589,7 @@
         <v>2.10199999809265</v>
       </c>
       <c r="G180" t="n">
-        <v>1.49610793590546</v>
+        <v>1.49610781669617</v>
       </c>
       <c r="H180" t="n">
         <v>560948</v>
@@ -5647,7 +5647,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G182" t="n">
-        <v>1.50891935825348</v>
+        <v>1.50891923904419</v>
       </c>
       <c r="H182" t="n">
         <v>874668</v>
@@ -5676,7 +5676,7 @@
         <v>2.11800003051758</v>
       </c>
       <c r="G183" t="n">
-        <v>1.50749611854553</v>
+        <v>1.50749588012695</v>
       </c>
       <c r="H183" t="n">
         <v>393698</v>
@@ -5705,7 +5705,7 @@
         <v>2.13000011444092</v>
       </c>
       <c r="G184" t="n">
-        <v>1.51603710651398</v>
+        <v>1.51603698730469</v>
       </c>
       <c r="H184" t="n">
         <v>194068</v>
@@ -5763,7 +5763,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G186" t="n">
-        <v>1.47333168983459</v>
+        <v>1.47333180904388</v>
       </c>
       <c r="H186" t="n">
         <v>837880</v>
@@ -5792,7 +5792,7 @@
         <v>2.08400011062622</v>
       </c>
       <c r="G187" t="n">
-        <v>1.48329639434814</v>
+        <v>1.48329627513885</v>
       </c>
       <c r="H187" t="n">
         <v>380163</v>
@@ -5821,7 +5821,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G188" t="n">
-        <v>1.46621417999268</v>
+        <v>1.46621406078339</v>
       </c>
       <c r="H188" t="n">
         <v>903456</v>
@@ -5850,7 +5850,7 @@
         <v>2.08800005912781</v>
       </c>
       <c r="G189" t="n">
-        <v>1.48614323139191</v>
+        <v>1.48614358901978</v>
       </c>
       <c r="H189" t="n">
         <v>619822</v>
@@ -5937,7 +5937,7 @@
         <v>2.2039999961853</v>
       </c>
       <c r="G192" t="n">
-        <v>1.56870687007904</v>
+        <v>1.56870675086975</v>
       </c>
       <c r="H192" t="n">
         <v>1949825</v>
@@ -5966,7 +5966,7 @@
         <v>2.20199990272522</v>
       </c>
       <c r="G193" t="n">
-        <v>1.56728315353394</v>
+        <v>1.56728303432465</v>
       </c>
       <c r="H193" t="n">
         <v>647560</v>
@@ -5995,7 +5995,7 @@
         <v>2.19600009918213</v>
       </c>
       <c r="G194" t="n">
-        <v>1.56301295757294</v>
+        <v>1.56301283836365</v>
       </c>
       <c r="H194" t="n">
         <v>336530</v>
@@ -6024,7 +6024,7 @@
         <v>2.17199993133545</v>
       </c>
       <c r="G195" t="n">
-        <v>1.54593062400818</v>
+        <v>1.54593074321747</v>
       </c>
       <c r="H195" t="n">
         <v>311766</v>
@@ -6082,7 +6082,7 @@
         <v>2.13000011444092</v>
       </c>
       <c r="G197" t="n">
-        <v>1.51603710651398</v>
+        <v>1.51603698730469</v>
       </c>
       <c r="H197" t="n">
         <v>441820</v>
@@ -6140,7 +6140,7 @@
         <v>2.08800005912781</v>
       </c>
       <c r="G199" t="n">
-        <v>1.48614323139191</v>
+        <v>1.48614358901978</v>
       </c>
       <c r="H199" t="n">
         <v>420378</v>
@@ -6198,7 +6198,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G201" t="n">
-        <v>1.47333168983459</v>
+        <v>1.47333180904388</v>
       </c>
       <c r="H201" t="n">
         <v>209320</v>
@@ -6227,7 +6227,7 @@
         <v>2.06599998474121</v>
       </c>
       <c r="G202" t="n">
-        <v>1.47048461437225</v>
+        <v>1.47048485279083</v>
       </c>
       <c r="H202" t="n">
         <v>401988</v>
@@ -6256,7 +6256,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G203" t="n">
-        <v>1.54450714588165</v>
+        <v>1.54450750350952</v>
       </c>
       <c r="H203" t="n">
         <v>631254</v>
@@ -6285,7 +6285,7 @@
         <v>2.16799998283386</v>
       </c>
       <c r="G204" t="n">
-        <v>1.54308366775513</v>
+        <v>1.54308354854584</v>
       </c>
       <c r="H204" t="n">
         <v>215809</v>
@@ -6343,7 +6343,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G206" t="n">
-        <v>1.55874216556549</v>
+        <v>1.55874252319336</v>
       </c>
       <c r="H206" t="n">
         <v>243793</v>
@@ -6372,7 +6372,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G207" t="n">
-        <v>1.55874216556549</v>
+        <v>1.55874252319336</v>
       </c>
       <c r="H207" t="n">
         <v>1391074</v>
@@ -6488,7 +6488,7 @@
         <v>2.23000001907349</v>
       </c>
       <c r="G211" t="n">
-        <v>1.58721232414246</v>
+        <v>1.58721256256104</v>
       </c>
       <c r="H211" t="n">
         <v>254288</v>
@@ -6517,7 +6517,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G212" t="n">
-        <v>1.56585967540741</v>
+        <v>1.5658597946167</v>
       </c>
       <c r="H212" t="n">
         <v>527759</v>
@@ -6546,7 +6546,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G213" t="n">
-        <v>1.56585967540741</v>
+        <v>1.5658597946167</v>
       </c>
       <c r="H213" t="n">
         <v>354969</v>
@@ -6575,7 +6575,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G214" t="n">
-        <v>1.56585967540741</v>
+        <v>1.5658597946167</v>
       </c>
       <c r="H214" t="n">
         <v>263580</v>
@@ -6662,7 +6662,7 @@
         <v>2.21600008010864</v>
       </c>
       <c r="G217" t="n">
-        <v>1.57724797725677</v>
+        <v>1.5772477388382</v>
       </c>
       <c r="H217" t="n">
         <v>963635</v>
@@ -6720,7 +6720,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G219" t="n">
-        <v>1.56585967540741</v>
+        <v>1.5658597946167</v>
       </c>
       <c r="H219" t="n">
         <v>469751</v>
@@ -6749,7 +6749,7 @@
         <v>2.27800011634827</v>
       </c>
       <c r="G220" t="n">
-        <v>1.62137687206268</v>
+        <v>1.6213766336441</v>
       </c>
       <c r="H220" t="n">
         <v>852052</v>
@@ -6778,7 +6778,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G221" t="n">
-        <v>1.63703501224518</v>
+        <v>1.63703525066376</v>
       </c>
       <c r="H221" t="n">
         <v>2372952</v>
@@ -6807,7 +6807,7 @@
         <v>2.3659999370575</v>
       </c>
       <c r="G222" t="n">
-        <v>1.68401098251343</v>
+        <v>1.68401086330414</v>
       </c>
       <c r="H222" t="n">
         <v>1531650</v>
@@ -6836,7 +6836,7 @@
         <v>2.40400004386902</v>
       </c>
       <c r="G223" t="n">
-        <v>1.71105790138245</v>
+        <v>1.71105766296387</v>
       </c>
       <c r="H223" t="n">
         <v>2061488</v>
@@ -7039,7 +7039,7 @@
         <v>2.43600010871887</v>
       </c>
       <c r="G230" t="n">
-        <v>1.73383378982544</v>
+        <v>1.73383402824402</v>
       </c>
       <c r="H230" t="n">
         <v>2391456</v>
@@ -7068,7 +7068,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G231" t="n">
-        <v>1.75803375244141</v>
+        <v>1.75803351402283</v>
       </c>
       <c r="H231" t="n">
         <v>961642</v>
@@ -7126,7 +7126,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G233" t="n">
-        <v>1.72244572639465</v>
+        <v>1.72244596481323</v>
       </c>
       <c r="H233" t="n">
         <v>333808</v>
@@ -7155,7 +7155,7 @@
         <v>2.28800010681152</v>
       </c>
       <c r="G234" t="n">
-        <v>1.62849414348602</v>
+        <v>1.62849426269531</v>
       </c>
       <c r="H234" t="n">
         <v>999727</v>
@@ -7184,7 +7184,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G235" t="n">
-        <v>1.67262291908264</v>
+        <v>1.67262303829193</v>
       </c>
       <c r="H235" t="n">
         <v>1024681</v>
@@ -7213,7 +7213,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G236" t="n">
-        <v>1.6939754486084</v>
+        <v>1.69397568702698</v>
       </c>
       <c r="H236" t="n">
         <v>763066</v>
@@ -7242,7 +7242,7 @@
         <v>2.40599989891052</v>
       </c>
       <c r="G237" t="n">
-        <v>1.71248126029968</v>
+        <v>1.71248114109039</v>
       </c>
       <c r="H237" t="n">
         <v>438235</v>
@@ -7271,7 +7271,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G238" t="n">
-        <v>1.73668110370636</v>
+        <v>1.73668086528778</v>
       </c>
       <c r="H238" t="n">
         <v>687735</v>
@@ -7300,7 +7300,7 @@
         <v>2.43799996376038</v>
       </c>
       <c r="G239" t="n">
-        <v>1.73525714874268</v>
+        <v>1.73525750637054</v>
       </c>
       <c r="H239" t="n">
         <v>616032</v>
@@ -7358,7 +7358,7 @@
         <v>2.55599999427795</v>
       </c>
       <c r="G241" t="n">
-        <v>1.81924438476562</v>
+        <v>1.81924450397491</v>
       </c>
       <c r="H241" t="n">
         <v>1303692</v>
@@ -7387,7 +7387,7 @@
         <v>2.63000011444092</v>
       </c>
       <c r="G242" t="n">
-        <v>1.87191414833069</v>
+        <v>1.8719140291214</v>
       </c>
       <c r="H242" t="n">
         <v>820486</v>
@@ -7445,7 +7445,7 @@
         <v>2.57599997520447</v>
       </c>
       <c r="G244" t="n">
-        <v>1.83347940444946</v>
+        <v>1.83347928524017</v>
       </c>
       <c r="H244" t="n">
         <v>551418</v>
@@ -7474,7 +7474,7 @@
         <v>2.62800002098083</v>
       </c>
       <c r="G245" t="n">
-        <v>1.87049090862274</v>
+        <v>1.87049067020416</v>
       </c>
       <c r="H245" t="n">
         <v>654879</v>
@@ -7561,7 +7561,7 @@
         <v>2.58400011062622</v>
       </c>
       <c r="G248" t="n">
-        <v>1.83917367458344</v>
+        <v>1.83917391300201</v>
       </c>
       <c r="H248" t="n">
         <v>382203</v>
@@ -7590,7 +7590,7 @@
         <v>2.59800004959106</v>
       </c>
       <c r="G249" t="n">
-        <v>1.84913790225983</v>
+        <v>1.84913814067841</v>
       </c>
       <c r="H249" t="n">
         <v>311467</v>
@@ -7677,7 +7677,7 @@
         <v>2.57800006866455</v>
       </c>
       <c r="G252" t="n">
-        <v>1.83490324020386</v>
+        <v>1.83490312099457</v>
       </c>
       <c r="H252" t="n">
         <v>566735</v>
@@ -7706,7 +7706,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G253" t="n">
-        <v>1.83632624149323</v>
+        <v>1.83632671833038</v>
       </c>
       <c r="H253" t="n">
         <v>479181</v>
@@ -7735,7 +7735,7 @@
         <v>2.60599994659424</v>
       </c>
       <c r="G254" t="n">
-        <v>1.8548321723938</v>
+        <v>1.85483229160309</v>
       </c>
       <c r="H254" t="n">
         <v>179370</v>
@@ -7764,7 +7764,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G255" t="n">
-        <v>1.83632624149323</v>
+        <v>1.83632671833038</v>
       </c>
       <c r="H255" t="n">
         <v>157456</v>
@@ -7793,7 +7793,7 @@
         <v>2.58999991416931</v>
       </c>
       <c r="G256" t="n">
-        <v>1.84344398975372</v>
+        <v>1.84344375133514</v>
       </c>
       <c r="H256" t="n">
         <v>179038</v>
@@ -7822,7 +7822,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G257" t="n">
-        <v>1.83632624149323</v>
+        <v>1.83632671833038</v>
       </c>
       <c r="H257" t="n">
         <v>202440</v>
@@ -7880,7 +7880,7 @@
         <v>2.75</v>
       </c>
       <c r="G259" t="n">
-        <v>1.95732474327087</v>
+        <v>1.95732462406158</v>
       </c>
       <c r="H259" t="n">
         <v>1207812</v>
@@ -8112,7 +8112,7 @@
         <v>2.76200008392334</v>
       </c>
       <c r="G267" t="n">
-        <v>1.96586585044861</v>
+        <v>1.96586573123932</v>
       </c>
       <c r="H267" t="n">
         <v>377569</v>
@@ -8199,7 +8199,7 @@
         <v>2.66199994087219</v>
       </c>
       <c r="G270" t="n">
-        <v>1.89469063282013</v>
+        <v>1.89469027519226</v>
       </c>
       <c r="H270" t="n">
         <v>724087</v>
@@ -8228,7 +8228,7 @@
         <v>2.55599999427795</v>
       </c>
       <c r="G271" t="n">
-        <v>1.81924438476562</v>
+        <v>1.81924450397491</v>
       </c>
       <c r="H271" t="n">
         <v>846702</v>
@@ -8257,7 +8257,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G272" t="n">
-        <v>1.83632624149323</v>
+        <v>1.83632671833038</v>
       </c>
       <c r="H272" t="n">
         <v>457504</v>
@@ -8286,7 +8286,7 @@
         <v>2.60199999809265</v>
       </c>
       <c r="G273" t="n">
-        <v>1.85198509693146</v>
+        <v>1.85198533535004</v>
       </c>
       <c r="H273" t="n">
         <v>253439</v>
@@ -8315,7 +8315,7 @@
         <v>2.62400007247925</v>
       </c>
       <c r="G274" t="n">
-        <v>1.8676438331604</v>
+        <v>1.86764407157898</v>
       </c>
       <c r="H274" t="n">
         <v>455012</v>
@@ -8344,7 +8344,7 @@
         <v>2.67000007629395</v>
       </c>
       <c r="G275" t="n">
-        <v>1.90038430690765</v>
+        <v>1.90038442611694</v>
       </c>
       <c r="H275" t="n">
         <v>972068</v>
@@ -8431,7 +8431,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G278" t="n">
-        <v>1.83632624149323</v>
+        <v>1.83632671833038</v>
       </c>
       <c r="H278" t="n">
         <v>349720</v>
@@ -8518,7 +8518,7 @@
         <v>2.64800000190735</v>
       </c>
       <c r="G281" t="n">
-        <v>1.88472580909729</v>
+        <v>1.88472557067871</v>
       </c>
       <c r="H281" t="n">
         <v>349865</v>
@@ -8547,7 +8547,7 @@
         <v>2.61800003051758</v>
       </c>
       <c r="G282" t="n">
-        <v>1.86337292194366</v>
+        <v>1.86337304115295</v>
       </c>
       <c r="H282" t="n">
         <v>193960</v>
@@ -8663,7 +8663,7 @@
         <v>2.59800004959106</v>
       </c>
       <c r="G286" t="n">
-        <v>1.84913790225983</v>
+        <v>1.84913814067841</v>
       </c>
       <c r="H286" t="n">
         <v>293717</v>
@@ -8692,7 +8692,7 @@
         <v>2.59599995613098</v>
       </c>
       <c r="G287" t="n">
-        <v>1.8477144241333</v>
+        <v>1.84771466255188</v>
       </c>
       <c r="H287" t="n">
         <v>418348</v>
@@ -8721,7 +8721,7 @@
         <v>2.62400007247925</v>
       </c>
       <c r="G288" t="n">
-        <v>1.8676438331604</v>
+        <v>1.86764407157898</v>
       </c>
       <c r="H288" t="n">
         <v>228030</v>
@@ -8750,7 +8750,7 @@
         <v>2.62599992752075</v>
       </c>
       <c r="G289" t="n">
-        <v>1.86906731128693</v>
+        <v>1.86906695365906</v>
       </c>
       <c r="H289" t="n">
         <v>436886</v>
@@ -8779,7 +8779,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G290" t="n">
-        <v>1.87903189659119</v>
+        <v>1.87903165817261</v>
       </c>
       <c r="H290" t="n">
         <v>299397</v>
@@ -8866,7 +8866,7 @@
         <v>2.60800004005432</v>
       </c>
       <c r="G293" t="n">
-        <v>1.85625565052032</v>
+        <v>1.85625541210175</v>
       </c>
       <c r="H293" t="n">
         <v>219590</v>
@@ -8895,7 +8895,7 @@
         <v>2.53200006484985</v>
       </c>
       <c r="G294" t="n">
-        <v>1.80216217041016</v>
+        <v>1.80216228961945</v>
       </c>
       <c r="H294" t="n">
         <v>472657</v>
@@ -8924,7 +8924,7 @@
         <v>2.58599996566772</v>
       </c>
       <c r="G295" t="n">
-        <v>1.84059691429138</v>
+        <v>1.84059679508209</v>
       </c>
       <c r="H295" t="n">
         <v>472512</v>
@@ -8953,7 +8953,7 @@
         <v>2.54800009727478</v>
       </c>
       <c r="G296" t="n">
-        <v>1.81355047225952</v>
+        <v>1.81355059146881</v>
       </c>
       <c r="H296" t="n">
         <v>295229</v>
@@ -8982,7 +8982,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G297" t="n">
-        <v>1.80785632133484</v>
+        <v>1.80785620212555</v>
       </c>
       <c r="H297" t="n">
         <v>653701</v>
@@ -9011,7 +9011,7 @@
         <v>2.51799988746643</v>
       </c>
       <c r="G298" t="n">
-        <v>1.79219746589661</v>
+        <v>1.7921975851059</v>
       </c>
       <c r="H298" t="n">
         <v>607572</v>
@@ -9040,7 +9040,7 @@
         <v>2.5699999332428</v>
       </c>
       <c r="G299" t="n">
-        <v>1.82920897006989</v>
+        <v>1.82920908927917</v>
       </c>
       <c r="H299" t="n">
         <v>346042</v>
@@ -9069,7 +9069,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G300" t="n">
-        <v>1.88614940643311</v>
+        <v>1.88614916801453</v>
       </c>
       <c r="H300" t="n">
         <v>697715</v>
@@ -9098,7 +9098,7 @@
         <v>2.64800000190735</v>
       </c>
       <c r="G301" t="n">
-        <v>1.88472580909729</v>
+        <v>1.88472557067871</v>
       </c>
       <c r="H301" t="n">
         <v>419428</v>
@@ -9127,7 +9127,7 @@
         <v>2.65599989891052</v>
       </c>
       <c r="G302" t="n">
-        <v>1.8904196023941</v>
+        <v>1.89041972160339</v>
       </c>
       <c r="H302" t="n">
         <v>432621</v>
@@ -9185,7 +9185,7 @@
         <v>2.67000007629395</v>
       </c>
       <c r="G304" t="n">
-        <v>1.90038430690765</v>
+        <v>1.90038442611694</v>
       </c>
       <c r="H304" t="n">
         <v>376722</v>
@@ -9214,7 +9214,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G305" t="n">
-        <v>1.87903189659119</v>
+        <v>1.87903165817261</v>
       </c>
       <c r="H305" t="n">
         <v>196525</v>
@@ -9272,7 +9272,7 @@
         <v>2.70199990272522</v>
       </c>
       <c r="G307" t="n">
-        <v>1.92316055297852</v>
+        <v>1.92316043376923</v>
       </c>
       <c r="H307" t="n">
         <v>605171</v>
@@ -9359,7 +9359,7 @@
         <v>2.76999998092651</v>
       </c>
       <c r="G310" t="n">
-        <v>1.97156023979187</v>
+        <v>1.97156000137329</v>
       </c>
       <c r="H310" t="n">
         <v>1790829</v>
@@ -9417,7 +9417,7 @@
         <v>3.24399995803833</v>
       </c>
       <c r="G312" t="n">
-        <v>2.30893182754517</v>
+        <v>2.30893158912659</v>
       </c>
       <c r="H312" t="n">
         <v>6104774</v>
@@ -9446,7 +9446,7 @@
         <v>3.25600004196167</v>
       </c>
       <c r="G313" t="n">
-        <v>2.31747269630432</v>
+        <v>2.31747245788574</v>
       </c>
       <c r="H313" t="n">
         <v>2072336</v>
@@ -9504,7 +9504,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G315" t="n">
-        <v>2.46267056465149</v>
+        <v>2.46267032623291</v>
       </c>
       <c r="H315" t="n">
         <v>2123167</v>
@@ -9562,7 +9562,7 @@
         <v>3.52800011634827</v>
       </c>
       <c r="G317" t="n">
-        <v>2.51107001304626</v>
+        <v>2.51106977462769</v>
       </c>
       <c r="H317" t="n">
         <v>2645859</v>
@@ -9591,7 +9591,7 @@
         <v>3.46600008010864</v>
       </c>
       <c r="G318" t="n">
-        <v>2.46694087982178</v>
+        <v>2.46694111824036</v>
       </c>
       <c r="H318" t="n">
         <v>1533360</v>
@@ -9765,7 +9765,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G324" t="n">
-        <v>2.56231594085693</v>
+        <v>2.56231617927551</v>
       </c>
       <c r="H324" t="n">
         <v>1395680</v>
@@ -9794,7 +9794,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G325" t="n">
-        <v>2.60502147674561</v>
+        <v>2.60502123832703</v>
       </c>
       <c r="H325" t="n">
         <v>1825968</v>
@@ -9852,7 +9852,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G327" t="n">
-        <v>2.67619633674622</v>
+        <v>2.67619705200195</v>
       </c>
       <c r="H327" t="n">
         <v>1570869</v>
@@ -9881,7 +9881,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G328" t="n">
-        <v>2.63349175453186</v>
+        <v>2.6334912776947</v>
       </c>
       <c r="H328" t="n">
         <v>1099577</v>
@@ -9910,7 +9910,7 @@
         <v>3.75799989700317</v>
       </c>
       <c r="G329" t="n">
-        <v>2.67477321624756</v>
+        <v>2.67477345466614</v>
       </c>
       <c r="H329" t="n">
         <v>2072398</v>
@@ -10026,7 +10026,7 @@
         <v>3.58999991416931</v>
       </c>
       <c r="G333" t="n">
-        <v>2.55519866943359</v>
+        <v>2.55519819259644</v>
       </c>
       <c r="H333" t="n">
         <v>656224</v>
@@ -10055,7 +10055,7 @@
         <v>3.58400011062622</v>
       </c>
       <c r="G334" t="n">
-        <v>2.55092811584473</v>
+        <v>2.55092835426331</v>
       </c>
       <c r="H334" t="n">
         <v>734296</v>
@@ -10084,7 +10084,7 @@
         <v>3.51399993896484</v>
       </c>
       <c r="G335" t="n">
-        <v>2.50110507011414</v>
+        <v>2.50110483169556</v>
       </c>
       <c r="H335" t="n">
         <v>577544</v>
@@ -10200,7 +10200,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G339" t="n">
-        <v>2.63349175453186</v>
+        <v>2.6334912776947</v>
       </c>
       <c r="H339" t="n">
         <v>760719</v>
@@ -10287,7 +10287,7 @@
         <v>3.53800010681152</v>
       </c>
       <c r="G342" t="n">
-        <v>2.58406400680542</v>
+        <v>2.58406448364258</v>
       </c>
       <c r="H342" t="n">
         <v>1269331</v>
@@ -10316,7 +10316,7 @@
         <v>3.67000007629395</v>
       </c>
       <c r="G343" t="n">
-        <v>2.68047308921814</v>
+        <v>2.68047332763672</v>
       </c>
       <c r="H343" t="n">
         <v>2317544</v>
@@ -10345,7 +10345,7 @@
         <v>3.67400002479553</v>
       </c>
       <c r="G344" t="n">
-        <v>2.68339467048645</v>
+        <v>2.68339490890503</v>
       </c>
       <c r="H344" t="n">
         <v>1039383</v>
@@ -10432,7 +10432,7 @@
         <v>3.99000000953674</v>
       </c>
       <c r="G347" t="n">
-        <v>2.91419315338135</v>
+        <v>2.91419291496277</v>
       </c>
       <c r="H347" t="n">
         <v>4197821</v>
@@ -10490,7 +10490,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G349" t="n">
-        <v>2.64395475387573</v>
+        <v>2.64395451545715</v>
       </c>
       <c r="H349" t="n">
         <v>1515640</v>
@@ -10519,7 +10519,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G350" t="n">
-        <v>2.62934708595276</v>
+        <v>2.62934732437134</v>
       </c>
       <c r="H350" t="n">
         <v>1262546</v>
@@ -10548,7 +10548,7 @@
         <v>3.58999991416931</v>
       </c>
       <c r="G351" t="n">
-        <v>2.62204313278198</v>
+        <v>2.62204337120056</v>
       </c>
       <c r="H351" t="n">
         <v>901934</v>
@@ -10577,7 +10577,7 @@
         <v>3.58999991416931</v>
       </c>
       <c r="G352" t="n">
-        <v>2.62204313278198</v>
+        <v>2.62204337120056</v>
       </c>
       <c r="H352" t="n">
         <v>2474482</v>
@@ -10635,7 +10635,7 @@
         <v>3.62400007247925</v>
       </c>
       <c r="G354" t="n">
-        <v>2.64687609672546</v>
+        <v>2.64687633514404</v>
       </c>
       <c r="H354" t="n">
         <v>854728</v>
@@ -10664,7 +10664,7 @@
         <v>3.58200001716614</v>
       </c>
       <c r="G355" t="n">
-        <v>2.61620044708252</v>
+        <v>2.61620020866394</v>
       </c>
       <c r="H355" t="n">
         <v>563734</v>
@@ -10722,7 +10722,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G357" t="n">
-        <v>2.62934708595276</v>
+        <v>2.62934732437134</v>
       </c>
       <c r="H357" t="n">
         <v>431432</v>
@@ -10751,7 +10751,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G358" t="n">
-        <v>2.64395475387573</v>
+        <v>2.64395451545715</v>
       </c>
       <c r="H358" t="n">
         <v>896876</v>
@@ -10780,7 +10780,7 @@
         <v>3.71600008010864</v>
       </c>
       <c r="G359" t="n">
-        <v>2.71407055854797</v>
+        <v>2.71407079696655</v>
       </c>
       <c r="H359" t="n">
         <v>1393493</v>
@@ -10809,7 +10809,7 @@
         <v>3.65400004386902</v>
       </c>
       <c r="G360" t="n">
-        <v>2.66878724098206</v>
+        <v>2.66878747940063</v>
       </c>
       <c r="H360" t="n">
         <v>969486</v>
@@ -10838,7 +10838,7 @@
         <v>3.67000007629395</v>
       </c>
       <c r="G361" t="n">
-        <v>2.68047308921814</v>
+        <v>2.68047332763672</v>
       </c>
       <c r="H361" t="n">
         <v>583788</v>
@@ -10925,7 +10925,7 @@
         <v>4.01999998092651</v>
       </c>
       <c r="G364" t="n">
-        <v>2.93610405921936</v>
+        <v>2.93610429763794</v>
       </c>
       <c r="H364" t="n">
         <v>4568335</v>
@@ -10983,7 +10983,7 @@
         <v>4.48999977111816</v>
       </c>
       <c r="G366" t="n">
-        <v>3.27937960624695</v>
+        <v>3.27938008308411</v>
       </c>
       <c r="H366" t="n">
         <v>4791473</v>
@@ -11012,7 +11012,7 @@
         <v>4.51999998092651</v>
       </c>
       <c r="G367" t="n">
-        <v>3.3012912273407</v>
+        <v>3.30129170417786</v>
       </c>
       <c r="H367" t="n">
         <v>3044084</v>
@@ -11041,7 +11041,7 @@
         <v>4.53000020980835</v>
       </c>
       <c r="G368" t="n">
-        <v>3.30859541893005</v>
+        <v>3.30859518051147</v>
       </c>
       <c r="H368" t="n">
         <v>2187492</v>
@@ -11070,7 +11070,7 @@
         <v>4.41400003433228</v>
       </c>
       <c r="G369" t="n">
-        <v>3.22387170791626</v>
+        <v>3.22387218475342</v>
       </c>
       <c r="H369" t="n">
         <v>2245020</v>
@@ -11099,7 +11099,7 @@
         <v>4.39400005340576</v>
       </c>
       <c r="G370" t="n">
-        <v>3.20926475524902</v>
+        <v>3.20926451683044</v>
       </c>
       <c r="H370" t="n">
         <v>1665028</v>
@@ -11128,7 +11128,7 @@
         <v>4.38000011444092</v>
       </c>
       <c r="G371" t="n">
-        <v>3.19903945922852</v>
+        <v>3.19903922080994</v>
       </c>
       <c r="H371" t="n">
         <v>1363257</v>
@@ -11186,7 +11186,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G373" t="n">
-        <v>3.14060950279236</v>
+        <v>3.14060926437378</v>
       </c>
       <c r="H373" t="n">
         <v>1472806</v>
@@ -11273,7 +11273,7 @@
         <v>4.21400022506714</v>
       </c>
       <c r="G376" t="n">
-        <v>3.07779717445374</v>
+        <v>3.07779693603516</v>
       </c>
       <c r="H376" t="n">
         <v>717223</v>
@@ -11331,7 +11331,7 @@
         <v>4.23400020599365</v>
       </c>
       <c r="G378" t="n">
-        <v>3.09240436553955</v>
+        <v>3.09240460395813</v>
       </c>
       <c r="H378" t="n">
         <v>1004468</v>
@@ -11360,7 +11360,7 @@
         <v>4.38399982452393</v>
       </c>
       <c r="G379" t="n">
-        <v>3.20196056365967</v>
+        <v>3.20196032524109</v>
       </c>
       <c r="H379" t="n">
         <v>1196994</v>
@@ -11476,7 +11476,7 @@
         <v>4.12400007247925</v>
       </c>
       <c r="G383" t="n">
-        <v>3.01206302642822</v>
+        <v>3.0120632648468</v>
       </c>
       <c r="H383" t="n">
         <v>853072</v>
@@ -11534,7 +11534,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G385" t="n">
-        <v>2.95801591873169</v>
+        <v>2.95801568031311</v>
       </c>
       <c r="H385" t="n">
         <v>1193312</v>
@@ -11592,7 +11592,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G387" t="n">
-        <v>3.14060950279236</v>
+        <v>3.14060926437378</v>
       </c>
       <c r="H387" t="n">
         <v>960023</v>
@@ -11621,7 +11621,7 @@
         <v>4.23799991607666</v>
       </c>
       <c r="G388" t="n">
-        <v>3.09532594680786</v>
+        <v>3.09532570838928</v>
       </c>
       <c r="H388" t="n">
         <v>595089</v>
@@ -11650,7 +11650,7 @@
         <v>4.18800020217896</v>
       </c>
       <c r="G389" t="n">
-        <v>3.05880737304688</v>
+        <v>3.0588071346283</v>
       </c>
       <c r="H389" t="n">
         <v>425357</v>
@@ -11679,7 +11679,7 @@
         <v>4.26999998092651</v>
       </c>
       <c r="G390" t="n">
-        <v>3.11869788169861</v>
+        <v>3.11869764328003</v>
       </c>
       <c r="H390" t="n">
         <v>462504</v>
@@ -11708,7 +11708,7 @@
         <v>4.17000007629395</v>
       </c>
       <c r="G391" t="n">
-        <v>3.04566049575806</v>
+        <v>3.04566073417664</v>
       </c>
       <c r="H391" t="n">
         <v>630856</v>
@@ -11824,7 +11824,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G395" t="n">
-        <v>3.08217883110046</v>
+        <v>3.08217906951904</v>
       </c>
       <c r="H395" t="n">
         <v>385077</v>
@@ -11853,7 +11853,7 @@
         <v>4.23400020599365</v>
       </c>
       <c r="G396" t="n">
-        <v>3.09240436553955</v>
+        <v>3.09240460395813</v>
       </c>
       <c r="H396" t="n">
         <v>485386</v>
@@ -11911,7 +11911,7 @@
         <v>4.25400018692017</v>
       </c>
       <c r="G398" t="n">
-        <v>3.10701203346252</v>
+        <v>3.1070122718811</v>
       </c>
       <c r="H398" t="n">
         <v>1999318</v>
@@ -11940,7 +11940,7 @@
         <v>4.21400022506714</v>
       </c>
       <c r="G399" t="n">
-        <v>3.07779717445374</v>
+        <v>3.07779693603516</v>
       </c>
       <c r="H399" t="n">
         <v>1049550</v>
@@ -11969,7 +11969,7 @@
         <v>4.26800012588501</v>
       </c>
       <c r="G400" t="n">
-        <v>3.11723732948303</v>
+        <v>3.11723756790161</v>
       </c>
       <c r="H400" t="n">
         <v>876487</v>
@@ -11998,7 +11998,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G401" t="n">
-        <v>3.16982436180115</v>
+        <v>3.16982460021973</v>
       </c>
       <c r="H401" t="n">
         <v>739022</v>
@@ -12027,7 +12027,7 @@
         <v>4.44799995422363</v>
       </c>
       <c r="G402" t="n">
-        <v>3.24870467185974</v>
+        <v>3.24870443344116</v>
       </c>
       <c r="H402" t="n">
         <v>1608154</v>
@@ -12056,7 +12056,7 @@
         <v>4.51999998092651</v>
       </c>
       <c r="G403" t="n">
-        <v>3.3012912273407</v>
+        <v>3.30129170417786</v>
       </c>
       <c r="H403" t="n">
         <v>2962793</v>
@@ -12085,7 +12085,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G404" t="n">
-        <v>3.3597207069397</v>
+        <v>3.35972118377686</v>
       </c>
       <c r="H404" t="n">
         <v>1699595</v>
@@ -12143,7 +12143,7 @@
         <v>4.64200019836426</v>
       </c>
       <c r="G406" t="n">
-        <v>3.39039707183838</v>
+        <v>3.39039731025696</v>
       </c>
       <c r="H406" t="n">
         <v>2198972</v>
@@ -12172,7 +12172,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G407" t="n">
-        <v>3.44736623764038</v>
+        <v>3.4473659992218</v>
       </c>
       <c r="H407" t="n">
         <v>1759565</v>
@@ -12259,7 +12259,7 @@
         <v>4.60599994659424</v>
       </c>
       <c r="G410" t="n">
-        <v>3.36410355567932</v>
+        <v>3.3641037940979</v>
       </c>
       <c r="H410" t="n">
         <v>448439</v>
@@ -12346,7 +12346,7 @@
         <v>4.78999996185303</v>
       </c>
       <c r="G413" t="n">
-        <v>3.4984929561615</v>
+        <v>3.49849247932434</v>
       </c>
       <c r="H413" t="n">
         <v>1092923</v>
@@ -12375,7 +12375,7 @@
         <v>4.67000007629395</v>
       </c>
       <c r="G414" t="n">
-        <v>3.41084766387939</v>
+        <v>3.41084790229797</v>
       </c>
       <c r="H414" t="n">
         <v>797800</v>
@@ -12433,7 +12433,7 @@
         <v>5.04500007629395</v>
       </c>
       <c r="G416" t="n">
-        <v>3.68473815917969</v>
+        <v>3.68473768234253</v>
       </c>
       <c r="H416" t="n">
         <v>2954441</v>
@@ -12491,7 +12491,7 @@
         <v>5</v>
       </c>
       <c r="G418" t="n">
-        <v>3.65187072753906</v>
+        <v>3.65187096595764</v>
       </c>
       <c r="H418" t="n">
         <v>782492</v>
@@ -12549,7 +12549,7 @@
         <v>5.03999996185303</v>
       </c>
       <c r="G420" t="n">
-        <v>3.68108630180359</v>
+        <v>3.68108606338501</v>
       </c>
       <c r="H420" t="n">
         <v>1258543</v>
@@ -12607,7 +12607,7 @@
         <v>4.99599981307983</v>
       </c>
       <c r="G422" t="n">
-        <v>3.64894866943359</v>
+        <v>3.64894962310791</v>
       </c>
       <c r="H422" t="n">
         <v>985145</v>
@@ -12636,7 +12636,7 @@
         <v>4.98600006103516</v>
       </c>
       <c r="G423" t="n">
-        <v>3.64164543151855</v>
+        <v>3.64164590835571</v>
       </c>
       <c r="H423" t="n">
         <v>598956</v>
@@ -12665,7 +12665,7 @@
         <v>4.9060001373291</v>
       </c>
       <c r="G424" t="n">
-        <v>3.5832154750824</v>
+        <v>3.58321595191956</v>
       </c>
       <c r="H424" t="n">
         <v>845512</v>
@@ -12694,7 +12694,7 @@
         <v>4.86999988555908</v>
       </c>
       <c r="G425" t="n">
-        <v>3.55692291259766</v>
+        <v>3.55692195892334</v>
       </c>
       <c r="H425" t="n">
         <v>1064355</v>
@@ -12723,7 +12723,7 @@
         <v>4.94199991226196</v>
       </c>
       <c r="G426" t="n">
-        <v>3.60950970649719</v>
+        <v>3.60950899124146</v>
       </c>
       <c r="H426" t="n">
         <v>1027416</v>
@@ -12752,7 +12752,7 @@
         <v>5.09499979019165</v>
       </c>
       <c r="G427" t="n">
-        <v>3.72125673294067</v>
+        <v>3.72125649452209</v>
       </c>
       <c r="H427" t="n">
         <v>1575846</v>
@@ -12781,7 +12781,7 @@
         <v>5.14499998092651</v>
       </c>
       <c r="G428" t="n">
-        <v>3.7577760219574</v>
+        <v>3.75777530670166</v>
       </c>
       <c r="H428" t="n">
         <v>1193106</v>
@@ -12810,7 +12810,7 @@
         <v>5.32000017166138</v>
       </c>
       <c r="G429" t="n">
-        <v>3.88559079170227</v>
+        <v>3.88559103012085</v>
       </c>
       <c r="H429" t="n">
         <v>4718108</v>
@@ -12839,7 +12839,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G430" t="n">
-        <v>3.87098360061646</v>
+        <v>3.87098288536072</v>
       </c>
       <c r="H430" t="n">
         <v>1070273</v>
@@ -12868,7 +12868,7 @@
         <v>5.28000020980835</v>
       </c>
       <c r="G431" t="n">
-        <v>3.85637593269348</v>
+        <v>3.8563756942749</v>
       </c>
       <c r="H431" t="n">
         <v>1287102</v>
@@ -12897,7 +12897,7 @@
         <v>5.26999998092651</v>
       </c>
       <c r="G432" t="n">
-        <v>3.84907221794128</v>
+        <v>3.84907197952271</v>
       </c>
       <c r="H432" t="n">
         <v>770255</v>
@@ -12926,7 +12926,7 @@
         <v>5.30499982833862</v>
       </c>
       <c r="G433" t="n">
-        <v>3.87463545799255</v>
+        <v>3.87463450431824</v>
       </c>
       <c r="H433" t="n">
         <v>800491</v>
@@ -12984,7 +12984,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G435" t="n">
-        <v>3.94402074813843</v>
+        <v>3.94402050971985</v>
       </c>
       <c r="H435" t="n">
         <v>1164002</v>
@@ -13013,7 +13013,7 @@
         <v>5.30499982833862</v>
       </c>
       <c r="G436" t="n">
-        <v>3.87463545799255</v>
+        <v>3.87463450431824</v>
       </c>
       <c r="H436" t="n">
         <v>785094</v>
@@ -13042,7 +13042,7 @@
         <v>5.2350001335144</v>
       </c>
       <c r="G437" t="n">
-        <v>3.82350873947144</v>
+        <v>3.82350945472717</v>
       </c>
       <c r="H437" t="n">
         <v>1278252</v>
@@ -13071,7 +13071,7 @@
         <v>4.80399990081787</v>
       </c>
       <c r="G438" t="n">
-        <v>3.50871777534485</v>
+        <v>3.50871801376343</v>
       </c>
       <c r="H438" t="n">
         <v>8610626</v>
@@ -13100,7 +13100,7 @@
         <v>4.84999990463257</v>
       </c>
       <c r="G439" t="n">
-        <v>3.54231476783752</v>
+        <v>3.5423150062561</v>
       </c>
       <c r="H439" t="n">
         <v>1525015</v>
@@ -13129,7 +13129,7 @@
         <v>4.67600011825562</v>
       </c>
       <c r="G440" t="n">
-        <v>3.4152295589447</v>
+        <v>3.41522979736328</v>
       </c>
       <c r="H440" t="n">
         <v>2692706</v>
@@ -13187,7 +13187,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G442" t="n">
-        <v>3.3597207069397</v>
+        <v>3.35972118377686</v>
       </c>
       <c r="H442" t="n">
         <v>2609133</v>
@@ -13216,7 +13216,7 @@
         <v>4.57000017166138</v>
       </c>
       <c r="G443" t="n">
-        <v>3.33781027793884</v>
+        <v>3.33781051635742</v>
       </c>
       <c r="H443" t="n">
         <v>1130511</v>
@@ -13274,7 +13274,7 @@
         <v>4.46999979019165</v>
       </c>
       <c r="G445" t="n">
-        <v>3.26477313041687</v>
+        <v>3.26477289199829</v>
       </c>
       <c r="H445" t="n">
         <v>1503291</v>
@@ -13303,7 +13303,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G446" t="n">
-        <v>3.32320308685303</v>
+        <v>3.32320237159729</v>
       </c>
       <c r="H446" t="n">
         <v>1959263</v>
@@ -13332,7 +13332,7 @@
         <v>4.66200017929077</v>
       </c>
       <c r="G447" t="n">
-        <v>3.40500450134277</v>
+        <v>3.40500473976135</v>
       </c>
       <c r="H447" t="n">
         <v>1860068</v>
@@ -13361,7 +13361,7 @@
         <v>4.68200016021729</v>
       </c>
       <c r="G448" t="n">
-        <v>3.41961169242859</v>
+        <v>3.41961216926575</v>
       </c>
       <c r="H448" t="n">
         <v>1800630</v>
@@ -13419,7 +13419,7 @@
         <v>4.78599977493286</v>
       </c>
       <c r="G450" t="n">
-        <v>3.49557065963745</v>
+        <v>3.49557089805603</v>
       </c>
       <c r="H450" t="n">
         <v>1759692</v>
@@ -13448,7 +13448,7 @@
         <v>4.63600015640259</v>
       </c>
       <c r="G451" t="n">
-        <v>3.38601517677307</v>
+        <v>3.38601493835449</v>
       </c>
       <c r="H451" t="n">
         <v>1182798</v>
@@ -13477,7 +13477,7 @@
         <v>4.66200017929077</v>
       </c>
       <c r="G452" t="n">
-        <v>3.40500450134277</v>
+        <v>3.40500473976135</v>
       </c>
       <c r="H452" t="n">
         <v>1401039</v>
@@ -13506,7 +13506,7 @@
         <v>4.65799999237061</v>
       </c>
       <c r="G453" t="n">
-        <v>3.40208315849304</v>
+        <v>3.40208292007446</v>
       </c>
       <c r="H453" t="n">
         <v>725506</v>
@@ -13564,7 +13564,7 @@
         <v>4.5479998588562</v>
       </c>
       <c r="G455" t="n">
-        <v>3.32174134254456</v>
+        <v>3.32174205780029</v>
       </c>
       <c r="H455" t="n">
         <v>1117252</v>
@@ -13622,7 +13622,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G457" t="n">
-        <v>3.32320308685303</v>
+        <v>3.32320237159729</v>
       </c>
       <c r="H457" t="n">
         <v>1164935</v>
@@ -13680,7 +13680,7 @@
         <v>4.67600011825562</v>
       </c>
       <c r="G459" t="n">
-        <v>3.4152295589447</v>
+        <v>3.41522979736328</v>
       </c>
       <c r="H459" t="n">
         <v>786652</v>
@@ -13709,7 +13709,7 @@
         <v>4.66200017929077</v>
       </c>
       <c r="G460" t="n">
-        <v>3.40500450134277</v>
+        <v>3.40500473976135</v>
       </c>
       <c r="H460" t="n">
         <v>975846</v>
@@ -13738,7 +13738,7 @@
         <v>4.6399998664856</v>
       </c>
       <c r="G461" t="n">
-        <v>3.38893604278564</v>
+        <v>3.3889365196228</v>
       </c>
       <c r="H461" t="n">
         <v>746729</v>
@@ -13825,7 +13825,7 @@
         <v>4.68599987030029</v>
       </c>
       <c r="G464" t="n">
-        <v>3.42253351211548</v>
+        <v>3.42253398895264</v>
       </c>
       <c r="H464" t="n">
         <v>1498520</v>
@@ -13854,7 +13854,7 @@
         <v>4.72399997711182</v>
       </c>
       <c r="G465" t="n">
-        <v>3.45028781890869</v>
+        <v>3.45028758049011</v>
       </c>
       <c r="H465" t="n">
         <v>1244111</v>
@@ -13883,7 +13883,7 @@
         <v>4.63199996948242</v>
       </c>
       <c r="G466" t="n">
-        <v>3.38309335708618</v>
+        <v>3.38309383392334</v>
       </c>
       <c r="H466" t="n">
         <v>1099763</v>
@@ -13912,7 +13912,7 @@
         <v>4.69600009918213</v>
       </c>
       <c r="G467" t="n">
-        <v>3.42983770370483</v>
+        <v>3.42983722686768</v>
       </c>
       <c r="H467" t="n">
         <v>1149311</v>
@@ -13941,7 +13941,7 @@
         <v>4.67799997329712</v>
       </c>
       <c r="G468" t="n">
-        <v>3.41669034957886</v>
+        <v>3.41669082641602</v>
       </c>
       <c r="H468" t="n">
         <v>852749</v>
@@ -14057,7 +14057,7 @@
         <v>4.88800001144409</v>
       </c>
       <c r="G472" t="n">
-        <v>3.57006931304932</v>
+        <v>3.57006883621216</v>
       </c>
       <c r="H472" t="n">
         <v>3242330</v>
@@ -14144,7 +14144,7 @@
         <v>4.72399997711182</v>
       </c>
       <c r="G475" t="n">
-        <v>3.45028781890869</v>
+        <v>3.45028758049011</v>
       </c>
       <c r="H475" t="n">
         <v>5668124</v>
@@ -14173,7 +14173,7 @@
         <v>4.25400018692017</v>
       </c>
       <c r="G476" t="n">
-        <v>3.10701203346252</v>
+        <v>3.1070122718811</v>
       </c>
       <c r="H476" t="n">
         <v>13059436</v>
@@ -14202,7 +14202,7 @@
         <v>4.05999994277954</v>
       </c>
       <c r="G477" t="n">
-        <v>2.96531963348389</v>
+        <v>2.96531915664673</v>
       </c>
       <c r="H477" t="n">
         <v>8176905</v>
@@ -14231,7 +14231,7 @@
         <v>4.28399991989136</v>
       </c>
       <c r="G478" t="n">
-        <v>3.12892317771912</v>
+        <v>3.12892270088196</v>
       </c>
       <c r="H478" t="n">
         <v>5219522</v>
@@ -14260,7 +14260,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G479" t="n">
-        <v>2.9872305393219</v>
+        <v>2.98723077774048</v>
       </c>
       <c r="H479" t="n">
         <v>2890659</v>
@@ -14289,7 +14289,7 @@
         <v>3.98799991607666</v>
       </c>
       <c r="G480" t="n">
-        <v>2.91273212432861</v>
+        <v>2.91273236274719</v>
       </c>
       <c r="H480" t="n">
         <v>3857907</v>
@@ -14318,7 +14318,7 @@
         <v>4.03200006484985</v>
       </c>
       <c r="G481" t="n">
-        <v>2.94486880302429</v>
+        <v>2.94486904144287</v>
       </c>
       <c r="H481" t="n">
         <v>3248454</v>
@@ -14347,7 +14347,7 @@
         <v>4.07000017166138</v>
       </c>
       <c r="G482" t="n">
-        <v>2.9726231098175</v>
+        <v>2.97262334823608</v>
       </c>
       <c r="H482" t="n">
         <v>1891076</v>
@@ -14376,7 +14376,7 @@
         <v>4.07000017166138</v>
       </c>
       <c r="G483" t="n">
-        <v>2.9726231098175</v>
+        <v>2.97262334823608</v>
       </c>
       <c r="H483" t="n">
         <v>1212165</v>
@@ -14434,7 +14434,7 @@
         <v>4.15399980545044</v>
       </c>
       <c r="G485" t="n">
-        <v>3.03397440910339</v>
+        <v>3.03397464752197</v>
       </c>
       <c r="H485" t="n">
         <v>1284797</v>
@@ -14463,7 +14463,7 @@
         <v>4.19600009918213</v>
       </c>
       <c r="G486" t="n">
-        <v>3.06465005874634</v>
+        <v>3.0646505355835</v>
       </c>
       <c r="H486" t="n">
         <v>1066719</v>
@@ -14492,7 +14492,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G487" t="n">
-        <v>3.09678649902344</v>
+        <v>3.09678626060486</v>
       </c>
       <c r="H487" t="n">
         <v>1571146</v>
@@ -14521,7 +14521,7 @@
         <v>4.24399995803833</v>
       </c>
       <c r="G488" t="n">
-        <v>3.09970808029175</v>
+        <v>3.09970855712891</v>
       </c>
       <c r="H488" t="n">
         <v>1320516</v>
@@ -14550,7 +14550,7 @@
         <v>4.13399982452393</v>
       </c>
       <c r="G489" t="n">
-        <v>3.019366979599</v>
+        <v>3.01936650276184</v>
       </c>
       <c r="H489" t="n">
         <v>1397544</v>
@@ -14608,7 +14608,7 @@
         <v>3.73399996757507</v>
       </c>
       <c r="G491" t="n">
-        <v>2.72721695899963</v>
+        <v>2.72721719741821</v>
       </c>
       <c r="H491" t="n">
         <v>4547770</v>
@@ -14637,7 +14637,7 @@
         <v>3.86199998855591</v>
       </c>
       <c r="G492" t="n">
-        <v>2.82070517539978</v>
+        <v>2.82070541381836</v>
       </c>
       <c r="H492" t="n">
         <v>2865916</v>
@@ -14666,7 +14666,7 @@
         <v>3.7260000705719</v>
       </c>
       <c r="G493" t="n">
-        <v>2.72137451171875</v>
+        <v>2.72137403488159</v>
       </c>
       <c r="H493" t="n">
         <v>3115446</v>
@@ -14695,7 +14695,7 @@
         <v>3.86800003051758</v>
       </c>
       <c r="G494" t="n">
-        <v>2.82508730888367</v>
+        <v>2.82508754730225</v>
       </c>
       <c r="H494" t="n">
         <v>2667264</v>
@@ -14753,7 +14753,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G496" t="n">
-        <v>2.73159956932068</v>
+        <v>2.7315993309021</v>
       </c>
       <c r="H496" t="n">
         <v>1253644</v>
@@ -14782,7 +14782,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G497" t="n">
-        <v>2.8192446231842</v>
+        <v>2.81924414634705</v>
       </c>
       <c r="H497" t="n">
         <v>1803333</v>
@@ -14811,7 +14811,7 @@
         <v>3.90799999237061</v>
       </c>
       <c r="G498" t="n">
-        <v>2.85430240631104</v>
+        <v>2.85430216789246</v>
       </c>
       <c r="H498" t="n">
         <v>935309</v>
@@ -14869,7 +14869,7 @@
         <v>3.91199994087219</v>
       </c>
       <c r="G500" t="n">
-        <v>2.85722398757935</v>
+        <v>2.85722374916077</v>
       </c>
       <c r="H500" t="n">
         <v>1496665</v>
@@ -14898,7 +14898,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G501" t="n">
-        <v>2.84845972061157</v>
+        <v>2.84845948219299</v>
       </c>
       <c r="H501" t="n">
         <v>1149762</v>
@@ -14927,7 +14927,7 @@
         <v>3.88199996948242</v>
       </c>
       <c r="G502" t="n">
-        <v>2.83531284332275</v>
+        <v>2.83531260490417</v>
       </c>
       <c r="H502" t="n">
         <v>875177</v>
@@ -14956,7 +14956,7 @@
         <v>4.05800008773804</v>
       </c>
       <c r="G503" t="n">
-        <v>2.96385884284973</v>
+        <v>2.96385836601257</v>
       </c>
       <c r="H503" t="n">
         <v>2546236</v>
@@ -15014,7 +15014,7 @@
         <v>4.07000017166138</v>
       </c>
       <c r="G505" t="n">
-        <v>2.9726231098175</v>
+        <v>2.97262334823608</v>
       </c>
       <c r="H505" t="n">
         <v>1441473</v>
@@ -15072,7 +15072,7 @@
         <v>4.17199993133545</v>
       </c>
       <c r="G507" t="n">
-        <v>3.04712104797363</v>
+        <v>3.04712152481079</v>
       </c>
       <c r="H507" t="n">
         <v>1288265</v>
@@ -15101,7 +15101,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G508" t="n">
-        <v>3.09678649902344</v>
+        <v>3.09678626060486</v>
       </c>
       <c r="H508" t="n">
         <v>1505653</v>
@@ -15130,7 +15130,7 @@
         <v>4.27600002288818</v>
       </c>
       <c r="G509" t="n">
-        <v>3.1230800151825</v>
+        <v>3.12308025360107</v>
       </c>
       <c r="H509" t="n">
         <v>1055614</v>
@@ -15188,7 +15188,7 @@
         <v>4.31799983978271</v>
       </c>
       <c r="G511" t="n">
-        <v>3.15375566482544</v>
+        <v>3.15375590324402</v>
       </c>
       <c r="H511" t="n">
         <v>855946</v>
@@ -15217,7 +15217,7 @@
         <v>4.27600002288818</v>
       </c>
       <c r="G512" t="n">
-        <v>3.1230800151825</v>
+        <v>3.12308025360107</v>
       </c>
       <c r="H512" t="n">
         <v>1441598</v>
@@ -15246,7 +15246,7 @@
         <v>4.26599979400635</v>
       </c>
       <c r="G513" t="n">
-        <v>3.11577606201172</v>
+        <v>3.1157763004303</v>
       </c>
       <c r="H513" t="n">
         <v>989524</v>
@@ -15275,7 +15275,7 @@
         <v>4.37599992752075</v>
       </c>
       <c r="G514" t="n">
-        <v>3.19611763954163</v>
+        <v>3.19611787796021</v>
       </c>
       <c r="H514" t="n">
         <v>1297302</v>
@@ -15304,7 +15304,7 @@
         <v>4.37400007247925</v>
       </c>
       <c r="G515" t="n">
-        <v>3.19465708732605</v>
+        <v>3.19465684890747</v>
       </c>
       <c r="H515" t="n">
         <v>1279062</v>
@@ -15362,7 +15362,7 @@
         <v>4.35400009155273</v>
       </c>
       <c r="G517" t="n">
-        <v>3.18004965782166</v>
+        <v>3.1800491809845</v>
       </c>
       <c r="H517" t="n">
         <v>1488465</v>
@@ -15391,7 +15391,7 @@
         <v>4.41400003433228</v>
       </c>
       <c r="G518" t="n">
-        <v>3.22387170791626</v>
+        <v>3.22387218475342</v>
       </c>
       <c r="H518" t="n">
         <v>1447824</v>
@@ -15420,7 +15420,7 @@
         <v>4.46199989318848</v>
       </c>
       <c r="G519" t="n">
-        <v>3.25892996788025</v>
+        <v>3.25892972946167</v>
       </c>
       <c r="H519" t="n">
         <v>1177723</v>
@@ -15449,7 +15449,7 @@
         <v>4.46199989318848</v>
       </c>
       <c r="G520" t="n">
-        <v>3.25892996788025</v>
+        <v>3.25892972946167</v>
       </c>
       <c r="H520" t="n">
         <v>1812364</v>
@@ -15478,7 +15478,7 @@
         <v>4.47200012207031</v>
       </c>
       <c r="G521" t="n">
-        <v>3.26623320579529</v>
+        <v>3.26623368263245</v>
       </c>
       <c r="H521" t="n">
         <v>769824</v>
@@ -15507,7 +15507,7 @@
         <v>4.44999980926514</v>
       </c>
       <c r="G522" t="n">
-        <v>3.2501654624939</v>
+        <v>3.25016522407532</v>
       </c>
       <c r="H522" t="n">
         <v>1001717</v>
@@ -15536,7 +15536,7 @@
         <v>4.30600023269653</v>
       </c>
       <c r="G523" t="n">
-        <v>3.14499187469482</v>
+        <v>3.14499139785767</v>
       </c>
       <c r="H523" t="n">
         <v>2365832</v>
@@ -15565,7 +15565,7 @@
         <v>4.39400005340576</v>
       </c>
       <c r="G524" t="n">
-        <v>3.20926475524902</v>
+        <v>3.20926451683044</v>
       </c>
       <c r="H524" t="n">
         <v>1499817</v>
@@ -15594,7 +15594,7 @@
         <v>4.37400007247925</v>
       </c>
       <c r="G525" t="n">
-        <v>3.19465708732605</v>
+        <v>3.19465684890747</v>
       </c>
       <c r="H525" t="n">
         <v>1490471</v>
@@ -15623,7 +15623,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G526" t="n">
-        <v>3.25746917724609</v>
+        <v>3.25746941566467</v>
       </c>
       <c r="H526" t="n">
         <v>1195732</v>
@@ -15652,7 +15652,7 @@
         <v>4.46999979019165</v>
       </c>
       <c r="G527" t="n">
-        <v>3.26477313041687</v>
+        <v>3.26477289199829</v>
       </c>
       <c r="H527" t="n">
         <v>1074482</v>
@@ -15681,7 +15681,7 @@
         <v>4.37400007247925</v>
       </c>
       <c r="G528" t="n">
-        <v>3.19465708732605</v>
+        <v>3.19465684890747</v>
       </c>
       <c r="H528" t="n">
         <v>1115667</v>
@@ -15710,7 +15710,7 @@
         <v>4.35599994659424</v>
       </c>
       <c r="G529" t="n">
-        <v>3.18150973320007</v>
+        <v>3.18151021003723</v>
       </c>
       <c r="H529" t="n">
         <v>2007212</v>
@@ -15739,7 +15739,7 @@
         <v>4.34800004959106</v>
       </c>
       <c r="G530" t="n">
-        <v>3.17566680908203</v>
+        <v>3.17566704750061</v>
       </c>
       <c r="H530" t="n">
         <v>2421487</v>
@@ -15768,7 +15768,7 @@
         <v>4.29400014877319</v>
       </c>
       <c r="G531" t="n">
-        <v>3.13622736930847</v>
+        <v>3.13622713088989</v>
       </c>
       <c r="H531" t="n">
         <v>1131789</v>
@@ -15797,7 +15797,7 @@
         <v>4.16200017929077</v>
       </c>
       <c r="G532" t="n">
-        <v>3.03981757164001</v>
+        <v>3.03981733322144</v>
       </c>
       <c r="H532" t="n">
         <v>1639422</v>
@@ -15855,7 +15855,7 @@
         <v>4.19000005722046</v>
       </c>
       <c r="G534" t="n">
-        <v>3.06026792526245</v>
+        <v>3.06026816368103</v>
       </c>
       <c r="H534" t="n">
         <v>2302959</v>
@@ -15913,7 +15913,7 @@
         <v>4.05999994277954</v>
       </c>
       <c r="G536" t="n">
-        <v>2.96531963348389</v>
+        <v>2.96531915664673</v>
       </c>
       <c r="H536" t="n">
         <v>1245804</v>
@@ -15942,7 +15942,7 @@
         <v>3.9300000667572</v>
       </c>
       <c r="G537" t="n">
-        <v>2.87037038803101</v>
+        <v>2.87037062644958</v>
       </c>
       <c r="H537" t="n">
         <v>1688364</v>
@@ -16000,7 +16000,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G539" t="n">
-        <v>2.73159956932068</v>
+        <v>2.7315993309021</v>
       </c>
       <c r="H539" t="n">
         <v>1036569</v>
@@ -16029,7 +16029,7 @@
         <v>3.71799993515015</v>
       </c>
       <c r="G540" t="n">
-        <v>2.71553134918213</v>
+        <v>2.71553158760071</v>
       </c>
       <c r="H540" t="n">
         <v>1103068</v>
@@ -16058,7 +16058,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G541" t="n">
-        <v>2.73159956932068</v>
+        <v>2.7315993309021</v>
       </c>
       <c r="H541" t="n">
         <v>1181795</v>
@@ -16087,7 +16087,7 @@
         <v>3.66799998283386</v>
       </c>
       <c r="G542" t="n">
-        <v>2.67901253700256</v>
+        <v>2.67901277542114</v>
       </c>
       <c r="H542" t="n">
         <v>562740</v>
@@ -16116,7 +16116,7 @@
         <v>3.72399997711182</v>
       </c>
       <c r="G543" t="n">
-        <v>2.71991372108459</v>
+        <v>2.71991348266602</v>
       </c>
       <c r="H543" t="n">
         <v>940742</v>
@@ -16203,7 +16203,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G546" t="n">
-        <v>2.76811814308167</v>
+        <v>2.76811838150024</v>
       </c>
       <c r="H546" t="n">
         <v>636644</v>
@@ -16232,7 +16232,7 @@
         <v>3.76399993896484</v>
       </c>
       <c r="G547" t="n">
-        <v>2.74912881851196</v>
+        <v>2.74912858009338</v>
       </c>
       <c r="H547" t="n">
         <v>535970</v>
@@ -16261,7 +16261,7 @@
         <v>3.78200006484985</v>
       </c>
       <c r="G548" t="n">
-        <v>2.76227498054504</v>
+        <v>2.76227521896362</v>
       </c>
       <c r="H548" t="n">
         <v>378051</v>
@@ -16319,7 +16319,7 @@
         <v>3.72399997711182</v>
       </c>
       <c r="G550" t="n">
-        <v>2.71991372108459</v>
+        <v>2.71991348266602</v>
       </c>
       <c r="H550" t="n">
         <v>973499</v>
@@ -16348,7 +16348,7 @@
         <v>4.03000020980835</v>
       </c>
       <c r="G551" t="n">
-        <v>2.94340825080872</v>
+        <v>2.94340801239014</v>
       </c>
       <c r="H551" t="n">
         <v>4340802</v>
@@ -16377,7 +16377,7 @@
         <v>3.97000002861023</v>
       </c>
       <c r="G552" t="n">
-        <v>2.89958596229553</v>
+        <v>2.89958572387695</v>
       </c>
       <c r="H552" t="n">
         <v>1229486</v>
@@ -16406,7 +16406,7 @@
         <v>4</v>
       </c>
       <c r="G553" t="n">
-        <v>2.92149662971497</v>
+        <v>2.92149686813354</v>
       </c>
       <c r="H553" t="n">
         <v>1691621</v>
@@ -16435,7 +16435,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G554" t="n">
-        <v>2.84845972061157</v>
+        <v>2.84845948219299</v>
       </c>
       <c r="H554" t="n">
         <v>955088</v>
@@ -16464,7 +16464,7 @@
         <v>3.74600005149841</v>
       </c>
       <c r="G555" t="n">
-        <v>2.73598170280457</v>
+        <v>2.73598194122314</v>
       </c>
       <c r="H555" t="n">
         <v>1575398</v>
@@ -16609,7 +16609,7 @@
         <v>3.9760000705719</v>
       </c>
       <c r="G560" t="n">
-        <v>2.90396809577942</v>
+        <v>2.90396785736084</v>
       </c>
       <c r="H560" t="n">
         <v>1015956</v>
@@ -16725,7 +16725,7 @@
         <v>4.06599998474121</v>
       </c>
       <c r="G564" t="n">
-        <v>2.96970176696777</v>
+        <v>2.96970129013062</v>
       </c>
       <c r="H564" t="n">
         <v>1912241</v>
@@ -16754,7 +16754,7 @@
         <v>4.32000017166138</v>
       </c>
       <c r="G565" t="n">
-        <v>3.15521693229675</v>
+        <v>3.15521669387817</v>
       </c>
       <c r="H565" t="n">
         <v>3665068</v>
@@ -16986,7 +16986,7 @@
         <v>4.09200000762939</v>
       </c>
       <c r="G573" t="n">
-        <v>2.98869132995605</v>
+        <v>2.98869156837463</v>
       </c>
       <c r="H573" t="n">
         <v>1027649</v>
@@ -17015,7 +17015,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G574" t="n">
-        <v>3.05296397209167</v>
+        <v>3.05296421051025</v>
       </c>
       <c r="H574" t="n">
         <v>1494435</v>
@@ -17160,7 +17160,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G579" t="n">
-        <v>3.09678649902344</v>
+        <v>3.09678626060486</v>
       </c>
       <c r="H579" t="n">
         <v>529997</v>
@@ -17218,7 +17218,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G581" t="n">
-        <v>2.9799268245697</v>
+        <v>2.97992658615112</v>
       </c>
       <c r="H581" t="n">
         <v>824437</v>
@@ -17247,7 +17247,7 @@
         <v>4.08599996566772</v>
       </c>
       <c r="G582" t="n">
-        <v>2.98430943489075</v>
+        <v>2.98430919647217</v>
       </c>
       <c r="H582" t="n">
         <v>1016103</v>
@@ -17305,7 +17305,7 @@
         <v>4.18599987030029</v>
       </c>
       <c r="G584" t="n">
-        <v>3.05734610557556</v>
+        <v>3.05734634399414</v>
       </c>
       <c r="H584" t="n">
         <v>960169</v>
@@ -17334,7 +17334,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G585" t="n">
-        <v>3.09678649902344</v>
+        <v>3.09678626060486</v>
       </c>
       <c r="H585" t="n">
         <v>1549183</v>
@@ -17392,7 +17392,7 @@
         <v>4.38000011444092</v>
       </c>
       <c r="G587" t="n">
-        <v>3.19903945922852</v>
+        <v>3.19903922080994</v>
       </c>
       <c r="H587" t="n">
         <v>1370793</v>
@@ -17421,7 +17421,7 @@
         <v>4.32600021362305</v>
       </c>
       <c r="G588" t="n">
-        <v>3.1595995426178</v>
+        <v>3.15959906578064</v>
       </c>
       <c r="H588" t="n">
         <v>605039</v>
@@ -17450,7 +17450,7 @@
         <v>4.36600017547607</v>
       </c>
       <c r="G589" t="n">
-        <v>3.18881416320801</v>
+        <v>3.18881440162659</v>
       </c>
       <c r="H589" t="n">
         <v>962876</v>
@@ -17479,7 +17479,7 @@
         <v>4.2979998588562</v>
       </c>
       <c r="G590" t="n">
-        <v>3.13914823532104</v>
+        <v>3.13914847373962</v>
       </c>
       <c r="H590" t="n">
         <v>1240040</v>
@@ -17508,7 +17508,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G591" t="n">
-        <v>3.14060950279236</v>
+        <v>3.14060926437378</v>
       </c>
       <c r="H591" t="n">
         <v>491402</v>
@@ -17537,7 +17537,7 @@
         <v>4.3899998664856</v>
       </c>
       <c r="G592" t="n">
-        <v>3.20634317398071</v>
+        <v>3.20634269714355</v>
       </c>
       <c r="H592" t="n">
         <v>953280</v>
@@ -17566,7 +17566,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G593" t="n">
-        <v>3.14060950279236</v>
+        <v>3.14060926437378</v>
       </c>
       <c r="H593" t="n">
         <v>1136863</v>
@@ -17595,7 +17595,7 @@
         <v>4.22200012207031</v>
       </c>
       <c r="G594" t="n">
-        <v>3.17824864387512</v>
+        <v>3.17824840545654</v>
       </c>
       <c r="H594" t="n">
         <v>685890</v>
@@ -17624,7 +17624,7 @@
         <v>4.31799983978271</v>
       </c>
       <c r="G595" t="n">
-        <v>3.25051522254944</v>
+        <v>3.25051546096802</v>
       </c>
       <c r="H595" t="n">
         <v>1016588</v>
@@ -17682,7 +17682,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G597" t="n">
-        <v>3.42516136169434</v>
+        <v>3.42516088485718</v>
       </c>
       <c r="H597" t="n">
         <v>5557232</v>
@@ -17711,7 +17711,7 @@
         <v>4.65399980545044</v>
       </c>
       <c r="G598" t="n">
-        <v>3.50345015525818</v>
+        <v>3.50345039367676</v>
       </c>
       <c r="H598" t="n">
         <v>2139481</v>
@@ -17740,7 +17740,7 @@
         <v>4.5</v>
       </c>
       <c r="G599" t="n">
-        <v>3.38752174377441</v>
+        <v>3.38752150535583</v>
       </c>
       <c r="H599" t="n">
         <v>1718727</v>
@@ -17798,7 +17798,7 @@
         <v>4.40399980545044</v>
       </c>
       <c r="G601" t="n">
-        <v>3.31525468826294</v>
+        <v>3.31525444984436</v>
       </c>
       <c r="H601" t="n">
         <v>672682</v>
@@ -17827,7 +17827,7 @@
         <v>4.42600011825562</v>
       </c>
       <c r="G602" t="n">
-        <v>3.33181619644165</v>
+        <v>3.33181595802307</v>
       </c>
       <c r="H602" t="n">
         <v>1073095</v>
@@ -17856,7 +17856,7 @@
         <v>4.39400005340576</v>
       </c>
       <c r="G603" t="n">
-        <v>3.30772733688354</v>
+        <v>3.30772709846497</v>
       </c>
       <c r="H603" t="n">
         <v>988659</v>
@@ -17914,7 +17914,7 @@
         <v>4.2480001449585</v>
       </c>
       <c r="G605" t="n">
-        <v>3.19782066345215</v>
+        <v>3.19782090187073</v>
       </c>
       <c r="H605" t="n">
         <v>1691708</v>
@@ -17943,7 +17943,7 @@
         <v>4.29199981689453</v>
       </c>
       <c r="G606" t="n">
-        <v>3.23094296455383</v>
+        <v>3.23094320297241</v>
       </c>
       <c r="H606" t="n">
         <v>1025027</v>
@@ -17972,7 +17972,7 @@
         <v>4.14799976348877</v>
       </c>
       <c r="G607" t="n">
-        <v>3.12254190444946</v>
+        <v>3.12254214286804</v>
       </c>
       <c r="H607" t="n">
         <v>958730</v>
@@ -18030,7 +18030,7 @@
         <v>4.21000003814697</v>
       </c>
       <c r="G609" t="n">
-        <v>3.16921496391296</v>
+        <v>3.16921472549438</v>
       </c>
       <c r="H609" t="n">
         <v>563891</v>
@@ -18059,7 +18059,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G610" t="n">
-        <v>3.12404799461365</v>
+        <v>3.12404823303223</v>
       </c>
       <c r="H610" t="n">
         <v>508048</v>
@@ -18117,7 +18117,7 @@
         <v>4.13399982452393</v>
       </c>
       <c r="G612" t="n">
-        <v>3.11200332641602</v>
+        <v>3.11200308799744</v>
       </c>
       <c r="H612" t="n">
         <v>665026</v>
@@ -18233,7 +18233,7 @@
         <v>3.87800002098083</v>
       </c>
       <c r="G616" t="n">
-        <v>2.9192910194397</v>
+        <v>2.91929125785828</v>
       </c>
       <c r="H616" t="n">
         <v>1122626</v>
@@ -18291,7 +18291,7 @@
         <v>3.98600006103516</v>
       </c>
       <c r="G618" t="n">
-        <v>3.00059175491333</v>
+        <v>3.00059151649475</v>
       </c>
       <c r="H618" t="n">
         <v>757294</v>
@@ -18320,7 +18320,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G619" t="n">
-        <v>3.08640885353088</v>
+        <v>3.0864086151123</v>
       </c>
       <c r="H619" t="n">
         <v>695473</v>
@@ -18378,7 +18378,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G621" t="n">
-        <v>3.07888102531433</v>
+        <v>3.07888126373291</v>
       </c>
       <c r="H621" t="n">
         <v>723177</v>
@@ -18407,7 +18407,7 @@
         <v>4.11399984359741</v>
       </c>
       <c r="G622" t="n">
-        <v>3.09694790840149</v>
+        <v>3.09694743156433</v>
       </c>
       <c r="H622" t="n">
         <v>447299</v>
@@ -18668,7 +18668,7 @@
         <v>3.93400001525879</v>
       </c>
       <c r="G631" t="n">
-        <v>2.96144700050354</v>
+        <v>2.96144676208496</v>
       </c>
       <c r="H631" t="n">
         <v>1052341</v>
@@ -18726,7 +18726,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G633" t="n">
-        <v>2.9057412147522</v>
+        <v>2.90574097633362</v>
       </c>
       <c r="H633" t="n">
         <v>670328</v>
@@ -18755,7 +18755,7 @@
         <v>3.89400005340576</v>
       </c>
       <c r="G634" t="n">
-        <v>2.93133568763733</v>
+        <v>2.93133544921875</v>
       </c>
       <c r="H634" t="n">
         <v>753913</v>
@@ -18784,7 +18784,7 @@
         <v>3.83400011062622</v>
       </c>
       <c r="G635" t="n">
-        <v>2.88616871833801</v>
+        <v>2.88616895675659</v>
       </c>
       <c r="H635" t="n">
         <v>1512874</v>
@@ -18813,7 +18813,7 @@
         <v>3.89000010490417</v>
       </c>
       <c r="G636" t="n">
-        <v>2.92832446098328</v>
+        <v>2.92832469940186</v>
       </c>
       <c r="H636" t="n">
         <v>980560</v>
@@ -18871,7 +18871,7 @@
         <v>3.86999988555908</v>
       </c>
       <c r="G638" t="n">
-        <v>2.91326880455017</v>
+        <v>2.91326856613159</v>
       </c>
       <c r="H638" t="n">
         <v>971790</v>
@@ -18929,7 +18929,7 @@
         <v>4.16599988937378</v>
       </c>
       <c r="G640" t="n">
-        <v>3.1360924243927</v>
+        <v>3.13609194755554</v>
       </c>
       <c r="H640" t="n">
         <v>996729</v>
@@ -18958,7 +18958,7 @@
         <v>4.24399995803833</v>
       </c>
       <c r="G641" t="n">
-        <v>3.1948094367981</v>
+        <v>3.19480967521667</v>
       </c>
       <c r="H641" t="n">
         <v>1054195</v>
@@ -18987,7 +18987,7 @@
         <v>4.2480001449585</v>
       </c>
       <c r="G642" t="n">
-        <v>3.19782066345215</v>
+        <v>3.19782090187073</v>
       </c>
       <c r="H642" t="n">
         <v>695838</v>
@@ -19016,7 +19016,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G643" t="n">
-        <v>3.23696565628052</v>
+        <v>3.23696517944336</v>
       </c>
       <c r="H643" t="n">
         <v>863118</v>
@@ -19045,7 +19045,7 @@
         <v>4.34200000762939</v>
       </c>
       <c r="G644" t="n">
-        <v>3.26858234405518</v>
+        <v>3.2685821056366</v>
       </c>
       <c r="H644" t="n">
         <v>672789</v>
@@ -19132,7 +19132,7 @@
         <v>4.30600023269653</v>
       </c>
       <c r="G647" t="n">
-        <v>3.2414824962616</v>
+        <v>3.24148201942444</v>
       </c>
       <c r="H647" t="n">
         <v>641366</v>
@@ -19161,7 +19161,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G648" t="n">
-        <v>3.17674231529236</v>
+        <v>3.17674255371094</v>
       </c>
       <c r="H648" t="n">
         <v>557526</v>
@@ -19277,7 +19277,7 @@
         <v>4.20800018310547</v>
       </c>
       <c r="G652" t="n">
-        <v>3.16770935058594</v>
+        <v>3.16770958900452</v>
       </c>
       <c r="H652" t="n">
         <v>653981</v>
@@ -19364,7 +19364,7 @@
         <v>4.18800020217896</v>
       </c>
       <c r="G655" t="n">
-        <v>3.15265393257141</v>
+        <v>3.15265369415283</v>
       </c>
       <c r="H655" t="n">
         <v>466576</v>
@@ -19422,7 +19422,7 @@
         <v>4.48400020599365</v>
       </c>
       <c r="G657" t="n">
-        <v>3.37547731399536</v>
+        <v>3.37547779083252</v>
       </c>
       <c r="H657" t="n">
         <v>1577359</v>
@@ -19480,7 +19480,7 @@
         <v>4.43800020217896</v>
       </c>
       <c r="G659" t="n">
-        <v>3.34084963798523</v>
+        <v>3.34084987640381</v>
       </c>
       <c r="H659" t="n">
         <v>754004</v>
@@ -19509,7 +19509,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G660" t="n">
-        <v>3.23696565628052</v>
+        <v>3.23696517944336</v>
       </c>
       <c r="H660" t="n">
         <v>709269</v>
@@ -19596,7 +19596,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G663" t="n">
-        <v>3.09393668174744</v>
+        <v>3.09393692016602</v>
       </c>
       <c r="H663" t="n">
         <v>380190</v>
@@ -19625,7 +19625,7 @@
         <v>4.2039999961853</v>
       </c>
       <c r="G664" t="n">
-        <v>3.16469812393188</v>
+        <v>3.16469836235046</v>
       </c>
       <c r="H664" t="n">
         <v>435583</v>
@@ -19683,7 +19683,7 @@
         <v>4.14400005340576</v>
       </c>
       <c r="G666" t="n">
-        <v>3.11953115463257</v>
+        <v>3.11953139305115</v>
       </c>
       <c r="H666" t="n">
         <v>757007</v>
@@ -19741,7 +19741,7 @@
         <v>4.01000022888184</v>
       </c>
       <c r="G668" t="n">
-        <v>3.01865863800049</v>
+        <v>3.01865839958191</v>
       </c>
       <c r="H668" t="n">
         <v>542005</v>
@@ -19828,7 +19828,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G671" t="n">
-        <v>2.89068555831909</v>
+        <v>2.89068531990051</v>
       </c>
       <c r="H671" t="n">
         <v>747256</v>
@@ -19886,7 +19886,7 @@
         <v>3.91799998283386</v>
       </c>
       <c r="G673" t="n">
-        <v>2.94940257072449</v>
+        <v>2.94940233230591</v>
       </c>
       <c r="H673" t="n">
         <v>587910</v>
@@ -20002,7 +20002,7 @@
         <v>3.83800005912781</v>
       </c>
       <c r="G677" t="n">
-        <v>2.88917970657349</v>
+        <v>2.88917946815491</v>
       </c>
       <c r="H677" t="n">
         <v>326228</v>
@@ -20031,7 +20031,7 @@
         <v>3.93400001525879</v>
       </c>
       <c r="G678" t="n">
-        <v>2.96144700050354</v>
+        <v>2.96144676208496</v>
       </c>
       <c r="H678" t="n">
         <v>783908</v>
@@ -20060,7 +20060,7 @@
         <v>4.11800003051758</v>
       </c>
       <c r="G679" t="n">
-        <v>3.09995889663696</v>
+        <v>3.09995913505554</v>
       </c>
       <c r="H679" t="n">
         <v>1415988</v>
@@ -20118,7 +20118,7 @@
         <v>3.99799990653992</v>
       </c>
       <c r="G681" t="n">
-        <v>3.00962519645691</v>
+        <v>3.00962495803833</v>
       </c>
       <c r="H681" t="n">
         <v>862154</v>
@@ -20147,7 +20147,7 @@
         <v>4.2039999961853</v>
       </c>
       <c r="G682" t="n">
-        <v>3.16469812393188</v>
+        <v>3.16469836235046</v>
       </c>
       <c r="H682" t="n">
         <v>1099663</v>
@@ -20176,7 +20176,7 @@
         <v>4.2039999961853</v>
       </c>
       <c r="G683" t="n">
-        <v>3.16469812393188</v>
+        <v>3.16469836235046</v>
       </c>
       <c r="H683" t="n">
         <v>776205</v>
@@ -20205,7 +20205,7 @@
         <v>4.13399982452393</v>
       </c>
       <c r="G684" t="n">
-        <v>3.11200332641602</v>
+        <v>3.11200308799744</v>
       </c>
       <c r="H684" t="n">
         <v>759701</v>
@@ -20234,7 +20234,7 @@
         <v>4.05200004577637</v>
       </c>
       <c r="G685" t="n">
-        <v>3.05027532577515</v>
+        <v>3.05027508735657</v>
       </c>
       <c r="H685" t="n">
         <v>528971</v>
@@ -20263,7 +20263,7 @@
         <v>4.06599998474121</v>
       </c>
       <c r="G686" t="n">
-        <v>3.06081438064575</v>
+        <v>3.06081414222717</v>
       </c>
       <c r="H686" t="n">
         <v>272564</v>
@@ -20292,7 +20292,7 @@
         <v>4.0939998626709</v>
       </c>
       <c r="G687" t="n">
-        <v>3.08189225196838</v>
+        <v>3.0818920135498</v>
       </c>
       <c r="H687" t="n">
         <v>324359</v>
@@ -20321,7 +20321,7 @@
         <v>4.10400009155273</v>
       </c>
       <c r="G688" t="n">
-        <v>3.08941984176636</v>
+        <v>3.08942008018494</v>
       </c>
       <c r="H688" t="n">
         <v>375946</v>
@@ -20379,7 +20379,7 @@
         <v>4.05800008773804</v>
       </c>
       <c r="G690" t="n">
-        <v>3.05479216575623</v>
+        <v>3.05479192733765</v>
       </c>
       <c r="H690" t="n">
         <v>186324</v>
@@ -20437,7 +20437,7 @@
         <v>4.10200023651123</v>
       </c>
       <c r="G692" t="n">
-        <v>3.08791470527649</v>
+        <v>3.08791446685791</v>
       </c>
       <c r="H692" t="n">
         <v>224951</v>
@@ -20466,7 +20466,7 @@
         <v>4.10400009155273</v>
       </c>
       <c r="G693" t="n">
-        <v>3.08941984176636</v>
+        <v>3.08942008018494</v>
       </c>
       <c r="H693" t="n">
         <v>350091</v>
@@ -20495,7 +20495,7 @@
         <v>4.06599998474121</v>
       </c>
       <c r="G694" t="n">
-        <v>3.06081438064575</v>
+        <v>3.06081414222717</v>
       </c>
       <c r="H694" t="n">
         <v>569049</v>
@@ -20553,7 +20553,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G696" t="n">
-        <v>3.0487699508667</v>
+        <v>3.04876971244812</v>
       </c>
       <c r="H696" t="n">
         <v>391191</v>
@@ -20611,7 +20611,7 @@
         <v>4.05999994277954</v>
       </c>
       <c r="G698" t="n">
-        <v>3.05629777908325</v>
+        <v>3.05629754066467</v>
       </c>
       <c r="H698" t="n">
         <v>417539</v>
@@ -20640,7 +20640,7 @@
         <v>4.02400016784668</v>
       </c>
       <c r="G699" t="n">
-        <v>3.02919745445251</v>
+        <v>3.02919769287109</v>
       </c>
       <c r="H699" t="n">
         <v>663273</v>
@@ -20669,7 +20669,7 @@
         <v>3.97399997711182</v>
       </c>
       <c r="G700" t="n">
-        <v>2.99155807495117</v>
+        <v>2.99155831336975</v>
       </c>
       <c r="H700" t="n">
         <v>494138</v>
@@ -20698,7 +20698,7 @@
         <v>3.87800002098083</v>
       </c>
       <c r="G701" t="n">
-        <v>2.9192910194397</v>
+        <v>2.91929125785828</v>
       </c>
       <c r="H701" t="n">
         <v>770144</v>
@@ -20756,7 +20756,7 @@
         <v>3.84200000762939</v>
       </c>
       <c r="G703" t="n">
-        <v>2.89219093322754</v>
+        <v>2.89219069480896</v>
       </c>
       <c r="H703" t="n">
         <v>465104</v>
@@ -20785,7 +20785,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G704" t="n">
-        <v>2.9207968711853</v>
+        <v>2.92079663276672</v>
       </c>
       <c r="H704" t="n">
         <v>384718</v>
@@ -20843,7 +20843,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G706" t="n">
-        <v>2.79282331466675</v>
+        <v>2.79282355308533</v>
       </c>
       <c r="H706" t="n">
         <v>1049632</v>
@@ -20930,7 +20930,7 @@
         <v>3.71799993515015</v>
       </c>
       <c r="G709" t="n">
-        <v>2.79884576797485</v>
+        <v>2.79884600639343</v>
       </c>
       <c r="H709" t="n">
         <v>839279</v>
@@ -21046,7 +21046,7 @@
         <v>3.86999988555908</v>
       </c>
       <c r="G713" t="n">
-        <v>2.91326880455017</v>
+        <v>2.91326856613159</v>
       </c>
       <c r="H713" t="n">
         <v>725616</v>
@@ -21075,7 +21075,7 @@
         <v>3.74200010299683</v>
       </c>
       <c r="G714" t="n">
-        <v>2.81691241264343</v>
+        <v>2.81691288948059</v>
       </c>
       <c r="H714" t="n">
         <v>483056</v>
@@ -21104,7 +21104,7 @@
         <v>3.74200010299683</v>
       </c>
       <c r="G715" t="n">
-        <v>2.81691241264343</v>
+        <v>2.81691288948059</v>
       </c>
       <c r="H715" t="n">
         <v>628300</v>
@@ -21220,7 +21220,7 @@
         <v>3.68199992179871</v>
       </c>
       <c r="G719" t="n">
-        <v>2.77174544334412</v>
+        <v>2.7717456817627</v>
       </c>
       <c r="H719" t="n">
         <v>305392</v>
@@ -21278,7 +21278,7 @@
         <v>3.71799993515015</v>
       </c>
       <c r="G721" t="n">
-        <v>2.79884576797485</v>
+        <v>2.79884600639343</v>
       </c>
       <c r="H721" t="n">
         <v>455606</v>
@@ -21307,7 +21307,7 @@
         <v>3.83400011062622</v>
       </c>
       <c r="G722" t="n">
-        <v>2.88616871833801</v>
+        <v>2.88616895675659</v>
       </c>
       <c r="H722" t="n">
         <v>324122</v>
@@ -21336,7 +21336,7 @@
         <v>3.84400010108948</v>
       </c>
       <c r="G723" t="n">
-        <v>2.89369630813599</v>
+        <v>2.89369654655457</v>
       </c>
       <c r="H723" t="n">
         <v>164196</v>
@@ -21365,7 +21365,7 @@
         <v>3.86800003051758</v>
       </c>
       <c r="G724" t="n">
-        <v>2.91176319122314</v>
+        <v>2.91176295280457</v>
       </c>
       <c r="H724" t="n">
         <v>830274</v>
@@ -21423,7 +21423,7 @@
         <v>3.87800002098083</v>
       </c>
       <c r="G726" t="n">
-        <v>2.9192910194397</v>
+        <v>2.91929125785828</v>
       </c>
       <c r="H726" t="n">
         <v>603075</v>
@@ -21481,7 +21481,7 @@
         <v>3.91000008583069</v>
       </c>
       <c r="G728" t="n">
-        <v>2.9433798789978</v>
+        <v>2.94338011741638</v>
       </c>
       <c r="H728" t="n">
         <v>353919</v>
@@ -21510,7 +21510,7 @@
         <v>3.86999988555908</v>
       </c>
       <c r="G729" t="n">
-        <v>2.91326880455017</v>
+        <v>2.91326856613159</v>
       </c>
       <c r="H729" t="n">
         <v>1659165</v>
@@ -21539,7 +21539,7 @@
         <v>3.5699999332428</v>
       </c>
       <c r="G730" t="n">
-        <v>2.68743371963501</v>
+        <v>2.68743395805359</v>
       </c>
       <c r="H730" t="n">
         <v>3700588</v>
@@ -21568,7 +21568,7 @@
         <v>3.43400001525879</v>
       </c>
       <c r="G731" t="n">
-        <v>2.58505535125732</v>
+        <v>2.5850555896759</v>
       </c>
       <c r="H731" t="n">
         <v>1206059</v>
@@ -21597,7 +21597,7 @@
         <v>3.32399988174438</v>
       </c>
       <c r="G732" t="n">
-        <v>2.50224947929382</v>
+        <v>2.50224924087524</v>
       </c>
       <c r="H732" t="n">
         <v>994529</v>
@@ -21626,7 +21626,7 @@
         <v>3.26200008392334</v>
       </c>
       <c r="G733" t="n">
-        <v>2.4555766582489</v>
+        <v>2.45557689666748</v>
       </c>
       <c r="H733" t="n">
         <v>799710</v>
@@ -21713,7 +21713,7 @@
         <v>3.2279999256134</v>
       </c>
       <c r="G736" t="n">
-        <v>2.42998218536377</v>
+        <v>2.42998242378235</v>
       </c>
       <c r="H736" t="n">
         <v>794982</v>
@@ -21742,7 +21742,7 @@
         <v>3.17000007629395</v>
       </c>
       <c r="G737" t="n">
-        <v>2.38632130622864</v>
+        <v>2.38632106781006</v>
       </c>
       <c r="H737" t="n">
         <v>428808</v>
@@ -21771,7 +21771,7 @@
         <v>3.06399989128113</v>
       </c>
       <c r="G738" t="n">
-        <v>2.30652594566345</v>
+        <v>2.30652570724487</v>
       </c>
       <c r="H738" t="n">
         <v>689149</v>
@@ -21800,7 +21800,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G739" t="n">
-        <v>2.37126541137695</v>
+        <v>2.37126517295837</v>
       </c>
       <c r="H739" t="n">
         <v>1184105</v>
@@ -21829,7 +21829,7 @@
         <v>3.25600004196167</v>
       </c>
       <c r="G740" t="n">
-        <v>2.4510600566864</v>
+        <v>2.45106029510498</v>
       </c>
       <c r="H740" t="n">
         <v>938750</v>
@@ -21858,7 +21858,7 @@
         <v>3.2279999256134</v>
       </c>
       <c r="G741" t="n">
-        <v>2.42998218536377</v>
+        <v>2.42998242378235</v>
       </c>
       <c r="H741" t="n">
         <v>598234</v>
@@ -21887,7 +21887,7 @@
         <v>3.30599999427795</v>
       </c>
       <c r="G742" t="n">
-        <v>2.48869943618774</v>
+        <v>2.48869967460632</v>
       </c>
       <c r="H742" t="n">
         <v>1577636</v>
@@ -21945,7 +21945,7 @@
         <v>3.39599990844727</v>
       </c>
       <c r="G744" t="n">
-        <v>2.55644989013672</v>
+        <v>2.55644965171814</v>
       </c>
       <c r="H744" t="n">
         <v>1061136</v>
@@ -21974,7 +21974,7 @@
         <v>3.39599990844727</v>
       </c>
       <c r="G745" t="n">
-        <v>2.55644989013672</v>
+        <v>2.55644965171814</v>
       </c>
       <c r="H745" t="n">
         <v>491756</v>
@@ -22003,7 +22003,7 @@
         <v>3.45000004768372</v>
       </c>
       <c r="G746" t="n">
-        <v>2.59710025787354</v>
+        <v>2.59710001945496</v>
       </c>
       <c r="H746" t="n">
         <v>688615</v>
@@ -22090,7 +22090,7 @@
         <v>3.37199997901917</v>
       </c>
       <c r="G749" t="n">
-        <v>2.53838300704956</v>
+        <v>2.53838324546814</v>
       </c>
       <c r="H749" t="n">
         <v>705793</v>
@@ -22148,7 +22148,7 @@
         <v>3.25600004196167</v>
       </c>
       <c r="G751" t="n">
-        <v>2.4510600566864</v>
+        <v>2.45106029510498</v>
       </c>
       <c r="H751" t="n">
         <v>768527</v>
@@ -22177,7 +22177,7 @@
         <v>3.14400005340576</v>
       </c>
       <c r="G752" t="n">
-        <v>2.36674880981445</v>
+        <v>2.36674857139587</v>
       </c>
       <c r="H752" t="n">
         <v>784660</v>
@@ -22206,7 +22206,7 @@
         <v>3.22199988365173</v>
       </c>
       <c r="G753" t="n">
-        <v>2.42546534538269</v>
+        <v>2.42546558380127</v>
       </c>
       <c r="H753" t="n">
         <v>602078</v>
@@ -22235,7 +22235,7 @@
         <v>3.15199995040894</v>
       </c>
       <c r="G754" t="n">
-        <v>2.37277102470398</v>
+        <v>2.3727707862854</v>
       </c>
       <c r="H754" t="n">
         <v>664384</v>
@@ -22293,7 +22293,7 @@
         <v>3.18199992179871</v>
       </c>
       <c r="G756" t="n">
-        <v>2.39535403251648</v>
+        <v>2.39535427093506</v>
       </c>
       <c r="H756" t="n">
         <v>437404</v>
@@ -22351,7 +22351,7 @@
         <v>3.10999989509583</v>
       </c>
       <c r="G758" t="n">
-        <v>2.34115409851074</v>
+        <v>2.34115386009216</v>
       </c>
       <c r="H758" t="n">
         <v>773445</v>
@@ -22380,7 +22380,7 @@
         <v>3.10599994659424</v>
       </c>
       <c r="G759" t="n">
-        <v>2.33814263343811</v>
+        <v>2.33814311027527</v>
       </c>
       <c r="H759" t="n">
         <v>841864</v>
@@ -22438,7 +22438,7 @@
         <v>3.20600008964539</v>
       </c>
       <c r="G761" t="n">
-        <v>2.41342115402222</v>
+        <v>2.41342091560364</v>
       </c>
       <c r="H761" t="n">
         <v>1155805</v>
@@ -22467,7 +22467,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G762" t="n">
-        <v>2.40890455245972</v>
+        <v>2.4089047908783</v>
       </c>
       <c r="H762" t="n">
         <v>2030109</v>
@@ -22496,7 +22496,7 @@
         <v>3.21000003814697</v>
       </c>
       <c r="G763" t="n">
-        <v>2.41643238067627</v>
+        <v>2.41643214225769</v>
       </c>
       <c r="H763" t="n">
         <v>804569</v>
@@ -22525,7 +22525,7 @@
         <v>3.22199988365173</v>
       </c>
       <c r="G764" t="n">
-        <v>2.42546534538269</v>
+        <v>2.42546558380127</v>
       </c>
       <c r="H764" t="n">
         <v>627767</v>
@@ -22554,7 +22554,7 @@
         <v>3.24200010299683</v>
       </c>
       <c r="G765" t="n">
-        <v>2.44052124023438</v>
+        <v>2.44052147865295</v>
       </c>
       <c r="H765" t="n">
         <v>506419</v>
@@ -22583,7 +22583,7 @@
         <v>3.35800004005432</v>
       </c>
       <c r="G766" t="n">
-        <v>2.52784395217896</v>
+        <v>2.52784419059753</v>
       </c>
       <c r="H766" t="n">
         <v>602295</v>
@@ -22641,7 +22641,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G768" t="n">
-        <v>2.5745165348053</v>
+        <v>2.57451677322388</v>
       </c>
       <c r="H768" t="n">
         <v>708006</v>
@@ -22670,7 +22670,7 @@
         <v>3.39400005340576</v>
       </c>
       <c r="G769" t="n">
-        <v>2.55494427680969</v>
+        <v>2.55494451522827</v>
       </c>
       <c r="H769" t="n">
         <v>1045766</v>
@@ -22699,7 +22699,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G770" t="n">
-        <v>2.55193328857422</v>
+        <v>2.5519335269928</v>
       </c>
       <c r="H770" t="n">
         <v>539440</v>
@@ -22757,7 +22757,7 @@
         <v>3.39599990844727</v>
       </c>
       <c r="G772" t="n">
-        <v>2.55644989013672</v>
+        <v>2.55644965171814</v>
       </c>
       <c r="H772" t="n">
         <v>732957</v>
@@ -22786,7 +22786,7 @@
         <v>3.41400003433228</v>
       </c>
       <c r="G773" t="n">
-        <v>2.56999969482422</v>
+        <v>2.5699999332428</v>
       </c>
       <c r="H773" t="n">
         <v>547724</v>
@@ -22844,7 +22844,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G775" t="n">
-        <v>2.60462808609009</v>
+        <v>2.60462784767151</v>
       </c>
       <c r="H775" t="n">
         <v>630952</v>
@@ -22931,7 +22931,7 @@
         <v>3.45600008964539</v>
       </c>
       <c r="G778" t="n">
-        <v>2.60161685943604</v>
+        <v>2.60161709785461</v>
       </c>
       <c r="H778" t="n">
         <v>556082</v>
@@ -22989,7 +22989,7 @@
         <v>3.41599988937378</v>
       </c>
       <c r="G780" t="n">
-        <v>2.57150530815125</v>
+        <v>2.57150554656982</v>
       </c>
       <c r="H780" t="n">
         <v>674782</v>
@@ -23018,7 +23018,7 @@
         <v>3.48000001907349</v>
       </c>
       <c r="G781" t="n">
-        <v>2.61968350410461</v>
+        <v>2.61968374252319</v>
       </c>
       <c r="H781" t="n">
         <v>873558</v>
@@ -23134,7 +23134,7 @@
         <v>3.50399994850159</v>
       </c>
       <c r="G785" t="n">
-        <v>2.63775062561035</v>
+        <v>2.63775014877319</v>
       </c>
       <c r="H785" t="n">
         <v>995876</v>
@@ -23192,7 +23192,7 @@
         <v>3.53200006484985</v>
       </c>
       <c r="G787" t="n">
-        <v>2.65882849693298</v>
+        <v>2.6588282585144</v>
       </c>
       <c r="H787" t="n">
         <v>1483623</v>
@@ -23221,7 +23221,7 @@
         <v>3.58800005912781</v>
       </c>
       <c r="G788" t="n">
-        <v>2.70098447799683</v>
+        <v>2.70098400115967</v>
       </c>
       <c r="H788" t="n">
         <v>682242</v>
@@ -23308,7 +23308,7 @@
         <v>3.48399996757507</v>
       </c>
       <c r="G791" t="n">
-        <v>2.62269496917725</v>
+        <v>2.62269473075867</v>
       </c>
       <c r="H791" t="n">
         <v>1803357</v>
@@ -23395,7 +23395,7 @@
         <v>3.49200010299683</v>
       </c>
       <c r="G794" t="n">
-        <v>2.62871718406677</v>
+        <v>2.62871694564819</v>
       </c>
       <c r="H794" t="n">
         <v>407334</v>
@@ -23424,7 +23424,7 @@
         <v>3.49799990653992</v>
       </c>
       <c r="G795" t="n">
-        <v>2.63323378562927</v>
+        <v>2.63323354721069</v>
       </c>
       <c r="H795" t="n">
         <v>619858</v>
@@ -23482,7 +23482,7 @@
         <v>3.61400008201599</v>
       </c>
       <c r="G797" t="n">
-        <v>2.72055673599243</v>
+        <v>2.72055649757385</v>
       </c>
       <c r="H797" t="n">
         <v>281501</v>
@@ -23511,7 +23511,7 @@
         <v>3.46399998664856</v>
       </c>
       <c r="G798" t="n">
-        <v>2.60763883590698</v>
+        <v>2.60763907432556</v>
       </c>
       <c r="H798" t="n">
         <v>1529710</v>
@@ -23598,7 +23598,7 @@
         <v>3.50399994850159</v>
       </c>
       <c r="G801" t="n">
-        <v>2.63775062561035</v>
+        <v>2.63775014877319</v>
       </c>
       <c r="H801" t="n">
         <v>164742</v>
@@ -23685,7 +23685,7 @@
         <v>3.53800010681152</v>
       </c>
       <c r="G804" t="n">
-        <v>2.66334509849548</v>
+        <v>2.66334533691406</v>
       </c>
       <c r="H804" t="n">
         <v>888830</v>
@@ -23714,7 +23714,7 @@
         <v>3.58800005912781</v>
       </c>
       <c r="G805" t="n">
-        <v>2.70098447799683</v>
+        <v>2.70098400115967</v>
       </c>
       <c r="H805" t="n">
         <v>1048188</v>
@@ -23772,7 +23772,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G807" t="n">
-        <v>2.72507333755493</v>
+        <v>2.72507286071777</v>
       </c>
       <c r="H807" t="n">
         <v>345190</v>
@@ -23830,7 +23830,7 @@
         <v>3.55800008773804</v>
       </c>
       <c r="G809" t="n">
-        <v>2.67840075492859</v>
+        <v>2.67840051651001</v>
       </c>
       <c r="H809" t="n">
         <v>864990</v>
@@ -23859,7 +23859,7 @@
         <v>3.52800011634827</v>
       </c>
       <c r="G810" t="n">
-        <v>2.65581703186035</v>
+        <v>2.65581727027893</v>
       </c>
       <c r="H810" t="n">
         <v>1313610</v>
@@ -23888,7 +23888,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G811" t="n">
-        <v>2.60462808609009</v>
+        <v>2.60462784767151</v>
       </c>
       <c r="H811" t="n">
         <v>534181</v>
@@ -23946,7 +23946,7 @@
         <v>3.50399994850159</v>
       </c>
       <c r="G813" t="n">
-        <v>2.63775062561035</v>
+        <v>2.63775014877319</v>
       </c>
       <c r="H813" t="n">
         <v>721263</v>
@@ -24033,7 +24033,7 @@
         <v>3.48399996757507</v>
       </c>
       <c r="G816" t="n">
-        <v>2.62269496917725</v>
+        <v>2.62269473075867</v>
       </c>
       <c r="H816" t="n">
         <v>1719288</v>
@@ -24062,7 +24062,7 @@
         <v>3.58800005912781</v>
       </c>
       <c r="G817" t="n">
-        <v>2.70098447799683</v>
+        <v>2.70098400115967</v>
       </c>
       <c r="H817" t="n">
         <v>1493931</v>
@@ -24091,7 +24091,7 @@
         <v>3.57200002670288</v>
       </c>
       <c r="G818" t="n">
-        <v>2.68893980979919</v>
+        <v>2.68893957138062</v>
       </c>
       <c r="H818" t="n">
         <v>577568</v>
@@ -24120,7 +24120,7 @@
         <v>3.49200010299683</v>
       </c>
       <c r="G819" t="n">
-        <v>2.62871718406677</v>
+        <v>2.62871694564819</v>
       </c>
       <c r="H819" t="n">
         <v>601567</v>
@@ -24178,7 +24178,7 @@
         <v>3.51399993896484</v>
       </c>
       <c r="G821" t="n">
-        <v>2.64527797698975</v>
+        <v>2.64527821540833</v>
       </c>
       <c r="H821" t="n">
         <v>589226</v>
@@ -24207,7 +24207,7 @@
         <v>3.41400003433228</v>
       </c>
       <c r="G822" t="n">
-        <v>2.56999969482422</v>
+        <v>2.5699999332428</v>
       </c>
       <c r="H822" t="n">
         <v>552088</v>
@@ -24265,7 +24265,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G824" t="n">
-        <v>2.52182173728943</v>
+        <v>2.52182149887085</v>
       </c>
       <c r="H824" t="n">
         <v>710361</v>
@@ -24323,7 +24323,7 @@
         <v>3.39599990844727</v>
       </c>
       <c r="G826" t="n">
-        <v>2.55644989013672</v>
+        <v>2.55644965171814</v>
       </c>
       <c r="H826" t="n">
         <v>929615</v>
@@ -24352,7 +24352,7 @@
         <v>3.48000001907349</v>
       </c>
       <c r="G827" t="n">
-        <v>2.61968350410461</v>
+        <v>2.61968374252319</v>
       </c>
       <c r="H827" t="n">
         <v>788823</v>
@@ -24381,7 +24381,7 @@
         <v>3.4539999961853</v>
       </c>
       <c r="G828" t="n">
-        <v>2.60011100769043</v>
+        <v>2.60011124610901</v>
       </c>
       <c r="H828" t="n">
         <v>379614</v>
@@ -24439,7 +24439,7 @@
         <v>3.55200004577637</v>
       </c>
       <c r="G830" t="n">
-        <v>2.67388415336609</v>
+        <v>2.67388391494751</v>
       </c>
       <c r="H830" t="n">
         <v>479475</v>
@@ -24468,7 +24468,7 @@
         <v>3.55200004577637</v>
       </c>
       <c r="G831" t="n">
-        <v>2.67388415336609</v>
+        <v>2.67388391494751</v>
       </c>
       <c r="H831" t="n">
         <v>552276</v>
@@ -24526,7 +24526,7 @@
         <v>3.44199991226196</v>
       </c>
       <c r="G833" t="n">
-        <v>2.59107756614685</v>
+        <v>2.59107780456543</v>
       </c>
       <c r="H833" t="n">
         <v>637964</v>
@@ -24555,7 +24555,7 @@
         <v>3.45000004768372</v>
       </c>
       <c r="G834" t="n">
-        <v>2.59710025787354</v>
+        <v>2.59710001945496</v>
       </c>
       <c r="H834" t="n">
         <v>353398</v>
@@ -24584,7 +24584,7 @@
         <v>3.44799995422363</v>
       </c>
       <c r="G835" t="n">
-        <v>2.59559416770935</v>
+        <v>2.59559440612793</v>
       </c>
       <c r="H835" t="n">
         <v>400884</v>
@@ -24642,7 +24642,7 @@
         <v>3.37199997901917</v>
       </c>
       <c r="G837" t="n">
-        <v>2.53838300704956</v>
+        <v>2.53838324546814</v>
       </c>
       <c r="H837" t="n">
         <v>555356</v>
@@ -24671,7 +24671,7 @@
         <v>3.27600002288818</v>
       </c>
       <c r="G838" t="n">
-        <v>2.46611571311951</v>
+        <v>2.46611618995667</v>
       </c>
       <c r="H838" t="n">
         <v>1177799</v>
@@ -24700,7 +24700,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G839" t="n">
-        <v>2.46912717819214</v>
+        <v>2.46912693977356</v>
       </c>
       <c r="H839" t="n">
         <v>1143951</v>
@@ -24729,7 +24729,7 @@
         <v>3.29399991035461</v>
       </c>
       <c r="G840" t="n">
-        <v>2.47966575622559</v>
+        <v>2.47966599464417</v>
       </c>
       <c r="H840" t="n">
         <v>532008</v>
@@ -24758,7 +24758,7 @@
         <v>3.26200008392334</v>
       </c>
       <c r="G841" t="n">
-        <v>2.4555766582489</v>
+        <v>2.45557689666748</v>
       </c>
       <c r="H841" t="n">
         <v>749915</v>
@@ -24787,7 +24787,7 @@
         <v>3.26999998092651</v>
       </c>
       <c r="G842" t="n">
-        <v>2.46159911155701</v>
+        <v>2.46159934997559</v>
       </c>
       <c r="H842" t="n">
         <v>334139</v>
@@ -24903,7 +24903,7 @@
         <v>3.18199992179871</v>
       </c>
       <c r="G846" t="n">
-        <v>2.39535403251648</v>
+        <v>2.39535427093506</v>
       </c>
       <c r="H846" t="n">
         <v>661780</v>
@@ -24990,7 +24990,7 @@
         <v>3.04800009727478</v>
       </c>
       <c r="G849" t="n">
-        <v>2.38129949569702</v>
+        <v>2.3812997341156</v>
       </c>
       <c r="H849" t="n">
         <v>1111716</v>
@@ -25048,7 +25048,7 @@
         <v>2.98799991607666</v>
       </c>
       <c r="G851" t="n">
-        <v>2.33442330360413</v>
+        <v>2.33442354202271</v>
       </c>
       <c r="H851" t="n">
         <v>630408</v>
@@ -25106,7 +25106,7 @@
         <v>2.68799996376038</v>
       </c>
       <c r="G853" t="n">
-        <v>2.10004353523254</v>
+        <v>2.10004377365112</v>
       </c>
       <c r="H853" t="n">
         <v>2754571</v>
@@ -25164,7 +25164,7 @@
         <v>2.73600006103516</v>
       </c>
       <c r="G855" t="n">
-        <v>2.13754463195801</v>
+        <v>2.13754439353943</v>
       </c>
       <c r="H855" t="n">
         <v>2511883</v>
@@ -25367,7 +25367,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G862" t="n">
-        <v>1.97660350799561</v>
+        <v>1.9766036272049</v>
       </c>
       <c r="H862" t="n">
         <v>3935382</v>
@@ -25425,7 +25425,7 @@
         <v>2.62199997901917</v>
       </c>
       <c r="G864" t="n">
-        <v>2.04848051071167</v>
+        <v>2.04848027229309</v>
       </c>
       <c r="H864" t="n">
         <v>1011752</v>
@@ -25512,7 +25512,7 @@
         <v>2.55399990081787</v>
       </c>
       <c r="G867" t="n">
-        <v>1.99535381793976</v>
+        <v>1.99535393714905</v>
       </c>
       <c r="H867" t="n">
         <v>1333929</v>
@@ -25657,7 +25657,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G872" t="n">
-        <v>2.21098375320435</v>
+        <v>2.21098351478577</v>
       </c>
       <c r="H872" t="n">
         <v>2300083</v>
@@ -25773,7 +25773,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G876" t="n">
-        <v>2.2500467300415</v>
+        <v>2.25004696846008</v>
       </c>
       <c r="H876" t="n">
         <v>1808609</v>
@@ -25831,7 +25831,7 @@
         <v>2.81399989128113</v>
       </c>
       <c r="G878" t="n">
-        <v>2.19848322868347</v>
+        <v>2.19848299026489</v>
       </c>
       <c r="H878" t="n">
         <v>1532406</v>
@@ -25947,7 +25947,7 @@
         <v>2.91000008583069</v>
       </c>
       <c r="G882" t="n">
-        <v>2.27348494529724</v>
+        <v>2.27348518371582</v>
       </c>
       <c r="H882" t="n">
         <v>1215853</v>
@@ -25976,7 +25976,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G883" t="n">
-        <v>2.2812979221344</v>
+        <v>2.28129768371582</v>
       </c>
       <c r="H883" t="n">
         <v>1435865</v>
@@ -26063,7 +26063,7 @@
         <v>2.79200005531311</v>
       </c>
       <c r="G886" t="n">
-        <v>2.18129563331604</v>
+        <v>2.18129539489746</v>
       </c>
       <c r="H886" t="n">
         <v>941066</v>
@@ -26092,7 +26092,7 @@
         <v>2.80599999427795</v>
       </c>
       <c r="G887" t="n">
-        <v>2.1922333240509</v>
+        <v>2.19223308563232</v>
       </c>
       <c r="H887" t="n">
         <v>539021</v>
@@ -26150,7 +26150,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G889" t="n">
-        <v>2.2500467300415</v>
+        <v>2.25004696846008</v>
       </c>
       <c r="H889" t="n">
         <v>486669</v>
@@ -26237,7 +26237,7 @@
         <v>2.91799998283386</v>
       </c>
       <c r="G892" t="n">
-        <v>2.27973508834839</v>
+        <v>2.27973532676697</v>
       </c>
       <c r="H892" t="n">
         <v>1259768</v>
@@ -26324,7 +26324,7 @@
         <v>2.74600005149841</v>
       </c>
       <c r="G895" t="n">
-        <v>2.14535689353943</v>
+        <v>2.14535713195801</v>
       </c>
       <c r="H895" t="n">
         <v>1270001</v>
@@ -26440,7 +26440,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G899" t="n">
-        <v>2.04691743850708</v>
+        <v>2.0469172000885</v>
       </c>
       <c r="H899" t="n">
         <v>1966228</v>
@@ -26469,7 +26469,7 @@
         <v>2.5699999332428</v>
       </c>
       <c r="G900" t="n">
-        <v>2.00785422325134</v>
+        <v>2.00785446166992</v>
       </c>
       <c r="H900" t="n">
         <v>3139762</v>
@@ -26498,7 +26498,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G901" t="n">
-        <v>1.9687911272049</v>
+        <v>1.96879100799561</v>
       </c>
       <c r="H901" t="n">
         <v>1633406</v>
@@ -26527,7 +26527,7 @@
         <v>2.43199992179871</v>
       </c>
       <c r="G902" t="n">
-        <v>1.90003943443298</v>
+        <v>1.90003955364227</v>
       </c>
       <c r="H902" t="n">
         <v>3448634</v>
@@ -26585,7 +26585,7 @@
         <v>2.41799998283386</v>
       </c>
       <c r="G904" t="n">
-        <v>1.8891019821167</v>
+        <v>1.88910186290741</v>
       </c>
       <c r="H904" t="n">
         <v>719864</v>
@@ -26643,7 +26643,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G906" t="n">
-        <v>1.84378814697266</v>
+        <v>1.84378802776337</v>
       </c>
       <c r="H906" t="n">
         <v>3133669</v>
@@ -26701,7 +26701,7 @@
         <v>2.3659999370575</v>
       </c>
       <c r="G908" t="n">
-        <v>1.84847593307495</v>
+        <v>1.84847605228424</v>
       </c>
       <c r="H908" t="n">
         <v>3580554</v>
@@ -26730,7 +26730,7 @@
         <v>2.2279999256134</v>
       </c>
       <c r="G909" t="n">
-        <v>1.74066126346588</v>
+        <v>1.74066138267517</v>
       </c>
       <c r="H909" t="n">
         <v>4557686</v>
@@ -26962,7 +26962,7 @@
         <v>2.22399997711182</v>
       </c>
       <c r="G917" t="n">
-        <v>1.7375363111496</v>
+        <v>1.73753643035889</v>
       </c>
       <c r="H917" t="n">
         <v>994781</v>
@@ -26991,7 +26991,7 @@
         <v>2.13599991798401</v>
       </c>
       <c r="G918" t="n">
-        <v>1.66878473758698</v>
+        <v>1.66878485679626</v>
       </c>
       <c r="H918" t="n">
         <v>1421938</v>
@@ -27078,7 +27078,7 @@
         <v>2.01200008392334</v>
       </c>
       <c r="G921" t="n">
-        <v>1.57190775871277</v>
+        <v>1.57190787792206</v>
       </c>
       <c r="H921" t="n">
         <v>947836</v>
@@ -27107,7 +27107,7 @@
         <v>2.04800009727478</v>
       </c>
       <c r="G922" t="n">
-        <v>1.60003352165222</v>
+        <v>1.60003340244293</v>
       </c>
       <c r="H922" t="n">
         <v>638397</v>
@@ -27165,7 +27165,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G924" t="n">
-        <v>1.60940861701965</v>
+        <v>1.60940849781036</v>
       </c>
       <c r="H924" t="n">
         <v>403593</v>
@@ -27571,7 +27571,7 @@
         <v>2.31200003623962</v>
       </c>
       <c r="G938" t="n">
-        <v>1.80628752708435</v>
+        <v>1.80628764629364</v>
       </c>
       <c r="H938" t="n">
         <v>530544</v>
@@ -27600,7 +27600,7 @@
         <v>2.35800004005432</v>
       </c>
       <c r="G939" t="n">
-        <v>1.84222602844238</v>
+        <v>1.84222590923309</v>
       </c>
       <c r="H939" t="n">
         <v>1336003</v>
@@ -27658,7 +27658,7 @@
         <v>2.33800005912781</v>
       </c>
       <c r="G941" t="n">
-        <v>1.82660043239594</v>
+        <v>1.82660055160522</v>
       </c>
       <c r="H941" t="n">
         <v>1598786</v>
@@ -27687,7 +27687,7 @@
         <v>2.39199995994568</v>
       </c>
       <c r="G942" t="n">
-        <v>1.86878883838654</v>
+        <v>1.86878871917725</v>
       </c>
       <c r="H942" t="n">
         <v>1297738</v>
@@ -27832,7 +27832,7 @@
         <v>2.39199995994568</v>
       </c>
       <c r="G947" t="n">
-        <v>1.86878883838654</v>
+        <v>1.86878871917725</v>
       </c>
       <c r="H947" t="n">
         <v>788986</v>
@@ -27861,7 +27861,7 @@
         <v>2.31200003623962</v>
       </c>
       <c r="G948" t="n">
-        <v>1.80628752708435</v>
+        <v>1.80628764629364</v>
       </c>
       <c r="H948" t="n">
         <v>928777</v>
@@ -27890,7 +27890,7 @@
         <v>2.26799988746643</v>
       </c>
       <c r="G949" t="n">
-        <v>1.77191185951233</v>
+        <v>1.77191174030304</v>
       </c>
       <c r="H949" t="n">
         <v>1193444</v>
@@ -27919,7 +27919,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G950" t="n">
-        <v>1.73441112041473</v>
+        <v>1.73441123962402</v>
       </c>
       <c r="H950" t="n">
         <v>1134289</v>
@@ -27977,7 +27977,7 @@
         <v>2.2279999256134</v>
       </c>
       <c r="G952" t="n">
-        <v>1.74066126346588</v>
+        <v>1.74066138267517</v>
       </c>
       <c r="H952" t="n">
         <v>535492</v>
@@ -28122,7 +28122,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G957" t="n">
-        <v>1.70316052436829</v>
+        <v>1.703160405159</v>
       </c>
       <c r="H957" t="n">
         <v>1327462</v>
@@ -28180,7 +28180,7 @@
         <v>2.19199991226196</v>
       </c>
       <c r="G959" t="n">
-        <v>1.71253561973572</v>
+        <v>1.71253573894501</v>
       </c>
       <c r="H959" t="n">
         <v>815143</v>
@@ -28267,7 +28267,7 @@
         <v>2.30599999427795</v>
       </c>
       <c r="G962" t="n">
-        <v>1.80159986019135</v>
+        <v>1.80159997940063</v>
       </c>
       <c r="H962" t="n">
         <v>675884</v>
@@ -28325,7 +28325,7 @@
         <v>2.31200003623962</v>
       </c>
       <c r="G964" t="n">
-        <v>1.80628752708435</v>
+        <v>1.80628764629364</v>
       </c>
       <c r="H964" t="n">
         <v>777846</v>
@@ -28383,7 +28383,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G966" t="n">
-        <v>1.82816290855408</v>
+        <v>1.82816302776337</v>
       </c>
       <c r="H966" t="n">
         <v>1192110</v>
@@ -28412,7 +28412,7 @@
         <v>2.34400010108948</v>
       </c>
       <c r="G967" t="n">
-        <v>1.83128809928894</v>
+        <v>1.83128821849823</v>
       </c>
       <c r="H967" t="n">
         <v>631447</v>
@@ -28615,7 +28615,7 @@
         <v>2.42199993133545</v>
       </c>
       <c r="G974" t="n">
-        <v>1.89222705364227</v>
+        <v>1.89222693443298</v>
       </c>
       <c r="H974" t="n">
         <v>687309</v>
@@ -28673,7 +28673,7 @@
         <v>2.34599995613098</v>
       </c>
       <c r="G976" t="n">
-        <v>1.83285081386566</v>
+        <v>1.83285069465637</v>
       </c>
       <c r="H976" t="n">
         <v>531246</v>
@@ -28731,7 +28731,7 @@
         <v>2.44600009918213</v>
       </c>
       <c r="G978" t="n">
-        <v>1.910977602005</v>
+        <v>1.91097748279572</v>
       </c>
       <c r="H978" t="n">
         <v>1438909</v>
@@ -28789,7 +28789,7 @@
         <v>2.44400000572205</v>
       </c>
       <c r="G980" t="n">
-        <v>1.9094146490097</v>
+        <v>1.90941476821899</v>
       </c>
       <c r="H980" t="n">
         <v>590108</v>
@@ -28818,7 +28818,7 @@
         <v>2.46399998664856</v>
       </c>
       <c r="G981" t="n">
-        <v>1.92504012584686</v>
+        <v>1.92504024505615</v>
       </c>
       <c r="H981" t="n">
         <v>619573</v>
@@ -28963,7 +28963,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G986" t="n">
-        <v>1.85160100460052</v>
+        <v>1.85160112380981</v>
       </c>
       <c r="H986" t="n">
         <v>673534</v>
@@ -29021,7 +29021,7 @@
         <v>2.34400010108948</v>
       </c>
       <c r="G988" t="n">
-        <v>1.83128809928894</v>
+        <v>1.83128821849823</v>
       </c>
       <c r="H988" t="n">
         <v>903617</v>
@@ -29108,7 +29108,7 @@
         <v>2.36400008201599</v>
       </c>
       <c r="G991" t="n">
-        <v>1.84691369533539</v>
+        <v>1.8469135761261</v>
       </c>
       <c r="H991" t="n">
         <v>564934</v>
@@ -29137,7 +29137,7 @@
         <v>2.35800004005432</v>
       </c>
       <c r="G992" t="n">
-        <v>1.84222602844238</v>
+        <v>1.84222590923309</v>
       </c>
       <c r="H992" t="n">
         <v>908830</v>
@@ -29166,7 +29166,7 @@
         <v>2.4539999961853</v>
       </c>
       <c r="G993" t="n">
-        <v>1.91722750663757</v>
+        <v>1.91722738742828</v>
       </c>
       <c r="H993" t="n">
         <v>1931707</v>
@@ -29253,7 +29253,7 @@
         <v>2.50399994850159</v>
       </c>
       <c r="G996" t="n">
-        <v>1.95629096031189</v>
+        <v>1.9562908411026</v>
       </c>
       <c r="H996" t="n">
         <v>1403227</v>
@@ -29282,7 +29282,7 @@
         <v>2.51200008392334</v>
       </c>
       <c r="G997" t="n">
-        <v>1.96254086494446</v>
+        <v>1.96254074573517</v>
       </c>
       <c r="H997" t="n">
         <v>1610791</v>
@@ -29311,7 +29311,7 @@
         <v>2.4539999961853</v>
       </c>
       <c r="G998" t="n">
-        <v>1.91722750663757</v>
+        <v>1.91722738742828</v>
       </c>
       <c r="H998" t="n">
         <v>1365293</v>
@@ -29340,7 +29340,7 @@
         <v>2.39800000190735</v>
       </c>
       <c r="G999" t="n">
-        <v>1.87347662448883</v>
+        <v>1.87347674369812</v>
       </c>
       <c r="H999" t="n">
         <v>1190338</v>
@@ -29369,7 +29369,7 @@
         <v>2.52600002288818</v>
       </c>
       <c r="G1000" t="n">
-        <v>1.97347855567932</v>
+        <v>1.97347867488861</v>
       </c>
       <c r="H1000" t="n">
         <v>2328093</v>
@@ -29456,7 +29456,7 @@
         <v>2.53600001335144</v>
       </c>
       <c r="G1003" t="n">
-        <v>1.98129141330719</v>
+        <v>1.9812912940979</v>
       </c>
       <c r="H1003" t="n">
         <v>1319951</v>
@@ -29485,7 +29485,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G1004" t="n">
-        <v>1.97660350799561</v>
+        <v>1.9766036272049</v>
       </c>
       <c r="H1004" t="n">
         <v>979990</v>
@@ -29717,7 +29717,7 @@
         <v>2.43400001525879</v>
       </c>
       <c r="G1012" t="n">
-        <v>1.9016021490097</v>
+        <v>1.90160202980042</v>
       </c>
       <c r="H1012" t="n">
         <v>1072783</v>
@@ -29746,7 +29746,7 @@
         <v>2.46399998664856</v>
       </c>
       <c r="G1013" t="n">
-        <v>1.92504012584686</v>
+        <v>1.92504024505615</v>
       </c>
       <c r="H1013" t="n">
         <v>560620</v>
@@ -29775,7 +29775,7 @@
         <v>2.49799990653992</v>
       </c>
       <c r="G1014" t="n">
-        <v>1.95160305500031</v>
+        <v>1.95160293579102</v>
       </c>
       <c r="H1014" t="n">
         <v>1151978</v>
@@ -29833,7 +29833,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G1016" t="n">
-        <v>1.97660350799561</v>
+        <v>1.9766036272049</v>
       </c>
       <c r="H1016" t="n">
         <v>761350</v>
@@ -29920,7 +29920,7 @@
         <v>2.49799990653992</v>
       </c>
       <c r="G1019" t="n">
-        <v>1.95160305500031</v>
+        <v>1.95160293579102</v>
       </c>
       <c r="H1019" t="n">
         <v>356094</v>
@@ -29978,7 +29978,7 @@
         <v>2.43199992179871</v>
       </c>
       <c r="G1021" t="n">
-        <v>1.90003943443298</v>
+        <v>1.90003955364227</v>
       </c>
       <c r="H1021" t="n">
         <v>434246</v>
@@ -30007,7 +30007,7 @@
         <v>2.43199992179871</v>
       </c>
       <c r="G1022" t="n">
-        <v>1.90003943443298</v>
+        <v>1.90003955364227</v>
       </c>
       <c r="H1022" t="n">
         <v>468554</v>
@@ -30123,7 +30123,7 @@
         <v>2.63000011444092</v>
       </c>
       <c r="G1026" t="n">
-        <v>2.05473065376282</v>
+        <v>2.05473041534424</v>
       </c>
       <c r="H1026" t="n">
         <v>1167877</v>
@@ -30239,7 +30239,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G1030" t="n">
-        <v>1.97660350799561</v>
+        <v>1.9766036272049</v>
       </c>
       <c r="H1030" t="n">
         <v>774378</v>
@@ -30355,7 +30355,7 @@
         <v>2.55200004577637</v>
       </c>
       <c r="G1034" t="n">
-        <v>1.99379181861877</v>
+        <v>1.99379169940948</v>
       </c>
       <c r="H1034" t="n">
         <v>587849</v>
@@ -30384,7 +30384,7 @@
         <v>2.51200008392334</v>
       </c>
       <c r="G1035" t="n">
-        <v>1.96254086494446</v>
+        <v>1.96254074573517</v>
       </c>
       <c r="H1035" t="n">
         <v>713302</v>
@@ -30471,7 +30471,7 @@
         <v>2.2960000038147</v>
       </c>
       <c r="G1038" t="n">
-        <v>1.79378736019135</v>
+        <v>1.79378724098206</v>
       </c>
       <c r="H1038" t="n">
         <v>1205808</v>
@@ -30616,7 +30616,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G1043" t="n">
-        <v>1.94535303115845</v>
+        <v>1.94535315036774</v>
       </c>
       <c r="H1043" t="n">
         <v>656468</v>
@@ -30645,7 +30645,7 @@
         <v>2.5699999332428</v>
       </c>
       <c r="G1044" t="n">
-        <v>2.00785422325134</v>
+        <v>2.00785446166992</v>
       </c>
       <c r="H1044" t="n">
         <v>693402</v>
@@ -30674,7 +30674,7 @@
         <v>2.62199997901917</v>
       </c>
       <c r="G1045" t="n">
-        <v>2.04848051071167</v>
+        <v>2.04848027229309</v>
       </c>
       <c r="H1045" t="n">
         <v>1359675</v>
@@ -30761,7 +30761,7 @@
         <v>2.63000011444092</v>
       </c>
       <c r="G1048" t="n">
-        <v>2.05473065376282</v>
+        <v>2.05473041534424</v>
       </c>
       <c r="H1048" t="n">
         <v>694675</v>
@@ -30906,7 +30906,7 @@
         <v>2.43400001525879</v>
       </c>
       <c r="G1053" t="n">
-        <v>1.9016021490097</v>
+        <v>1.90160202980042</v>
       </c>
       <c r="H1053" t="n">
         <v>1686795</v>
@@ -30964,7 +30964,7 @@
         <v>2.51799988746643</v>
       </c>
       <c r="G1055" t="n">
-        <v>1.96722817420959</v>
+        <v>1.96722829341888</v>
       </c>
       <c r="H1055" t="n">
         <v>965431</v>
@@ -30993,7 +30993,7 @@
         <v>2.44799995422363</v>
       </c>
       <c r="G1056" t="n">
-        <v>1.91253972053528</v>
+        <v>1.91253983974457</v>
       </c>
       <c r="H1056" t="n">
         <v>841376</v>
@@ -31196,7 +31196,7 @@
         <v>1.85599994659424</v>
       </c>
       <c r="G1063" t="n">
-        <v>1.45003020763397</v>
+        <v>1.45003032684326</v>
       </c>
       <c r="H1063" t="n">
         <v>3460885</v>
@@ -31457,7 +31457,7 @@
         <v>1.60500001907349</v>
       </c>
       <c r="G1072" t="n">
-        <v>1.25393259525299</v>
+        <v>1.2539324760437</v>
       </c>
       <c r="H1072" t="n">
         <v>2545615</v>
@@ -31486,7 +31486,7 @@
         <v>1.48399996757507</v>
       </c>
       <c r="G1073" t="n">
-        <v>1.15939915180206</v>
+        <v>1.15939903259277</v>
       </c>
       <c r="H1073" t="n">
         <v>2089398</v>
@@ -31631,7 +31631,7 @@
         <v>1.41700005531311</v>
       </c>
       <c r="G1078" t="n">
-        <v>1.1070544719696</v>
+        <v>1.10705435276031</v>
       </c>
       <c r="H1078" t="n">
         <v>850034</v>
@@ -31776,7 +31776,7 @@
         <v>1.6360000371933</v>
       </c>
       <c r="G1083" t="n">
-        <v>1.278151512146</v>
+        <v>1.27815163135529</v>
       </c>
       <c r="H1083" t="n">
         <v>1171225</v>
@@ -31979,7 +31979,7 @@
         <v>1.71099996566772</v>
       </c>
       <c r="G1090" t="n">
-        <v>1.33674669265747</v>
+        <v>1.33674657344818</v>
       </c>
       <c r="H1090" t="n">
         <v>725280</v>
@@ -32008,7 +32008,7 @@
         <v>1.74399995803833</v>
       </c>
       <c r="G1091" t="n">
-        <v>1.3625283241272</v>
+        <v>1.36252844333649</v>
       </c>
       <c r="H1091" t="n">
         <v>598828</v>
@@ -32037,7 +32037,7 @@
         <v>1.72099995613098</v>
       </c>
       <c r="G1092" t="n">
-        <v>1.34455907344818</v>
+        <v>1.34455919265747</v>
       </c>
       <c r="H1092" t="n">
         <v>814813</v>
@@ -32182,7 +32182,7 @@
         <v>1.83000004291534</v>
       </c>
       <c r="G1097" t="n">
-        <v>1.4297171831131</v>
+        <v>1.42971730232239</v>
       </c>
       <c r="H1097" t="n">
         <v>724516</v>
@@ -32211,7 +32211,7 @@
         <v>1.80499994754791</v>
       </c>
       <c r="G1098" t="n">
-        <v>1.41018557548523</v>
+        <v>1.41018545627594</v>
       </c>
       <c r="H1098" t="n">
         <v>2431117</v>
@@ -32356,7 +32356,7 @@
         <v>1.56900000572205</v>
       </c>
       <c r="G1103" t="n">
-        <v>1.22580683231354</v>
+        <v>1.22580695152283</v>
       </c>
       <c r="H1103" t="n">
         <v>2039645</v>
@@ -32414,7 +32414,7 @@
         <v>1.49300003051758</v>
       </c>
       <c r="G1105" t="n">
-        <v>1.16643047332764</v>
+        <v>1.16643059253693</v>
       </c>
       <c r="H1105" t="n">
         <v>2783740</v>
@@ -32472,7 +32472,7 @@
         <v>1.46000003814697</v>
       </c>
       <c r="G1107" t="n">
-        <v>1.1406489610672</v>
+        <v>1.14064884185791</v>
       </c>
       <c r="H1107" t="n">
         <v>1760635</v>
@@ -32501,7 +32501,7 @@
         <v>1.41600000858307</v>
       </c>
       <c r="G1108" t="n">
-        <v>1.10627293586731</v>
+        <v>1.1062730550766</v>
       </c>
       <c r="H1108" t="n">
         <v>1780145</v>
@@ -32530,7 +32530,7 @@
         <v>1.41299998760223</v>
       </c>
       <c r="G1109" t="n">
-        <v>1.10392928123474</v>
+        <v>1.10392916202545</v>
       </c>
       <c r="H1109" t="n">
         <v>1286738</v>
@@ -32559,7 +32559,7 @@
         <v>1.43599998950958</v>
       </c>
       <c r="G1110" t="n">
-        <v>1.12189841270447</v>
+        <v>1.12189853191376</v>
       </c>
       <c r="H1110" t="n">
         <v>819909</v>
@@ -32588,7 +32588,7 @@
         <v>1.36000001430511</v>
       </c>
       <c r="G1111" t="n">
-        <v>1.06252217292786</v>
+        <v>1.06252205371857</v>
       </c>
       <c r="H1111" t="n">
         <v>1910320</v>
@@ -32733,7 +32733,7 @@
         <v>1.41199994087219</v>
       </c>
       <c r="G1116" t="n">
-        <v>1.10314798355103</v>
+        <v>1.10314810276031</v>
       </c>
       <c r="H1116" t="n">
         <v>1877981</v>
@@ -32762,7 +32762,7 @@
         <v>1.41199994087219</v>
       </c>
       <c r="G1117" t="n">
-        <v>1.10314798355103</v>
+        <v>1.10314810276031</v>
       </c>
       <c r="H1117" t="n">
         <v>1335874</v>
@@ -32820,7 +32820,7 @@
         <v>1.41600000858307</v>
       </c>
       <c r="G1119" t="n">
-        <v>1.10627293586731</v>
+        <v>1.1062730550766</v>
       </c>
       <c r="H1119" t="n">
         <v>1329889</v>
@@ -33023,7 +33023,7 @@
         <v>1.69500005245209</v>
       </c>
       <c r="G1126" t="n">
-        <v>1.32424640655518</v>
+        <v>1.32424652576447</v>
       </c>
       <c r="H1126" t="n">
         <v>5005945</v>
@@ -33139,7 +33139,7 @@
         <v>1.61800003051758</v>
       </c>
       <c r="G1130" t="n">
-        <v>1.26408863067627</v>
+        <v>1.26408874988556</v>
       </c>
       <c r="H1130" t="n">
         <v>1256084</v>
@@ -33168,7 +33168,7 @@
         <v>1.69500005245209</v>
       </c>
       <c r="G1131" t="n">
-        <v>1.32424640655518</v>
+        <v>1.32424652576447</v>
       </c>
       <c r="H1131" t="n">
         <v>2326202</v>
@@ -33197,7 +33197,7 @@
         <v>1.6710000038147</v>
       </c>
       <c r="G1132" t="n">
-        <v>1.30549585819244</v>
+        <v>1.30549597740173</v>
       </c>
       <c r="H1132" t="n">
         <v>1132847</v>
@@ -33226,7 +33226,7 @@
         <v>1.71000003814697</v>
       </c>
       <c r="G1133" t="n">
-        <v>1.33596527576447</v>
+        <v>1.33596539497375</v>
       </c>
       <c r="H1133" t="n">
         <v>1739894</v>
@@ -33255,7 +33255,7 @@
         <v>1.69500005245209</v>
       </c>
       <c r="G1134" t="n">
-        <v>1.32424640655518</v>
+        <v>1.32424652576447</v>
       </c>
       <c r="H1134" t="n">
         <v>1490920</v>
@@ -33284,7 +33284,7 @@
         <v>1.6710000038147</v>
       </c>
       <c r="G1135" t="n">
-        <v>1.30549585819244</v>
+        <v>1.30549597740173</v>
       </c>
       <c r="H1135" t="n">
         <v>945591</v>
@@ -33313,7 +33313,7 @@
         <v>1.73399996757507</v>
       </c>
       <c r="G1136" t="n">
-        <v>1.35471558570862</v>
+        <v>1.35471570491791</v>
       </c>
       <c r="H1136" t="n">
         <v>1407858</v>
@@ -33371,7 +33371,7 @@
         <v>1.64400005340576</v>
       </c>
       <c r="G1138" t="n">
-        <v>1.28440177440643</v>
+        <v>1.28440189361572</v>
       </c>
       <c r="H1138" t="n">
         <v>2066801</v>
@@ -33690,7 +33690,7 @@
         <v>1.65100002288818</v>
       </c>
       <c r="G1149" t="n">
-        <v>1.28987061977386</v>
+        <v>1.28987050056458</v>
       </c>
       <c r="H1149" t="n">
         <v>848740</v>
@@ -33719,7 +33719,7 @@
         <v>1.65100002288818</v>
       </c>
       <c r="G1150" t="n">
-        <v>1.28987061977386</v>
+        <v>1.28987050056458</v>
       </c>
       <c r="H1150" t="n">
         <v>1297129</v>
@@ -33980,7 +33980,7 @@
         <v>1.61500000953674</v>
       </c>
       <c r="G1159" t="n">
-        <v>1.26174509525299</v>
+        <v>1.2617449760437</v>
       </c>
       <c r="H1159" t="n">
         <v>1030678</v>
@@ -34009,7 +34009,7 @@
         <v>1.56599998474121</v>
       </c>
       <c r="G1160" t="n">
-        <v>1.22346317768097</v>
+        <v>1.22346305847168</v>
       </c>
       <c r="H1160" t="n">
         <v>795545</v>
@@ -34096,7 +34096,7 @@
         <v>1.51600003242493</v>
       </c>
       <c r="G1163" t="n">
-        <v>1.18439972400665</v>
+        <v>1.18439960479736</v>
       </c>
       <c r="H1163" t="n">
         <v>1659505</v>
@@ -34270,7 +34270,7 @@
         <v>1.57000005245209</v>
       </c>
       <c r="G1169" t="n">
-        <v>1.22658812999725</v>
+        <v>1.22658801078796</v>
       </c>
       <c r="H1169" t="n">
         <v>782213</v>
@@ -34299,7 +34299,7 @@
         <v>1.60500001907349</v>
       </c>
       <c r="G1170" t="n">
-        <v>1.25393259525299</v>
+        <v>1.2539324760437</v>
       </c>
       <c r="H1170" t="n">
         <v>522636</v>
@@ -34531,7 +34531,7 @@
         <v>1.60800004005432</v>
       </c>
       <c r="G1178" t="n">
-        <v>1.25627624988556</v>
+        <v>1.25627613067627</v>
       </c>
       <c r="H1178" t="n">
         <v>641616</v>
@@ -34618,7 +34618,7 @@
         <v>1.5900000333786</v>
       </c>
       <c r="G1181" t="n">
-        <v>1.24221336841583</v>
+        <v>1.24221348762512</v>
       </c>
       <c r="H1181" t="n">
         <v>501935</v>
@@ -34647,7 +34647,7 @@
         <v>1.57799994945526</v>
       </c>
       <c r="G1182" t="n">
-        <v>1.2328382730484</v>
+        <v>1.23283815383911</v>
       </c>
       <c r="H1182" t="n">
         <v>516445</v>
@@ -34676,7 +34676,7 @@
         <v>1.57000005245209</v>
       </c>
       <c r="G1183" t="n">
-        <v>1.22658812999725</v>
+        <v>1.22658801078796</v>
       </c>
       <c r="H1183" t="n">
         <v>632367</v>
@@ -34879,7 +34879,7 @@
         <v>1.48399996757507</v>
       </c>
       <c r="G1190" t="n">
-        <v>1.15939915180206</v>
+        <v>1.15939903259277</v>
       </c>
       <c r="H1190" t="n">
         <v>962209</v>
@@ -34908,7 +34908,7 @@
         <v>1.48800003528595</v>
       </c>
       <c r="G1191" t="n">
-        <v>1.16252422332764</v>
+        <v>1.16252410411835</v>
       </c>
       <c r="H1191" t="n">
         <v>608816</v>
@@ -34966,7 +34966,7 @@
         <v>1.49300003051758</v>
       </c>
       <c r="G1193" t="n">
-        <v>1.16643047332764</v>
+        <v>1.16643059253693</v>
       </c>
       <c r="H1193" t="n">
         <v>931594</v>
@@ -35053,7 +35053,7 @@
         <v>1.43900001049042</v>
       </c>
       <c r="G1196" t="n">
-        <v>1.12424230575562</v>
+        <v>1.12424218654633</v>
       </c>
       <c r="H1196" t="n">
         <v>899903</v>
@@ -35082,7 +35082,7 @@
         <v>1.43599998950958</v>
       </c>
       <c r="G1197" t="n">
-        <v>1.12189841270447</v>
+        <v>1.12189853191376</v>
       </c>
       <c r="H1197" t="n">
         <v>1581501</v>
@@ -35169,7 +35169,7 @@
         <v>1.41100001335144</v>
       </c>
       <c r="G1200" t="n">
-        <v>1.10236668586731</v>
+        <v>1.10236656665802</v>
       </c>
       <c r="H1200" t="n">
         <v>1048382</v>
@@ -35198,7 +35198,7 @@
         <v>1.41299998760223</v>
       </c>
       <c r="G1201" t="n">
-        <v>1.10392928123474</v>
+        <v>1.10392916202545</v>
       </c>
       <c r="H1201" t="n">
         <v>1122527</v>
@@ -35227,7 +35227,7 @@
         <v>1.41600000858307</v>
       </c>
       <c r="G1202" t="n">
-        <v>1.10627293586731</v>
+        <v>1.1062730550766</v>
       </c>
       <c r="H1202" t="n">
         <v>527751</v>
@@ -35256,7 +35256,7 @@
         <v>1.40799999237061</v>
       </c>
       <c r="G1203" t="n">
-        <v>1.10002291202545</v>
+        <v>1.10002303123474</v>
       </c>
       <c r="H1203" t="n">
         <v>648354</v>
@@ -35401,7 +35401,7 @@
         <v>1.43599998950958</v>
       </c>
       <c r="G1208" t="n">
-        <v>1.12189841270447</v>
+        <v>1.12189853191376</v>
       </c>
       <c r="H1208" t="n">
         <v>1117041</v>
@@ -35430,7 +35430,7 @@
         <v>1.41700005531311</v>
       </c>
       <c r="G1209" t="n">
-        <v>1.1070544719696</v>
+        <v>1.10705435276031</v>
       </c>
       <c r="H1209" t="n">
         <v>865235</v>
@@ -35575,7 +35575,7 @@
         <v>1.4559999704361</v>
       </c>
       <c r="G1214" t="n">
-        <v>1.13752377033234</v>
+        <v>1.13752365112305</v>
       </c>
       <c r="H1214" t="n">
         <v>426117</v>
@@ -35604,7 +35604,7 @@
         <v>1.41499996185303</v>
       </c>
       <c r="G1215" t="n">
-        <v>1.10549187660217</v>
+        <v>1.10549175739288</v>
       </c>
       <c r="H1215" t="n">
         <v>616239</v>
@@ -35807,7 +35807,7 @@
         <v>1.31099998950958</v>
       </c>
       <c r="G1222" t="n">
-        <v>1.02424025535583</v>
+        <v>1.02424013614655</v>
       </c>
       <c r="H1222" t="n">
         <v>1078321</v>
@@ -36010,7 +36010,7 @@
         <v>1.16199994087219</v>
       </c>
       <c r="G1229" t="n">
-        <v>0.907831370830536</v>
+        <v>0.907831430435181</v>
       </c>
       <c r="H1229" t="n">
         <v>1458641</v>
@@ -36039,7 +36039,7 @@
         <v>1.18499994277954</v>
       </c>
       <c r="G1230" t="n">
-        <v>0.925800502300262</v>
+        <v>0.925800561904907</v>
       </c>
       <c r="H1230" t="n">
         <v>894030</v>
@@ -36068,7 +36068,7 @@
         <v>1.16199994087219</v>
       </c>
       <c r="G1231" t="n">
-        <v>0.907831370830536</v>
+        <v>0.907831430435181</v>
       </c>
       <c r="H1231" t="n">
         <v>1698975</v>
@@ -36155,7 +36155,7 @@
         <v>1.13399994373322</v>
       </c>
       <c r="G1234" t="n">
-        <v>0.885955929756165</v>
+        <v>0.88595587015152</v>
       </c>
       <c r="H1234" t="n">
         <v>748628</v>
@@ -36184,7 +36184,7 @@
         <v>1.2849999666214</v>
       </c>
       <c r="G1235" t="n">
-        <v>1.00392711162567</v>
+        <v>1.00392723083496</v>
       </c>
       <c r="H1235" t="n">
         <v>2797103</v>
@@ -36329,7 +36329,7 @@
         <v>1.4539999961853</v>
       </c>
       <c r="G1240" t="n">
-        <v>1.13596129417419</v>
+        <v>1.1359611749649</v>
       </c>
       <c r="H1240" t="n">
         <v>4917931</v>
@@ -36358,7 +36358,7 @@
         <v>1.44000005722046</v>
       </c>
       <c r="G1241" t="n">
-        <v>1.12502336502075</v>
+        <v>1.12502348423004</v>
       </c>
       <c r="H1241" t="n">
         <v>1540311</v>
@@ -36387,7 +36387,7 @@
         <v>1.46000003814697</v>
       </c>
       <c r="G1242" t="n">
-        <v>1.1406489610672</v>
+        <v>1.14064884185791</v>
       </c>
       <c r="H1242" t="n">
         <v>2486058</v>
@@ -36416,7 +36416,7 @@
         <v>1.47899997234344</v>
       </c>
       <c r="G1243" t="n">
-        <v>1.15549266338348</v>
+        <v>1.15549278259277</v>
       </c>
       <c r="H1243" t="n">
         <v>1712373</v>
@@ -36474,7 +36474,7 @@
         <v>1.58000004291534</v>
       </c>
       <c r="G1245" t="n">
-        <v>1.23440086841583</v>
+        <v>1.23440074920654</v>
       </c>
       <c r="H1245" t="n">
         <v>5400870</v>
@@ -36503,7 +36503,7 @@
         <v>1.58000004291534</v>
       </c>
       <c r="G1246" t="n">
-        <v>1.23440086841583</v>
+        <v>1.23440074920654</v>
       </c>
       <c r="H1246" t="n">
         <v>2377776</v>
@@ -36590,7 +36590,7 @@
         <v>1.58599996566772</v>
       </c>
       <c r="G1249" t="n">
-        <v>1.23908829689026</v>
+        <v>1.23908841609955</v>
       </c>
       <c r="H1249" t="n">
         <v>886713</v>
@@ -36706,7 +36706,7 @@
         <v>1.5789999961853</v>
       </c>
       <c r="G1253" t="n">
-        <v>1.23361945152283</v>
+        <v>1.23361957073212</v>
       </c>
       <c r="H1253" t="n">
         <v>590847</v>
@@ -36880,7 +36880,7 @@
         <v>1.74300003051758</v>
       </c>
       <c r="G1259" t="n">
-        <v>1.36174726486206</v>
+        <v>1.36174714565277</v>
       </c>
       <c r="H1259" t="n">
         <v>3659321</v>
@@ -36996,7 +36996,7 @@
         <v>1.78199994564056</v>
       </c>
       <c r="G1263" t="n">
-        <v>1.39221656322479</v>
+        <v>1.3922164440155</v>
       </c>
       <c r="H1263" t="n">
         <v>870758</v>
@@ -37025,7 +37025,7 @@
         <v>1.76199996471405</v>
       </c>
       <c r="G1264" t="n">
-        <v>1.37659132480621</v>
+        <v>1.37659120559692</v>
       </c>
       <c r="H1264" t="n">
         <v>1137092</v>
@@ -37083,7 +37083,7 @@
         <v>1.66700005531311</v>
       </c>
       <c r="G1266" t="n">
-        <v>1.30237090587616</v>
+        <v>1.30237102508545</v>
       </c>
       <c r="H1266" t="n">
         <v>914481</v>
@@ -37112,7 +37112,7 @@
         <v>1.72099995613098</v>
       </c>
       <c r="G1267" t="n">
-        <v>1.34455907344818</v>
+        <v>1.34455919265747</v>
       </c>
       <c r="H1267" t="n">
         <v>1168845</v>
@@ -37170,7 +37170,7 @@
         <v>1.82599997520447</v>
       </c>
       <c r="G1269" t="n">
-        <v>1.42659211158752</v>
+        <v>1.42659223079681</v>
       </c>
       <c r="H1269" t="n">
         <v>4006922</v>
@@ -37286,7 +37286,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G1273" t="n">
-        <v>1.50784385204315</v>
+        <v>1.50784397125244</v>
       </c>
       <c r="H1273" t="n">
         <v>1489930</v>
@@ -37344,7 +37344,7 @@
         <v>2.00799989700317</v>
       </c>
       <c r="G1275" t="n">
-        <v>1.56878244876862</v>
+        <v>1.56878256797791</v>
       </c>
       <c r="H1275" t="n">
         <v>1609145</v>
@@ -37373,7 +37373,7 @@
         <v>2.00799989700317</v>
       </c>
       <c r="G1276" t="n">
-        <v>1.56878244876862</v>
+        <v>1.56878256797791</v>
       </c>
       <c r="H1276" t="n">
         <v>2952476</v>
@@ -37431,7 +37431,7 @@
         <v>2.01799988746643</v>
       </c>
       <c r="G1278" t="n">
-        <v>1.57659518718719</v>
+        <v>1.57659530639648</v>
       </c>
       <c r="H1278" t="n">
         <v>983583</v>
@@ -37518,7 +37518,7 @@
         <v>1.97599995136261</v>
       </c>
       <c r="G1281" t="n">
-        <v>1.5437821149826</v>
+        <v>1.54378223419189</v>
       </c>
       <c r="H1281" t="n">
         <v>2807824</v>
@@ -37576,7 +37576,7 @@
         <v>2.01799988746643</v>
       </c>
       <c r="G1283" t="n">
-        <v>1.57659518718719</v>
+        <v>1.57659530639648</v>
       </c>
       <c r="H1283" t="n">
         <v>1398647</v>
@@ -37750,7 +37750,7 @@
         <v>1.93400001525879</v>
       </c>
       <c r="G1289" t="n">
-        <v>1.51096892356873</v>
+        <v>1.51096904277802</v>
       </c>
       <c r="H1289" t="n">
         <v>1895432</v>
@@ -37808,7 +37808,7 @@
         <v>1.93400001525879</v>
       </c>
       <c r="G1291" t="n">
-        <v>1.51096892356873</v>
+        <v>1.51096904277802</v>
       </c>
       <c r="H1291" t="n">
         <v>2484200</v>
@@ -37837,7 +37837,7 @@
         <v>1.97000002861023</v>
       </c>
       <c r="G1292" t="n">
-        <v>1.53909468650818</v>
+        <v>1.53909456729889</v>
       </c>
       <c r="H1292" t="n">
         <v>1732450</v>
@@ -37924,7 +37924,7 @@
         <v>2.10400009155273</v>
       </c>
       <c r="G1295" t="n">
-        <v>1.64378416538239</v>
+        <v>1.64378428459167</v>
       </c>
       <c r="H1295" t="n">
         <v>1541619</v>
@@ -38098,7 +38098,7 @@
         <v>2.30599999427795</v>
       </c>
       <c r="G1301" t="n">
-        <v>1.80159986019135</v>
+        <v>1.80159997940063</v>
       </c>
       <c r="H1301" t="n">
         <v>1876616</v>
@@ -38243,7 +38243,7 @@
         <v>2.14800000190735</v>
       </c>
       <c r="G1306" t="n">
-        <v>1.67816007137299</v>
+        <v>1.6781599521637</v>
       </c>
       <c r="H1306" t="n">
         <v>681091</v>
@@ -38272,7 +38272,7 @@
         <v>2.13800001144409</v>
       </c>
       <c r="G1307" t="n">
-        <v>1.67034721374512</v>
+        <v>1.67034733295441</v>
       </c>
       <c r="H1307" t="n">
         <v>801980</v>
@@ -38591,7 +38591,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G1318" t="n">
-        <v>1.83597588539124</v>
+        <v>1.83597576618195</v>
       </c>
       <c r="H1318" t="n">
         <v>1717013</v>
@@ -38707,7 +38707,7 @@
         <v>2.5460000038147</v>
       </c>
       <c r="G1322" t="n">
-        <v>1.98910403251648</v>
+        <v>1.98910415172577</v>
       </c>
       <c r="H1322" t="n">
         <v>1428035</v>
@@ -38736,7 +38736,7 @@
         <v>2.50399994850159</v>
       </c>
       <c r="G1323" t="n">
-        <v>1.95629096031189</v>
+        <v>1.9562908411026</v>
       </c>
       <c r="H1323" t="n">
         <v>1869091</v>
@@ -38794,7 +38794,7 @@
         <v>2.42199993133545</v>
       </c>
       <c r="G1325" t="n">
-        <v>1.89222705364227</v>
+        <v>1.89222693443298</v>
       </c>
       <c r="H1325" t="n">
         <v>2745691</v>
@@ -38852,7 +38852,7 @@
         <v>2.42799997329712</v>
       </c>
       <c r="G1327" t="n">
-        <v>1.89691460132599</v>
+        <v>1.89691472053528</v>
       </c>
       <c r="H1327" t="n">
         <v>1121455</v>
@@ -38881,7 +38881,7 @@
         <v>2.43400001525879</v>
       </c>
       <c r="G1328" t="n">
-        <v>1.9016021490097</v>
+        <v>1.90160202980042</v>
       </c>
       <c r="H1328" t="n">
         <v>1783803</v>
@@ -39026,7 +39026,7 @@
         <v>2.50600004196167</v>
       </c>
       <c r="G1333" t="n">
-        <v>1.95785319805145</v>
+        <v>1.95785307884216</v>
       </c>
       <c r="H1333" t="n">
         <v>1706207</v>
@@ -39200,7 +39200,7 @@
         <v>2.51399993896484</v>
       </c>
       <c r="G1339" t="n">
-        <v>1.9641033411026</v>
+        <v>1.96410322189331</v>
       </c>
       <c r="H1339" t="n">
         <v>1491289</v>
@@ -39316,7 +39316,7 @@
         <v>2.68799996376038</v>
       </c>
       <c r="G1343" t="n">
-        <v>2.10004353523254</v>
+        <v>2.10004377365112</v>
       </c>
       <c r="H1343" t="n">
         <v>1867566</v>
@@ -39374,7 +39374,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G1345" t="n">
-        <v>1.99226546287537</v>
+        <v>1.99226534366608</v>
       </c>
       <c r="H1345" t="n">
         <v>2441554</v>
@@ -39432,7 +39432,7 @@
         <v>2.57399988174438</v>
       </c>
       <c r="G1347" t="n">
-        <v>2.10167694091797</v>
+        <v>2.10167670249939</v>
       </c>
       <c r="H1347" t="n">
         <v>1397518</v>
@@ -39461,7 +39461,7 @@
         <v>2.59400010108948</v>
       </c>
       <c r="G1348" t="n">
-        <v>2.11800694465637</v>
+        <v>2.11800670623779</v>
       </c>
       <c r="H1348" t="n">
         <v>1581439</v>
@@ -39635,7 +39635,7 @@
         <v>2.69199991226196</v>
       </c>
       <c r="G1354" t="n">
-        <v>2.19802379608154</v>
+        <v>2.19802403450012</v>
       </c>
       <c r="H1354" t="n">
         <v>1318011</v>
@@ -39751,7 +39751,7 @@
         <v>2.72199988365173</v>
       </c>
       <c r="G1358" t="n">
-        <v>2.22251915931702</v>
+        <v>2.22251892089844</v>
       </c>
       <c r="H1358" t="n">
         <v>2138513</v>
@@ -39809,7 +39809,7 @@
         <v>2.73399996757507</v>
       </c>
       <c r="G1360" t="n">
-        <v>2.23231720924377</v>
+        <v>2.23231744766235</v>
       </c>
       <c r="H1360" t="n">
         <v>1274607</v>
@@ -39838,7 +39838,7 @@
         <v>2.76600003242493</v>
       </c>
       <c r="G1361" t="n">
-        <v>2.25844526290894</v>
+        <v>2.25844550132751</v>
       </c>
       <c r="H1361" t="n">
         <v>877406</v>
@@ -39896,7 +39896,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G1363" t="n">
-        <v>2.31070113182068</v>
+        <v>2.31070137023926</v>
       </c>
       <c r="H1363" t="n">
         <v>1264352</v>
@@ -39954,7 +39954,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G1365" t="n">
-        <v>2.35969161987305</v>
+        <v>2.35969185829163</v>
       </c>
       <c r="H1365" t="n">
         <v>1573972</v>
@@ -40012,7 +40012,7 @@
         <v>2.88800001144409</v>
       </c>
       <c r="G1367" t="n">
-        <v>2.3580584526062</v>
+        <v>2.35805821418762</v>
       </c>
       <c r="H1367" t="n">
         <v>1393283</v>
@@ -40070,7 +40070,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G1369" t="n">
-        <v>2.34336137771606</v>
+        <v>2.34336161613464</v>
       </c>
       <c r="H1369" t="n">
         <v>571254</v>
@@ -40128,7 +40128,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G1371" t="n">
-        <v>2.32703113555908</v>
+        <v>2.32703137397766</v>
       </c>
       <c r="H1371" t="n">
         <v>473269</v>
@@ -40157,7 +40157,7 @@
         <v>2.93400001525879</v>
       </c>
       <c r="G1372" t="n">
-        <v>2.39561748504639</v>
+        <v>2.39561772346497</v>
       </c>
       <c r="H1372" t="n">
         <v>2105354</v>
@@ -40302,7 +40302,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G1377" t="n">
-        <v>2.61280727386475</v>
+        <v>2.61280703544617</v>
       </c>
       <c r="H1377" t="n">
         <v>2552055</v>
@@ -40331,7 +40331,7 @@
         <v>3.21000003814697</v>
       </c>
       <c r="G1378" t="n">
-        <v>2.62097239494324</v>
+        <v>2.62097215652466</v>
       </c>
       <c r="H1378" t="n">
         <v>928338</v>
@@ -40447,7 +40447,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G1382" t="n">
-        <v>2.62913727760315</v>
+        <v>2.62913703918457</v>
       </c>
       <c r="H1382" t="n">
         <v>941698</v>
@@ -40534,7 +40534,7 @@
         <v>3.25399994850159</v>
       </c>
       <c r="G1385" t="n">
-        <v>2.65689826011658</v>
+        <v>2.65689849853516</v>
       </c>
       <c r="H1385" t="n">
         <v>621956</v>
@@ -40679,7 +40679,7 @@
         <v>3.10800004005432</v>
       </c>
       <c r="G1390" t="n">
-        <v>2.5376889705658</v>
+        <v>2.53768920898438</v>
       </c>
       <c r="H1390" t="n">
         <v>743013</v>
@@ -40737,7 +40737,7 @@
         <v>3.08400011062622</v>
       </c>
       <c r="G1392" t="n">
-        <v>2.51809310913086</v>
+        <v>2.51809287071228</v>
       </c>
       <c r="H1392" t="n">
         <v>449477</v>
@@ -40824,7 +40824,7 @@
         <v>3.08400011062622</v>
       </c>
       <c r="G1395" t="n">
-        <v>2.51809310913086</v>
+        <v>2.51809287071228</v>
       </c>
       <c r="H1395" t="n">
         <v>261054</v>
@@ -40853,7 +40853,7 @@
         <v>3.08400011062622</v>
       </c>
       <c r="G1396" t="n">
-        <v>2.51809310913086</v>
+        <v>2.51809287071228</v>
       </c>
       <c r="H1396" t="n">
         <v>557953</v>
@@ -40882,7 +40882,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G1397" t="n">
-        <v>2.56381726264954</v>
+        <v>2.56381702423096</v>
       </c>
       <c r="H1397" t="n">
         <v>718858</v>
@@ -41143,7 +41143,7 @@
         <v>3.10400009155273</v>
       </c>
       <c r="G1406" t="n">
-        <v>2.53442335128784</v>
+        <v>2.53442311286926</v>
       </c>
       <c r="H1406" t="n">
         <v>358259</v>
@@ -41172,7 +41172,7 @@
         <v>3.09200000762939</v>
       </c>
       <c r="G1407" t="n">
-        <v>2.52462482452393</v>
+        <v>2.5246250629425</v>
       </c>
       <c r="H1407" t="n">
         <v>379769</v>
@@ -41346,7 +41346,7 @@
         <v>2.99600005149841</v>
       </c>
       <c r="G1413" t="n">
-        <v>2.44624066352844</v>
+        <v>2.44624090194702</v>
       </c>
       <c r="H1413" t="n">
         <v>369037</v>
@@ -41404,7 +41404,7 @@
         <v>3.06200003623962</v>
       </c>
       <c r="G1415" t="n">
-        <v>2.50012993812561</v>
+        <v>2.50012969970703</v>
       </c>
       <c r="H1415" t="n">
         <v>467773</v>
@@ -41520,7 +41520,7 @@
         <v>3.18199992179871</v>
       </c>
       <c r="G1419" t="n">
-        <v>2.59811043739319</v>
+        <v>2.59811019897461</v>
       </c>
       <c r="H1419" t="n">
         <v>934676</v>
@@ -41607,7 +41607,7 @@
         <v>3.1340000629425</v>
       </c>
       <c r="G1422" t="n">
-        <v>2.55891799926758</v>
+        <v>2.55891823768616</v>
       </c>
       <c r="H1422" t="n">
         <v>536502</v>
@@ -41665,7 +41665,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G1424" t="n">
-        <v>2.69445776939392</v>
+        <v>2.69445753097534</v>
       </c>
       <c r="H1424" t="n">
         <v>1491660</v>
@@ -41752,7 +41752,7 @@
         <v>3.31800007820129</v>
       </c>
       <c r="G1427" t="n">
-        <v>2.7091543674469</v>
+        <v>2.70915460586548</v>
       </c>
       <c r="H1427" t="n">
         <v>598233</v>
@@ -41810,7 +41810,7 @@
         <v>3.42600011825562</v>
       </c>
       <c r="G1429" t="n">
-        <v>2.7973370552063</v>
+        <v>2.79733681678772</v>
       </c>
       <c r="H1429" t="n">
         <v>1310061</v>
@@ -41897,7 +41897,7 @@
         <v>3.2960000038147</v>
       </c>
       <c r="G1432" t="n">
-        <v>2.69119143486023</v>
+        <v>2.69119167327881</v>
       </c>
       <c r="H1432" t="n">
         <v>799078</v>
@@ -41955,7 +41955,7 @@
         <v>3.33800005912781</v>
       </c>
       <c r="G1434" t="n">
-        <v>2.7254843711853</v>
+        <v>2.72548460960388</v>
       </c>
       <c r="H1434" t="n">
         <v>416259</v>
@@ -42042,7 +42042,7 @@
         <v>3.32200002670288</v>
       </c>
       <c r="G1437" t="n">
-        <v>2.71242046356201</v>
+        <v>2.71242022514343</v>
       </c>
       <c r="H1437" t="n">
         <v>431705</v>
@@ -42129,7 +42129,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G1440" t="n">
-        <v>2.69445776939392</v>
+        <v>2.69445753097534</v>
       </c>
       <c r="H1440" t="n">
         <v>521043</v>
@@ -42158,7 +42158,7 @@
         <v>3.32200002670288</v>
       </c>
       <c r="G1441" t="n">
-        <v>2.71242046356201</v>
+        <v>2.71242022514343</v>
       </c>
       <c r="H1441" t="n">
         <v>383848</v>
@@ -42187,7 +42187,7 @@
         <v>3.33800005912781</v>
       </c>
       <c r="G1442" t="n">
-        <v>2.7254843711853</v>
+        <v>2.72548460960388</v>
       </c>
       <c r="H1442" t="n">
         <v>717968</v>
@@ -42245,7 +42245,7 @@
         <v>3.39199995994568</v>
       </c>
       <c r="G1444" t="n">
-        <v>2.76957535743713</v>
+        <v>2.76957559585571</v>
       </c>
       <c r="H1444" t="n">
         <v>340684</v>
@@ -42448,7 +42448,7 @@
         <v>3.27600002288818</v>
       </c>
       <c r="G1451" t="n">
-        <v>2.67486143112183</v>
+        <v>2.67486166954041</v>
       </c>
       <c r="H1451" t="n">
         <v>358794</v>
@@ -42593,7 +42593,7 @@
         <v>3.36199998855591</v>
       </c>
       <c r="G1456" t="n">
-        <v>2.7450807094574</v>
+        <v>2.74508047103882</v>
       </c>
       <c r="H1456" t="n">
         <v>466779</v>
@@ -42651,7 +42651,7 @@
         <v>3.37800002098083</v>
       </c>
       <c r="G1458" t="n">
-        <v>2.75814437866211</v>
+        <v>2.75814461708069</v>
       </c>
       <c r="H1458" t="n">
         <v>309879</v>
@@ -42883,7 +42883,7 @@
         <v>3.31800007820129</v>
       </c>
       <c r="G1466" t="n">
-        <v>2.7091543674469</v>
+        <v>2.70915460586548</v>
       </c>
       <c r="H1466" t="n">
         <v>859029</v>
@@ -42912,7 +42912,7 @@
         <v>3.35599994659424</v>
       </c>
       <c r="G1467" t="n">
-        <v>2.74018168449402</v>
+        <v>2.74018144607544</v>
       </c>
       <c r="H1467" t="n">
         <v>1077702</v>
@@ -43028,7 +43028,7 @@
         <v>3.3840000629425</v>
       </c>
       <c r="G1471" t="n">
-        <v>2.76304364204407</v>
+        <v>2.76304340362549</v>
       </c>
       <c r="H1471" t="n">
         <v>314623</v>
@@ -43086,7 +43086,7 @@
         <v>3.51200008392334</v>
       </c>
       <c r="G1473" t="n">
-        <v>2.86755585670471</v>
+        <v>2.86755609512329</v>
       </c>
       <c r="H1473" t="n">
         <v>3355974</v>
@@ -43144,7 +43144,7 @@
         <v>3.58400011062622</v>
       </c>
       <c r="G1475" t="n">
-        <v>2.92634439468384</v>
+        <v>2.92634415626526</v>
       </c>
       <c r="H1475" t="n">
         <v>1695282</v>
@@ -43173,7 +43173,7 @@
         <v>3.63800001144409</v>
       </c>
       <c r="G1476" t="n">
-        <v>2.97043490409851</v>
+        <v>2.97043514251709</v>
       </c>
       <c r="H1476" t="n">
         <v>1140373</v>
@@ -43231,7 +43231,7 @@
         <v>3.76200008392334</v>
       </c>
       <c r="G1478" t="n">
-        <v>3.07168126106262</v>
+        <v>3.0716814994812</v>
       </c>
       <c r="H1478" t="n">
         <v>2560678</v>
@@ -43289,7 +43289,7 @@
         <v>3.72399997711182</v>
       </c>
       <c r="G1480" t="n">
-        <v>3.04065442085266</v>
+        <v>3.04065418243408</v>
       </c>
       <c r="H1480" t="n">
         <v>701322</v>
@@ -43463,7 +43463,7 @@
         <v>3.76200008392334</v>
       </c>
       <c r="G1486" t="n">
-        <v>3.07168126106262</v>
+        <v>3.0716814994812</v>
       </c>
       <c r="H1486" t="n">
         <v>1085473</v>
@@ -43521,7 +43521,7 @@
         <v>4.0460000038147</v>
       </c>
       <c r="G1488" t="n">
-        <v>3.3035683631897</v>
+        <v>3.30356812477112</v>
       </c>
       <c r="H1488" t="n">
         <v>4043739</v>
@@ -43724,7 +43724,7 @@
         <v>4.09600019454956</v>
       </c>
       <c r="G1495" t="n">
-        <v>3.344393491745</v>
+        <v>3.34439373016357</v>
       </c>
       <c r="H1495" t="n">
         <v>2410363</v>
@@ -43753,7 +43753,7 @@
         <v>4.10799980163574</v>
       </c>
       <c r="G1496" t="n">
-        <v>3.35419130325317</v>
+        <v>3.35419106483459</v>
       </c>
       <c r="H1496" t="n">
         <v>1760944</v>
@@ -43811,7 +43811,7 @@
         <v>4.02199983596802</v>
       </c>
       <c r="G1498" t="n">
-        <v>3.28397178649902</v>
+        <v>3.2839720249176</v>
       </c>
       <c r="H1498" t="n">
         <v>1794745</v>
@@ -43840,7 +43840,7 @@
         <v>4.06799983978271</v>
       </c>
       <c r="G1499" t="n">
-        <v>3.32153105735779</v>
+        <v>3.32153081893921</v>
       </c>
       <c r="H1499" t="n">
         <v>1045581</v>
@@ -43898,7 +43898,7 @@
         <v>3.9779999256134</v>
       </c>
       <c r="G1501" t="n">
-        <v>3.2480456829071</v>
+        <v>3.24804592132568</v>
       </c>
       <c r="H1501" t="n">
         <v>921019</v>
@@ -43985,7 +43985,7 @@
         <v>3.90199995040894</v>
       </c>
       <c r="G1504" t="n">
-        <v>3.18599152565002</v>
+        <v>3.1859917640686</v>
       </c>
       <c r="H1504" t="n">
         <v>950120</v>
@@ -44043,7 +44043,7 @@
         <v>4.01000022888184</v>
       </c>
       <c r="G1506" t="n">
-        <v>3.274174451828</v>
+        <v>3.27417421340942</v>
       </c>
       <c r="H1506" t="n">
         <v>1005053</v>
@@ -44072,7 +44072,7 @@
         <v>3.9760000705719</v>
       </c>
       <c r="G1507" t="n">
-        <v>3.24641299247742</v>
+        <v>3.24641275405884</v>
       </c>
       <c r="H1507" t="n">
         <v>1242404</v>
@@ -44159,7 +44159,7 @@
         <v>4.10799980163574</v>
       </c>
       <c r="G1510" t="n">
-        <v>3.35419130325317</v>
+        <v>3.35419106483459</v>
       </c>
       <c r="H1510" t="n">
         <v>2121824</v>
@@ -44217,7 +44217,7 @@
         <v>4.04199981689453</v>
       </c>
       <c r="G1512" t="n">
-        <v>3.30030202865601</v>
+        <v>3.30030226707458</v>
       </c>
       <c r="H1512" t="n">
         <v>859724</v>
@@ -44362,7 +44362,7 @@
         <v>4.01999998092651</v>
       </c>
       <c r="G1517" t="n">
-        <v>3.28233885765076</v>
+        <v>3.28233909606934</v>
       </c>
       <c r="H1517" t="n">
         <v>1723046</v>
@@ -44391,7 +44391,7 @@
         <v>4.00799989700317</v>
       </c>
       <c r="G1518" t="n">
-        <v>3.272540807724</v>
+        <v>3.27254056930542</v>
       </c>
       <c r="H1518" t="n">
         <v>1366355</v>
@@ -44420,7 +44420,7 @@
         <v>3.94600009918213</v>
       </c>
       <c r="G1519" t="n">
-        <v>3.2219181060791</v>
+        <v>3.22191786766052</v>
       </c>
       <c r="H1519" t="n">
         <v>1085785</v>
@@ -44449,7 +44449,7 @@
         <v>4.03000020980835</v>
       </c>
       <c r="G1520" t="n">
-        <v>3.29050445556641</v>
+        <v>3.29050421714783</v>
       </c>
       <c r="H1520" t="n">
         <v>827310</v>
@@ -44507,7 +44507,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G1522" t="n">
-        <v>3.37215447425842</v>
+        <v>3.37215423583984</v>
       </c>
       <c r="H1522" t="n">
         <v>1760528</v>
@@ -44739,7 +44739,7 @@
         <v>4.34999990463257</v>
       </c>
       <c r="G1530" t="n">
-        <v>3.55178499221802</v>
+        <v>3.55178475379944</v>
       </c>
       <c r="H1530" t="n">
         <v>1320405</v>
@@ -44768,7 +44768,7 @@
         <v>4.44999980926514</v>
       </c>
       <c r="G1531" t="n">
-        <v>3.63343524932861</v>
+        <v>3.63343501091003</v>
       </c>
       <c r="H1531" t="n">
         <v>1376273</v>
@@ -44855,7 +44855,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G1534" t="n">
-        <v>3.71508526802063</v>
+        <v>3.71508550643921</v>
       </c>
       <c r="H1534" t="n">
         <v>1554868</v>
@@ -44884,7 +44884,7 @@
         <v>4.61999988555908</v>
       </c>
       <c r="G1535" t="n">
-        <v>3.77223992347717</v>
+        <v>3.77224016189575</v>
       </c>
       <c r="H1535" t="n">
         <v>979197</v>
@@ -44942,7 +44942,7 @@
         <v>4.71600008010864</v>
       </c>
       <c r="G1537" t="n">
-        <v>3.85062479972839</v>
+        <v>3.85062503814697</v>
       </c>
       <c r="H1537" t="n">
         <v>1063075</v>
@@ -44971,7 +44971,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G1538" t="n">
-        <v>3.83756017684937</v>
+        <v>3.83756041526794</v>
       </c>
       <c r="H1538" t="n">
         <v>1240990</v>
@@ -45000,7 +45000,7 @@
         <v>4.46799993515015</v>
       </c>
       <c r="G1539" t="n">
-        <v>3.64813184738159</v>
+        <v>3.64813208580017</v>
       </c>
       <c r="H1539" t="n">
         <v>1331801</v>
@@ -45029,7 +45029,7 @@
         <v>4.46799993515015</v>
       </c>
       <c r="G1540" t="n">
-        <v>3.64813184738159</v>
+        <v>3.64813208580017</v>
       </c>
       <c r="H1540" t="n">
         <v>1327902</v>
@@ -45145,7 +45145,7 @@
         <v>4.34200000762939</v>
       </c>
       <c r="G1544" t="n">
-        <v>3.54525256156921</v>
+        <v>3.54525279998779</v>
       </c>
       <c r="H1544" t="n">
         <v>1860733</v>
@@ -45348,7 +45348,7 @@
         <v>3.93400001525879</v>
       </c>
       <c r="G1551" t="n">
-        <v>3.21212005615234</v>
+        <v>3.21211981773376</v>
       </c>
       <c r="H1551" t="n">
         <v>1278176</v>
@@ -45493,7 +45493,7 @@
         <v>4.06400012969971</v>
       </c>
       <c r="G1556" t="n">
-        <v>3.31826496124268</v>
+        <v>3.31826519966125</v>
       </c>
       <c r="H1556" t="n">
         <v>434117</v>
@@ -45580,7 +45580,7 @@
         <v>4.08400011062622</v>
       </c>
       <c r="G1559" t="n">
-        <v>3.33459496498108</v>
+        <v>3.33459520339966</v>
       </c>
       <c r="H1559" t="n">
         <v>678692</v>
@@ -45638,7 +45638,7 @@
         <v>3.97000002861023</v>
       </c>
       <c r="G1561" t="n">
-        <v>3.24151396751404</v>
+        <v>3.24151420593262</v>
       </c>
       <c r="H1561" t="n">
         <v>389301</v>
@@ -45870,7 +45870,7 @@
         <v>2.93799996376038</v>
       </c>
       <c r="G1569" t="n">
-        <v>2.39888381958008</v>
+        <v>2.3988835811615</v>
       </c>
       <c r="H1569" t="n">
         <v>3378865</v>
@@ -46218,7 +46218,7 @@
         <v>3.07599997520447</v>
       </c>
       <c r="G1581" t="n">
-        <v>2.51156067848206</v>
+        <v>2.51156091690063</v>
       </c>
       <c r="H1581" t="n">
         <v>1002766</v>
@@ -46276,7 +46276,7 @@
         <v>3.19199991226196</v>
       </c>
       <c r="G1583" t="n">
-        <v>2.60627508163452</v>
+        <v>2.6062753200531</v>
       </c>
       <c r="H1583" t="n">
         <v>1205622</v>
@@ -46334,7 +46334,7 @@
         <v>3.10400009155273</v>
       </c>
       <c r="G1585" t="n">
-        <v>2.53442335128784</v>
+        <v>2.53442311286926</v>
       </c>
       <c r="H1585" t="n">
         <v>859188</v>
@@ -46450,7 +46450,7 @@
         <v>3.18799996376038</v>
       </c>
       <c r="G1589" t="n">
-        <v>2.60300922393799</v>
+        <v>2.60300898551941</v>
       </c>
       <c r="H1589" t="n">
         <v>715593</v>
@@ -46479,7 +46479,7 @@
         <v>3.1340000629425</v>
       </c>
       <c r="G1590" t="n">
-        <v>2.55891799926758</v>
+        <v>2.55891823768616</v>
       </c>
       <c r="H1590" t="n">
         <v>511969</v>
@@ -46508,7 +46508,7 @@
         <v>3.17000007629395</v>
       </c>
       <c r="G1591" t="n">
-        <v>2.58831214904785</v>
+        <v>2.58831238746643</v>
       </c>
       <c r="H1591" t="n">
         <v>871576</v>
@@ -46740,7 +46740,7 @@
         <v>3.09200000762939</v>
       </c>
       <c r="G1599" t="n">
-        <v>2.52462482452393</v>
+        <v>2.5246250629425</v>
       </c>
       <c r="H1599" t="n">
         <v>536588</v>
@@ -80125,6 +80125,35 @@
         <v>793694</v>
       </c>
       <c r="I2750" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2751">
+      <c r="A2751" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2751" s="1" t="n">
+        <v>46322.3333333333</v>
+      </c>
+      <c r="C2751" t="n">
+        <v>12.5100002288818</v>
+      </c>
+      <c r="D2751" t="n">
+        <v>13.1300001144409</v>
+      </c>
+      <c r="E2751" t="n">
+        <v>11.7600002288818</v>
+      </c>
+      <c r="F2751" t="n">
+        <v>13.0200004577637</v>
+      </c>
+      <c r="G2751" t="n">
+        <v>13.0200004577637</v>
+      </c>
+      <c r="H2751" t="n">
+        <v>2463023</v>
+      </c>
+      <c r="I2751" t="s">
         <v>9</v>
       </c>
     </row>
